--- a/artfynd/A 52625-2022 artfynd.xlsx
+++ b/artfynd/A 52625-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126891918</v>
+        <v>126891921</v>
       </c>
       <c r="B2" t="n">
-        <v>80112</v>
+        <v>80143</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>865445</v>
+        <v>865428</v>
       </c>
       <c r="R2" t="n">
-        <v>7447390</v>
+        <v>7447586</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126891921</v>
+        <v>126891918</v>
       </c>
       <c r="B3" t="n">
-        <v>80112</v>
+        <v>80143</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>865428</v>
+        <v>865445</v>
       </c>
       <c r="R3" t="n">
-        <v>7447586</v>
+        <v>7447390</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,7 +880,7 @@
         <v>126892265</v>
       </c>
       <c r="B4" t="n">
-        <v>91263</v>
+        <v>91337</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>126893005</v>
       </c>
       <c r="B5" t="n">
-        <v>80119</v>
+        <v>80150</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>126891922</v>
       </c>
       <c r="B6" t="n">
-        <v>80112</v>
+        <v>80143</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,32 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126893295</v>
+        <v>126892019</v>
       </c>
       <c r="B7" t="n">
-        <v>78980</v>
+        <v>80143</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1218,7 +1218,7 @@
         <v>865429</v>
       </c>
       <c r="R7" t="n">
-        <v>7447550</v>
+        <v>7447523</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,12 +1265,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1284,7 +1284,7 @@
         <v>126893300</v>
       </c>
       <c r="B8" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,32 +1382,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126893275</v>
+        <v>126893295</v>
       </c>
       <c r="B9" t="n">
-        <v>80119</v>
+        <v>79011</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>865427</v>
+        <v>865429</v>
       </c>
       <c r="R9" t="n">
-        <v>7447587</v>
+        <v>7447550</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1483,10 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126892019</v>
+        <v>126893275</v>
       </c>
       <c r="B10" t="n">
-        <v>80112</v>
+        <v>80150</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1494,21 +1494,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>865429</v>
+        <v>865427</v>
       </c>
       <c r="R10" t="n">
-        <v>7447523</v>
+        <v>7447587</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1568,12 +1568,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1584,45 +1584,56 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126892173</v>
+        <v>126892270</v>
       </c>
       <c r="B11" t="n">
-        <v>80112</v>
+        <v>91893</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>760</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>865379</v>
+        <v>865437</v>
       </c>
       <c r="R11" t="n">
-        <v>7447558</v>
+        <v>7447594</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1663,18 +1674,19 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Svea Nikula, Jonas Göransson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1685,59 +1697,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126892270</v>
+        <v>126887992</v>
       </c>
       <c r="B12" t="n">
-        <v>91819</v>
+        <v>79011</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>865437</v>
+        <v>865406</v>
       </c>
       <c r="R12" t="n">
-        <v>7447594</v>
+        <v>7447461</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1775,33 +1776,28 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Svea Nikula, Jonas Göransson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126887992</v>
+        <v>126887991</v>
       </c>
       <c r="B13" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1833,10 +1829,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>865406</v>
+        <v>865422</v>
       </c>
       <c r="R13" t="n">
-        <v>7447461</v>
+        <v>7447458</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1895,32 +1891,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126887991</v>
+        <v>126892999</v>
       </c>
       <c r="B14" t="n">
-        <v>78980</v>
+        <v>80142</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1930,13 +1926,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>865422</v>
+        <v>865426</v>
       </c>
       <c r="R14" t="n">
-        <v>7447458</v>
+        <v>7447493</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1980,22 +1976,26 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126892999</v>
+        <v>126892173</v>
       </c>
       <c r="B15" t="n">
-        <v>80111</v>
+        <v>80143</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2003,21 +2003,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>865426</v>
+        <v>865379</v>
       </c>
       <c r="R15" t="n">
-        <v>7447493</v>
+        <v>7447558</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2077,12 +2077,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2096,7 +2096,7 @@
         <v>126893016</v>
       </c>
       <c r="B16" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2296,10 +2296,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126893301</v>
+        <v>126893017</v>
       </c>
       <c r="B18" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2331,10 +2331,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>865382</v>
+        <v>865409</v>
       </c>
       <c r="R18" t="n">
-        <v>7447699</v>
+        <v>7447573</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2381,12 +2381,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2397,10 +2397,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126893017</v>
+        <v>126893301</v>
       </c>
       <c r="B19" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>865409</v>
+        <v>865382</v>
       </c>
       <c r="R19" t="n">
-        <v>7447573</v>
+        <v>7447699</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2482,12 +2482,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2501,7 +2501,7 @@
         <v>126893004</v>
       </c>
       <c r="B20" t="n">
-        <v>80119</v>
+        <v>80150</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126891920</v>
+        <v>126893276</v>
       </c>
       <c r="B21" t="n">
-        <v>80112</v>
+        <v>80150</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2610,21 +2610,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2634,10 +2634,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>865438</v>
+        <v>865406</v>
       </c>
       <c r="R21" t="n">
-        <v>7447459</v>
+        <v>7447661</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2684,12 +2684,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2700,32 +2700,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126892172</v>
+        <v>126893293</v>
       </c>
       <c r="B22" t="n">
-        <v>80112</v>
+        <v>79011</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2735,10 +2735,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>865436</v>
+        <v>865430</v>
       </c>
       <c r="R22" t="n">
-        <v>7447532</v>
+        <v>7447483</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2785,12 +2785,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2801,32 +2801,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126893293</v>
+        <v>126891920</v>
       </c>
       <c r="B23" t="n">
-        <v>78980</v>
+        <v>80143</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2836,10 +2836,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>865430</v>
+        <v>865438</v>
       </c>
       <c r="R23" t="n">
-        <v>7447483</v>
+        <v>7447459</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2886,12 +2886,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2902,10 +2902,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126893276</v>
+        <v>126892172</v>
       </c>
       <c r="B24" t="n">
-        <v>80119</v>
+        <v>80143</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2913,21 +2913,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2937,10 +2937,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>865406</v>
+        <v>865436</v>
       </c>
       <c r="R24" t="n">
-        <v>7447661</v>
+        <v>7447532</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2987,12 +2987,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3003,32 +3003,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126887982</v>
+        <v>126888460</v>
       </c>
       <c r="B25" t="n">
-        <v>80119</v>
+        <v>79011</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3038,13 +3038,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>865434</v>
+        <v>865380</v>
       </c>
       <c r="R25" t="n">
-        <v>7447388</v>
+        <v>7447610</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3088,44 +3088,48 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
+          <t>Alva Dahlqvist Cederstrand</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126888460</v>
+        <v>126892261</v>
       </c>
       <c r="B26" t="n">
-        <v>78980</v>
+        <v>80150</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3135,10 +3139,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>865380</v>
+        <v>865434</v>
       </c>
       <c r="R26" t="n">
-        <v>7447610</v>
+        <v>7447569</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3185,12 +3189,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3201,10 +3205,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126892261</v>
+        <v>126887982</v>
       </c>
       <c r="B27" t="n">
-        <v>80119</v>
+        <v>80150</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3239,10 +3243,10 @@
         <v>865434</v>
       </c>
       <c r="R27" t="n">
-        <v>7447569</v>
+        <v>7447388</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3286,26 +3290,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
         <v>126892179</v>
       </c>
       <c r="B28" t="n">
-        <v>80119</v>
+        <v>80150</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>126893015</v>
       </c>
       <c r="B29" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
         <v>126892030</v>
       </c>
       <c r="B30" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>126893299</v>
       </c>
       <c r="B31" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>126892021</v>
       </c>
       <c r="B32" t="n">
-        <v>80112</v>
+        <v>80143</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3807,32 +3807,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126892259</v>
+        <v>126893306</v>
       </c>
       <c r="B33" t="n">
-        <v>98382</v>
+        <v>82852</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221952</v>
+        <v>1312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3842,10 +3842,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>865411</v>
+        <v>865378</v>
       </c>
       <c r="R33" t="n">
-        <v>7447533</v>
+        <v>7447665</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3892,12 +3892,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -3911,7 +3911,7 @@
         <v>126892262</v>
       </c>
       <c r="B34" t="n">
-        <v>80119</v>
+        <v>80150</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4009,32 +4009,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126887969</v>
+        <v>126892259</v>
       </c>
       <c r="B35" t="n">
-        <v>57817</v>
+        <v>98457</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4044,13 +4044,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>865406</v>
+        <v>865411</v>
       </c>
       <c r="R35" t="n">
-        <v>7447461</v>
+        <v>7447533</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4094,22 +4094,26 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
+          <t>Svea Nikula</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126893306</v>
+        <v>126887969</v>
       </c>
       <c r="B36" t="n">
-        <v>82792</v>
+        <v>57817</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4117,21 +4121,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4141,13 +4145,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>865378</v>
+        <v>865406</v>
       </c>
       <c r="R36" t="n">
-        <v>7447665</v>
+        <v>7447461</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4191,26 +4195,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126892978</v>
+        <v>126887993</v>
       </c>
       <c r="B37" t="n">
-        <v>75075</v>
+        <v>79011</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4218,21 +4218,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4242,13 +4242,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>865423</v>
+        <v>865389</v>
       </c>
       <c r="R37" t="n">
-        <v>7447442</v>
+        <v>7447521</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4292,26 +4292,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
         <v>126893298</v>
       </c>
       <c r="B38" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4409,10 +4405,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126887993</v>
+        <v>126892978</v>
       </c>
       <c r="B39" t="n">
-        <v>78980</v>
+        <v>75135</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4420,21 +4416,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4444,13 +4440,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>865389</v>
+        <v>865423</v>
       </c>
       <c r="R39" t="n">
-        <v>7447521</v>
+        <v>7447442</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4494,15 +4490,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4610,7 +4610,7 @@
         <v>126893266</v>
       </c>
       <c r="B41" t="n">
-        <v>80112</v>
+        <v>80143</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4708,32 +4708,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126893022</v>
+        <v>126893297</v>
       </c>
       <c r="B42" t="n">
-        <v>98278</v>
+        <v>79011</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4743,10 +4743,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>865404</v>
+        <v>865416</v>
       </c>
       <c r="R42" t="n">
-        <v>7447471</v>
+        <v>7447594</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4793,12 +4793,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -4809,32 +4809,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126893297</v>
+        <v>126893022</v>
       </c>
       <c r="B43" t="n">
-        <v>78980</v>
+        <v>98353</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4844,10 +4844,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>865416</v>
+        <v>865404</v>
       </c>
       <c r="R43" t="n">
-        <v>7447594</v>
+        <v>7447471</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4894,12 +4894,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -4910,10 +4910,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126893273</v>
+        <v>126892258</v>
       </c>
       <c r="B44" t="n">
-        <v>80119</v>
+        <v>80143</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4921,21 +4921,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4945,10 +4945,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>865406</v>
+        <v>865430</v>
       </c>
       <c r="R44" t="n">
-        <v>7447648</v>
+        <v>7447566</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4995,12 +4995,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5011,32 +5011,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126892268</v>
+        <v>126893273</v>
       </c>
       <c r="B45" t="n">
-        <v>78980</v>
+        <v>80150</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5046,10 +5046,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>865411</v>
+        <v>865406</v>
       </c>
       <c r="R45" t="n">
-        <v>7447532</v>
+        <v>7447648</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5096,12 +5096,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5112,32 +5112,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126892258</v>
+        <v>126892268</v>
       </c>
       <c r="B46" t="n">
-        <v>80112</v>
+        <v>79011</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5147,10 +5147,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>865430</v>
+        <v>865411</v>
       </c>
       <c r="R46" t="n">
-        <v>7447566</v>
+        <v>7447532</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5216,7 +5216,7 @@
         <v>126887994</v>
       </c>
       <c r="B47" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>126893028</v>
       </c>
       <c r="B48" t="n">
-        <v>80118</v>
+        <v>80149</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         <v>126892020</v>
       </c>
       <c r="B49" t="n">
-        <v>80112</v>
+        <v>80143</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         <v>126892254</v>
       </c>
       <c r="B50" t="n">
-        <v>75075</v>
+        <v>75135</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>126887983</v>
       </c>
       <c r="B51" t="n">
-        <v>80119</v>
+        <v>80150</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>126765146</v>
       </c>
       <c r="B52" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5816,32 +5816,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126892273</v>
+        <v>126893280</v>
       </c>
       <c r="B53" t="n">
-        <v>78386</v>
+        <v>91480</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6437</v>
+        <v>1503</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5851,10 +5851,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>865528</v>
+        <v>865490</v>
       </c>
       <c r="R53" t="n">
-        <v>7447193</v>
+        <v>7447213</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5901,12 +5901,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -5917,32 +5917,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126891927</v>
+        <v>126892273</v>
       </c>
       <c r="B54" t="n">
-        <v>98361</v>
+        <v>78417</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5952,10 +5952,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>865543</v>
+        <v>865528</v>
       </c>
       <c r="R54" t="n">
-        <v>7447122</v>
+        <v>7447193</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6002,12 +6002,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6021,7 +6021,7 @@
         <v>126892029</v>
       </c>
       <c r="B55" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
         <v>126892026</v>
       </c>
       <c r="B56" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6223,7 +6223,7 @@
         <v>126891916</v>
       </c>
       <c r="B57" t="n">
-        <v>80112</v>
+        <v>80143</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
         <v>126892985</v>
       </c>
       <c r="B58" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6422,32 +6422,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126893280</v>
+        <v>126893008</v>
       </c>
       <c r="B59" t="n">
-        <v>91406</v>
+        <v>80986</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1503</v>
+        <v>1049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6457,10 +6457,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>865490</v>
+        <v>865545</v>
       </c>
       <c r="R59" t="n">
-        <v>7447213</v>
+        <v>7447322</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6507,12 +6507,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6523,32 +6523,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126893008</v>
+        <v>126891927</v>
       </c>
       <c r="B60" t="n">
-        <v>80955</v>
+        <v>98436</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1049</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6558,10 +6558,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>865545</v>
+        <v>865543</v>
       </c>
       <c r="R60" t="n">
-        <v>7447322</v>
+        <v>7447122</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6608,12 +6608,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6624,10 +6624,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126891915</v>
+        <v>126892982</v>
       </c>
       <c r="B61" t="n">
-        <v>80112</v>
+        <v>91284</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6635,21 +6635,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6659,10 +6659,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>865551</v>
+        <v>865526</v>
       </c>
       <c r="R61" t="n">
-        <v>7447126</v>
+        <v>7447273</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6709,12 +6709,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6725,10 +6725,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126892982</v>
+        <v>126891915</v>
       </c>
       <c r="B62" t="n">
-        <v>91210</v>
+        <v>80143</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6736,21 +6736,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6760,10 +6760,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>865526</v>
+        <v>865551</v>
       </c>
       <c r="R62" t="n">
-        <v>7447273</v>
+        <v>7447126</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6810,12 +6810,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -6829,7 +6829,7 @@
         <v>126892177</v>
       </c>
       <c r="B63" t="n">
-        <v>92727</v>
+        <v>92802</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         <v>126887985</v>
       </c>
       <c r="B64" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7024,32 +7024,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126891925</v>
+        <v>126893010</v>
       </c>
       <c r="B65" t="n">
-        <v>98361</v>
+        <v>80986</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>1049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7059,10 +7059,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>865527</v>
+        <v>865490</v>
       </c>
       <c r="R65" t="n">
-        <v>7447333</v>
+        <v>7447332</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7109,12 +7109,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7125,32 +7125,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126892998</v>
+        <v>126893000</v>
       </c>
       <c r="B66" t="n">
-        <v>80111</v>
+        <v>92802</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6461</v>
+        <v>2079</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7160,10 +7160,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>865477</v>
+        <v>865559</v>
       </c>
       <c r="R66" t="n">
-        <v>7447327</v>
+        <v>7447299</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7226,32 +7226,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126888002</v>
+        <v>126892998</v>
       </c>
       <c r="B67" t="n">
-        <v>78647</v>
+        <v>80142</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>353</v>
+        <v>6461</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7261,13 +7261,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>865512</v>
+        <v>865477</v>
       </c>
       <c r="R67" t="n">
-        <v>7447340</v>
+        <v>7447327</v>
       </c>
       <c r="S67" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7311,44 +7311,48 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr"/>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126893010</v>
+        <v>126891925</v>
       </c>
       <c r="B68" t="n">
-        <v>80955</v>
+        <v>98436</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1049</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7358,10 +7362,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>865490</v>
+        <v>865527</v>
       </c>
       <c r="R68" t="n">
-        <v>7447332</v>
+        <v>7447333</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7408,12 +7412,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7424,10 +7428,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126892183</v>
+        <v>126888002</v>
       </c>
       <c r="B69" t="n">
-        <v>56840</v>
+        <v>78678</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7435,53 +7439,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>102612</v>
+        <v>353</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>pulli</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>pulli/nyligen flygga ungar</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>865484</v>
+        <v>865512</v>
       </c>
       <c r="R69" t="n">
-        <v>7447494</v>
+        <v>7447340</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7511,11 +7499,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Stötte up 5st kycklingar, höll till under en och samma fallen gran</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7530,26 +7513,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
         <v>126893312</v>
       </c>
       <c r="B70" t="n">
-        <v>77929</v>
+        <v>77989</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7647,10 +7626,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126893000</v>
+        <v>126892183</v>
       </c>
       <c r="B71" t="n">
-        <v>92727</v>
+        <v>56840</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7658,34 +7637,50 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2079</v>
+        <v>102612</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>pulli</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>pulli/nyligen flygga ungar</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>865559</v>
+        <v>865484</v>
       </c>
       <c r="R71" t="n">
-        <v>7447299</v>
+        <v>7447494</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7720,6 +7715,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Stötte up 5st kycklingar, höll till under en och samma fallen gran</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -7732,12 +7732,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -7751,7 +7751,7 @@
         <v>126891911</v>
       </c>
       <c r="B72" t="n">
-        <v>91210</v>
+        <v>91284</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7849,32 +7849,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126892187</v>
+        <v>126893282</v>
       </c>
       <c r="B73" t="n">
-        <v>91406</v>
+        <v>79011</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7884,10 +7884,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>865509</v>
+        <v>865611</v>
       </c>
       <c r="R73" t="n">
-        <v>7447371</v>
+        <v>7446989</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7934,12 +7934,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -7950,10 +7950,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126893012</v>
+        <v>126892187</v>
       </c>
       <c r="B74" t="n">
-        <v>91406</v>
+        <v>91480</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7985,10 +7985,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>865559</v>
+        <v>865509</v>
       </c>
       <c r="R74" t="n">
-        <v>7447299</v>
+        <v>7447371</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8035,12 +8035,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8051,32 +8051,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126893282</v>
+        <v>126893012</v>
       </c>
       <c r="B75" t="n">
-        <v>78980</v>
+        <v>91480</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8086,10 +8086,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>865611</v>
+        <v>865559</v>
       </c>
       <c r="R75" t="n">
-        <v>7446989</v>
+        <v>7447299</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8136,12 +8136,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8155,7 +8155,7 @@
         <v>126891926</v>
       </c>
       <c r="B76" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8253,32 +8253,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126887974</v>
+        <v>126891929</v>
       </c>
       <c r="B77" t="n">
-        <v>97245</v>
+        <v>79011</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8288,13 +8288,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>865641</v>
+        <v>865535</v>
       </c>
       <c r="R77" t="n">
-        <v>7447070</v>
+        <v>7447142</v>
       </c>
       <c r="S77" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8338,44 +8338,48 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr"/>
+          <t>Amanda Rudelius</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126893270</v>
+        <v>126891914</v>
       </c>
       <c r="B78" t="n">
-        <v>92727</v>
+        <v>80143</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2079</v>
+        <v>6462</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8385,10 +8389,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>865491</v>
+        <v>865539</v>
       </c>
       <c r="R78" t="n">
-        <v>7447267</v>
+        <v>7447115</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8435,12 +8439,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8562,32 +8566,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126891914</v>
+        <v>126893270</v>
       </c>
       <c r="B80" t="n">
-        <v>80112</v>
+        <v>92802</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6462</v>
+        <v>2079</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8597,10 +8601,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>865539</v>
+        <v>865491</v>
       </c>
       <c r="R80" t="n">
-        <v>7447115</v>
+        <v>7447267</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8647,12 +8651,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -8666,7 +8670,7 @@
         <v>126888001</v>
       </c>
       <c r="B81" t="n">
-        <v>78647</v>
+        <v>78678</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8760,32 +8764,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126891929</v>
+        <v>126887974</v>
       </c>
       <c r="B82" t="n">
-        <v>78980</v>
+        <v>97320</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8795,13 +8799,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>865535</v>
+        <v>865641</v>
       </c>
       <c r="R82" t="n">
-        <v>7447142</v>
+        <v>7447070</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8845,48 +8849,44 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126892271</v>
+        <v>126893277</v>
       </c>
       <c r="B83" t="n">
-        <v>80118</v>
+        <v>80986</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6463</v>
+        <v>1049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8896,10 +8896,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>865610</v>
+        <v>865647</v>
       </c>
       <c r="R83" t="n">
-        <v>7447145</v>
+        <v>7447060</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8946,12 +8946,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -8962,53 +8962,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126888454</v>
+        <v>126888457</v>
       </c>
       <c r="B84" t="n">
-        <v>57817</v>
+        <v>91480</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>103021</v>
+        <v>1503</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>865481</v>
+        <v>865528</v>
       </c>
       <c r="R84" t="n">
-        <v>7447376</v>
+        <v>7447201</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9071,32 +9063,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126887978</v>
+        <v>126892185</v>
       </c>
       <c r="B85" t="n">
-        <v>92727</v>
+        <v>91480</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2079</v>
+        <v>1503</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9106,13 +9098,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>865521</v>
+        <v>865490</v>
       </c>
       <c r="R85" t="n">
-        <v>7447240</v>
+        <v>7447287</v>
       </c>
       <c r="S85" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9156,44 +9148,48 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY85" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126893278</v>
+        <v>126892175</v>
       </c>
       <c r="B86" t="n">
-        <v>98361</v>
+        <v>92802</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>2079</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9203,10 +9199,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>865551</v>
+        <v>865509</v>
       </c>
       <c r="R86" t="n">
-        <v>7447276</v>
+        <v>7447217</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9253,12 +9249,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -9269,32 +9265,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126888457</v>
+        <v>126887978</v>
       </c>
       <c r="B87" t="n">
-        <v>91406</v>
+        <v>92802</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1503</v>
+        <v>2079</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9304,13 +9300,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>865528</v>
+        <v>865521</v>
       </c>
       <c r="R87" t="n">
-        <v>7447201</v>
+        <v>7447240</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9354,26 +9350,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
-        </is>
-      </c>
-      <c r="AY87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
         <v>126892192</v>
       </c>
       <c r="B88" t="n">
-        <v>92535</v>
+        <v>92609</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9471,45 +9463,53 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126892181</v>
+        <v>126888454</v>
       </c>
       <c r="B89" t="n">
-        <v>98361</v>
+        <v>57817</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>865459</v>
+        <v>865481</v>
       </c>
       <c r="R89" t="n">
-        <v>7447305</v>
+        <v>7447376</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9556,12 +9556,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -9575,7 +9575,7 @@
         <v>126893003</v>
       </c>
       <c r="B90" t="n">
-        <v>80119</v>
+        <v>80150</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9673,32 +9673,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126893277</v>
+        <v>126892271</v>
       </c>
       <c r="B91" t="n">
-        <v>80955</v>
+        <v>80149</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1049</v>
+        <v>6463</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9708,10 +9708,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>865647</v>
+        <v>865610</v>
       </c>
       <c r="R91" t="n">
-        <v>7447060</v>
+        <v>7447145</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9758,12 +9758,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -9774,10 +9774,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126892185</v>
+        <v>126892181</v>
       </c>
       <c r="B92" t="n">
-        <v>91406</v>
+        <v>98436</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9785,21 +9785,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1503</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9809,10 +9809,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>865490</v>
+        <v>865459</v>
       </c>
       <c r="R92" t="n">
-        <v>7447287</v>
+        <v>7447305</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9875,32 +9875,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126892175</v>
+        <v>126893278</v>
       </c>
       <c r="B93" t="n">
-        <v>92727</v>
+        <v>98436</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2079</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9910,10 +9910,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>865509</v>
+        <v>865551</v>
       </c>
       <c r="R93" t="n">
-        <v>7447217</v>
+        <v>7447276</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9960,12 +9960,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -9976,32 +9976,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126887997</v>
+        <v>126893281</v>
       </c>
       <c r="B94" t="n">
-        <v>98278</v>
+        <v>91480</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>219790</v>
+        <v>1503</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10011,13 +10011,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>865448</v>
+        <v>865513</v>
       </c>
       <c r="R94" t="n">
-        <v>7447350</v>
+        <v>7447339</v>
       </c>
       <c r="S94" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10061,44 +10061,48 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY94" t="inlineStr"/>
+          <t>Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126893023</v>
+        <v>126888000</v>
       </c>
       <c r="B95" t="n">
-        <v>91646</v>
+        <v>78678</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>715</v>
+        <v>353</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Finporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Gloeoporus pannocinctus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Romell) J.Erikss.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10108,13 +10112,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>865473</v>
+        <v>865597</v>
       </c>
       <c r="R95" t="n">
-        <v>7447321</v>
+        <v>7447186</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10158,48 +10162,44 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
-        </is>
-      </c>
-      <c r="AY95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126893281</v>
+        <v>126892981</v>
       </c>
       <c r="B96" t="n">
-        <v>91406</v>
+        <v>91284</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1503</v>
+        <v>5447</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10209,10 +10209,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>865513</v>
+        <v>865553</v>
       </c>
       <c r="R96" t="n">
-        <v>7447339</v>
+        <v>7447278</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10259,12 +10259,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10275,32 +10275,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126892178</v>
+        <v>126893023</v>
       </c>
       <c r="B97" t="n">
-        <v>92727</v>
+        <v>91720</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2079</v>
+        <v>715</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Finporing</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Gloeoporus pannocinctus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell) J.Erikss.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10310,10 +10310,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>865509</v>
+        <v>865473</v>
       </c>
       <c r="R97" t="n">
-        <v>7447375</v>
+        <v>7447321</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10360,12 +10360,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10376,10 +10376,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126887968</v>
+        <v>126892178</v>
       </c>
       <c r="B98" t="n">
-        <v>57817</v>
+        <v>92802</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10387,21 +10387,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>103021</v>
+        <v>2079</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10411,13 +10411,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>865523</v>
+        <v>865509</v>
       </c>
       <c r="R98" t="n">
-        <v>7447217</v>
+        <v>7447375</v>
       </c>
       <c r="S98" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10461,22 +10461,26 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY98" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126892981</v>
+        <v>126893025</v>
       </c>
       <c r="B99" t="n">
-        <v>91210</v>
+        <v>92609</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10484,21 +10488,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10508,10 +10512,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>865553</v>
+        <v>865518</v>
       </c>
       <c r="R99" t="n">
-        <v>7447278</v>
+        <v>7447235</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10574,10 +10578,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126888000</v>
+        <v>126892267</v>
       </c>
       <c r="B100" t="n">
-        <v>78647</v>
+        <v>79011</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10585,21 +10589,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10609,13 +10613,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>865597</v>
+        <v>865516</v>
       </c>
       <c r="R100" t="n">
-        <v>7447186</v>
+        <v>7447351</v>
       </c>
       <c r="S100" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10659,44 +10663,48 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY100" t="inlineStr"/>
+          <t>Svea Nikula</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126893025</v>
+        <v>126887968</v>
       </c>
       <c r="B101" t="n">
-        <v>92535</v>
+        <v>57817</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10706,13 +10714,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>865518</v>
+        <v>865523</v>
       </c>
       <c r="R101" t="n">
-        <v>7447235</v>
+        <v>7447217</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10756,48 +10764,44 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
-        </is>
-      </c>
-      <c r="AY101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126892267</v>
+        <v>126887997</v>
       </c>
       <c r="B102" t="n">
-        <v>78980</v>
+        <v>98353</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10807,13 +10811,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>865516</v>
+        <v>865448</v>
       </c>
       <c r="R102" t="n">
-        <v>7447351</v>
+        <v>7447350</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -10857,48 +10861,44 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
-        </is>
-      </c>
-      <c r="AY102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126893033</v>
+        <v>126892186</v>
       </c>
       <c r="B103" t="n">
-        <v>78386</v>
+        <v>91480</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6437</v>
+        <v>1503</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10908,10 +10908,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>865500</v>
+        <v>865491</v>
       </c>
       <c r="R103" t="n">
-        <v>7447283</v>
+        <v>7447290</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10958,12 +10958,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -10974,32 +10974,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126892186</v>
+        <v>126893033</v>
       </c>
       <c r="B104" t="n">
-        <v>91406</v>
+        <v>78417</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1503</v>
+        <v>6437</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11009,10 +11009,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>865491</v>
+        <v>865500</v>
       </c>
       <c r="R104" t="n">
-        <v>7447290</v>
+        <v>7447283</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11059,12 +11059,12 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -11078,7 +11078,7 @@
         <v>126891923</v>
       </c>
       <c r="B105" t="n">
-        <v>79987</v>
+        <v>80018</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11176,32 +11176,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126892028</v>
+        <v>126893310</v>
       </c>
       <c r="B106" t="n">
-        <v>78980</v>
+        <v>91580</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11211,10 +11211,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>865533</v>
+        <v>865653</v>
       </c>
       <c r="R106" t="n">
-        <v>7447130</v>
+        <v>7447052</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11261,12 +11261,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -11277,32 +11277,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126893310</v>
+        <v>126892028</v>
       </c>
       <c r="B107" t="n">
-        <v>91506</v>
+        <v>79011</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11312,10 +11312,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>865653</v>
+        <v>865533</v>
       </c>
       <c r="R107" t="n">
-        <v>7447052</v>
+        <v>7447130</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11362,12 +11362,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
@@ -11381,7 +11381,7 @@
         <v>126887980</v>
       </c>
       <c r="B108" t="n">
-        <v>92727</v>
+        <v>92802</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11475,32 +11475,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126887990</v>
+        <v>126887975</v>
       </c>
       <c r="B109" t="n">
-        <v>78980</v>
+        <v>97320</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11510,10 +11510,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>865447</v>
+        <v>865479</v>
       </c>
       <c r="R109" t="n">
-        <v>7447371</v>
+        <v>7447358</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -11572,32 +11572,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126887987</v>
+        <v>126887976</v>
       </c>
       <c r="B110" t="n">
-        <v>91406</v>
+        <v>97320</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1503</v>
+        <v>221941</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11607,10 +11607,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>865510</v>
+        <v>865452</v>
       </c>
       <c r="R110" t="n">
-        <v>7447247</v>
+        <v>7447334</v>
       </c>
       <c r="S110" t="n">
         <v>25</v>
@@ -11669,32 +11669,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126892024</v>
+        <v>126893009</v>
       </c>
       <c r="B111" t="n">
-        <v>98361</v>
+        <v>80986</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>220787</v>
+        <v>1049</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11704,10 +11704,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>865546</v>
+        <v>865553</v>
       </c>
       <c r="R111" t="n">
-        <v>7447138</v>
+        <v>7447326</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11754,12 +11754,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
@@ -11770,32 +11770,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126887976</v>
+        <v>126887987</v>
       </c>
       <c r="B112" t="n">
-        <v>97245</v>
+        <v>91480</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>221941</v>
+        <v>1503</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11805,10 +11805,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>865452</v>
+        <v>865510</v>
       </c>
       <c r="R112" t="n">
-        <v>7447334</v>
+        <v>7447247</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -11867,32 +11867,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126887965</v>
+        <v>126887977</v>
       </c>
       <c r="B113" t="n">
-        <v>57479</v>
+        <v>92802</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>102976</v>
+        <v>2079</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11902,10 +11902,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>865583</v>
+        <v>865643</v>
       </c>
       <c r="R113" t="n">
-        <v>7447214</v>
+        <v>7447067</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -11964,32 +11964,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126887975</v>
+        <v>126892191</v>
       </c>
       <c r="B114" t="n">
-        <v>97245</v>
+        <v>91580</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>221941</v>
+        <v>65</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11999,13 +11999,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>865479</v>
+        <v>865540</v>
       </c>
       <c r="R114" t="n">
-        <v>7447358</v>
+        <v>7447366</v>
       </c>
       <c r="S114" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12049,44 +12049,48 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY114" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126892191</v>
+        <v>126887990</v>
       </c>
       <c r="B115" t="n">
-        <v>91506</v>
+        <v>79011</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12096,13 +12100,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>865540</v>
+        <v>865447</v>
       </c>
       <c r="R115" t="n">
-        <v>7447366</v>
+        <v>7447371</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12146,26 +12150,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126892018</v>
+        <v>126892263</v>
       </c>
       <c r="B116" t="n">
-        <v>57817</v>
+        <v>56840</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12173,33 +12173,29 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N116" t="inlineStr"/>
@@ -12209,10 +12205,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>865561</v>
+        <v>865544</v>
       </c>
       <c r="R116" t="n">
-        <v>7447155</v>
+        <v>7447281</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12259,12 +12255,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
@@ -12275,32 +12271,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126893009</v>
+        <v>126887965</v>
       </c>
       <c r="B117" t="n">
-        <v>80955</v>
+        <v>57479</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1049</v>
+        <v>102976</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12310,13 +12306,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>865553</v>
+        <v>865583</v>
       </c>
       <c r="R117" t="n">
-        <v>7447326</v>
+        <v>7447214</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12360,26 +12356,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
-        </is>
-      </c>
-      <c r="AY117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126887977</v>
+        <v>126892018</v>
       </c>
       <c r="B118" t="n">
-        <v>92727</v>
+        <v>57817</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12387,37 +12379,49 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>2079</v>
+        <v>103021</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>865643</v>
+        <v>865561</v>
       </c>
       <c r="R118" t="n">
-        <v>7447067</v>
+        <v>7447155</v>
       </c>
       <c r="S118" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -12461,65 +12465,61 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY118" t="inlineStr"/>
+          <t>Julia Frejd</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126892263</v>
+        <v>126891928</v>
       </c>
       <c r="B119" t="n">
-        <v>56840</v>
+        <v>98436</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>865544</v>
+        <v>865549</v>
       </c>
       <c r="R119" t="n">
-        <v>7447281</v>
+        <v>7447136</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12566,12 +12566,12 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
@@ -12582,10 +12582,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126891928</v>
+        <v>126892024</v>
       </c>
       <c r="B120" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12617,10 +12617,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>865549</v>
+        <v>865546</v>
       </c>
       <c r="R120" t="n">
-        <v>7447136</v>
+        <v>7447138</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12667,12 +12667,12 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
@@ -12683,10 +12683,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126893260</v>
+        <v>126893267</v>
       </c>
       <c r="B121" t="n">
-        <v>91167</v>
+        <v>92802</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12694,21 +12694,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>3242</v>
+        <v>2079</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12718,10 +12718,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>865498</v>
+        <v>865648</v>
       </c>
       <c r="R121" t="n">
-        <v>7447359</v>
+        <v>7447056</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12784,32 +12784,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126887981</v>
+        <v>126893308</v>
       </c>
       <c r="B122" t="n">
-        <v>80119</v>
+        <v>91580</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6464</v>
+        <v>65</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12819,13 +12819,13 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>865448</v>
+        <v>865659</v>
       </c>
       <c r="R122" t="n">
-        <v>7447345</v>
+        <v>7447048</v>
       </c>
       <c r="S122" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -12869,22 +12869,26 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY122" t="inlineStr"/>
+          <t>Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126893030</v>
+        <v>126893260</v>
       </c>
       <c r="B123" t="n">
-        <v>77929</v>
+        <v>91241</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12892,21 +12896,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6487</v>
+        <v>3242</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12916,10 +12920,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>865545</v>
+        <v>865498</v>
       </c>
       <c r="R123" t="n">
-        <v>7447323</v>
+        <v>7447359</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12966,12 +12970,12 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
@@ -12982,32 +12986,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126893267</v>
+        <v>126893262</v>
       </c>
       <c r="B124" t="n">
-        <v>92727</v>
+        <v>91284</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>2079</v>
+        <v>5447</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13017,10 +13021,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>865648</v>
+        <v>865522</v>
       </c>
       <c r="R124" t="n">
-        <v>7447056</v>
+        <v>7447308</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13083,32 +13087,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126893308</v>
+        <v>126893030</v>
       </c>
       <c r="B125" t="n">
-        <v>91506</v>
+        <v>77989</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>65</v>
+        <v>6487</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13118,10 +13122,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>865659</v>
+        <v>865545</v>
       </c>
       <c r="R125" t="n">
-        <v>7447048</v>
+        <v>7447323</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13168,12 +13172,12 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
@@ -13184,32 +13188,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126892170</v>
+        <v>126887981</v>
       </c>
       <c r="B126" t="n">
-        <v>57479</v>
+        <v>80150</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>102976</v>
+        <v>6464</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13219,13 +13223,13 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>865489</v>
+        <v>865448</v>
       </c>
       <c r="R126" t="n">
-        <v>7447377</v>
+        <v>7447345</v>
       </c>
       <c r="S126" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13255,11 +13259,6 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Förbiflygande</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13274,48 +13273,44 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126893262</v>
+        <v>126892170</v>
       </c>
       <c r="B127" t="n">
-        <v>91210</v>
+        <v>57479</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5447</v>
+        <v>102976</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13325,10 +13320,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>865522</v>
+        <v>865489</v>
       </c>
       <c r="R127" t="n">
-        <v>7447308</v>
+        <v>7447377</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13363,6 +13358,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Förbiflygande</t>
+        </is>
+      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
@@ -13375,12 +13375,12 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
@@ -13391,32 +13391,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126893274</v>
+        <v>126887988</v>
       </c>
       <c r="B128" t="n">
-        <v>80119</v>
+        <v>91480</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6464</v>
+        <v>1503</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13426,13 +13426,13 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>865476</v>
+        <v>865515</v>
       </c>
       <c r="R128" t="n">
-        <v>7447236</v>
+        <v>7447377</v>
       </c>
       <c r="S128" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13476,48 +13476,44 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
-        </is>
-      </c>
-      <c r="AY128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126887970</v>
+        <v>126893269</v>
       </c>
       <c r="B129" t="n">
-        <v>80112</v>
+        <v>92802</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6462</v>
+        <v>2079</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13527,13 +13523,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>865529</v>
+        <v>865647</v>
       </c>
       <c r="R129" t="n">
-        <v>7447327</v>
+        <v>7447057</v>
       </c>
       <c r="S129" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -13577,44 +13573,48 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY129" t="inlineStr"/>
+          <t>Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126893313</v>
+        <v>126887970</v>
       </c>
       <c r="B130" t="n">
-        <v>78386</v>
+        <v>80143</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6437</v>
+        <v>6462</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13624,13 +13624,13 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>865598</v>
+        <v>865529</v>
       </c>
       <c r="R130" t="n">
-        <v>7447181</v>
+        <v>7447327</v>
       </c>
       <c r="S130" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -13674,26 +13674,22 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
-        </is>
-      </c>
-      <c r="AY130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126893269</v>
+        <v>126893313</v>
       </c>
       <c r="B131" t="n">
-        <v>92727</v>
+        <v>78417</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13701,21 +13697,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>2079</v>
+        <v>6437</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13725,10 +13721,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>865647</v>
+        <v>865598</v>
       </c>
       <c r="R131" t="n">
-        <v>7447057</v>
+        <v>7447181</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13791,32 +13787,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126893292</v>
+        <v>126893274</v>
       </c>
       <c r="B132" t="n">
-        <v>78980</v>
+        <v>80150</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13826,10 +13822,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>865501</v>
+        <v>865476</v>
       </c>
       <c r="R132" t="n">
-        <v>7447191</v>
+        <v>7447236</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13892,32 +13888,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126887988</v>
+        <v>126893292</v>
       </c>
       <c r="B133" t="n">
-        <v>91406</v>
+        <v>79011</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13927,13 +13923,13 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>865515</v>
+        <v>865501</v>
       </c>
       <c r="R133" t="n">
-        <v>7447377</v>
+        <v>7447191</v>
       </c>
       <c r="S133" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -13977,44 +13973,48 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY133" t="inlineStr"/>
+          <t>Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126892176</v>
+        <v>126892256</v>
       </c>
       <c r="B134" t="n">
-        <v>92727</v>
+        <v>91284</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>2079</v>
+        <v>5447</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14024,10 +14024,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>865490</v>
+        <v>865491</v>
       </c>
       <c r="R134" t="n">
-        <v>7447287</v>
+        <v>7447326</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14074,12 +14074,12 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
@@ -14093,7 +14093,7 @@
         <v>126893034</v>
       </c>
       <c r="B135" t="n">
-        <v>78386</v>
+        <v>78417</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14191,10 +14191,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126887962</v>
+        <v>126893290</v>
       </c>
       <c r="B136" t="n">
-        <v>79598</v>
+        <v>79011</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14202,21 +14202,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14226,13 +14226,13 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>865519</v>
+        <v>865505</v>
       </c>
       <c r="R136" t="n">
-        <v>7447214</v>
+        <v>7447150</v>
       </c>
       <c r="S136" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -14276,22 +14276,26 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY136" t="inlineStr"/>
+          <t>Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
         <v>126892189</v>
       </c>
       <c r="B137" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14392,7 +14396,7 @@
         <v>126892984</v>
       </c>
       <c r="B138" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14490,32 +14494,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126892256</v>
+        <v>126887962</v>
       </c>
       <c r="B139" t="n">
-        <v>91210</v>
+        <v>79629</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14525,13 +14529,13 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>865491</v>
+        <v>865519</v>
       </c>
       <c r="R139" t="n">
-        <v>7447326</v>
+        <v>7447214</v>
       </c>
       <c r="S139" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -14575,26 +14579,22 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
-        </is>
-      </c>
-      <c r="AY139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126893290</v>
+        <v>126892176</v>
       </c>
       <c r="B140" t="n">
-        <v>78980</v>
+        <v>92802</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14602,21 +14602,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14626,10 +14626,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>865505</v>
+        <v>865490</v>
       </c>
       <c r="R140" t="n">
-        <v>7447150</v>
+        <v>7447287</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14676,12 +14676,12 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
@@ -14692,10 +14692,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126892253</v>
+        <v>126888456</v>
       </c>
       <c r="B141" t="n">
-        <v>91167</v>
+        <v>92802</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14703,21 +14703,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>3242</v>
+        <v>2079</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14727,10 +14727,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>865491</v>
+        <v>865506</v>
       </c>
       <c r="R141" t="n">
-        <v>7447326</v>
+        <v>7447238</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14777,12 +14777,12 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
@@ -14793,32 +14793,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126887971</v>
+        <v>126892253</v>
       </c>
       <c r="B142" t="n">
-        <v>80112</v>
+        <v>91241</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6462</v>
+        <v>3242</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14828,13 +14828,13 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>865452</v>
+        <v>865491</v>
       </c>
       <c r="R142" t="n">
-        <v>7447318</v>
+        <v>7447326</v>
       </c>
       <c r="S142" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -14878,44 +14878,48 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY142" t="inlineStr"/>
+          <t>Svea Nikula</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126888456</v>
+        <v>126887971</v>
       </c>
       <c r="B143" t="n">
-        <v>92727</v>
+        <v>80143</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>2079</v>
+        <v>6462</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14925,13 +14929,13 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>865506</v>
+        <v>865452</v>
       </c>
       <c r="R143" t="n">
-        <v>7447238</v>
+        <v>7447318</v>
       </c>
       <c r="S143" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -14975,26 +14979,22 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
-        </is>
-      </c>
-      <c r="AY143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
         <v>126892991</v>
       </c>
       <c r="B144" t="n">
-        <v>80112</v>
+        <v>80143</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15095,7 +15095,7 @@
         <v>126891917</v>
       </c>
       <c r="B145" t="n">
-        <v>80112</v>
+        <v>80143</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15193,32 +15193,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126892266</v>
+        <v>126893264</v>
       </c>
       <c r="B146" t="n">
-        <v>78980</v>
+        <v>57479</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>102976</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15228,10 +15228,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>865495</v>
+        <v>865598</v>
       </c>
       <c r="R146" t="n">
-        <v>7447285</v>
+        <v>7447180</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15278,12 +15278,12 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
@@ -15294,10 +15294,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>126888459</v>
+        <v>126892983</v>
       </c>
       <c r="B147" t="n">
-        <v>78980</v>
+        <v>79629</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15305,21 +15305,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15329,10 +15329,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>865501</v>
+        <v>865546</v>
       </c>
       <c r="R147" t="n">
-        <v>7447386</v>
+        <v>7447275</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15379,12 +15379,12 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
@@ -15395,32 +15395,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126893264</v>
+        <v>126892266</v>
       </c>
       <c r="B148" t="n">
-        <v>57479</v>
+        <v>79011</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>102976</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15430,10 +15430,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>865598</v>
+        <v>865495</v>
       </c>
       <c r="R148" t="n">
-        <v>7447180</v>
+        <v>7447285</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15480,12 +15480,12 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
@@ -15496,10 +15496,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126892983</v>
+        <v>126888459</v>
       </c>
       <c r="B149" t="n">
-        <v>79598</v>
+        <v>79011</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15507,21 +15507,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15531,10 +15531,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>865546</v>
+        <v>865501</v>
       </c>
       <c r="R149" t="n">
-        <v>7447275</v>
+        <v>7447386</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15581,12 +15581,12 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
@@ -15597,32 +15597,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126892980</v>
+        <v>126893259</v>
       </c>
       <c r="B150" t="n">
-        <v>91210</v>
+        <v>91241</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>5447</v>
+        <v>3242</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15632,10 +15632,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>865554</v>
+        <v>865646</v>
       </c>
       <c r="R150" t="n">
-        <v>7447301</v>
+        <v>7447063</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15682,12 +15682,12 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
@@ -15698,57 +15698,45 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126892023</v>
+        <v>126892980</v>
       </c>
       <c r="B151" t="n">
-        <v>98361</v>
+        <v>91284</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
-      <c r="N151" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>865539</v>
+        <v>865554</v>
       </c>
       <c r="R151" t="n">
-        <v>7447133</v>
+        <v>7447301</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15789,19 +15777,18 @@
       <c r="AE151" t="b">
         <v>0</v>
       </c>
-      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
@@ -15812,10 +15799,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>126893259</v>
+        <v>126891909</v>
       </c>
       <c r="B152" t="n">
-        <v>91167</v>
+        <v>75135</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15823,21 +15810,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>3242</v>
+        <v>6440</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15847,10 +15834,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>865646</v>
+        <v>865542</v>
       </c>
       <c r="R152" t="n">
-        <v>7447063</v>
+        <v>7447122</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15897,12 +15884,12 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
@@ -15913,45 +15900,57 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>126891909</v>
+        <v>126892023</v>
       </c>
       <c r="B153" t="n">
-        <v>75075</v>
+        <v>98436</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>865542</v>
+        <v>865539</v>
       </c>
       <c r="R153" t="n">
-        <v>7447122</v>
+        <v>7447133</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -15992,18 +15991,19 @@
       <c r="AE153" t="b">
         <v>0</v>
       </c>
+      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
       </c>
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
@@ -16014,10 +16014,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>126892272</v>
+        <v>126893011</v>
       </c>
       <c r="B154" t="n">
-        <v>77929</v>
+        <v>80986</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16025,21 +16025,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6487</v>
+        <v>1049</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16049,10 +16049,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>865528</v>
+        <v>865498</v>
       </c>
       <c r="R154" t="n">
-        <v>7447192</v>
+        <v>7447379</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16099,12 +16099,12 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
@@ -16115,32 +16115,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126892255</v>
+        <v>126887979</v>
       </c>
       <c r="B155" t="n">
-        <v>91210</v>
+        <v>92802</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>5447</v>
+        <v>2079</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16150,13 +16150,13 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>865462</v>
+        <v>865510</v>
       </c>
       <c r="R155" t="n">
-        <v>7447413</v>
+        <v>7447251</v>
       </c>
       <c r="S155" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -16200,26 +16200,22 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
-        </is>
-      </c>
-      <c r="AY155" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>126893011</v>
+        <v>126892974</v>
       </c>
       <c r="B156" t="n">
-        <v>80955</v>
+        <v>91241</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16227,21 +16223,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1049</v>
+        <v>3242</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16251,10 +16247,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>865498</v>
+        <v>865494</v>
       </c>
       <c r="R156" t="n">
-        <v>7447379</v>
+        <v>7447322</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16317,32 +16313,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126892974</v>
+        <v>126892255</v>
       </c>
       <c r="B157" t="n">
-        <v>91167</v>
+        <v>91284</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>3242</v>
+        <v>5447</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16352,10 +16348,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>865494</v>
+        <v>865462</v>
       </c>
       <c r="R157" t="n">
-        <v>7447322</v>
+        <v>7447413</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16402,12 +16398,12 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
@@ -16418,10 +16414,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>126887979</v>
+        <v>126892272</v>
       </c>
       <c r="B158" t="n">
-        <v>92727</v>
+        <v>77989</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16429,21 +16425,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>2079</v>
+        <v>6487</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16453,13 +16449,13 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>865510</v>
+        <v>865528</v>
       </c>
       <c r="R158" t="n">
-        <v>7447251</v>
+        <v>7447192</v>
       </c>
       <c r="S158" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -16503,44 +16499,48 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY158" t="inlineStr"/>
+          <t>Svea Nikula</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>126893272</v>
+        <v>126888458</v>
       </c>
       <c r="B159" t="n">
-        <v>92727</v>
+        <v>91480</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>2079</v>
+        <v>1503</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16550,10 +16550,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>865520</v>
+        <v>865502</v>
       </c>
       <c r="R159" t="n">
-        <v>7447337</v>
+        <v>7447310</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16600,12 +16600,12 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
@@ -16616,10 +16616,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>126887961</v>
+        <v>126893272</v>
       </c>
       <c r="B160" t="n">
-        <v>79598</v>
+        <v>92802</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16627,21 +16627,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16651,13 +16651,13 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>865602</v>
+        <v>865520</v>
       </c>
       <c r="R160" t="n">
-        <v>7447176</v>
+        <v>7447337</v>
       </c>
       <c r="S160" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -16701,44 +16701,48 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY160" t="inlineStr"/>
+          <t>Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>126888458</v>
+        <v>126887961</v>
       </c>
       <c r="B161" t="n">
-        <v>91406</v>
+        <v>79629</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16748,13 +16752,13 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>865502</v>
+        <v>865602</v>
       </c>
       <c r="R161" t="n">
-        <v>7447310</v>
+        <v>7447176</v>
       </c>
       <c r="S161" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -16798,26 +16802,22 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
-        </is>
-      </c>
-      <c r="AY161" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
         <v>126893291</v>
       </c>
       <c r="B162" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16915,48 +16915,45 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>126891924</v>
+        <v>126892016</v>
       </c>
       <c r="B163" t="n">
-        <v>78738</v>
+        <v>91284</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
-      <c r="K163" t="inlineStr"/>
-      <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>865562</v>
+        <v>865558</v>
       </c>
       <c r="R163" t="n">
-        <v>7447150</v>
+        <v>7447154</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -16997,19 +16994,18 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
-      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
@@ -17020,10 +17016,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>126892016</v>
+        <v>126893265</v>
       </c>
       <c r="B164" t="n">
-        <v>91210</v>
+        <v>80143</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17031,21 +17027,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17055,10 +17051,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>865558</v>
+        <v>865530</v>
       </c>
       <c r="R164" t="n">
-        <v>7447154</v>
+        <v>7447304</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17105,12 +17101,12 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
@@ -17121,45 +17117,48 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>126893265</v>
+        <v>126891924</v>
       </c>
       <c r="B165" t="n">
-        <v>80112</v>
+        <v>78769</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>865530</v>
+        <v>865562</v>
       </c>
       <c r="R165" t="n">
-        <v>7447304</v>
+        <v>7447150</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17200,18 +17199,19 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
+      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
@@ -17225,7 +17225,7 @@
         <v>126891919</v>
       </c>
       <c r="B166" t="n">
-        <v>80112</v>
+        <v>80143</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17323,32 +17323,32 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>126893309</v>
+        <v>126892988</v>
       </c>
       <c r="B167" t="n">
-        <v>91506</v>
+        <v>57479</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>65</v>
+        <v>102976</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17358,10 +17358,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>865661</v>
+        <v>865530</v>
       </c>
       <c r="R167" t="n">
-        <v>7447053</v>
+        <v>7447298</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17408,12 +17408,12 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
@@ -17424,32 +17424,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>126892988</v>
+        <v>126893021</v>
       </c>
       <c r="B168" t="n">
-        <v>57479</v>
+        <v>91580</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>102976</v>
+        <v>65</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17459,10 +17459,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>865530</v>
+        <v>865547</v>
       </c>
       <c r="R168" t="n">
-        <v>7447298</v>
+        <v>7447316</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17525,32 +17525,32 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>126893031</v>
+        <v>126893309</v>
       </c>
       <c r="B169" t="n">
-        <v>77929</v>
+        <v>91580</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6487</v>
+        <v>65</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17560,10 +17560,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>865490</v>
+        <v>865661</v>
       </c>
       <c r="R169" t="n">
-        <v>7447338</v>
+        <v>7447053</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17610,12 +17610,12 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
@@ -17626,32 +17626,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>126893021</v>
+        <v>126893284</v>
       </c>
       <c r="B170" t="n">
-        <v>91506</v>
+        <v>79011</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17661,10 +17661,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>865547</v>
+        <v>865543</v>
       </c>
       <c r="R170" t="n">
-        <v>7447316</v>
+        <v>7447053</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17711,12 +17711,12 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr">
@@ -17727,10 +17727,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>126893284</v>
+        <v>126893031</v>
       </c>
       <c r="B171" t="n">
-        <v>78980</v>
+        <v>77989</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17738,21 +17738,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -17762,10 +17762,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>865543</v>
+        <v>865490</v>
       </c>
       <c r="R171" t="n">
-        <v>7447053</v>
+        <v>7447338</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17812,12 +17812,12 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
@@ -17828,10 +17828,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>126892986</v>
+        <v>126892174</v>
       </c>
       <c r="B172" t="n">
-        <v>79569</v>
+        <v>92802</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17839,21 +17839,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>229821</v>
+        <v>2079</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -17863,10 +17863,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>865489</v>
+        <v>865517</v>
       </c>
       <c r="R172" t="n">
-        <v>7447329</v>
+        <v>7447401</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -17913,12 +17913,12 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
@@ -17929,32 +17929,32 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>126892174</v>
+        <v>126892997</v>
       </c>
       <c r="B173" t="n">
-        <v>92727</v>
+        <v>79035</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>2079</v>
+        <v>6434</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -17964,10 +17964,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>865517</v>
+        <v>865545</v>
       </c>
       <c r="R173" t="n">
-        <v>7447401</v>
+        <v>7447323</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18014,12 +18014,12 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
@@ -18030,10 +18030,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>126893263</v>
+        <v>126893294</v>
       </c>
       <c r="B174" t="n">
-        <v>91245</v>
+        <v>79011</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18041,21 +18041,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18065,10 +18065,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>865485</v>
+        <v>865457</v>
       </c>
       <c r="R174" t="n">
-        <v>7447224</v>
+        <v>7447523</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18131,10 +18131,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>126893314</v>
+        <v>126893263</v>
       </c>
       <c r="B175" t="n">
-        <v>78386</v>
+        <v>91319</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18142,21 +18142,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6437</v>
+        <v>1202</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18166,10 +18166,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>865647</v>
+        <v>865485</v>
       </c>
       <c r="R175" t="n">
-        <v>7447060</v>
+        <v>7447224</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18232,32 +18232,32 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>126893294</v>
+        <v>126892188</v>
       </c>
       <c r="B176" t="n">
-        <v>78980</v>
+        <v>91480</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18267,10 +18267,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>865457</v>
+        <v>865520</v>
       </c>
       <c r="R176" t="n">
-        <v>7447523</v>
+        <v>7447364</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18317,12 +18317,12 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr">
@@ -18336,7 +18336,7 @@
         <v>126887986</v>
       </c>
       <c r="B177" t="n">
-        <v>91406</v>
+        <v>91480</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18430,10 +18430,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>126891913</v>
+        <v>126893314</v>
       </c>
       <c r="B178" t="n">
-        <v>79598</v>
+        <v>78417</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18441,21 +18441,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18465,10 +18465,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>865557</v>
+        <v>865647</v>
       </c>
       <c r="R178" t="n">
-        <v>7447153</v>
+        <v>7447060</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18515,12 +18515,12 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr">
@@ -18531,32 +18531,32 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>126892188</v>
+        <v>126891913</v>
       </c>
       <c r="B179" t="n">
-        <v>91406</v>
+        <v>79629</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -18566,10 +18566,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>865520</v>
+        <v>865557</v>
       </c>
       <c r="R179" t="n">
-        <v>7447364</v>
+        <v>7447153</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18616,12 +18616,12 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
@@ -18632,32 +18632,32 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>126892997</v>
+        <v>126892986</v>
       </c>
       <c r="B180" t="n">
-        <v>79004</v>
+        <v>79600</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6434</v>
+        <v>229821</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -18667,10 +18667,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>865545</v>
+        <v>865489</v>
       </c>
       <c r="R180" t="n">
-        <v>7447323</v>
+        <v>7447329</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>

--- a/artfynd/A 52625-2022 artfynd.xlsx
+++ b/artfynd/A 52625-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126891921</v>
       </c>
       <c r="B2" t="n">
-        <v>80143</v>
+        <v>80146</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126891918</v>
       </c>
       <c r="B3" t="n">
-        <v>80143</v>
+        <v>80146</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>126892265</v>
       </c>
       <c r="B4" t="n">
-        <v>91337</v>
+        <v>91343</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>126893005</v>
       </c>
       <c r="B5" t="n">
-        <v>80150</v>
+        <v>80153</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>126891922</v>
       </c>
       <c r="B6" t="n">
-        <v>80143</v>
+        <v>80146</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126892019</v>
+        <v>126893275</v>
       </c>
       <c r="B7" t="n">
-        <v>80143</v>
+        <v>80153</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>865429</v>
+        <v>865427</v>
       </c>
       <c r="R7" t="n">
-        <v>7447523</v>
+        <v>7447587</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,12 +1265,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1281,32 +1281,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126893300</v>
+        <v>126892019</v>
       </c>
       <c r="B8" t="n">
-        <v>79011</v>
+        <v>80146</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>865378</v>
+        <v>865429</v>
       </c>
       <c r="R8" t="n">
-        <v>7447665</v>
+        <v>7447523</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1366,12 +1366,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1385,7 +1385,7 @@
         <v>126893295</v>
       </c>
       <c r="B9" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1483,32 +1483,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126893275</v>
+        <v>126893300</v>
       </c>
       <c r="B10" t="n">
-        <v>80150</v>
+        <v>79014</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>865427</v>
+        <v>865378</v>
       </c>
       <c r="R10" t="n">
-        <v>7447587</v>
+        <v>7447665</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1584,56 +1584,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126892270</v>
+        <v>126892999</v>
       </c>
       <c r="B11" t="n">
-        <v>91893</v>
+        <v>80145</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>760</v>
+        <v>6461</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>865437</v>
+        <v>865426</v>
       </c>
       <c r="R11" t="n">
-        <v>7447594</v>
+        <v>7447493</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1674,19 +1663,18 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Svea Nikula, Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1697,32 +1685,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126887992</v>
+        <v>126892173</v>
       </c>
       <c r="B12" t="n">
-        <v>79011</v>
+        <v>80146</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1732,13 +1720,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>865406</v>
+        <v>865379</v>
       </c>
       <c r="R12" t="n">
-        <v>7447461</v>
+        <v>7447558</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1782,60 +1770,75 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126887991</v>
+        <v>126892270</v>
       </c>
       <c r="B13" t="n">
-        <v>79011</v>
+        <v>91899</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>865422</v>
+        <v>865437</v>
       </c>
       <c r="R13" t="n">
-        <v>7447458</v>
+        <v>7447594</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1873,50 +1876,55 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Svea Nikula, Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126892999</v>
+        <v>126887991</v>
       </c>
       <c r="B14" t="n">
-        <v>80142</v>
+        <v>79014</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1926,13 +1934,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>865426</v>
+        <v>865422</v>
       </c>
       <c r="R14" t="n">
-        <v>7447493</v>
+        <v>7447458</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1976,48 +1984,44 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126892173</v>
+        <v>126887992</v>
       </c>
       <c r="B15" t="n">
-        <v>80143</v>
+        <v>79014</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2027,13 +2031,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>865379</v>
+        <v>865406</v>
       </c>
       <c r="R15" t="n">
-        <v>7447558</v>
+        <v>7447461</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2077,26 +2081,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>126893016</v>
       </c>
       <c r="B16" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2296,10 +2296,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126893017</v>
+        <v>126893301</v>
       </c>
       <c r="B18" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2331,10 +2331,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>865409</v>
+        <v>865382</v>
       </c>
       <c r="R18" t="n">
-        <v>7447573</v>
+        <v>7447699</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2381,12 +2381,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2397,10 +2397,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126893301</v>
+        <v>126893017</v>
       </c>
       <c r="B19" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>865382</v>
+        <v>865409</v>
       </c>
       <c r="R19" t="n">
-        <v>7447699</v>
+        <v>7447573</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2482,12 +2482,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2501,7 +2501,7 @@
         <v>126893004</v>
       </c>
       <c r="B20" t="n">
-        <v>80150</v>
+        <v>80153</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2599,10 +2599,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126893276</v>
+        <v>126891920</v>
       </c>
       <c r="B21" t="n">
-        <v>80150</v>
+        <v>80146</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2610,21 +2610,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2634,10 +2634,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>865406</v>
+        <v>865438</v>
       </c>
       <c r="R21" t="n">
-        <v>7447661</v>
+        <v>7447459</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2684,12 +2684,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2700,32 +2700,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126893293</v>
+        <v>126892172</v>
       </c>
       <c r="B22" t="n">
-        <v>79011</v>
+        <v>80146</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2735,10 +2735,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>865430</v>
+        <v>865436</v>
       </c>
       <c r="R22" t="n">
-        <v>7447483</v>
+        <v>7447532</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2785,12 +2785,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2801,10 +2801,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126891920</v>
+        <v>126893276</v>
       </c>
       <c r="B23" t="n">
-        <v>80143</v>
+        <v>80153</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2812,21 +2812,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2836,10 +2836,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>865438</v>
+        <v>865406</v>
       </c>
       <c r="R23" t="n">
-        <v>7447459</v>
+        <v>7447661</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2886,12 +2886,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2902,32 +2902,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126892172</v>
+        <v>126893293</v>
       </c>
       <c r="B24" t="n">
-        <v>80143</v>
+        <v>79014</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2937,10 +2937,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>865436</v>
+        <v>865430</v>
       </c>
       <c r="R24" t="n">
-        <v>7447532</v>
+        <v>7447483</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2987,12 +2987,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3003,32 +3003,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126888460</v>
+        <v>126892261</v>
       </c>
       <c r="B25" t="n">
-        <v>79011</v>
+        <v>80153</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>865380</v>
+        <v>865434</v>
       </c>
       <c r="R25" t="n">
-        <v>7447610</v>
+        <v>7447569</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3088,12 +3088,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3104,10 +3104,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126892261</v>
+        <v>126887982</v>
       </c>
       <c r="B26" t="n">
-        <v>80150</v>
+        <v>80153</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3142,10 +3142,10 @@
         <v>865434</v>
       </c>
       <c r="R26" t="n">
-        <v>7447569</v>
+        <v>7447388</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3189,48 +3189,44 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126887982</v>
+        <v>126888460</v>
       </c>
       <c r="B27" t="n">
-        <v>80150</v>
+        <v>79014</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3240,13 +3236,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>865434</v>
+        <v>865380</v>
       </c>
       <c r="R27" t="n">
-        <v>7447388</v>
+        <v>7447610</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3290,44 +3286,48 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Alva Dahlqvist Cederstrand</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126892179</v>
+        <v>126892030</v>
       </c>
       <c r="B28" t="n">
-        <v>80150</v>
+        <v>79014</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>865377</v>
+        <v>865389</v>
       </c>
       <c r="R28" t="n">
-        <v>7447525</v>
+        <v>7447613</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3387,12 +3387,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3406,7 +3406,7 @@
         <v>126893015</v>
       </c>
       <c r="B29" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3504,32 +3504,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126892030</v>
+        <v>126892179</v>
       </c>
       <c r="B30" t="n">
-        <v>79011</v>
+        <v>80153</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3539,10 +3539,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>865389</v>
+        <v>865377</v>
       </c>
       <c r="R30" t="n">
-        <v>7447613</v>
+        <v>7447525</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3589,12 +3589,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3605,32 +3605,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126893299</v>
+        <v>126892021</v>
       </c>
       <c r="B31" t="n">
-        <v>79011</v>
+        <v>80146</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3640,10 +3640,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>865406</v>
+        <v>865441</v>
       </c>
       <c r="R31" t="n">
-        <v>7447648</v>
+        <v>7447441</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3690,12 +3690,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3706,32 +3706,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126892021</v>
+        <v>126893299</v>
       </c>
       <c r="B32" t="n">
-        <v>80143</v>
+        <v>79014</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3741,10 +3741,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>865441</v>
+        <v>865406</v>
       </c>
       <c r="R32" t="n">
-        <v>7447441</v>
+        <v>7447648</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3791,12 +3791,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -3807,32 +3807,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126893306</v>
+        <v>126892262</v>
       </c>
       <c r="B33" t="n">
-        <v>82852</v>
+        <v>80153</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3842,10 +3842,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>865378</v>
+        <v>865404</v>
       </c>
       <c r="R33" t="n">
-        <v>7447665</v>
+        <v>7447633</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3892,12 +3892,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -3908,32 +3908,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126892262</v>
+        <v>126893306</v>
       </c>
       <c r="B34" t="n">
-        <v>80150</v>
+        <v>82855</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3943,10 +3943,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>865404</v>
+        <v>865378</v>
       </c>
       <c r="R34" t="n">
-        <v>7447633</v>
+        <v>7447665</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3993,12 +3993,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4012,7 +4012,7 @@
         <v>126892259</v>
       </c>
       <c r="B35" t="n">
-        <v>98457</v>
+        <v>98463</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4207,10 +4207,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126887993</v>
+        <v>126892978</v>
       </c>
       <c r="B37" t="n">
-        <v>79011</v>
+        <v>75138</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4218,21 +4218,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4242,13 +4242,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>865389</v>
+        <v>865423</v>
       </c>
       <c r="R37" t="n">
-        <v>7447521</v>
+        <v>7447442</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4292,22 +4292,26 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
         <v>126893298</v>
       </c>
       <c r="B38" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4405,10 +4409,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126892978</v>
+        <v>126887993</v>
       </c>
       <c r="B39" t="n">
-        <v>75135</v>
+        <v>79014</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4416,21 +4420,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4440,13 +4444,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>865423</v>
+        <v>865389</v>
       </c>
       <c r="R39" t="n">
-        <v>7447442</v>
+        <v>7447521</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4490,19 +4494,15 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4610,7 +4610,7 @@
         <v>126893266</v>
       </c>
       <c r="B41" t="n">
-        <v>80143</v>
+        <v>80146</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>126893297</v>
       </c>
       <c r="B42" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>126893022</v>
       </c>
       <c r="B43" t="n">
-        <v>98353</v>
+        <v>98359</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4910,10 +4910,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126892258</v>
+        <v>126893273</v>
       </c>
       <c r="B44" t="n">
-        <v>80143</v>
+        <v>80153</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4921,21 +4921,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4945,10 +4945,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>865430</v>
+        <v>865406</v>
       </c>
       <c r="R44" t="n">
-        <v>7447566</v>
+        <v>7447648</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4995,12 +4995,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5011,10 +5011,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126893273</v>
+        <v>126892258</v>
       </c>
       <c r="B45" t="n">
-        <v>80150</v>
+        <v>80146</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5022,21 +5022,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5046,10 +5046,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>865406</v>
+        <v>865430</v>
       </c>
       <c r="R45" t="n">
-        <v>7447648</v>
+        <v>7447566</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5096,12 +5096,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5115,7 +5115,7 @@
         <v>126892268</v>
       </c>
       <c r="B46" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5213,27 +5213,27 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126887994</v>
+        <v>126893028</v>
       </c>
       <c r="B47" t="n">
-        <v>79011</v>
+        <v>80152</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5248,13 +5248,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>865368</v>
+        <v>865390</v>
       </c>
       <c r="R47" t="n">
-        <v>7447606</v>
+        <v>7447609</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5298,22 +5298,26 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126893028</v>
+        <v>126892020</v>
       </c>
       <c r="B48" t="n">
-        <v>80149</v>
+        <v>80146</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5321,21 +5325,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5345,10 +5349,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>865390</v>
+        <v>865440</v>
       </c>
       <c r="R48" t="n">
-        <v>7447609</v>
+        <v>7447393</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5395,12 +5399,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5411,32 +5415,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126892020</v>
+        <v>126887994</v>
       </c>
       <c r="B49" t="n">
-        <v>80143</v>
+        <v>79014</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5446,13 +5450,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>865440</v>
+        <v>865368</v>
       </c>
       <c r="R49" t="n">
-        <v>7447393</v>
+        <v>7447606</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5496,26 +5500,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
         <v>126892254</v>
       </c>
       <c r="B50" t="n">
-        <v>75135</v>
+        <v>75138</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>126887983</v>
       </c>
       <c r="B51" t="n">
-        <v>80150</v>
+        <v>80153</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>126765146</v>
       </c>
       <c r="B52" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5816,32 +5816,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126893280</v>
+        <v>126892273</v>
       </c>
       <c r="B53" t="n">
-        <v>91480</v>
+        <v>78420</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1503</v>
+        <v>6437</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5851,10 +5851,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>865490</v>
+        <v>865528</v>
       </c>
       <c r="R53" t="n">
-        <v>7447213</v>
+        <v>7447193</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5901,12 +5901,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -5917,10 +5917,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126892273</v>
+        <v>126893008</v>
       </c>
       <c r="B54" t="n">
-        <v>78417</v>
+        <v>80989</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5928,21 +5928,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6437</v>
+        <v>1049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5952,10 +5952,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>865528</v>
+        <v>865545</v>
       </c>
       <c r="R54" t="n">
-        <v>7447193</v>
+        <v>7447322</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6002,12 +6002,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6018,32 +6018,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126892029</v>
+        <v>126891916</v>
       </c>
       <c r="B55" t="n">
-        <v>79011</v>
+        <v>80146</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6053,10 +6053,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>865448</v>
+        <v>865546</v>
       </c>
       <c r="R55" t="n">
-        <v>7447418</v>
+        <v>7447133</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6103,12 +6103,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6122,7 +6122,7 @@
         <v>126892026</v>
       </c>
       <c r="B56" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6220,32 +6220,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126891916</v>
+        <v>126892029</v>
       </c>
       <c r="B57" t="n">
-        <v>80143</v>
+        <v>79014</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6255,10 +6255,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>865546</v>
+        <v>865448</v>
       </c>
       <c r="R57" t="n">
-        <v>7447133</v>
+        <v>7447418</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6305,12 +6305,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6321,32 +6321,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126892985</v>
+        <v>126893280</v>
       </c>
       <c r="B58" t="n">
-        <v>79629</v>
+        <v>91486</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6356,10 +6356,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>865491</v>
+        <v>865490</v>
       </c>
       <c r="R58" t="n">
-        <v>7447332</v>
+        <v>7447213</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6406,12 +6406,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6422,32 +6422,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126893008</v>
+        <v>126891927</v>
       </c>
       <c r="B59" t="n">
-        <v>80986</v>
+        <v>98442</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1049</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6457,10 +6457,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>865545</v>
+        <v>865543</v>
       </c>
       <c r="R59" t="n">
-        <v>7447322</v>
+        <v>7447122</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6507,12 +6507,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6523,32 +6523,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126891927</v>
+        <v>126892985</v>
       </c>
       <c r="B60" t="n">
-        <v>98436</v>
+        <v>79632</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6558,10 +6558,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>865543</v>
+        <v>865491</v>
       </c>
       <c r="R60" t="n">
-        <v>7447122</v>
+        <v>7447332</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6608,12 +6608,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6627,7 +6627,7 @@
         <v>126892982</v>
       </c>
       <c r="B61" t="n">
-        <v>91284</v>
+        <v>91290</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>126891915</v>
       </c>
       <c r="B62" t="n">
-        <v>80143</v>
+        <v>80146</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6829,7 +6829,7 @@
         <v>126892177</v>
       </c>
       <c r="B63" t="n">
-        <v>92802</v>
+        <v>92808</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         <v>126887985</v>
       </c>
       <c r="B64" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
         <v>126893010</v>
       </c>
       <c r="B65" t="n">
-        <v>80986</v>
+        <v>80989</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7125,10 +7125,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126893000</v>
+        <v>126888002</v>
       </c>
       <c r="B66" t="n">
-        <v>92802</v>
+        <v>78681</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7136,21 +7136,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7160,13 +7160,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>865559</v>
+        <v>865512</v>
       </c>
       <c r="R66" t="n">
-        <v>7447299</v>
+        <v>7447340</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7210,48 +7210,44 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126892998</v>
+        <v>126893312</v>
       </c>
       <c r="B67" t="n">
-        <v>80142</v>
+        <v>77992</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6461</v>
+        <v>6487</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7261,10 +7257,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>865477</v>
+        <v>865598</v>
       </c>
       <c r="R67" t="n">
-        <v>7447327</v>
+        <v>7447181</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7311,12 +7307,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7327,32 +7323,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126891925</v>
+        <v>126892998</v>
       </c>
       <c r="B68" t="n">
-        <v>98436</v>
+        <v>80145</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7362,10 +7358,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>865527</v>
+        <v>865477</v>
       </c>
       <c r="R68" t="n">
-        <v>7447333</v>
+        <v>7447327</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7412,12 +7408,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7428,10 +7424,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126888002</v>
+        <v>126893000</v>
       </c>
       <c r="B69" t="n">
-        <v>78678</v>
+        <v>92808</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7439,21 +7435,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7463,13 +7459,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>865512</v>
+        <v>865559</v>
       </c>
       <c r="R69" t="n">
-        <v>7447340</v>
+        <v>7447299</v>
       </c>
       <c r="S69" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7513,22 +7509,26 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr"/>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126893312</v>
+        <v>126892183</v>
       </c>
       <c r="B70" t="n">
-        <v>77989</v>
+        <v>56840</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7536,34 +7536,50 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6487</v>
+        <v>102612</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>pulli</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>pulli/nyligen flygga ungar</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>865598</v>
+        <v>865484</v>
       </c>
       <c r="R70" t="n">
-        <v>7447181</v>
+        <v>7447494</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7598,6 +7614,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Stötte up 5st kycklingar, höll till under en och samma fallen gran</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -7610,12 +7631,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7626,61 +7647,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126892183</v>
+        <v>126891925</v>
       </c>
       <c r="B71" t="n">
-        <v>56840</v>
+        <v>98442</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>pulli</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>pulli/nyligen flygga ungar</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>865484</v>
+        <v>865527</v>
       </c>
       <c r="R71" t="n">
-        <v>7447494</v>
+        <v>7447333</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7715,11 +7720,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Stötte up 5st kycklingar, höll till under en och samma fallen gran</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -7732,12 +7732,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -7748,32 +7748,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126891911</v>
+        <v>126892187</v>
       </c>
       <c r="B72" t="n">
-        <v>91284</v>
+        <v>91486</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5447</v>
+        <v>1503</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7783,10 +7783,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>865557</v>
+        <v>865509</v>
       </c>
       <c r="R72" t="n">
-        <v>7447153</v>
+        <v>7447371</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7833,12 +7833,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -7849,32 +7849,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126893282</v>
+        <v>126893012</v>
       </c>
       <c r="B73" t="n">
-        <v>79011</v>
+        <v>91486</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7884,10 +7884,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>865611</v>
+        <v>865559</v>
       </c>
       <c r="R73" t="n">
-        <v>7446989</v>
+        <v>7447299</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7934,12 +7934,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -7950,32 +7950,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126892187</v>
+        <v>126891911</v>
       </c>
       <c r="B74" t="n">
-        <v>91480</v>
+        <v>91290</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1503</v>
+        <v>5447</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7985,10 +7985,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>865509</v>
+        <v>865557</v>
       </c>
       <c r="R74" t="n">
-        <v>7447371</v>
+        <v>7447153</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8035,12 +8035,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8051,32 +8051,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126893012</v>
+        <v>126893282</v>
       </c>
       <c r="B75" t="n">
-        <v>91480</v>
+        <v>79014</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8086,10 +8086,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>865559</v>
+        <v>865611</v>
       </c>
       <c r="R75" t="n">
-        <v>7447299</v>
+        <v>7446989</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8136,12 +8136,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8155,7 +8155,7 @@
         <v>126891926</v>
       </c>
       <c r="B76" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8253,32 +8253,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126891929</v>
+        <v>126891914</v>
       </c>
       <c r="B77" t="n">
-        <v>79011</v>
+        <v>80146</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8288,10 +8288,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>865535</v>
+        <v>865539</v>
       </c>
       <c r="R77" t="n">
-        <v>7447142</v>
+        <v>7447115</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8354,32 +8354,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126891914</v>
+        <v>126891929</v>
       </c>
       <c r="B78" t="n">
-        <v>80143</v>
+        <v>79014</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8389,10 +8389,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>865539</v>
+        <v>865535</v>
       </c>
       <c r="R78" t="n">
-        <v>7447115</v>
+        <v>7447142</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8455,54 +8455,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126891930</v>
+        <v>126893270</v>
       </c>
       <c r="B79" t="n">
-        <v>8436</v>
+        <v>92808</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>106554</v>
+        <v>2079</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>865561</v>
+        <v>865491</v>
       </c>
       <c r="R79" t="n">
-        <v>7447167</v>
+        <v>7447267</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8543,19 +8534,18 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8566,32 +8556,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126893270</v>
+        <v>126887974</v>
       </c>
       <c r="B80" t="n">
-        <v>92802</v>
+        <v>97326</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2079</v>
+        <v>221941</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8601,13 +8591,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>865491</v>
+        <v>865641</v>
       </c>
       <c r="R80" t="n">
-        <v>7447267</v>
+        <v>7447070</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8651,26 +8641,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
         <v>126888001</v>
       </c>
       <c r="B81" t="n">
-        <v>78678</v>
+        <v>78681</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8764,10 +8750,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126887974</v>
+        <v>126891930</v>
       </c>
       <c r="B82" t="n">
-        <v>97320</v>
+        <v>8436</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8775,37 +8761,46 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221941</v>
+        <v>106554</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>865641</v>
+        <v>865561</v>
       </c>
       <c r="R82" t="n">
-        <v>7447070</v>
+        <v>7447167</v>
       </c>
       <c r="S82" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8843,28 +8838,33 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr"/>
+          <t>Amanda Rudelius</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
         <v>126893277</v>
       </c>
       <c r="B83" t="n">
-        <v>80986</v>
+        <v>80989</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8962,45 +8962,53 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126888457</v>
+        <v>126888454</v>
       </c>
       <c r="B84" t="n">
-        <v>91480</v>
+        <v>57817</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1503</v>
+        <v>103021</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>865528</v>
+        <v>865481</v>
       </c>
       <c r="R84" t="n">
-        <v>7447201</v>
+        <v>7447376</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9063,10 +9071,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126892185</v>
+        <v>126893278</v>
       </c>
       <c r="B85" t="n">
-        <v>91480</v>
+        <v>98442</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9074,21 +9082,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1503</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9098,10 +9106,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>865490</v>
+        <v>865551</v>
       </c>
       <c r="R85" t="n">
-        <v>7447287</v>
+        <v>7447276</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9148,12 +9156,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -9164,32 +9172,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126892175</v>
+        <v>126892181</v>
       </c>
       <c r="B86" t="n">
-        <v>92802</v>
+        <v>98442</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2079</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9199,10 +9207,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>865509</v>
+        <v>865459</v>
       </c>
       <c r="R86" t="n">
-        <v>7447217</v>
+        <v>7447305</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9265,32 +9273,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126887978</v>
+        <v>126893003</v>
       </c>
       <c r="B87" t="n">
-        <v>92802</v>
+        <v>80153</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2079</v>
+        <v>6464</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9300,13 +9308,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>865521</v>
+        <v>865532</v>
       </c>
       <c r="R87" t="n">
-        <v>7447240</v>
+        <v>7447307</v>
       </c>
       <c r="S87" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9350,22 +9358,26 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY87" t="inlineStr"/>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126892192</v>
+        <v>126892271</v>
       </c>
       <c r="B88" t="n">
-        <v>92609</v>
+        <v>80152</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9373,21 +9385,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4364</v>
+        <v>6463</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9397,10 +9409,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>865502</v>
+        <v>865610</v>
       </c>
       <c r="R88" t="n">
-        <v>7447389</v>
+        <v>7447145</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9447,12 +9459,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -9463,53 +9475,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126888454</v>
+        <v>126888457</v>
       </c>
       <c r="B89" t="n">
-        <v>57817</v>
+        <v>91486</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>103021</v>
+        <v>1503</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>865481</v>
+        <v>865528</v>
       </c>
       <c r="R89" t="n">
-        <v>7447376</v>
+        <v>7447201</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9572,32 +9576,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126893003</v>
+        <v>126892185</v>
       </c>
       <c r="B90" t="n">
-        <v>80150</v>
+        <v>91486</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6464</v>
+        <v>1503</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9607,10 +9611,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>865532</v>
+        <v>865490</v>
       </c>
       <c r="R90" t="n">
-        <v>7447307</v>
+        <v>7447287</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9657,12 +9661,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -9673,32 +9677,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126892271</v>
+        <v>126892175</v>
       </c>
       <c r="B91" t="n">
-        <v>80149</v>
+        <v>92808</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6463</v>
+        <v>2079</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9708,10 +9712,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>865610</v>
+        <v>865509</v>
       </c>
       <c r="R91" t="n">
-        <v>7447145</v>
+        <v>7447217</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9758,12 +9762,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -9774,32 +9778,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126892181</v>
+        <v>126887978</v>
       </c>
       <c r="B92" t="n">
-        <v>98436</v>
+        <v>92808</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>2079</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9809,13 +9813,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>865459</v>
+        <v>865521</v>
       </c>
       <c r="R92" t="n">
-        <v>7447305</v>
+        <v>7447240</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9859,48 +9863,44 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126893278</v>
+        <v>126892192</v>
       </c>
       <c r="B93" t="n">
-        <v>98436</v>
+        <v>92615</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9910,10 +9910,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>865551</v>
+        <v>865502</v>
       </c>
       <c r="R93" t="n">
-        <v>7447276</v>
+        <v>7447389</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9960,12 +9960,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -9976,32 +9976,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126893281</v>
+        <v>126892267</v>
       </c>
       <c r="B94" t="n">
-        <v>91480</v>
+        <v>79014</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10011,10 +10011,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>865513</v>
+        <v>865516</v>
       </c>
       <c r="R94" t="n">
-        <v>7447339</v>
+        <v>7447351</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10061,12 +10061,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10077,32 +10077,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126888000</v>
+        <v>126893281</v>
       </c>
       <c r="B95" t="n">
-        <v>78678</v>
+        <v>91486</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10112,13 +10112,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>865597</v>
+        <v>865513</v>
       </c>
       <c r="R95" t="n">
-        <v>7447186</v>
+        <v>7447339</v>
       </c>
       <c r="S95" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10162,44 +10162,48 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY95" t="inlineStr"/>
+          <t>Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126892981</v>
+        <v>126892178</v>
       </c>
       <c r="B96" t="n">
-        <v>91284</v>
+        <v>92808</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5447</v>
+        <v>2079</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10209,10 +10213,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>865553</v>
+        <v>865509</v>
       </c>
       <c r="R96" t="n">
-        <v>7447278</v>
+        <v>7447375</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10259,12 +10263,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10275,32 +10279,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126893023</v>
+        <v>126893025</v>
       </c>
       <c r="B97" t="n">
-        <v>91720</v>
+        <v>92615</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>715</v>
+        <v>4364</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Finporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Gloeoporus pannocinctus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Romell) J.Erikss.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10310,10 +10314,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>865473</v>
+        <v>865518</v>
       </c>
       <c r="R97" t="n">
-        <v>7447321</v>
+        <v>7447235</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10376,32 +10380,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126892178</v>
+        <v>126892981</v>
       </c>
       <c r="B98" t="n">
-        <v>92802</v>
+        <v>91290</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2079</v>
+        <v>5447</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10411,10 +10415,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>865509</v>
+        <v>865553</v>
       </c>
       <c r="R98" t="n">
-        <v>7447375</v>
+        <v>7447278</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10461,12 +10465,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10477,10 +10481,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126893025</v>
+        <v>126887997</v>
       </c>
       <c r="B99" t="n">
-        <v>92609</v>
+        <v>98359</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10488,21 +10492,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4364</v>
+        <v>219790</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10512,13 +10516,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>865518</v>
+        <v>865448</v>
       </c>
       <c r="R99" t="n">
-        <v>7447235</v>
+        <v>7447350</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10562,26 +10566,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
-        </is>
-      </c>
-      <c r="AY99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126892267</v>
+        <v>126888000</v>
       </c>
       <c r="B100" t="n">
-        <v>79011</v>
+        <v>78681</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10589,21 +10589,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10613,13 +10613,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>865516</v>
+        <v>865597</v>
       </c>
       <c r="R100" t="n">
-        <v>7447351</v>
+        <v>7447186</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10663,48 +10663,44 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
-        </is>
-      </c>
-      <c r="AY100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126887968</v>
+        <v>126893023</v>
       </c>
       <c r="B101" t="n">
-        <v>57817</v>
+        <v>91726</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>103021</v>
+        <v>715</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Finporing</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Gloeoporus pannocinctus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Romell) J.Erikss.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10714,13 +10710,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>865523</v>
+        <v>865473</v>
       </c>
       <c r="R101" t="n">
-        <v>7447217</v>
+        <v>7447321</v>
       </c>
       <c r="S101" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10764,44 +10760,48 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY101" t="inlineStr"/>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126887997</v>
+        <v>126887968</v>
       </c>
       <c r="B102" t="n">
-        <v>98353</v>
+        <v>57817</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>865448</v>
+        <v>865523</v>
       </c>
       <c r="R102" t="n">
-        <v>7447350</v>
+        <v>7447217</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -10876,7 +10876,7 @@
         <v>126892186</v>
       </c>
       <c r="B103" t="n">
-        <v>91480</v>
+        <v>91486</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>126893033</v>
       </c>
       <c r="B104" t="n">
-        <v>78417</v>
+        <v>78420</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11078,7 +11078,7 @@
         <v>126891923</v>
       </c>
       <c r="B105" t="n">
-        <v>80018</v>
+        <v>80021</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11179,7 +11179,7 @@
         <v>126893310</v>
       </c>
       <c r="B106" t="n">
-        <v>91580</v>
+        <v>91586</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11280,7 +11280,7 @@
         <v>126892028</v>
       </c>
       <c r="B107" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11381,7 +11381,7 @@
         <v>126887980</v>
       </c>
       <c r="B108" t="n">
-        <v>92802</v>
+        <v>92808</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11475,32 +11475,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126887975</v>
+        <v>126887990</v>
       </c>
       <c r="B109" t="n">
-        <v>97320</v>
+        <v>79014</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11510,10 +11510,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>865479</v>
+        <v>865447</v>
       </c>
       <c r="R109" t="n">
-        <v>7447358</v>
+        <v>7447371</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -11572,48 +11572,56 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126887976</v>
+        <v>126892263</v>
       </c>
       <c r="B110" t="n">
-        <v>97320</v>
+        <v>56840</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>221941</v>
+        <v>102612</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>865452</v>
+        <v>865544</v>
       </c>
       <c r="R110" t="n">
-        <v>7447334</v>
+        <v>7447281</v>
       </c>
       <c r="S110" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -11657,44 +11665,48 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY110" t="inlineStr"/>
+          <t>Svea Nikula</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126893009</v>
+        <v>126887965</v>
       </c>
       <c r="B111" t="n">
-        <v>80986</v>
+        <v>57479</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1049</v>
+        <v>102976</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11704,13 +11716,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>865553</v>
+        <v>865583</v>
       </c>
       <c r="R111" t="n">
-        <v>7447326</v>
+        <v>7447214</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -11754,26 +11766,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
-        </is>
-      </c>
-      <c r="AY111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126887987</v>
+        <v>126891928</v>
       </c>
       <c r="B112" t="n">
-        <v>91480</v>
+        <v>98442</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11781,21 +11789,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1503</v>
+        <v>220787</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11805,13 +11813,13 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>865510</v>
+        <v>865549</v>
       </c>
       <c r="R112" t="n">
-        <v>7447247</v>
+        <v>7447136</v>
       </c>
       <c r="S112" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -11855,44 +11863,48 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY112" t="inlineStr"/>
+          <t>Amanda Rudelius</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126887977</v>
+        <v>126892024</v>
       </c>
       <c r="B113" t="n">
-        <v>92802</v>
+        <v>98442</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>2079</v>
+        <v>220787</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11902,13 +11914,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>865643</v>
+        <v>865546</v>
       </c>
       <c r="R113" t="n">
-        <v>7447067</v>
+        <v>7447138</v>
       </c>
       <c r="S113" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -11952,44 +11964,48 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY113" t="inlineStr"/>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126892191</v>
+        <v>126887975</v>
       </c>
       <c r="B114" t="n">
-        <v>91580</v>
+        <v>97326</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>65</v>
+        <v>221941</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11999,13 +12015,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>865540</v>
+        <v>865479</v>
       </c>
       <c r="R114" t="n">
-        <v>7447366</v>
+        <v>7447358</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12049,48 +12065,44 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126887990</v>
+        <v>126887976</v>
       </c>
       <c r="B115" t="n">
-        <v>79011</v>
+        <v>97326</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12100,10 +12112,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>865447</v>
+        <v>865452</v>
       </c>
       <c r="R115" t="n">
-        <v>7447371</v>
+        <v>7447334</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -12162,53 +12174,45 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126892263</v>
+        <v>126892191</v>
       </c>
       <c r="B116" t="n">
-        <v>56840</v>
+        <v>91586</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>102612</v>
+        <v>65</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>865544</v>
+        <v>865540</v>
       </c>
       <c r="R116" t="n">
-        <v>7447281</v>
+        <v>7447366</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12255,12 +12259,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
@@ -12271,32 +12275,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126887965</v>
+        <v>126893009</v>
       </c>
       <c r="B117" t="n">
-        <v>57479</v>
+        <v>80989</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>102976</v>
+        <v>1049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12306,13 +12310,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>865583</v>
+        <v>865553</v>
       </c>
       <c r="R117" t="n">
-        <v>7447214</v>
+        <v>7447326</v>
       </c>
       <c r="S117" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12356,22 +12360,26 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY117" t="inlineStr"/>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126892018</v>
+        <v>126887977</v>
       </c>
       <c r="B118" t="n">
-        <v>57817</v>
+        <v>92808</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12379,49 +12387,37 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>103021</v>
+        <v>2079</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr"/>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>865561</v>
+        <v>865643</v>
       </c>
       <c r="R118" t="n">
-        <v>7447155</v>
+        <v>7447067</v>
       </c>
       <c r="S118" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -12465,26 +12461,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
-        </is>
-      </c>
-      <c r="AY118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126891928</v>
+        <v>126887987</v>
       </c>
       <c r="B119" t="n">
-        <v>98436</v>
+        <v>91486</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12492,21 +12484,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>220787</v>
+        <v>1503</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12516,13 +12508,13 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>865549</v>
+        <v>865510</v>
       </c>
       <c r="R119" t="n">
-        <v>7447136</v>
+        <v>7447247</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -12566,61 +12558,69 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
-        </is>
-      </c>
-      <c r="AY119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126892024</v>
+        <v>126892018</v>
       </c>
       <c r="B120" t="n">
-        <v>98436</v>
+        <v>57817</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>865546</v>
+        <v>865561</v>
       </c>
       <c r="R120" t="n">
-        <v>7447138</v>
+        <v>7447155</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12672,7 +12672,7 @@
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
@@ -12683,32 +12683,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126893267</v>
+        <v>126893308</v>
       </c>
       <c r="B121" t="n">
-        <v>92802</v>
+        <v>91586</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>2079</v>
+        <v>65</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12718,10 +12718,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>865648</v>
+        <v>865659</v>
       </c>
       <c r="R121" t="n">
-        <v>7447056</v>
+        <v>7447048</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12784,32 +12784,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126893308</v>
+        <v>126893030</v>
       </c>
       <c r="B122" t="n">
-        <v>91580</v>
+        <v>77992</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>65</v>
+        <v>6487</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12819,10 +12819,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>865659</v>
+        <v>865545</v>
       </c>
       <c r="R122" t="n">
-        <v>7447048</v>
+        <v>7447323</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12869,12 +12869,12 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
@@ -12885,32 +12885,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126893260</v>
+        <v>126887981</v>
       </c>
       <c r="B123" t="n">
-        <v>91241</v>
+        <v>80153</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>3242</v>
+        <v>6464</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12920,13 +12920,13 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>865498</v>
+        <v>865448</v>
       </c>
       <c r="R123" t="n">
-        <v>7447359</v>
+        <v>7447345</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -12970,26 +12970,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
-        </is>
-      </c>
-      <c r="AY123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
         <v>126893262</v>
       </c>
       <c r="B124" t="n">
-        <v>91284</v>
+        <v>91290</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13087,10 +13083,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126893030</v>
+        <v>126893267</v>
       </c>
       <c r="B125" t="n">
-        <v>77989</v>
+        <v>92808</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13098,21 +13094,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6487</v>
+        <v>2079</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13122,10 +13118,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>865545</v>
+        <v>865648</v>
       </c>
       <c r="R125" t="n">
-        <v>7447323</v>
+        <v>7447056</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13172,12 +13168,12 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
@@ -13188,32 +13184,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126887981</v>
+        <v>126893260</v>
       </c>
       <c r="B126" t="n">
-        <v>80150</v>
+        <v>91247</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6464</v>
+        <v>3242</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13223,13 +13219,13 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>865448</v>
+        <v>865498</v>
       </c>
       <c r="R126" t="n">
-        <v>7447345</v>
+        <v>7447359</v>
       </c>
       <c r="S126" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13273,15 +13269,19 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY126" t="inlineStr"/>
+          <t>Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13391,32 +13391,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126887988</v>
+        <v>126893313</v>
       </c>
       <c r="B128" t="n">
-        <v>91480</v>
+        <v>78420</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1503</v>
+        <v>6437</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13426,13 +13426,13 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>865515</v>
+        <v>865598</v>
       </c>
       <c r="R128" t="n">
-        <v>7447377</v>
+        <v>7447181</v>
       </c>
       <c r="S128" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13476,44 +13476,48 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY128" t="inlineStr"/>
+          <t>Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126893269</v>
+        <v>126887970</v>
       </c>
       <c r="B129" t="n">
-        <v>92802</v>
+        <v>80146</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>2079</v>
+        <v>6462</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13523,13 +13527,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>865647</v>
+        <v>865529</v>
       </c>
       <c r="R129" t="n">
-        <v>7447057</v>
+        <v>7447327</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -13573,26 +13577,22 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
-        </is>
-      </c>
-      <c r="AY129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126887970</v>
+        <v>126893274</v>
       </c>
       <c r="B130" t="n">
-        <v>80143</v>
+        <v>80153</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13600,21 +13600,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13624,13 +13624,13 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>865529</v>
+        <v>865476</v>
       </c>
       <c r="R130" t="n">
-        <v>7447327</v>
+        <v>7447236</v>
       </c>
       <c r="S130" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -13674,22 +13674,26 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY130" t="inlineStr"/>
+          <t>Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126893313</v>
+        <v>126893292</v>
       </c>
       <c r="B131" t="n">
-        <v>78417</v>
+        <v>79014</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13697,21 +13701,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13721,10 +13725,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>865598</v>
+        <v>865501</v>
       </c>
       <c r="R131" t="n">
-        <v>7447181</v>
+        <v>7447191</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13787,32 +13791,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126893274</v>
+        <v>126887988</v>
       </c>
       <c r="B132" t="n">
-        <v>80150</v>
+        <v>91486</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6464</v>
+        <v>1503</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13822,13 +13826,13 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>865476</v>
+        <v>865515</v>
       </c>
       <c r="R132" t="n">
-        <v>7447236</v>
+        <v>7447377</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -13872,26 +13876,22 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
-        </is>
-      </c>
-      <c r="AY132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126893292</v>
+        <v>126893269</v>
       </c>
       <c r="B133" t="n">
-        <v>79011</v>
+        <v>92808</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13899,21 +13899,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13923,10 +13923,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>865501</v>
+        <v>865647</v>
       </c>
       <c r="R133" t="n">
-        <v>7447191</v>
+        <v>7447057</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13989,32 +13989,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126892256</v>
+        <v>126892984</v>
       </c>
       <c r="B134" t="n">
-        <v>91284</v>
+        <v>79632</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14024,10 +14024,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>865491</v>
+        <v>865523</v>
       </c>
       <c r="R134" t="n">
-        <v>7447326</v>
+        <v>7447267</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14074,12 +14074,12 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
@@ -14090,10 +14090,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126893034</v>
+        <v>126887962</v>
       </c>
       <c r="B135" t="n">
-        <v>78417</v>
+        <v>79632</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14101,21 +14101,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14125,13 +14125,13 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>865544</v>
+        <v>865519</v>
       </c>
       <c r="R135" t="n">
-        <v>7447321</v>
+        <v>7447214</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -14175,26 +14175,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
-        </is>
-      </c>
-      <c r="AY135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126893290</v>
+        <v>126893034</v>
       </c>
       <c r="B136" t="n">
-        <v>79011</v>
+        <v>78420</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14202,21 +14198,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14226,10 +14222,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>865505</v>
+        <v>865544</v>
       </c>
       <c r="R136" t="n">
-        <v>7447150</v>
+        <v>7447321</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14276,12 +14272,12 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
@@ -14295,7 +14291,7 @@
         <v>126892189</v>
       </c>
       <c r="B137" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14393,10 +14389,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126892984</v>
+        <v>126893290</v>
       </c>
       <c r="B138" t="n">
-        <v>79629</v>
+        <v>79014</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14404,21 +14400,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14428,10 +14424,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>865523</v>
+        <v>865505</v>
       </c>
       <c r="R138" t="n">
-        <v>7447267</v>
+        <v>7447150</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14478,12 +14474,12 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
@@ -14494,10 +14490,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126887962</v>
+        <v>126892176</v>
       </c>
       <c r="B139" t="n">
-        <v>79629</v>
+        <v>92808</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14505,21 +14501,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14529,13 +14525,13 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>865519</v>
+        <v>865490</v>
       </c>
       <c r="R139" t="n">
-        <v>7447214</v>
+        <v>7447287</v>
       </c>
       <c r="S139" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -14579,44 +14575,48 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY139" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126892176</v>
+        <v>126892256</v>
       </c>
       <c r="B140" t="n">
-        <v>92802</v>
+        <v>91290</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2079</v>
+        <v>5447</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14626,10 +14626,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>865490</v>
+        <v>865491</v>
       </c>
       <c r="R140" t="n">
-        <v>7447287</v>
+        <v>7447326</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14676,12 +14676,12 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
@@ -14695,7 +14695,7 @@
         <v>126888456</v>
       </c>
       <c r="B141" t="n">
-        <v>92802</v>
+        <v>92808</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14793,32 +14793,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126892253</v>
+        <v>126887971</v>
       </c>
       <c r="B142" t="n">
-        <v>91241</v>
+        <v>80146</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>3242</v>
+        <v>6462</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14828,13 +14828,13 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>865491</v>
+        <v>865452</v>
       </c>
       <c r="R142" t="n">
-        <v>7447326</v>
+        <v>7447318</v>
       </c>
       <c r="S142" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -14878,26 +14878,22 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
-        </is>
-      </c>
-      <c r="AY142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126887971</v>
+        <v>126892991</v>
       </c>
       <c r="B143" t="n">
-        <v>80143</v>
+        <v>80146</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14929,13 +14925,13 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>865452</v>
+        <v>865531</v>
       </c>
       <c r="R143" t="n">
-        <v>7447318</v>
+        <v>7447308</v>
       </c>
       <c r="S143" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -14979,22 +14975,26 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY143" t="inlineStr"/>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>126892991</v>
+        <v>126891917</v>
       </c>
       <c r="B144" t="n">
-        <v>80143</v>
+        <v>80146</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15026,10 +15026,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>865531</v>
+        <v>865561</v>
       </c>
       <c r="R144" t="n">
-        <v>7447308</v>
+        <v>7447152</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15076,12 +15076,12 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
@@ -15092,32 +15092,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126891917</v>
+        <v>126892253</v>
       </c>
       <c r="B145" t="n">
-        <v>80143</v>
+        <v>91247</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6462</v>
+        <v>3242</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15127,10 +15127,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>865561</v>
+        <v>865491</v>
       </c>
       <c r="R145" t="n">
-        <v>7447152</v>
+        <v>7447326</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15177,12 +15177,12 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
@@ -15193,32 +15193,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126893264</v>
+        <v>126892983</v>
       </c>
       <c r="B146" t="n">
-        <v>57479</v>
+        <v>79632</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>102976</v>
+        <v>6453</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15228,10 +15228,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>865598</v>
+        <v>865546</v>
       </c>
       <c r="R146" t="n">
-        <v>7447180</v>
+        <v>7447275</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15278,12 +15278,12 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
@@ -15294,10 +15294,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>126892983</v>
+        <v>126892266</v>
       </c>
       <c r="B147" t="n">
-        <v>79629</v>
+        <v>79014</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15305,21 +15305,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15329,10 +15329,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>865546</v>
+        <v>865495</v>
       </c>
       <c r="R147" t="n">
-        <v>7447275</v>
+        <v>7447285</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15379,12 +15379,12 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
@@ -15395,10 +15395,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126892266</v>
+        <v>126888459</v>
       </c>
       <c r="B148" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15430,10 +15430,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>865495</v>
+        <v>865501</v>
       </c>
       <c r="R148" t="n">
-        <v>7447285</v>
+        <v>7447386</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15480,12 +15480,12 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
@@ -15496,32 +15496,32 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126888459</v>
+        <v>126893264</v>
       </c>
       <c r="B149" t="n">
-        <v>79011</v>
+        <v>57479</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>102976</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15531,10 +15531,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>865501</v>
+        <v>865598</v>
       </c>
       <c r="R149" t="n">
-        <v>7447386</v>
+        <v>7447180</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15581,12 +15581,12 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
@@ -15597,10 +15597,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126893259</v>
+        <v>126891909</v>
       </c>
       <c r="B150" t="n">
-        <v>91241</v>
+        <v>75138</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15608,21 +15608,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>3242</v>
+        <v>6440</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15632,10 +15632,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>865646</v>
+        <v>865542</v>
       </c>
       <c r="R150" t="n">
-        <v>7447063</v>
+        <v>7447122</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15682,12 +15682,12 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
@@ -15701,7 +15701,7 @@
         <v>126892980</v>
       </c>
       <c r="B151" t="n">
-        <v>91284</v>
+        <v>91290</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15799,10 +15799,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>126891909</v>
+        <v>126893259</v>
       </c>
       <c r="B152" t="n">
-        <v>75135</v>
+        <v>91247</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15810,21 +15810,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6440</v>
+        <v>3242</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15834,10 +15834,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>865542</v>
+        <v>865646</v>
       </c>
       <c r="R152" t="n">
-        <v>7447122</v>
+        <v>7447063</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15884,12 +15884,12 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
@@ -15903,7 +15903,7 @@
         <v>126892023</v>
       </c>
       <c r="B153" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16017,7 +16017,7 @@
         <v>126893011</v>
       </c>
       <c r="B154" t="n">
-        <v>80986</v>
+        <v>80989</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16115,10 +16115,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126887979</v>
+        <v>126892272</v>
       </c>
       <c r="B155" t="n">
-        <v>92802</v>
+        <v>77992</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16126,21 +16126,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>2079</v>
+        <v>6487</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16150,13 +16150,13 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>865510</v>
+        <v>865528</v>
       </c>
       <c r="R155" t="n">
-        <v>7447251</v>
+        <v>7447192</v>
       </c>
       <c r="S155" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -16200,44 +16200,48 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY155" t="inlineStr"/>
+          <t>Svea Nikula</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>126892974</v>
+        <v>126892255</v>
       </c>
       <c r="B156" t="n">
-        <v>91241</v>
+        <v>91290</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>3242</v>
+        <v>5447</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16247,10 +16251,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>865494</v>
+        <v>865462</v>
       </c>
       <c r="R156" t="n">
-        <v>7447322</v>
+        <v>7447413</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16297,12 +16301,12 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
@@ -16313,32 +16317,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126892255</v>
+        <v>126887979</v>
       </c>
       <c r="B157" t="n">
-        <v>91284</v>
+        <v>92808</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>5447</v>
+        <v>2079</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16348,13 +16352,13 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>865462</v>
+        <v>865510</v>
       </c>
       <c r="R157" t="n">
-        <v>7447413</v>
+        <v>7447251</v>
       </c>
       <c r="S157" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -16398,26 +16402,22 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
-        </is>
-      </c>
-      <c r="AY157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>126892272</v>
+        <v>126892974</v>
       </c>
       <c r="B158" t="n">
-        <v>77989</v>
+        <v>91247</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16425,21 +16425,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6487</v>
+        <v>3242</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16449,10 +16449,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>865528</v>
+        <v>865494</v>
       </c>
       <c r="R158" t="n">
-        <v>7447192</v>
+        <v>7447322</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16499,12 +16499,12 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
@@ -16515,45 +16515,48 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>126888458</v>
+        <v>126891924</v>
       </c>
       <c r="B159" t="n">
-        <v>91480</v>
+        <v>78772</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>865502</v>
+        <v>865562</v>
       </c>
       <c r="R159" t="n">
-        <v>7447310</v>
+        <v>7447150</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16594,18 +16597,19 @@
       <c r="AE159" t="b">
         <v>0</v>
       </c>
+      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
@@ -16616,10 +16620,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>126893272</v>
+        <v>126887961</v>
       </c>
       <c r="B160" t="n">
-        <v>92802</v>
+        <v>79632</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16627,21 +16631,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16651,13 +16655,13 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>865520</v>
+        <v>865602</v>
       </c>
       <c r="R160" t="n">
-        <v>7447337</v>
+        <v>7447176</v>
       </c>
       <c r="S160" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -16701,48 +16705,44 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
-        </is>
-      </c>
-      <c r="AY160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>126887961</v>
+        <v>126893265</v>
       </c>
       <c r="B161" t="n">
-        <v>79629</v>
+        <v>80146</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6453</v>
+        <v>6462</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16752,13 +16752,13 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>865602</v>
+        <v>865530</v>
       </c>
       <c r="R161" t="n">
-        <v>7447176</v>
+        <v>7447304</v>
       </c>
       <c r="S161" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -16802,44 +16802,48 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY161" t="inlineStr"/>
+          <t>Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>126893291</v>
+        <v>126891919</v>
       </c>
       <c r="B162" t="n">
-        <v>79011</v>
+        <v>80146</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16849,10 +16853,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>865507</v>
+        <v>865447</v>
       </c>
       <c r="R162" t="n">
-        <v>7447151</v>
+        <v>7447440</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16899,12 +16903,12 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
@@ -16915,32 +16919,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>126892016</v>
+        <v>126893291</v>
       </c>
       <c r="B163" t="n">
-        <v>91284</v>
+        <v>79014</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -16950,10 +16954,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>865558</v>
+        <v>865507</v>
       </c>
       <c r="R163" t="n">
-        <v>7447154</v>
+        <v>7447151</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17000,12 +17004,12 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
@@ -17016,10 +17020,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>126893265</v>
+        <v>126892016</v>
       </c>
       <c r="B164" t="n">
-        <v>80143</v>
+        <v>91290</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17027,21 +17031,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17051,10 +17055,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>865530</v>
+        <v>865558</v>
       </c>
       <c r="R164" t="n">
-        <v>7447304</v>
+        <v>7447154</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17101,12 +17105,12 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
@@ -17117,10 +17121,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>126891924</v>
+        <v>126893272</v>
       </c>
       <c r="B165" t="n">
-        <v>78769</v>
+        <v>92808</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17128,37 +17132,34 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>865562</v>
+        <v>865520</v>
       </c>
       <c r="R165" t="n">
-        <v>7447150</v>
+        <v>7447337</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17199,19 +17200,18 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
-      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
@@ -17222,32 +17222,32 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>126891919</v>
+        <v>126888458</v>
       </c>
       <c r="B166" t="n">
-        <v>80143</v>
+        <v>91486</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6462</v>
+        <v>1503</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17257,10 +17257,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>865447</v>
+        <v>865502</v>
       </c>
       <c r="R166" t="n">
-        <v>7447440</v>
+        <v>7447310</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17307,12 +17307,12 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
@@ -17323,32 +17323,32 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>126892988</v>
+        <v>126893021</v>
       </c>
       <c r="B167" t="n">
-        <v>57479</v>
+        <v>91586</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>102976</v>
+        <v>65</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17358,10 +17358,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>865530</v>
+        <v>865547</v>
       </c>
       <c r="R167" t="n">
-        <v>7447298</v>
+        <v>7447316</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17424,10 +17424,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>126893021</v>
+        <v>126893309</v>
       </c>
       <c r="B168" t="n">
-        <v>91580</v>
+        <v>91586</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17459,10 +17459,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>865547</v>
+        <v>865661</v>
       </c>
       <c r="R168" t="n">
-        <v>7447316</v>
+        <v>7447053</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17509,12 +17509,12 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
@@ -17525,32 +17525,32 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>126893309</v>
+        <v>126893031</v>
       </c>
       <c r="B169" t="n">
-        <v>91580</v>
+        <v>77992</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>65</v>
+        <v>6487</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17560,10 +17560,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>865661</v>
+        <v>865490</v>
       </c>
       <c r="R169" t="n">
-        <v>7447053</v>
+        <v>7447338</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17610,12 +17610,12 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
@@ -17629,7 +17629,7 @@
         <v>126893284</v>
       </c>
       <c r="B170" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17727,32 +17727,32 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>126893031</v>
+        <v>126892988</v>
       </c>
       <c r="B171" t="n">
-        <v>77989</v>
+        <v>57479</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6487</v>
+        <v>102976</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -17762,10 +17762,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>865490</v>
+        <v>865530</v>
       </c>
       <c r="R171" t="n">
-        <v>7447338</v>
+        <v>7447298</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17828,32 +17828,32 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>126892174</v>
+        <v>126892997</v>
       </c>
       <c r="B172" t="n">
-        <v>92802</v>
+        <v>79038</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>2079</v>
+        <v>6434</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -17863,10 +17863,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>865517</v>
+        <v>865545</v>
       </c>
       <c r="R172" t="n">
-        <v>7447401</v>
+        <v>7447323</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -17913,12 +17913,12 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
@@ -17929,32 +17929,32 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>126892997</v>
+        <v>126893314</v>
       </c>
       <c r="B173" t="n">
-        <v>79035</v>
+        <v>78420</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6434</v>
+        <v>6437</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -17964,10 +17964,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>865545</v>
+        <v>865647</v>
       </c>
       <c r="R173" t="n">
-        <v>7447323</v>
+        <v>7447060</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18014,12 +18014,12 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
@@ -18030,10 +18030,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>126893294</v>
+        <v>126891913</v>
       </c>
       <c r="B174" t="n">
-        <v>79011</v>
+        <v>79632</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18041,21 +18041,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18065,10 +18065,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>865457</v>
+        <v>865557</v>
       </c>
       <c r="R174" t="n">
-        <v>7447523</v>
+        <v>7447153</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18115,12 +18115,12 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr">
@@ -18131,10 +18131,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>126893263</v>
+        <v>126893294</v>
       </c>
       <c r="B175" t="n">
-        <v>91319</v>
+        <v>79014</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18142,21 +18142,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18166,10 +18166,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>865485</v>
+        <v>865457</v>
       </c>
       <c r="R175" t="n">
-        <v>7447224</v>
+        <v>7447523</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18235,7 +18235,7 @@
         <v>126892188</v>
       </c>
       <c r="B176" t="n">
-        <v>91480</v>
+        <v>91486</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18336,7 +18336,7 @@
         <v>126887986</v>
       </c>
       <c r="B177" t="n">
-        <v>91480</v>
+        <v>91486</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18430,10 +18430,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>126893314</v>
+        <v>126892174</v>
       </c>
       <c r="B178" t="n">
-        <v>78417</v>
+        <v>92808</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18441,21 +18441,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6437</v>
+        <v>2079</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18465,10 +18465,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>865647</v>
+        <v>865517</v>
       </c>
       <c r="R178" t="n">
-        <v>7447060</v>
+        <v>7447401</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18515,12 +18515,12 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr">
@@ -18531,10 +18531,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>126891913</v>
+        <v>126892986</v>
       </c>
       <c r="B179" t="n">
-        <v>79629</v>
+        <v>79603</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -18542,21 +18542,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -18566,10 +18566,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>865557</v>
+        <v>865489</v>
       </c>
       <c r="R179" t="n">
-        <v>7447153</v>
+        <v>7447329</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18616,12 +18616,12 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
@@ -18632,10 +18632,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>126892986</v>
+        <v>126893263</v>
       </c>
       <c r="B180" t="n">
-        <v>79600</v>
+        <v>91325</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18643,21 +18643,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -18667,10 +18667,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>865489</v>
+        <v>865485</v>
       </c>
       <c r="R180" t="n">
-        <v>7447329</v>
+        <v>7447224</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18717,12 +18717,12 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">

--- a/artfynd/A 52625-2022 artfynd.xlsx
+++ b/artfynd/A 52625-2022 artfynd.xlsx
@@ -1180,32 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126893275</v>
+        <v>126893295</v>
       </c>
       <c r="B7" t="n">
-        <v>80153</v>
+        <v>79014</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>865427</v>
+        <v>865429</v>
       </c>
       <c r="R7" t="n">
-        <v>7447587</v>
+        <v>7447550</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,32 +1281,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126892019</v>
+        <v>126893300</v>
       </c>
       <c r="B8" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>865429</v>
+        <v>865378</v>
       </c>
       <c r="R8" t="n">
-        <v>7447523</v>
+        <v>7447665</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1366,12 +1366,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1382,32 +1382,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126893295</v>
+        <v>126893275</v>
       </c>
       <c r="B9" t="n">
-        <v>79014</v>
+        <v>80153</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>865429</v>
+        <v>865427</v>
       </c>
       <c r="R9" t="n">
-        <v>7447550</v>
+        <v>7447587</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1483,32 +1483,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126893300</v>
+        <v>126892019</v>
       </c>
       <c r="B10" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>865378</v>
+        <v>865429</v>
       </c>
       <c r="R10" t="n">
-        <v>7447665</v>
+        <v>7447523</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1568,12 +1568,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1584,32 +1584,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126892999</v>
+        <v>126887991</v>
       </c>
       <c r="B11" t="n">
-        <v>80145</v>
+        <v>79014</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1619,13 +1619,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>865426</v>
+        <v>865422</v>
       </c>
       <c r="R11" t="n">
-        <v>7447493</v>
+        <v>7447458</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1669,48 +1669,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126892173</v>
+        <v>126887992</v>
       </c>
       <c r="B12" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1720,13 +1716,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>865379</v>
+        <v>865406</v>
       </c>
       <c r="R12" t="n">
-        <v>7447558</v>
+        <v>7447461</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1770,72 +1766,57 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126892270</v>
+        <v>126892999</v>
       </c>
       <c r="B13" t="n">
-        <v>91899</v>
+        <v>80145</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>760</v>
+        <v>6461</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>865437</v>
+        <v>865426</v>
       </c>
       <c r="R13" t="n">
-        <v>7447594</v>
+        <v>7447493</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1876,19 +1857,18 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Svea Nikula, Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1899,32 +1879,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126887991</v>
+        <v>126892173</v>
       </c>
       <c r="B14" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1934,13 +1914,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>865422</v>
+        <v>865379</v>
       </c>
       <c r="R14" t="n">
-        <v>7447458</v>
+        <v>7447558</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1984,60 +1964,75 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126887992</v>
+        <v>126892270</v>
       </c>
       <c r="B15" t="n">
-        <v>79014</v>
+        <v>91899</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>865406</v>
+        <v>865437</v>
       </c>
       <c r="R15" t="n">
-        <v>7447461</v>
+        <v>7447594</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2075,50 +2070,55 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Svea Nikula, Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126893016</v>
+        <v>126892264</v>
       </c>
       <c r="B16" t="n">
-        <v>79014</v>
+        <v>58516</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>208249</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>865412</v>
+        <v>865410</v>
       </c>
       <c r="R16" t="n">
-        <v>7447514</v>
+        <v>7447525</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2172,18 +2172,19 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2194,32 +2195,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126892264</v>
+        <v>126893016</v>
       </c>
       <c r="B17" t="n">
-        <v>58516</v>
+        <v>79014</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>208249</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2229,10 +2230,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>865410</v>
+        <v>865412</v>
       </c>
       <c r="R17" t="n">
-        <v>7447525</v>
+        <v>7447514</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2273,19 +2274,18 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2296,7 +2296,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126893301</v>
+        <v>126893017</v>
       </c>
       <c r="B18" t="n">
         <v>79014</v>
@@ -2331,10 +2331,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>865382</v>
+        <v>865409</v>
       </c>
       <c r="R18" t="n">
-        <v>7447699</v>
+        <v>7447573</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2381,12 +2381,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2397,7 +2397,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126893017</v>
+        <v>126893301</v>
       </c>
       <c r="B19" t="n">
         <v>79014</v>
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>865409</v>
+        <v>865382</v>
       </c>
       <c r="R19" t="n">
-        <v>7447573</v>
+        <v>7447699</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2482,12 +2482,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2599,32 +2599,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126891920</v>
+        <v>126893293</v>
       </c>
       <c r="B21" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2634,10 +2634,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>865438</v>
+        <v>865430</v>
       </c>
       <c r="R21" t="n">
-        <v>7447459</v>
+        <v>7447483</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2684,12 +2684,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2700,7 +2700,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126892172</v>
+        <v>126891920</v>
       </c>
       <c r="B22" t="n">
         <v>80146</v>
@@ -2735,10 +2735,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>865436</v>
+        <v>865438</v>
       </c>
       <c r="R22" t="n">
-        <v>7447532</v>
+        <v>7447459</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2785,12 +2785,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2902,32 +2902,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126893293</v>
+        <v>126892172</v>
       </c>
       <c r="B24" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2937,10 +2937,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>865430</v>
+        <v>865436</v>
       </c>
       <c r="R24" t="n">
-        <v>7447483</v>
+        <v>7447532</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2987,12 +2987,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3807,32 +3807,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126892262</v>
+        <v>126893306</v>
       </c>
       <c r="B33" t="n">
-        <v>80153</v>
+        <v>82855</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3842,10 +3842,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>865404</v>
+        <v>865378</v>
       </c>
       <c r="R33" t="n">
-        <v>7447633</v>
+        <v>7447665</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3892,12 +3892,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -3908,32 +3908,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126893306</v>
+        <v>126892262</v>
       </c>
       <c r="B34" t="n">
-        <v>82855</v>
+        <v>80153</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3943,10 +3943,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>865378</v>
+        <v>865404</v>
       </c>
       <c r="R34" t="n">
-        <v>7447665</v>
+        <v>7447633</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3993,12 +3993,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4009,32 +4009,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126892259</v>
+        <v>126887969</v>
       </c>
       <c r="B35" t="n">
-        <v>98463</v>
+        <v>57817</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4044,13 +4044,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>865411</v>
+        <v>865406</v>
       </c>
       <c r="R35" t="n">
-        <v>7447533</v>
+        <v>7447461</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4094,48 +4094,44 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126887969</v>
+        <v>126892259</v>
       </c>
       <c r="B36" t="n">
-        <v>57817</v>
+        <v>98463</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4145,13 +4141,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>865406</v>
+        <v>865411</v>
       </c>
       <c r="R36" t="n">
-        <v>7447461</v>
+        <v>7447533</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4195,22 +4191,26 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
+          <t>Svea Nikula</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126892978</v>
+        <v>126887993</v>
       </c>
       <c r="B37" t="n">
-        <v>75138</v>
+        <v>79014</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4218,21 +4218,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4242,13 +4242,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>865423</v>
+        <v>865389</v>
       </c>
       <c r="R37" t="n">
-        <v>7447442</v>
+        <v>7447521</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4292,19 +4292,15 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4409,10 +4405,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126887993</v>
+        <v>126892978</v>
       </c>
       <c r="B39" t="n">
-        <v>79014</v>
+        <v>75138</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4420,21 +4416,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4444,13 +4440,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>865389</v>
+        <v>865423</v>
       </c>
       <c r="R39" t="n">
-        <v>7447521</v>
+        <v>7447442</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4494,44 +4490,48 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126892989</v>
+        <v>126893266</v>
       </c>
       <c r="B40" t="n">
-        <v>57817</v>
+        <v>80146</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4541,10 +4541,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>865425</v>
+        <v>865423</v>
       </c>
       <c r="R40" t="n">
-        <v>7447474</v>
+        <v>7447628</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4591,12 +4591,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4607,32 +4607,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126893266</v>
+        <v>126892989</v>
       </c>
       <c r="B41" t="n">
-        <v>80146</v>
+        <v>57817</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4642,10 +4642,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>865423</v>
+        <v>865425</v>
       </c>
       <c r="R41" t="n">
-        <v>7447628</v>
+        <v>7447474</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4692,12 +4692,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4708,32 +4708,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126893297</v>
+        <v>126893022</v>
       </c>
       <c r="B42" t="n">
-        <v>79014</v>
+        <v>98359</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4743,10 +4743,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>865416</v>
+        <v>865404</v>
       </c>
       <c r="R42" t="n">
-        <v>7447594</v>
+        <v>7447471</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4793,12 +4793,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -4809,32 +4809,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126893022</v>
+        <v>126893297</v>
       </c>
       <c r="B43" t="n">
-        <v>98359</v>
+        <v>79014</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4844,10 +4844,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>865404</v>
+        <v>865416</v>
       </c>
       <c r="R43" t="n">
-        <v>7447471</v>
+        <v>7447594</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4894,12 +4894,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -4910,32 +4910,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126893273</v>
+        <v>126892268</v>
       </c>
       <c r="B44" t="n">
-        <v>80153</v>
+        <v>79014</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4945,10 +4945,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>865406</v>
+        <v>865411</v>
       </c>
       <c r="R44" t="n">
-        <v>7447648</v>
+        <v>7447532</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4995,12 +4995,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5112,32 +5112,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126892268</v>
+        <v>126893273</v>
       </c>
       <c r="B46" t="n">
-        <v>79014</v>
+        <v>80153</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5147,10 +5147,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>865411</v>
+        <v>865406</v>
       </c>
       <c r="R46" t="n">
-        <v>7447532</v>
+        <v>7447648</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5197,12 +5197,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5213,27 +5213,27 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126893028</v>
+        <v>126887994</v>
       </c>
       <c r="B47" t="n">
-        <v>80152</v>
+        <v>79014</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5248,13 +5248,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>865390</v>
+        <v>865368</v>
       </c>
       <c r="R47" t="n">
-        <v>7447609</v>
+        <v>7447606</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5298,26 +5298,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126892020</v>
+        <v>126893028</v>
       </c>
       <c r="B48" t="n">
-        <v>80146</v>
+        <v>80152</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5325,21 +5321,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5349,10 +5345,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>865440</v>
+        <v>865390</v>
       </c>
       <c r="R48" t="n">
-        <v>7447393</v>
+        <v>7447609</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5399,12 +5395,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5415,32 +5411,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126887994</v>
+        <v>126892020</v>
       </c>
       <c r="B49" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5450,13 +5446,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>865368</v>
+        <v>865440</v>
       </c>
       <c r="R49" t="n">
-        <v>7447606</v>
+        <v>7447393</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5500,15 +5496,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr"/>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5917,10 +5917,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126893008</v>
+        <v>126892985</v>
       </c>
       <c r="B54" t="n">
-        <v>80989</v>
+        <v>79632</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5928,21 +5928,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5952,10 +5952,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>865545</v>
+        <v>865491</v>
       </c>
       <c r="R54" t="n">
-        <v>7447322</v>
+        <v>7447332</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6119,32 +6119,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126892026</v>
+        <v>126891927</v>
       </c>
       <c r="B56" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>865538</v>
+        <v>865543</v>
       </c>
       <c r="R56" t="n">
-        <v>7447072</v>
+        <v>7447122</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6204,12 +6204,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6220,32 +6220,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126892029</v>
+        <v>126893280</v>
       </c>
       <c r="B57" t="n">
-        <v>79014</v>
+        <v>91486</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6255,10 +6255,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>865448</v>
+        <v>865490</v>
       </c>
       <c r="R57" t="n">
-        <v>7447418</v>
+        <v>7447213</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6305,12 +6305,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6321,32 +6321,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126893280</v>
+        <v>126893008</v>
       </c>
       <c r="B58" t="n">
-        <v>91486</v>
+        <v>80989</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1503</v>
+        <v>1049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6356,10 +6356,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>865490</v>
+        <v>865545</v>
       </c>
       <c r="R58" t="n">
-        <v>7447213</v>
+        <v>7447322</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6406,12 +6406,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6422,32 +6422,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126891927</v>
+        <v>126892026</v>
       </c>
       <c r="B59" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6457,10 +6457,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>865543</v>
+        <v>865538</v>
       </c>
       <c r="R59" t="n">
-        <v>7447122</v>
+        <v>7447072</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6507,12 +6507,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6523,10 +6523,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126892985</v>
+        <v>126892029</v>
       </c>
       <c r="B60" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6534,21 +6534,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6558,10 +6558,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>865491</v>
+        <v>865448</v>
       </c>
       <c r="R60" t="n">
-        <v>7447332</v>
+        <v>7447418</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6608,12 +6608,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -6725,32 +6725,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126891915</v>
+        <v>126887985</v>
       </c>
       <c r="B62" t="n">
-        <v>80146</v>
+        <v>98442</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6760,13 +6760,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>865551</v>
+        <v>865583</v>
       </c>
       <c r="R62" t="n">
-        <v>7447126</v>
+        <v>7447137</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6810,19 +6810,15 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6927,32 +6923,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126887985</v>
+        <v>126891915</v>
       </c>
       <c r="B64" t="n">
-        <v>98442</v>
+        <v>80146</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6962,13 +6958,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>865583</v>
+        <v>865551</v>
       </c>
       <c r="R64" t="n">
-        <v>7447137</v>
+        <v>7447126</v>
       </c>
       <c r="S64" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7012,22 +7008,26 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr"/>
+          <t>Amanda Rudelius</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126893010</v>
+        <v>126888002</v>
       </c>
       <c r="B65" t="n">
-        <v>80989</v>
+        <v>78681</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7035,21 +7035,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1049</v>
+        <v>353</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7059,13 +7059,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>865490</v>
+        <v>865512</v>
       </c>
       <c r="R65" t="n">
-        <v>7447332</v>
+        <v>7447340</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7109,48 +7109,44 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126888002</v>
+        <v>126891925</v>
       </c>
       <c r="B66" t="n">
-        <v>78681</v>
+        <v>98442</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7160,13 +7156,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>865512</v>
+        <v>865527</v>
       </c>
       <c r="R66" t="n">
-        <v>7447340</v>
+        <v>7447333</v>
       </c>
       <c r="S66" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7210,22 +7206,26 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr"/>
+          <t>Amanda Rudelius</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126893312</v>
+        <v>126893010</v>
       </c>
       <c r="B67" t="n">
-        <v>77992</v>
+        <v>80989</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7233,21 +7233,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6487</v>
+        <v>1049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7257,10 +7257,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>865598</v>
+        <v>865490</v>
       </c>
       <c r="R67" t="n">
-        <v>7447181</v>
+        <v>7447332</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7307,12 +7307,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7323,32 +7323,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126892998</v>
+        <v>126893000</v>
       </c>
       <c r="B68" t="n">
-        <v>80145</v>
+        <v>92808</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6461</v>
+        <v>2079</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7358,10 +7358,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>865477</v>
+        <v>865559</v>
       </c>
       <c r="R68" t="n">
-        <v>7447327</v>
+        <v>7447299</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7424,10 +7424,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126893000</v>
+        <v>126893312</v>
       </c>
       <c r="B69" t="n">
-        <v>92808</v>
+        <v>77992</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7435,21 +7435,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2079</v>
+        <v>6487</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7459,10 +7459,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>865559</v>
+        <v>865598</v>
       </c>
       <c r="R69" t="n">
-        <v>7447299</v>
+        <v>7447181</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7509,12 +7509,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -7525,61 +7525,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126892183</v>
+        <v>126892998</v>
       </c>
       <c r="B70" t="n">
-        <v>56840</v>
+        <v>80145</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>102612</v>
+        <v>6461</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>pulli</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>pulli/nyligen flygga ungar</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>865484</v>
+        <v>865477</v>
       </c>
       <c r="R70" t="n">
-        <v>7447494</v>
+        <v>7447327</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7614,11 +7598,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Stötte up 5st kycklingar, höll till under en och samma fallen gran</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -7631,12 +7610,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7647,45 +7626,61 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126891925</v>
+        <v>126892183</v>
       </c>
       <c r="B71" t="n">
-        <v>98442</v>
+        <v>56840</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>pulli</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>pulli/nyligen flygga ungar</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>865527</v>
+        <v>865484</v>
       </c>
       <c r="R71" t="n">
-        <v>7447333</v>
+        <v>7447494</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7720,6 +7715,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Stötte up 5st kycklingar, höll till under en och samma fallen gran</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -7732,12 +7732,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -8354,32 +8354,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126891929</v>
+        <v>126887974</v>
       </c>
       <c r="B78" t="n">
-        <v>79014</v>
+        <v>97326</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8389,13 +8389,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>865535</v>
+        <v>865641</v>
       </c>
       <c r="R78" t="n">
-        <v>7447142</v>
+        <v>7447070</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8439,26 +8439,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126893270</v>
+        <v>126888001</v>
       </c>
       <c r="B79" t="n">
-        <v>92808</v>
+        <v>78681</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8466,21 +8462,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8490,13 +8486,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>865491</v>
+        <v>865527</v>
       </c>
       <c r="R79" t="n">
-        <v>7447267</v>
+        <v>7447205</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8540,48 +8536,44 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
-        </is>
-      </c>
-      <c r="AY79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126887974</v>
+        <v>126893270</v>
       </c>
       <c r="B80" t="n">
-        <v>97326</v>
+        <v>92808</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221941</v>
+        <v>2079</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8591,13 +8583,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>865641</v>
+        <v>865491</v>
       </c>
       <c r="R80" t="n">
-        <v>7447070</v>
+        <v>7447267</v>
       </c>
       <c r="S80" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8641,22 +8633,26 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr"/>
+          <t>Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126888001</v>
+        <v>126891929</v>
       </c>
       <c r="B81" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8664,21 +8660,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8688,13 +8684,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>865527</v>
+        <v>865535</v>
       </c>
       <c r="R81" t="n">
-        <v>7447205</v>
+        <v>7447142</v>
       </c>
       <c r="S81" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8738,15 +8734,19 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY81" t="inlineStr"/>
+          <t>Amanda Rudelius</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8861,32 +8861,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126893277</v>
+        <v>126888457</v>
       </c>
       <c r="B83" t="n">
-        <v>80989</v>
+        <v>91486</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1049</v>
+        <v>1503</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8896,10 +8896,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>865647</v>
+        <v>865528</v>
       </c>
       <c r="R83" t="n">
-        <v>7447060</v>
+        <v>7447201</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8946,12 +8946,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -8962,53 +8962,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126888454</v>
+        <v>126892185</v>
       </c>
       <c r="B84" t="n">
-        <v>57817</v>
+        <v>91486</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>103021</v>
+        <v>1503</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>865481</v>
+        <v>865490</v>
       </c>
       <c r="R84" t="n">
-        <v>7447376</v>
+        <v>7447287</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9055,12 +9047,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9071,32 +9063,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126893278</v>
+        <v>126892175</v>
       </c>
       <c r="B85" t="n">
-        <v>98442</v>
+        <v>92808</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>2079</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9106,10 +9098,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>865551</v>
+        <v>865509</v>
       </c>
       <c r="R85" t="n">
-        <v>7447276</v>
+        <v>7447217</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9156,12 +9148,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -9172,32 +9164,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126892181</v>
+        <v>126887978</v>
       </c>
       <c r="B86" t="n">
-        <v>98442</v>
+        <v>92808</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>2079</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9207,13 +9199,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>865459</v>
+        <v>865521</v>
       </c>
       <c r="R86" t="n">
-        <v>7447305</v>
+        <v>7447240</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9257,48 +9249,44 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126893003</v>
+        <v>126893277</v>
       </c>
       <c r="B87" t="n">
-        <v>80153</v>
+        <v>80989</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6464</v>
+        <v>1049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9308,10 +9296,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>865532</v>
+        <v>865647</v>
       </c>
       <c r="R87" t="n">
-        <v>7447307</v>
+        <v>7447060</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9358,12 +9346,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -9374,10 +9362,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126892271</v>
+        <v>126892192</v>
       </c>
       <c r="B88" t="n">
-        <v>80152</v>
+        <v>92615</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9385,21 +9373,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6463</v>
+        <v>4364</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9409,10 +9397,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>865610</v>
+        <v>865502</v>
       </c>
       <c r="R88" t="n">
-        <v>7447145</v>
+        <v>7447389</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9459,12 +9447,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -9475,32 +9463,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126888457</v>
+        <v>126893003</v>
       </c>
       <c r="B89" t="n">
-        <v>91486</v>
+        <v>80153</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1503</v>
+        <v>6464</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9510,10 +9498,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>865528</v>
+        <v>865532</v>
       </c>
       <c r="R89" t="n">
-        <v>7447201</v>
+        <v>7447307</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9560,12 +9548,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -9576,32 +9564,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126892185</v>
+        <v>126892271</v>
       </c>
       <c r="B90" t="n">
-        <v>91486</v>
+        <v>80152</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1503</v>
+        <v>6463</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9611,10 +9599,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>865490</v>
+        <v>865610</v>
       </c>
       <c r="R90" t="n">
-        <v>7447287</v>
+        <v>7447145</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9661,12 +9649,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -9677,10 +9665,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126892175</v>
+        <v>126888454</v>
       </c>
       <c r="B91" t="n">
-        <v>92808</v>
+        <v>57817</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9688,34 +9676,42 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2079</v>
+        <v>103021</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>865509</v>
+        <v>865481</v>
       </c>
       <c r="R91" t="n">
-        <v>7447217</v>
+        <v>7447376</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9762,12 +9758,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -9778,32 +9774,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126887978</v>
+        <v>126893278</v>
       </c>
       <c r="B92" t="n">
-        <v>92808</v>
+        <v>98442</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2079</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9813,13 +9809,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>865521</v>
+        <v>865551</v>
       </c>
       <c r="R92" t="n">
-        <v>7447240</v>
+        <v>7447276</v>
       </c>
       <c r="S92" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9863,44 +9859,48 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY92" t="inlineStr"/>
+          <t>Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126892192</v>
+        <v>126892181</v>
       </c>
       <c r="B93" t="n">
-        <v>92615</v>
+        <v>98442</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9910,10 +9910,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>865502</v>
+        <v>865459</v>
       </c>
       <c r="R93" t="n">
-        <v>7447389</v>
+        <v>7447305</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9976,32 +9976,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126892267</v>
+        <v>126893281</v>
       </c>
       <c r="B94" t="n">
-        <v>79014</v>
+        <v>91486</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10011,10 +10011,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>865516</v>
+        <v>865513</v>
       </c>
       <c r="R94" t="n">
-        <v>7447351</v>
+        <v>7447339</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10061,12 +10061,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10077,32 +10077,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126893281</v>
+        <v>126892178</v>
       </c>
       <c r="B95" t="n">
-        <v>91486</v>
+        <v>92808</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1503</v>
+        <v>2079</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10112,10 +10112,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>865513</v>
+        <v>865509</v>
       </c>
       <c r="R95" t="n">
-        <v>7447339</v>
+        <v>7447375</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10162,12 +10162,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10178,32 +10178,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126892178</v>
+        <v>126893025</v>
       </c>
       <c r="B96" t="n">
-        <v>92808</v>
+        <v>92615</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10213,10 +10213,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>865509</v>
+        <v>865518</v>
       </c>
       <c r="R96" t="n">
-        <v>7447375</v>
+        <v>7447235</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10263,12 +10263,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10279,32 +10279,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126893025</v>
+        <v>126887968</v>
       </c>
       <c r="B97" t="n">
-        <v>92615</v>
+        <v>57817</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10314,13 +10314,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>865518</v>
+        <v>865523</v>
       </c>
       <c r="R97" t="n">
-        <v>7447235</v>
+        <v>7447217</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10364,48 +10364,44 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
-        </is>
-      </c>
-      <c r="AY97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126892981</v>
+        <v>126888000</v>
       </c>
       <c r="B98" t="n">
-        <v>91290</v>
+        <v>78681</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10415,13 +10411,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>865553</v>
+        <v>865597</v>
       </c>
       <c r="R98" t="n">
-        <v>7447278</v>
+        <v>7447186</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10465,48 +10461,44 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
-        </is>
-      </c>
-      <c r="AY98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126887997</v>
+        <v>126893023</v>
       </c>
       <c r="B99" t="n">
-        <v>98359</v>
+        <v>91726</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>219790</v>
+        <v>715</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Finporing</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Gloeoporus pannocinctus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Romell) J.Erikss.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10516,13 +10508,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>865448</v>
+        <v>865473</v>
       </c>
       <c r="R99" t="n">
-        <v>7447350</v>
+        <v>7447321</v>
       </c>
       <c r="S99" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10566,44 +10558,48 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY99" t="inlineStr"/>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126888000</v>
+        <v>126892981</v>
       </c>
       <c r="B100" t="n">
-        <v>78681</v>
+        <v>91290</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10613,13 +10609,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>865597</v>
+        <v>865553</v>
       </c>
       <c r="R100" t="n">
-        <v>7447186</v>
+        <v>7447278</v>
       </c>
       <c r="S100" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10663,44 +10659,48 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY100" t="inlineStr"/>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126893023</v>
+        <v>126892267</v>
       </c>
       <c r="B101" t="n">
-        <v>91726</v>
+        <v>79014</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>715</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Finporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Gloeoporus pannocinctus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Romell) J.Erikss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10710,10 +10710,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>865473</v>
+        <v>865516</v>
       </c>
       <c r="R101" t="n">
-        <v>7447321</v>
+        <v>7447351</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10760,12 +10760,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -10776,32 +10776,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126887968</v>
+        <v>126887997</v>
       </c>
       <c r="B102" t="n">
-        <v>57817</v>
+        <v>98359</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>103021</v>
+        <v>219790</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>865523</v>
+        <v>865448</v>
       </c>
       <c r="R102" t="n">
-        <v>7447217</v>
+        <v>7447350</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -11277,10 +11277,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126892028</v>
+        <v>126887980</v>
       </c>
       <c r="B107" t="n">
-        <v>79014</v>
+        <v>92808</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11288,21 +11288,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11312,13 +11312,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>865533</v>
+        <v>865511</v>
       </c>
       <c r="R107" t="n">
-        <v>7447130</v>
+        <v>7447249</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11362,26 +11362,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126887980</v>
+        <v>126892028</v>
       </c>
       <c r="B108" t="n">
-        <v>92808</v>
+        <v>79014</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11389,21 +11385,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11413,13 +11409,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>865511</v>
+        <v>865533</v>
       </c>
       <c r="R108" t="n">
-        <v>7447249</v>
+        <v>7447130</v>
       </c>
       <c r="S108" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11463,22 +11459,26 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY108" t="inlineStr"/>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126887990</v>
+        <v>126892263</v>
       </c>
       <c r="B109" t="n">
-        <v>79014</v>
+        <v>56840</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11486,37 +11486,45 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>865447</v>
+        <v>865544</v>
       </c>
       <c r="R109" t="n">
-        <v>7447371</v>
+        <v>7447281</v>
       </c>
       <c r="S109" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -11560,22 +11568,26 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY109" t="inlineStr"/>
+          <t>Svea Nikula</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126892263</v>
+        <v>126892018</v>
       </c>
       <c r="B110" t="n">
-        <v>56840</v>
+        <v>57817</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11583,29 +11595,33 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N110" t="inlineStr"/>
@@ -11615,10 +11631,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>865544</v>
+        <v>865561</v>
       </c>
       <c r="R110" t="n">
-        <v>7447281</v>
+        <v>7447155</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11665,12 +11681,12 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
@@ -11681,32 +11697,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126887965</v>
+        <v>126892191</v>
       </c>
       <c r="B111" t="n">
-        <v>57479</v>
+        <v>91586</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>102976</v>
+        <v>65</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11716,13 +11732,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>865583</v>
+        <v>865540</v>
       </c>
       <c r="R111" t="n">
-        <v>7447214</v>
+        <v>7447366</v>
       </c>
       <c r="S111" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -11766,44 +11782,48 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY111" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126891928</v>
+        <v>126893009</v>
       </c>
       <c r="B112" t="n">
-        <v>98442</v>
+        <v>80989</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>220787</v>
+        <v>1049</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11813,10 +11833,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>865549</v>
+        <v>865553</v>
       </c>
       <c r="R112" t="n">
-        <v>7447136</v>
+        <v>7447326</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11863,12 +11883,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
@@ -11879,32 +11899,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126892024</v>
+        <v>126887977</v>
       </c>
       <c r="B113" t="n">
-        <v>98442</v>
+        <v>92808</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>220787</v>
+        <v>2079</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11914,13 +11934,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>865546</v>
+        <v>865643</v>
       </c>
       <c r="R113" t="n">
-        <v>7447138</v>
+        <v>7447067</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -11964,48 +11984,44 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126887975</v>
+        <v>126887987</v>
       </c>
       <c r="B114" t="n">
-        <v>97326</v>
+        <v>91486</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>221941</v>
+        <v>1503</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12015,10 +12031,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>865479</v>
+        <v>865510</v>
       </c>
       <c r="R114" t="n">
-        <v>7447358</v>
+        <v>7447247</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -12077,32 +12093,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126887976</v>
+        <v>126887990</v>
       </c>
       <c r="B115" t="n">
-        <v>97326</v>
+        <v>79014</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12112,10 +12128,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>865452</v>
+        <v>865447</v>
       </c>
       <c r="R115" t="n">
-        <v>7447334</v>
+        <v>7447371</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -12174,32 +12190,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126892191</v>
+        <v>126887965</v>
       </c>
       <c r="B116" t="n">
-        <v>91586</v>
+        <v>57479</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>65</v>
+        <v>102976</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12209,13 +12225,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>865540</v>
+        <v>865583</v>
       </c>
       <c r="R116" t="n">
-        <v>7447366</v>
+        <v>7447214</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12259,48 +12275,44 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126893009</v>
+        <v>126891928</v>
       </c>
       <c r="B117" t="n">
-        <v>80989</v>
+        <v>98442</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1049</v>
+        <v>220787</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12310,10 +12322,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>865553</v>
+        <v>865549</v>
       </c>
       <c r="R117" t="n">
-        <v>7447326</v>
+        <v>7447136</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12360,12 +12372,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
@@ -12376,32 +12388,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126887977</v>
+        <v>126887975</v>
       </c>
       <c r="B118" t="n">
-        <v>92808</v>
+        <v>97326</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>2079</v>
+        <v>221941</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12411,10 +12423,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>865643</v>
+        <v>865479</v>
       </c>
       <c r="R118" t="n">
-        <v>7447067</v>
+        <v>7447358</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -12473,32 +12485,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126887987</v>
+        <v>126887976</v>
       </c>
       <c r="B119" t="n">
-        <v>91486</v>
+        <v>97326</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1503</v>
+        <v>221941</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12508,10 +12520,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>865510</v>
+        <v>865452</v>
       </c>
       <c r="R119" t="n">
-        <v>7447247</v>
+        <v>7447334</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -12570,57 +12582,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126892018</v>
+        <v>126892024</v>
       </c>
       <c r="B120" t="n">
-        <v>57817</v>
+        <v>98442</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N120" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>865561</v>
+        <v>865546</v>
       </c>
       <c r="R120" t="n">
-        <v>7447155</v>
+        <v>7447138</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12672,7 +12672,7 @@
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
@@ -12683,32 +12683,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126893308</v>
+        <v>126893262</v>
       </c>
       <c r="B121" t="n">
-        <v>91586</v>
+        <v>91290</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>65</v>
+        <v>5447</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12718,10 +12718,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>865659</v>
+        <v>865522</v>
       </c>
       <c r="R121" t="n">
-        <v>7447048</v>
+        <v>7447308</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12784,10 +12784,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126893030</v>
+        <v>126893260</v>
       </c>
       <c r="B122" t="n">
-        <v>77992</v>
+        <v>91247</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12795,21 +12795,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6487</v>
+        <v>3242</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12819,10 +12819,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>865545</v>
+        <v>865498</v>
       </c>
       <c r="R122" t="n">
-        <v>7447323</v>
+        <v>7447359</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12869,12 +12869,12 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
@@ -12885,32 +12885,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126887981</v>
+        <v>126893030</v>
       </c>
       <c r="B123" t="n">
-        <v>80153</v>
+        <v>77992</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6464</v>
+        <v>6487</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12920,13 +12920,13 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>865448</v>
+        <v>865545</v>
       </c>
       <c r="R123" t="n">
-        <v>7447345</v>
+        <v>7447323</v>
       </c>
       <c r="S123" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -12970,22 +12970,26 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY123" t="inlineStr"/>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126893262</v>
+        <v>126887981</v>
       </c>
       <c r="B124" t="n">
-        <v>91290</v>
+        <v>80153</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12993,21 +12997,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5447</v>
+        <v>6464</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13017,13 +13021,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>865522</v>
+        <v>865448</v>
       </c>
       <c r="R124" t="n">
-        <v>7447308</v>
+        <v>7447345</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13067,48 +13071,44 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
-        </is>
-      </c>
-      <c r="AY124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126893267</v>
+        <v>126893308</v>
       </c>
       <c r="B125" t="n">
-        <v>92808</v>
+        <v>91586</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>2079</v>
+        <v>65</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13118,10 +13118,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>865648</v>
+        <v>865659</v>
       </c>
       <c r="R125" t="n">
-        <v>7447056</v>
+        <v>7447048</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13184,10 +13184,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126893260</v>
+        <v>126893267</v>
       </c>
       <c r="B126" t="n">
-        <v>91247</v>
+        <v>92808</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13195,21 +13195,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>3242</v>
+        <v>2079</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13219,10 +13219,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>865498</v>
+        <v>865648</v>
       </c>
       <c r="R126" t="n">
-        <v>7447359</v>
+        <v>7447056</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13391,10 +13391,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126893313</v>
+        <v>126893292</v>
       </c>
       <c r="B128" t="n">
-        <v>78420</v>
+        <v>79014</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13402,21 +13402,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13426,10 +13426,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>865598</v>
+        <v>865501</v>
       </c>
       <c r="R128" t="n">
-        <v>7447181</v>
+        <v>7447191</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13492,32 +13492,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126887970</v>
+        <v>126893313</v>
       </c>
       <c r="B129" t="n">
-        <v>80146</v>
+        <v>78420</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6462</v>
+        <v>6437</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13527,13 +13527,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>865529</v>
+        <v>865598</v>
       </c>
       <c r="R129" t="n">
-        <v>7447327</v>
+        <v>7447181</v>
       </c>
       <c r="S129" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -13577,44 +13577,48 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY129" t="inlineStr"/>
+          <t>Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126893274</v>
+        <v>126887988</v>
       </c>
       <c r="B130" t="n">
-        <v>80153</v>
+        <v>91486</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6464</v>
+        <v>1503</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13624,13 +13628,13 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>865476</v>
+        <v>865515</v>
       </c>
       <c r="R130" t="n">
-        <v>7447236</v>
+        <v>7447377</v>
       </c>
       <c r="S130" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -13674,26 +13678,22 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
-        </is>
-      </c>
-      <c r="AY130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126893292</v>
+        <v>126893269</v>
       </c>
       <c r="B131" t="n">
-        <v>79014</v>
+        <v>92808</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13701,21 +13701,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13725,10 +13725,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>865501</v>
+        <v>865647</v>
       </c>
       <c r="R131" t="n">
-        <v>7447191</v>
+        <v>7447057</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13791,32 +13791,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126887988</v>
+        <v>126887970</v>
       </c>
       <c r="B132" t="n">
-        <v>91486</v>
+        <v>80146</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1503</v>
+        <v>6462</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13826,10 +13826,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>865515</v>
+        <v>865529</v>
       </c>
       <c r="R132" t="n">
-        <v>7447377</v>
+        <v>7447327</v>
       </c>
       <c r="S132" t="n">
         <v>25</v>
@@ -13888,32 +13888,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126893269</v>
+        <v>126893274</v>
       </c>
       <c r="B133" t="n">
-        <v>92808</v>
+        <v>80153</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>2079</v>
+        <v>6464</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13923,10 +13923,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>865647</v>
+        <v>865476</v>
       </c>
       <c r="R133" t="n">
-        <v>7447057</v>
+        <v>7447236</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -13989,10 +13989,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126892984</v>
+        <v>126892176</v>
       </c>
       <c r="B134" t="n">
-        <v>79632</v>
+        <v>92808</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14000,21 +14000,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14024,10 +14024,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>865523</v>
+        <v>865490</v>
       </c>
       <c r="R134" t="n">
-        <v>7447267</v>
+        <v>7447287</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14074,12 +14074,12 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
@@ -14090,32 +14090,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126887962</v>
+        <v>126892256</v>
       </c>
       <c r="B135" t="n">
-        <v>79632</v>
+        <v>91290</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14125,13 +14125,13 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>865519</v>
+        <v>865491</v>
       </c>
       <c r="R135" t="n">
-        <v>7447214</v>
+        <v>7447326</v>
       </c>
       <c r="S135" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -14175,22 +14175,26 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY135" t="inlineStr"/>
+          <t>Svea Nikula</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126893034</v>
+        <v>126892189</v>
       </c>
       <c r="B136" t="n">
-        <v>78420</v>
+        <v>79014</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14198,21 +14202,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14222,10 +14226,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>865544</v>
+        <v>865551</v>
       </c>
       <c r="R136" t="n">
-        <v>7447321</v>
+        <v>7447310</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14272,12 +14276,12 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
@@ -14288,7 +14292,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126892189</v>
+        <v>126893290</v>
       </c>
       <c r="B137" t="n">
         <v>79014</v>
@@ -14323,10 +14327,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>865551</v>
+        <v>865505</v>
       </c>
       <c r="R137" t="n">
-        <v>7447310</v>
+        <v>7447150</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14373,12 +14377,12 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
@@ -14389,10 +14393,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126893290</v>
+        <v>126893034</v>
       </c>
       <c r="B138" t="n">
-        <v>79014</v>
+        <v>78420</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14400,21 +14404,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14424,10 +14428,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>865505</v>
+        <v>865544</v>
       </c>
       <c r="R138" t="n">
-        <v>7447150</v>
+        <v>7447321</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14474,12 +14478,12 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
@@ -14490,10 +14494,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126892176</v>
+        <v>126892984</v>
       </c>
       <c r="B139" t="n">
-        <v>92808</v>
+        <v>79632</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14501,21 +14505,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14525,10 +14529,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>865490</v>
+        <v>865523</v>
       </c>
       <c r="R139" t="n">
-        <v>7447287</v>
+        <v>7447267</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14575,12 +14579,12 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
@@ -14591,32 +14595,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126892256</v>
+        <v>126887962</v>
       </c>
       <c r="B140" t="n">
-        <v>91290</v>
+        <v>79632</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14626,13 +14630,13 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>865491</v>
+        <v>865519</v>
       </c>
       <c r="R140" t="n">
-        <v>7447326</v>
+        <v>7447214</v>
       </c>
       <c r="S140" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -14676,26 +14680,22 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
-        </is>
-      </c>
-      <c r="AY140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126888456</v>
+        <v>126892253</v>
       </c>
       <c r="B141" t="n">
-        <v>92808</v>
+        <v>91247</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14703,21 +14703,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2079</v>
+        <v>3242</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14727,10 +14727,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>865506</v>
+        <v>865491</v>
       </c>
       <c r="R141" t="n">
-        <v>7447238</v>
+        <v>7447326</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14777,12 +14777,12 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
@@ -14793,7 +14793,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126887971</v>
+        <v>126892991</v>
       </c>
       <c r="B142" t="n">
         <v>80146</v>
@@ -14828,13 +14828,13 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>865452</v>
+        <v>865531</v>
       </c>
       <c r="R142" t="n">
-        <v>7447318</v>
+        <v>7447308</v>
       </c>
       <c r="S142" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -14878,44 +14878,48 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY142" t="inlineStr"/>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126892991</v>
+        <v>126888456</v>
       </c>
       <c r="B143" t="n">
-        <v>80146</v>
+        <v>92808</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6462</v>
+        <v>2079</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14925,10 +14929,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>865531</v>
+        <v>865506</v>
       </c>
       <c r="R143" t="n">
-        <v>7447308</v>
+        <v>7447238</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14975,12 +14979,12 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
@@ -14991,7 +14995,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>126891917</v>
+        <v>126887971</v>
       </c>
       <c r="B144" t="n">
         <v>80146</v>
@@ -15026,13 +15030,13 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>865561</v>
+        <v>865452</v>
       </c>
       <c r="R144" t="n">
-        <v>7447152</v>
+        <v>7447318</v>
       </c>
       <c r="S144" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -15076,48 +15080,44 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
-        </is>
-      </c>
-      <c r="AY144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126892253</v>
+        <v>126891917</v>
       </c>
       <c r="B145" t="n">
-        <v>91247</v>
+        <v>80146</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>3242</v>
+        <v>6462</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15127,10 +15127,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>865491</v>
+        <v>865561</v>
       </c>
       <c r="R145" t="n">
-        <v>7447326</v>
+        <v>7447152</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15177,12 +15177,12 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
@@ -15193,10 +15193,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126892983</v>
+        <v>126892266</v>
       </c>
       <c r="B146" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15204,21 +15204,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15228,10 +15228,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>865546</v>
+        <v>865495</v>
       </c>
       <c r="R146" t="n">
-        <v>7447275</v>
+        <v>7447285</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15278,12 +15278,12 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
@@ -15294,7 +15294,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>126892266</v>
+        <v>126888459</v>
       </c>
       <c r="B147" t="n">
         <v>79014</v>
@@ -15329,10 +15329,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>865495</v>
+        <v>865501</v>
       </c>
       <c r="R147" t="n">
-        <v>7447285</v>
+        <v>7447386</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15379,12 +15379,12 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
@@ -15395,10 +15395,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126888459</v>
+        <v>126892983</v>
       </c>
       <c r="B148" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15406,21 +15406,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15430,10 +15430,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>865501</v>
+        <v>865546</v>
       </c>
       <c r="R148" t="n">
-        <v>7447386</v>
+        <v>7447275</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15480,12 +15480,12 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
@@ -15597,45 +15597,57 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126891909</v>
+        <v>126892023</v>
       </c>
       <c r="B150" t="n">
-        <v>75138</v>
+        <v>98442</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>865542</v>
+        <v>865539</v>
       </c>
       <c r="R150" t="n">
-        <v>7447122</v>
+        <v>7447133</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15676,18 +15688,19 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
+      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
@@ -15900,57 +15913,45 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>126892023</v>
+        <v>126891909</v>
       </c>
       <c r="B153" t="n">
-        <v>98442</v>
+        <v>75138</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K153" t="inlineStr"/>
-      <c r="L153" t="inlineStr"/>
-      <c r="N153" t="inlineStr"/>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>865539</v>
+        <v>865542</v>
       </c>
       <c r="R153" t="n">
-        <v>7447133</v>
+        <v>7447122</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -15991,19 +15992,18 @@
       <c r="AE153" t="b">
         <v>0</v>
       </c>
-      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
       </c>
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
@@ -16115,10 +16115,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126892272</v>
+        <v>126887979</v>
       </c>
       <c r="B155" t="n">
-        <v>77992</v>
+        <v>92808</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16126,21 +16126,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6487</v>
+        <v>2079</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16150,13 +16150,13 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>865528</v>
+        <v>865510</v>
       </c>
       <c r="R155" t="n">
-        <v>7447192</v>
+        <v>7447251</v>
       </c>
       <c r="S155" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -16200,19 +16200,15 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
-        </is>
-      </c>
-      <c r="AY155" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16317,10 +16313,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126887979</v>
+        <v>126892974</v>
       </c>
       <c r="B157" t="n">
-        <v>92808</v>
+        <v>91247</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16328,21 +16324,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>2079</v>
+        <v>3242</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16352,13 +16348,13 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>865510</v>
+        <v>865494</v>
       </c>
       <c r="R157" t="n">
-        <v>7447251</v>
+        <v>7447322</v>
       </c>
       <c r="S157" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -16402,22 +16398,26 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY157" t="inlineStr"/>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>126892974</v>
+        <v>126892272</v>
       </c>
       <c r="B158" t="n">
-        <v>91247</v>
+        <v>77992</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16425,21 +16425,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>3242</v>
+        <v>6487</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16449,10 +16449,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>865494</v>
+        <v>865528</v>
       </c>
       <c r="R158" t="n">
-        <v>7447322</v>
+        <v>7447192</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16499,12 +16499,12 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
@@ -16620,10 +16620,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>126887961</v>
+        <v>126893291</v>
       </c>
       <c r="B160" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16631,21 +16631,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16655,13 +16655,13 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>865602</v>
+        <v>865507</v>
       </c>
       <c r="R160" t="n">
-        <v>7447176</v>
+        <v>7447151</v>
       </c>
       <c r="S160" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -16705,44 +16705,48 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY160" t="inlineStr"/>
+          <t>Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>126893265</v>
+        <v>126887961</v>
       </c>
       <c r="B161" t="n">
-        <v>80146</v>
+        <v>79632</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16752,13 +16756,13 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>865530</v>
+        <v>865602</v>
       </c>
       <c r="R161" t="n">
-        <v>7447304</v>
+        <v>7447176</v>
       </c>
       <c r="S161" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -16802,19 +16806,15 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
-        </is>
-      </c>
-      <c r="AY161" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -16919,10 +16919,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>126893291</v>
+        <v>126893272</v>
       </c>
       <c r="B163" t="n">
-        <v>79014</v>
+        <v>92808</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16930,21 +16930,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -16954,10 +16954,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>865507</v>
+        <v>865520</v>
       </c>
       <c r="R163" t="n">
-        <v>7447151</v>
+        <v>7447337</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17020,32 +17020,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>126892016</v>
+        <v>126888458</v>
       </c>
       <c r="B164" t="n">
-        <v>91290</v>
+        <v>91486</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>5447</v>
+        <v>1503</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17055,10 +17055,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>865558</v>
+        <v>865502</v>
       </c>
       <c r="R164" t="n">
-        <v>7447154</v>
+        <v>7447310</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17105,12 +17105,12 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
@@ -17121,32 +17121,32 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>126893272</v>
+        <v>126892016</v>
       </c>
       <c r="B165" t="n">
-        <v>92808</v>
+        <v>91290</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>2079</v>
+        <v>5447</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17156,10 +17156,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>865520</v>
+        <v>865558</v>
       </c>
       <c r="R165" t="n">
-        <v>7447337</v>
+        <v>7447154</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17206,12 +17206,12 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
@@ -17222,32 +17222,32 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>126888458</v>
+        <v>126893265</v>
       </c>
       <c r="B166" t="n">
-        <v>91486</v>
+        <v>80146</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>1503</v>
+        <v>6462</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17257,10 +17257,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>865502</v>
+        <v>865530</v>
       </c>
       <c r="R166" t="n">
-        <v>7447310</v>
+        <v>7447304</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17307,12 +17307,12 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
@@ -17323,32 +17323,32 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>126893021</v>
+        <v>126893031</v>
       </c>
       <c r="B167" t="n">
-        <v>91586</v>
+        <v>77992</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>65</v>
+        <v>6487</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17358,10 +17358,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>865547</v>
+        <v>865490</v>
       </c>
       <c r="R167" t="n">
-        <v>7447316</v>
+        <v>7447338</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17424,32 +17424,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>126893309</v>
+        <v>126892988</v>
       </c>
       <c r="B168" t="n">
-        <v>91586</v>
+        <v>57479</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>65</v>
+        <v>102976</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17459,10 +17459,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>865661</v>
+        <v>865530</v>
       </c>
       <c r="R168" t="n">
-        <v>7447053</v>
+        <v>7447298</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17509,12 +17509,12 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
@@ -17525,32 +17525,32 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>126893031</v>
+        <v>126893021</v>
       </c>
       <c r="B169" t="n">
-        <v>77992</v>
+        <v>91586</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6487</v>
+        <v>65</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17560,10 +17560,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>865490</v>
+        <v>865547</v>
       </c>
       <c r="R169" t="n">
-        <v>7447338</v>
+        <v>7447316</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17626,32 +17626,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>126893284</v>
+        <v>126893309</v>
       </c>
       <c r="B170" t="n">
-        <v>79014</v>
+        <v>91586</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17661,7 +17661,7 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>865543</v>
+        <v>865661</v>
       </c>
       <c r="R170" t="n">
         <v>7447053</v>
@@ -17727,32 +17727,32 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>126892988</v>
+        <v>126893284</v>
       </c>
       <c r="B171" t="n">
-        <v>57479</v>
+        <v>79014</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>102976</v>
+        <v>6425</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -17762,10 +17762,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>865530</v>
+        <v>865543</v>
       </c>
       <c r="R171" t="n">
-        <v>7447298</v>
+        <v>7447053</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17812,12 +17812,12 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
@@ -17828,32 +17828,32 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>126892997</v>
+        <v>126892188</v>
       </c>
       <c r="B172" t="n">
-        <v>79038</v>
+        <v>91486</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6434</v>
+        <v>1503</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -17863,10 +17863,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>865545</v>
+        <v>865520</v>
       </c>
       <c r="R172" t="n">
-        <v>7447323</v>
+        <v>7447364</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -17913,12 +17913,12 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
@@ -17929,10 +17929,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>126893314</v>
+        <v>126893263</v>
       </c>
       <c r="B173" t="n">
-        <v>78420</v>
+        <v>91325</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17940,21 +17940,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6437</v>
+        <v>1202</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -17964,10 +17964,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>865647</v>
+        <v>865485</v>
       </c>
       <c r="R173" t="n">
-        <v>7447060</v>
+        <v>7447224</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18030,32 +18030,32 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>126891913</v>
+        <v>126887986</v>
       </c>
       <c r="B174" t="n">
-        <v>79632</v>
+        <v>91486</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18065,13 +18065,13 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>865557</v>
+        <v>865539</v>
       </c>
       <c r="R174" t="n">
-        <v>7447153</v>
+        <v>7447206</v>
       </c>
       <c r="S174" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -18115,26 +18115,22 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
-        </is>
-      </c>
-      <c r="AY174" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>126893294</v>
+        <v>126892174</v>
       </c>
       <c r="B175" t="n">
-        <v>79014</v>
+        <v>92808</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18142,21 +18138,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18166,10 +18162,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>865457</v>
+        <v>865517</v>
       </c>
       <c r="R175" t="n">
-        <v>7447523</v>
+        <v>7447401</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18216,12 +18212,12 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
@@ -18232,32 +18228,32 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>126892188</v>
+        <v>126892997</v>
       </c>
       <c r="B176" t="n">
-        <v>91486</v>
+        <v>79038</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>1503</v>
+        <v>6434</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18267,10 +18263,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>865520</v>
+        <v>865545</v>
       </c>
       <c r="R176" t="n">
-        <v>7447364</v>
+        <v>7447323</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18317,12 +18313,12 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr">
@@ -18333,32 +18329,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>126887986</v>
+        <v>126893294</v>
       </c>
       <c r="B177" t="n">
-        <v>91486</v>
+        <v>79014</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18368,13 +18364,13 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>865539</v>
+        <v>865457</v>
       </c>
       <c r="R177" t="n">
-        <v>7447206</v>
+        <v>7447523</v>
       </c>
       <c r="S177" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -18418,22 +18414,26 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY177" t="inlineStr"/>
+          <t>Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>126892174</v>
+        <v>126893314</v>
       </c>
       <c r="B178" t="n">
-        <v>92808</v>
+        <v>78420</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18441,21 +18441,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>2079</v>
+        <v>6437</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18465,10 +18465,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>865517</v>
+        <v>865647</v>
       </c>
       <c r="R178" t="n">
-        <v>7447401</v>
+        <v>7447060</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18515,12 +18515,12 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr">
@@ -18531,10 +18531,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>126892986</v>
+        <v>126891913</v>
       </c>
       <c r="B179" t="n">
-        <v>79603</v>
+        <v>79632</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -18542,21 +18542,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -18566,10 +18566,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>865489</v>
+        <v>865557</v>
       </c>
       <c r="R179" t="n">
-        <v>7447329</v>
+        <v>7447153</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18616,12 +18616,12 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
@@ -18632,10 +18632,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>126893263</v>
+        <v>126892986</v>
       </c>
       <c r="B180" t="n">
-        <v>91325</v>
+        <v>79603</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18643,21 +18643,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -18667,10 +18667,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>865485</v>
+        <v>865489</v>
       </c>
       <c r="R180" t="n">
-        <v>7447224</v>
+        <v>7447329</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18717,12 +18717,12 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">

--- a/artfynd/A 52625-2022 artfynd.xlsx
+++ b/artfynd/A 52625-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126891921</v>
+        <v>126891918</v>
       </c>
       <c r="B2" t="n">
         <v>80146</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>865428</v>
+        <v>865445</v>
       </c>
       <c r="R2" t="n">
-        <v>7447586</v>
+        <v>7447390</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,7 +776,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126891918</v>
+        <v>126891921</v>
       </c>
       <c r="B3" t="n">
         <v>80146</v>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>865445</v>
+        <v>865428</v>
       </c>
       <c r="R3" t="n">
-        <v>7447390</v>
+        <v>7447586</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1584,48 +1584,59 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126887991</v>
+        <v>126892270</v>
       </c>
       <c r="B11" t="n">
-        <v>79014</v>
+        <v>91899</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>865422</v>
+        <v>865437</v>
       </c>
       <c r="R11" t="n">
-        <v>7447458</v>
+        <v>7447594</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1663,25 +1674,30 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Svea Nikula, Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126887992</v>
+        <v>126887991</v>
       </c>
       <c r="B12" t="n">
         <v>79014</v>
@@ -1716,10 +1732,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>865406</v>
+        <v>865422</v>
       </c>
       <c r="R12" t="n">
-        <v>7447461</v>
+        <v>7447458</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1778,32 +1794,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126892999</v>
+        <v>126887992</v>
       </c>
       <c r="B13" t="n">
-        <v>80145</v>
+        <v>79014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1813,13 +1829,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>865426</v>
+        <v>865406</v>
       </c>
       <c r="R13" t="n">
-        <v>7447493</v>
+        <v>7447461</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1863,26 +1879,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126892173</v>
+        <v>126892999</v>
       </c>
       <c r="B14" t="n">
-        <v>80146</v>
+        <v>80145</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1890,21 +1902,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1914,10 +1926,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>865379</v>
+        <v>865426</v>
       </c>
       <c r="R14" t="n">
-        <v>7447558</v>
+        <v>7447493</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1964,12 +1976,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -1980,56 +1992,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126892270</v>
+        <v>126892173</v>
       </c>
       <c r="B15" t="n">
-        <v>91899</v>
+        <v>80146</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>760</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>865437</v>
+        <v>865379</v>
       </c>
       <c r="R15" t="n">
-        <v>7447594</v>
+        <v>7447558</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2070,19 +2071,18 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Svea Nikula, Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2093,32 +2093,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126892264</v>
+        <v>126893016</v>
       </c>
       <c r="B16" t="n">
-        <v>58516</v>
+        <v>79014</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>208249</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>865410</v>
+        <v>865412</v>
       </c>
       <c r="R16" t="n">
-        <v>7447525</v>
+        <v>7447514</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2172,19 +2172,18 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2195,32 +2194,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126893016</v>
+        <v>126892264</v>
       </c>
       <c r="B17" t="n">
-        <v>79014</v>
+        <v>58516</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>208249</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2230,10 +2229,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>865412</v>
+        <v>865410</v>
       </c>
       <c r="R17" t="n">
-        <v>7447514</v>
+        <v>7447525</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2274,18 +2273,19 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -3003,32 +3003,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126892261</v>
+        <v>126888460</v>
       </c>
       <c r="B25" t="n">
-        <v>80153</v>
+        <v>79014</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>865434</v>
+        <v>865380</v>
       </c>
       <c r="R25" t="n">
-        <v>7447569</v>
+        <v>7447610</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3088,12 +3088,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3104,7 +3104,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126887982</v>
+        <v>126892261</v>
       </c>
       <c r="B26" t="n">
         <v>80153</v>
@@ -3142,10 +3142,10 @@
         <v>865434</v>
       </c>
       <c r="R26" t="n">
-        <v>7447388</v>
+        <v>7447569</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3189,44 +3189,48 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Svea Nikula</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126888460</v>
+        <v>126887982</v>
       </c>
       <c r="B27" t="n">
-        <v>79014</v>
+        <v>80153</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3236,13 +3240,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>865380</v>
+        <v>865434</v>
       </c>
       <c r="R27" t="n">
-        <v>7447610</v>
+        <v>7447388</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3286,19 +3290,15 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3807,10 +3807,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126893306</v>
+        <v>126887969</v>
       </c>
       <c r="B33" t="n">
-        <v>82855</v>
+        <v>57817</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3818,21 +3818,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>865378</v>
+        <v>865406</v>
       </c>
       <c r="R33" t="n">
-        <v>7447665</v>
+        <v>7447461</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3892,26 +3892,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126892262</v>
+        <v>126892259</v>
       </c>
       <c r="B34" t="n">
-        <v>80153</v>
+        <v>98463</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3919,21 +3915,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6464</v>
+        <v>221952</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3943,10 +3939,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>865404</v>
+        <v>865411</v>
       </c>
       <c r="R34" t="n">
-        <v>7447633</v>
+        <v>7447533</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4009,10 +4005,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126887969</v>
+        <v>126893306</v>
       </c>
       <c r="B35" t="n">
-        <v>57817</v>
+        <v>82855</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4020,21 +4016,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4044,13 +4040,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>865406</v>
+        <v>865378</v>
       </c>
       <c r="R35" t="n">
-        <v>7447461</v>
+        <v>7447665</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4094,22 +4090,26 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
+          <t>Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126892259</v>
+        <v>126892262</v>
       </c>
       <c r="B36" t="n">
-        <v>98463</v>
+        <v>80153</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4117,21 +4117,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221952</v>
+        <v>6464</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4141,10 +4141,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>865411</v>
+        <v>865404</v>
       </c>
       <c r="R36" t="n">
-        <v>7447533</v>
+        <v>7447633</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4708,32 +4708,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126893022</v>
+        <v>126893297</v>
       </c>
       <c r="B42" t="n">
-        <v>98359</v>
+        <v>79014</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4743,10 +4743,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>865404</v>
+        <v>865416</v>
       </c>
       <c r="R42" t="n">
-        <v>7447471</v>
+        <v>7447594</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4793,12 +4793,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -4809,32 +4809,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126893297</v>
+        <v>126893022</v>
       </c>
       <c r="B43" t="n">
-        <v>79014</v>
+        <v>98359</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4844,10 +4844,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>865416</v>
+        <v>865404</v>
       </c>
       <c r="R43" t="n">
-        <v>7447594</v>
+        <v>7447471</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4894,12 +4894,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5011,10 +5011,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126892258</v>
+        <v>126893273</v>
       </c>
       <c r="B45" t="n">
-        <v>80146</v>
+        <v>80153</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5022,21 +5022,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5046,10 +5046,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>865430</v>
+        <v>865406</v>
       </c>
       <c r="R45" t="n">
-        <v>7447566</v>
+        <v>7447648</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5096,12 +5096,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5112,10 +5112,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126893273</v>
+        <v>126892258</v>
       </c>
       <c r="B46" t="n">
-        <v>80153</v>
+        <v>80146</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5123,21 +5123,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5147,10 +5147,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>865406</v>
+        <v>865430</v>
       </c>
       <c r="R46" t="n">
-        <v>7447648</v>
+        <v>7447566</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5197,12 +5197,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -5816,32 +5816,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126892273</v>
+        <v>126891927</v>
       </c>
       <c r="B53" t="n">
-        <v>78420</v>
+        <v>98442</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5851,10 +5851,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>865528</v>
+        <v>865543</v>
       </c>
       <c r="R53" t="n">
-        <v>7447193</v>
+        <v>7447122</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5901,12 +5901,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -5917,32 +5917,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126892985</v>
+        <v>126893280</v>
       </c>
       <c r="B54" t="n">
-        <v>79632</v>
+        <v>91486</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5952,10 +5952,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>865491</v>
+        <v>865490</v>
       </c>
       <c r="R54" t="n">
-        <v>7447332</v>
+        <v>7447213</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6002,12 +6002,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6018,32 +6018,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126891916</v>
+        <v>126893008</v>
       </c>
       <c r="B55" t="n">
-        <v>80146</v>
+        <v>80989</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6462</v>
+        <v>1049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6053,10 +6053,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>865546</v>
+        <v>865545</v>
       </c>
       <c r="R55" t="n">
-        <v>7447133</v>
+        <v>7447322</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6103,12 +6103,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6119,32 +6119,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126891927</v>
+        <v>126892026</v>
       </c>
       <c r="B56" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>865543</v>
+        <v>865538</v>
       </c>
       <c r="R56" t="n">
-        <v>7447122</v>
+        <v>7447072</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6204,12 +6204,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6220,32 +6220,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126893280</v>
+        <v>126892029</v>
       </c>
       <c r="B57" t="n">
-        <v>91486</v>
+        <v>79014</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6255,10 +6255,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>865490</v>
+        <v>865448</v>
       </c>
       <c r="R57" t="n">
-        <v>7447213</v>
+        <v>7447418</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6305,12 +6305,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6321,10 +6321,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126893008</v>
+        <v>126892273</v>
       </c>
       <c r="B58" t="n">
-        <v>80989</v>
+        <v>78420</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6332,21 +6332,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1049</v>
+        <v>6437</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6356,10 +6356,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>865545</v>
+        <v>865528</v>
       </c>
       <c r="R58" t="n">
-        <v>7447322</v>
+        <v>7447193</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6406,12 +6406,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6422,10 +6422,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126892026</v>
+        <v>126892985</v>
       </c>
       <c r="B59" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6433,21 +6433,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6457,10 +6457,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>865538</v>
+        <v>865491</v>
       </c>
       <c r="R59" t="n">
-        <v>7447072</v>
+        <v>7447332</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6507,12 +6507,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6523,32 +6523,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126892029</v>
+        <v>126891916</v>
       </c>
       <c r="B60" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6558,10 +6558,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>865448</v>
+        <v>865546</v>
       </c>
       <c r="R60" t="n">
-        <v>7447418</v>
+        <v>7447133</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6608,12 +6608,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -8253,32 +8253,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126891914</v>
+        <v>126888001</v>
       </c>
       <c r="B77" t="n">
-        <v>80146</v>
+        <v>78681</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6462</v>
+        <v>353</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8288,13 +8288,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>865539</v>
+        <v>865527</v>
       </c>
       <c r="R77" t="n">
-        <v>7447115</v>
+        <v>7447205</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8338,48 +8338,44 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126887974</v>
+        <v>126893270</v>
       </c>
       <c r="B78" t="n">
-        <v>97326</v>
+        <v>92808</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221941</v>
+        <v>2079</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8389,13 +8385,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>865641</v>
+        <v>865491</v>
       </c>
       <c r="R78" t="n">
-        <v>7447070</v>
+        <v>7447267</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8439,22 +8435,26 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr"/>
+          <t>Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126888001</v>
+        <v>126891929</v>
       </c>
       <c r="B79" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8462,21 +8462,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8486,13 +8486,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>865527</v>
+        <v>865535</v>
       </c>
       <c r="R79" t="n">
-        <v>7447205</v>
+        <v>7447142</v>
       </c>
       <c r="S79" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8536,57 +8536,70 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY79" t="inlineStr"/>
+          <t>Amanda Rudelius</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126893270</v>
+        <v>126891930</v>
       </c>
       <c r="B80" t="n">
-        <v>92808</v>
+        <v>8436</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2079</v>
+        <v>106554</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>865491</v>
+        <v>865561</v>
       </c>
       <c r="R80" t="n">
-        <v>7447267</v>
+        <v>7447167</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8627,18 +8640,19 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -8649,32 +8663,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126891929</v>
+        <v>126891914</v>
       </c>
       <c r="B81" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8684,10 +8698,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>865535</v>
+        <v>865539</v>
       </c>
       <c r="R81" t="n">
-        <v>7447142</v>
+        <v>7447115</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8750,10 +8764,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126891930</v>
+        <v>126887974</v>
       </c>
       <c r="B82" t="n">
-        <v>8436</v>
+        <v>97326</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8761,46 +8775,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106554</v>
+        <v>221941</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>865561</v>
+        <v>865641</v>
       </c>
       <c r="R82" t="n">
-        <v>7447167</v>
+        <v>7447070</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8838,26 +8843,21 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -11176,32 +11176,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126893310</v>
+        <v>126887980</v>
       </c>
       <c r="B106" t="n">
-        <v>91586</v>
+        <v>92808</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>65</v>
+        <v>2079</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11211,13 +11211,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>865653</v>
+        <v>865511</v>
       </c>
       <c r="R106" t="n">
-        <v>7447052</v>
+        <v>7447249</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11261,26 +11261,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
-        </is>
-      </c>
-      <c r="AY106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126887980</v>
+        <v>126892028</v>
       </c>
       <c r="B107" t="n">
-        <v>92808</v>
+        <v>79014</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11288,21 +11284,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11312,13 +11308,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>865511</v>
+        <v>865533</v>
       </c>
       <c r="R107" t="n">
-        <v>7447249</v>
+        <v>7447130</v>
       </c>
       <c r="S107" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11362,44 +11358,48 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY107" t="inlineStr"/>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126892028</v>
+        <v>126893310</v>
       </c>
       <c r="B108" t="n">
-        <v>79014</v>
+        <v>91586</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11409,10 +11409,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>865533</v>
+        <v>865653</v>
       </c>
       <c r="R108" t="n">
-        <v>7447130</v>
+        <v>7447052</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11459,12 +11459,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
@@ -13989,10 +13989,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126892176</v>
+        <v>126892189</v>
       </c>
       <c r="B134" t="n">
-        <v>92808</v>
+        <v>79014</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14000,21 +14000,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14024,10 +14024,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>865490</v>
+        <v>865551</v>
       </c>
       <c r="R134" t="n">
-        <v>7447287</v>
+        <v>7447310</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14090,32 +14090,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126892256</v>
+        <v>126892176</v>
       </c>
       <c r="B135" t="n">
-        <v>91290</v>
+        <v>92808</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5447</v>
+        <v>2079</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14125,10 +14125,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>865491</v>
+        <v>865490</v>
       </c>
       <c r="R135" t="n">
-        <v>7447326</v>
+        <v>7447287</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14175,12 +14175,12 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
@@ -14191,32 +14191,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126892189</v>
+        <v>126892256</v>
       </c>
       <c r="B136" t="n">
-        <v>79014</v>
+        <v>91290</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14226,10 +14226,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>865551</v>
+        <v>865491</v>
       </c>
       <c r="R136" t="n">
-        <v>7447310</v>
+        <v>7447326</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14276,12 +14276,12 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
@@ -14692,10 +14692,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126892253</v>
+        <v>126888456</v>
       </c>
       <c r="B141" t="n">
-        <v>91247</v>
+        <v>92808</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14703,21 +14703,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>3242</v>
+        <v>2079</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14727,10 +14727,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>865491</v>
+        <v>865506</v>
       </c>
       <c r="R141" t="n">
-        <v>7447326</v>
+        <v>7447238</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14777,12 +14777,12 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
@@ -14793,7 +14793,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126892991</v>
+        <v>126887971</v>
       </c>
       <c r="B142" t="n">
         <v>80146</v>
@@ -14828,13 +14828,13 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>865531</v>
+        <v>865452</v>
       </c>
       <c r="R142" t="n">
-        <v>7447308</v>
+        <v>7447318</v>
       </c>
       <c r="S142" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -14878,48 +14878,44 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
-        </is>
-      </c>
-      <c r="AY142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126888456</v>
+        <v>126891917</v>
       </c>
       <c r="B143" t="n">
-        <v>92808</v>
+        <v>80146</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>2079</v>
+        <v>6462</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14929,10 +14925,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>865506</v>
+        <v>865561</v>
       </c>
       <c r="R143" t="n">
-        <v>7447238</v>
+        <v>7447152</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -14979,12 +14975,12 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
@@ -14995,32 +14991,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>126887971</v>
+        <v>126892253</v>
       </c>
       <c r="B144" t="n">
-        <v>80146</v>
+        <v>91247</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6462</v>
+        <v>3242</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15030,13 +15026,13 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>865452</v>
+        <v>865491</v>
       </c>
       <c r="R144" t="n">
-        <v>7447318</v>
+        <v>7447326</v>
       </c>
       <c r="S144" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -15080,19 +15076,23 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY144" t="inlineStr"/>
+          <t>Svea Nikula</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126891917</v>
+        <v>126892991</v>
       </c>
       <c r="B145" t="n">
         <v>80146</v>
@@ -15127,10 +15127,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>865561</v>
+        <v>865531</v>
       </c>
       <c r="R145" t="n">
-        <v>7447152</v>
+        <v>7447308</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15177,12 +15177,12 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
@@ -15597,57 +15597,45 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126892023</v>
+        <v>126892980</v>
       </c>
       <c r="B150" t="n">
-        <v>98442</v>
+        <v>91290</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>865539</v>
+        <v>865554</v>
       </c>
       <c r="R150" t="n">
-        <v>7447133</v>
+        <v>7447301</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15688,19 +15676,18 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
-      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
@@ -15711,32 +15698,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126892980</v>
+        <v>126893259</v>
       </c>
       <c r="B151" t="n">
-        <v>91290</v>
+        <v>91247</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5447</v>
+        <v>3242</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15746,10 +15733,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>865554</v>
+        <v>865646</v>
       </c>
       <c r="R151" t="n">
-        <v>7447301</v>
+        <v>7447063</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15796,12 +15783,12 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
@@ -15812,10 +15799,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>126893259</v>
+        <v>126891909</v>
       </c>
       <c r="B152" t="n">
-        <v>91247</v>
+        <v>75138</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15823,21 +15810,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>3242</v>
+        <v>6440</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15847,10 +15834,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>865646</v>
+        <v>865542</v>
       </c>
       <c r="R152" t="n">
-        <v>7447063</v>
+        <v>7447122</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15897,12 +15884,12 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
@@ -15913,45 +15900,57 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>126891909</v>
+        <v>126892023</v>
       </c>
       <c r="B153" t="n">
-        <v>75138</v>
+        <v>98442</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>865542</v>
+        <v>865539</v>
       </c>
       <c r="R153" t="n">
-        <v>7447122</v>
+        <v>7447133</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -15992,18 +15991,19 @@
       <c r="AE153" t="b">
         <v>0</v>
       </c>
+      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
       </c>
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
@@ -16818,7 +16818,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>126891919</v>
+        <v>126893265</v>
       </c>
       <c r="B162" t="n">
         <v>80146</v>
@@ -16853,10 +16853,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>865447</v>
+        <v>865530</v>
       </c>
       <c r="R162" t="n">
-        <v>7447440</v>
+        <v>7447304</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16903,12 +16903,12 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
@@ -16919,32 +16919,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>126893272</v>
+        <v>126891919</v>
       </c>
       <c r="B163" t="n">
-        <v>92808</v>
+        <v>80146</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>2079</v>
+        <v>6462</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -16954,10 +16954,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>865520</v>
+        <v>865447</v>
       </c>
       <c r="R163" t="n">
-        <v>7447337</v>
+        <v>7447440</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17004,12 +17004,12 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
@@ -17020,32 +17020,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>126888458</v>
+        <v>126893272</v>
       </c>
       <c r="B164" t="n">
-        <v>91486</v>
+        <v>92808</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1503</v>
+        <v>2079</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17055,10 +17055,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>865502</v>
+        <v>865520</v>
       </c>
       <c r="R164" t="n">
-        <v>7447310</v>
+        <v>7447337</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17105,12 +17105,12 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
@@ -17121,32 +17121,32 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>126892016</v>
+        <v>126888458</v>
       </c>
       <c r="B165" t="n">
-        <v>91290</v>
+        <v>91486</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>5447</v>
+        <v>1503</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17156,10 +17156,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>865558</v>
+        <v>865502</v>
       </c>
       <c r="R165" t="n">
-        <v>7447154</v>
+        <v>7447310</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17206,12 +17206,12 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
@@ -17222,10 +17222,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>126893265</v>
+        <v>126892016</v>
       </c>
       <c r="B166" t="n">
-        <v>80146</v>
+        <v>91290</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17233,21 +17233,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17257,10 +17257,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>865530</v>
+        <v>865558</v>
       </c>
       <c r="R166" t="n">
-        <v>7447304</v>
+        <v>7447154</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17307,12 +17307,12 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
@@ -18228,32 +18228,32 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>126892997</v>
+        <v>126892986</v>
       </c>
       <c r="B176" t="n">
-        <v>79038</v>
+        <v>79603</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6434</v>
+        <v>229821</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18263,10 +18263,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>865545</v>
+        <v>865489</v>
       </c>
       <c r="R176" t="n">
-        <v>7447323</v>
+        <v>7447329</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18329,32 +18329,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>126893294</v>
+        <v>126892997</v>
       </c>
       <c r="B177" t="n">
-        <v>79014</v>
+        <v>79038</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18364,10 +18364,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>865457</v>
+        <v>865545</v>
       </c>
       <c r="R177" t="n">
-        <v>7447523</v>
+        <v>7447323</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18414,12 +18414,12 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
@@ -18430,10 +18430,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>126893314</v>
+        <v>126893294</v>
       </c>
       <c r="B178" t="n">
-        <v>78420</v>
+        <v>79014</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18441,21 +18441,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18465,10 +18465,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>865647</v>
+        <v>865457</v>
       </c>
       <c r="R178" t="n">
-        <v>7447060</v>
+        <v>7447523</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18531,10 +18531,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>126891913</v>
+        <v>126893314</v>
       </c>
       <c r="B179" t="n">
-        <v>79632</v>
+        <v>78420</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -18542,21 +18542,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -18566,10 +18566,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>865557</v>
+        <v>865647</v>
       </c>
       <c r="R179" t="n">
-        <v>7447153</v>
+        <v>7447060</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18616,12 +18616,12 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
@@ -18632,10 +18632,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>126892986</v>
+        <v>126891913</v>
       </c>
       <c r="B180" t="n">
-        <v>79603</v>
+        <v>79632</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18643,21 +18643,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -18667,10 +18667,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>865489</v>
+        <v>865557</v>
       </c>
       <c r="R180" t="n">
-        <v>7447329</v>
+        <v>7447153</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18717,12 +18717,12 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">

--- a/artfynd/A 52625-2022 artfynd.xlsx
+++ b/artfynd/A 52625-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126891918</v>
+        <v>126891921</v>
       </c>
       <c r="B2" t="n">
         <v>80146</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>865445</v>
+        <v>865428</v>
       </c>
       <c r="R2" t="n">
-        <v>7447390</v>
+        <v>7447586</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -776,7 +776,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126891921</v>
+        <v>126891918</v>
       </c>
       <c r="B3" t="n">
         <v>80146</v>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>865428</v>
+        <v>865445</v>
       </c>
       <c r="R3" t="n">
-        <v>7447586</v>
+        <v>7447390</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,7 +880,7 @@
         <v>126892265</v>
       </c>
       <c r="B4" t="n">
-        <v>91343</v>
+        <v>91344</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1180,32 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126893295</v>
+        <v>126893275</v>
       </c>
       <c r="B7" t="n">
-        <v>79014</v>
+        <v>80153</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>865429</v>
+        <v>865427</v>
       </c>
       <c r="R7" t="n">
-        <v>7447550</v>
+        <v>7447587</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,32 +1281,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126893300</v>
+        <v>126892019</v>
       </c>
       <c r="B8" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>865378</v>
+        <v>865429</v>
       </c>
       <c r="R8" t="n">
-        <v>7447665</v>
+        <v>7447523</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1366,12 +1366,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1382,32 +1382,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126893275</v>
+        <v>126893295</v>
       </c>
       <c r="B9" t="n">
-        <v>80153</v>
+        <v>79014</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>865427</v>
+        <v>865429</v>
       </c>
       <c r="R9" t="n">
-        <v>7447587</v>
+        <v>7447550</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1483,32 +1483,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126892019</v>
+        <v>126893300</v>
       </c>
       <c r="B10" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>865429</v>
+        <v>865378</v>
       </c>
       <c r="R10" t="n">
-        <v>7447523</v>
+        <v>7447665</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1568,12 +1568,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1584,59 +1584,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126892270</v>
+        <v>126887991</v>
       </c>
       <c r="B11" t="n">
-        <v>91899</v>
+        <v>79014</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>865437</v>
+        <v>865422</v>
       </c>
       <c r="R11" t="n">
-        <v>7447594</v>
+        <v>7447458</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1674,30 +1663,25 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Svea Nikula, Jonas Göransson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126887991</v>
+        <v>126887992</v>
       </c>
       <c r="B12" t="n">
         <v>79014</v>
@@ -1732,10 +1716,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>865422</v>
+        <v>865406</v>
       </c>
       <c r="R12" t="n">
-        <v>7447458</v>
+        <v>7447461</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1794,32 +1778,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126887992</v>
+        <v>126892999</v>
       </c>
       <c r="B13" t="n">
-        <v>79014</v>
+        <v>80145</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1829,13 +1813,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>865406</v>
+        <v>865426</v>
       </c>
       <c r="R13" t="n">
-        <v>7447461</v>
+        <v>7447493</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1879,22 +1863,26 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126892999</v>
+        <v>126892173</v>
       </c>
       <c r="B14" t="n">
-        <v>80145</v>
+        <v>80146</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1902,21 +1890,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1926,10 +1914,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>865426</v>
+        <v>865379</v>
       </c>
       <c r="R14" t="n">
-        <v>7447493</v>
+        <v>7447558</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1976,12 +1964,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -1992,45 +1980,56 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126892173</v>
+        <v>126892270</v>
       </c>
       <c r="B15" t="n">
-        <v>80146</v>
+        <v>91900</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>760</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>865379</v>
+        <v>865437</v>
       </c>
       <c r="R15" t="n">
-        <v>7447558</v>
+        <v>7447594</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2071,18 +2070,19 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Svea Nikula, Jonas Göransson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2296,7 +2296,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126893017</v>
+        <v>126893301</v>
       </c>
       <c r="B18" t="n">
         <v>79014</v>
@@ -2331,10 +2331,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>865409</v>
+        <v>865382</v>
       </c>
       <c r="R18" t="n">
-        <v>7447573</v>
+        <v>7447699</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2381,12 +2381,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2397,7 +2397,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126893301</v>
+        <v>126893017</v>
       </c>
       <c r="B19" t="n">
         <v>79014</v>
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>865382</v>
+        <v>865409</v>
       </c>
       <c r="R19" t="n">
-        <v>7447699</v>
+        <v>7447573</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2482,12 +2482,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2801,10 +2801,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126893276</v>
+        <v>126892172</v>
       </c>
       <c r="B23" t="n">
-        <v>80153</v>
+        <v>80146</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2812,21 +2812,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2836,10 +2836,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>865406</v>
+        <v>865436</v>
       </c>
       <c r="R23" t="n">
-        <v>7447661</v>
+        <v>7447532</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2886,12 +2886,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2902,10 +2902,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126892172</v>
+        <v>126893276</v>
       </c>
       <c r="B24" t="n">
-        <v>80146</v>
+        <v>80153</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2913,21 +2913,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2937,10 +2937,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>865436</v>
+        <v>865406</v>
       </c>
       <c r="R24" t="n">
-        <v>7447532</v>
+        <v>7447661</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2987,12 +2987,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3302,32 +3302,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126892030</v>
+        <v>126892179</v>
       </c>
       <c r="B28" t="n">
-        <v>79014</v>
+        <v>80153</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>865389</v>
+        <v>865377</v>
       </c>
       <c r="R28" t="n">
-        <v>7447613</v>
+        <v>7447525</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3387,12 +3387,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3403,7 +3403,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126893015</v>
+        <v>126892030</v>
       </c>
       <c r="B29" t="n">
         <v>79014</v>
@@ -3438,10 +3438,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>865423</v>
+        <v>865389</v>
       </c>
       <c r="R29" t="n">
-        <v>7447442</v>
+        <v>7447613</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3488,12 +3488,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3504,32 +3504,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126892179</v>
+        <v>126893015</v>
       </c>
       <c r="B30" t="n">
-        <v>80153</v>
+        <v>79014</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3539,10 +3539,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>865377</v>
+        <v>865423</v>
       </c>
       <c r="R30" t="n">
-        <v>7447525</v>
+        <v>7447442</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3589,12 +3589,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3904,10 +3904,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126892259</v>
+        <v>126892262</v>
       </c>
       <c r="B34" t="n">
-        <v>98463</v>
+        <v>80153</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3915,21 +3915,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221952</v>
+        <v>6464</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3939,10 +3939,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>865411</v>
+        <v>865404</v>
       </c>
       <c r="R34" t="n">
-        <v>7447533</v>
+        <v>7447633</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4106,10 +4106,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126892262</v>
+        <v>126892259</v>
       </c>
       <c r="B36" t="n">
-        <v>80153</v>
+        <v>98464</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4117,21 +4117,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6464</v>
+        <v>221952</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4141,10 +4141,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>865404</v>
+        <v>865411</v>
       </c>
       <c r="R36" t="n">
-        <v>7447633</v>
+        <v>7447533</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4207,7 +4207,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126887993</v>
+        <v>126893298</v>
       </c>
       <c r="B37" t="n">
         <v>79014</v>
@@ -4242,13 +4242,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>865389</v>
+        <v>865423</v>
       </c>
       <c r="R37" t="n">
-        <v>7447521</v>
+        <v>7447632</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4292,19 +4292,23 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
+          <t>Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126893298</v>
+        <v>126887993</v>
       </c>
       <c r="B38" t="n">
         <v>79014</v>
@@ -4339,13 +4343,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>865423</v>
+        <v>865389</v>
       </c>
       <c r="R38" t="n">
-        <v>7447632</v>
+        <v>7447521</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4389,19 +4393,15 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4506,32 +4506,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126893266</v>
+        <v>126892989</v>
       </c>
       <c r="B40" t="n">
-        <v>80146</v>
+        <v>57817</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4541,10 +4541,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>865423</v>
+        <v>865425</v>
       </c>
       <c r="R40" t="n">
-        <v>7447628</v>
+        <v>7447474</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4591,12 +4591,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4607,32 +4607,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126892989</v>
+        <v>126893266</v>
       </c>
       <c r="B41" t="n">
-        <v>57817</v>
+        <v>80146</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4642,10 +4642,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>865425</v>
+        <v>865423</v>
       </c>
       <c r="R41" t="n">
-        <v>7447474</v>
+        <v>7447628</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4692,12 +4692,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4708,32 +4708,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126893297</v>
+        <v>126893022</v>
       </c>
       <c r="B42" t="n">
-        <v>79014</v>
+        <v>98360</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4743,10 +4743,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>865416</v>
+        <v>865404</v>
       </c>
       <c r="R42" t="n">
-        <v>7447594</v>
+        <v>7447471</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4793,12 +4793,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -4809,32 +4809,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126893022</v>
+        <v>126893297</v>
       </c>
       <c r="B43" t="n">
-        <v>98359</v>
+        <v>79014</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4844,10 +4844,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>865404</v>
+        <v>865416</v>
       </c>
       <c r="R43" t="n">
-        <v>7447471</v>
+        <v>7447594</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4894,12 +4894,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -4910,32 +4910,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126892268</v>
+        <v>126893273</v>
       </c>
       <c r="B44" t="n">
-        <v>79014</v>
+        <v>80153</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4945,10 +4945,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>865411</v>
+        <v>865406</v>
       </c>
       <c r="R44" t="n">
-        <v>7447532</v>
+        <v>7447648</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4995,12 +4995,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5011,32 +5011,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126893273</v>
+        <v>126892268</v>
       </c>
       <c r="B45" t="n">
-        <v>80153</v>
+        <v>79014</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5046,10 +5046,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>865406</v>
+        <v>865411</v>
       </c>
       <c r="R45" t="n">
-        <v>7447648</v>
+        <v>7447532</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5096,12 +5096,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5213,27 +5213,27 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126887994</v>
+        <v>126893028</v>
       </c>
       <c r="B47" t="n">
-        <v>79014</v>
+        <v>80152</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5248,13 +5248,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>865368</v>
+        <v>865390</v>
       </c>
       <c r="R47" t="n">
-        <v>7447606</v>
+        <v>7447609</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5298,22 +5298,26 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126893028</v>
+        <v>126892020</v>
       </c>
       <c r="B48" t="n">
-        <v>80152</v>
+        <v>80146</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5321,21 +5325,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5345,10 +5349,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>865390</v>
+        <v>865440</v>
       </c>
       <c r="R48" t="n">
-        <v>7447609</v>
+        <v>7447393</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5395,12 +5399,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5411,32 +5415,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126892020</v>
+        <v>126887994</v>
       </c>
       <c r="B49" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5446,13 +5450,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>865440</v>
+        <v>865368</v>
       </c>
       <c r="R49" t="n">
-        <v>7447393</v>
+        <v>7447606</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5496,48 +5500,44 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126892254</v>
+        <v>126887983</v>
       </c>
       <c r="B50" t="n">
-        <v>75138</v>
+        <v>80153</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6440</v>
+        <v>6464</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5547,13 +5547,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>865423</v>
+        <v>865378</v>
       </c>
       <c r="R50" t="n">
-        <v>7447468</v>
+        <v>7447577</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5597,48 +5597,44 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126887983</v>
+        <v>126892254</v>
       </c>
       <c r="B51" t="n">
-        <v>80153</v>
+        <v>75138</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5648,13 +5644,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>865378</v>
+        <v>865423</v>
       </c>
       <c r="R51" t="n">
-        <v>7447577</v>
+        <v>7447468</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5698,22 +5694,26 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
+          <t>Svea Nikula</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
         <v>126765146</v>
       </c>
       <c r="B52" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5816,32 +5816,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126891927</v>
+        <v>126892026</v>
       </c>
       <c r="B53" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5851,10 +5851,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>865543</v>
+        <v>865538</v>
       </c>
       <c r="R53" t="n">
-        <v>7447122</v>
+        <v>7447072</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5901,12 +5901,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -5917,32 +5917,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126893280</v>
+        <v>126892029</v>
       </c>
       <c r="B54" t="n">
-        <v>91486</v>
+        <v>79014</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5952,10 +5952,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>865490</v>
+        <v>865448</v>
       </c>
       <c r="R54" t="n">
-        <v>7447213</v>
+        <v>7447418</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6002,12 +6002,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6018,10 +6018,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126893008</v>
+        <v>126892273</v>
       </c>
       <c r="B55" t="n">
-        <v>80989</v>
+        <v>78420</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6029,21 +6029,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1049</v>
+        <v>6437</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6053,10 +6053,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>865545</v>
+        <v>865528</v>
       </c>
       <c r="R55" t="n">
-        <v>7447322</v>
+        <v>7447193</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6103,12 +6103,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6119,10 +6119,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126892026</v>
+        <v>126892985</v>
       </c>
       <c r="B56" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6130,21 +6130,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>865538</v>
+        <v>865491</v>
       </c>
       <c r="R56" t="n">
-        <v>7447072</v>
+        <v>7447332</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6204,12 +6204,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6220,32 +6220,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126892029</v>
+        <v>126891916</v>
       </c>
       <c r="B57" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6255,10 +6255,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>865448</v>
+        <v>865546</v>
       </c>
       <c r="R57" t="n">
-        <v>7447418</v>
+        <v>7447133</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6305,12 +6305,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6321,32 +6321,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126892273</v>
+        <v>126893280</v>
       </c>
       <c r="B58" t="n">
-        <v>78420</v>
+        <v>91487</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6437</v>
+        <v>1503</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6356,10 +6356,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>865528</v>
+        <v>865490</v>
       </c>
       <c r="R58" t="n">
-        <v>7447193</v>
+        <v>7447213</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6406,12 +6406,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6422,10 +6422,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126892985</v>
+        <v>126893008</v>
       </c>
       <c r="B59" t="n">
-        <v>79632</v>
+        <v>80989</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6433,21 +6433,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6457,10 +6457,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>865491</v>
+        <v>865545</v>
       </c>
       <c r="R59" t="n">
-        <v>7447332</v>
+        <v>7447322</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6523,32 +6523,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126891916</v>
+        <v>126891927</v>
       </c>
       <c r="B60" t="n">
-        <v>80146</v>
+        <v>98443</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6558,10 +6558,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>865546</v>
+        <v>865543</v>
       </c>
       <c r="R60" t="n">
-        <v>7447133</v>
+        <v>7447122</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6624,32 +6624,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126892982</v>
+        <v>126892177</v>
       </c>
       <c r="B61" t="n">
-        <v>91290</v>
+        <v>92809</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5447</v>
+        <v>2079</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6659,10 +6659,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>865526</v>
+        <v>865522</v>
       </c>
       <c r="R61" t="n">
-        <v>7447273</v>
+        <v>7447338</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6709,12 +6709,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6725,32 +6725,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126887985</v>
+        <v>126892982</v>
       </c>
       <c r="B62" t="n">
-        <v>98442</v>
+        <v>91291</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6760,13 +6760,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>865583</v>
+        <v>865526</v>
       </c>
       <c r="R62" t="n">
-        <v>7447137</v>
+        <v>7447273</v>
       </c>
       <c r="S62" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6810,44 +6810,48 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr"/>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126892177</v>
+        <v>126891915</v>
       </c>
       <c r="B63" t="n">
-        <v>92808</v>
+        <v>80146</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2079</v>
+        <v>6462</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6857,10 +6861,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>865522</v>
+        <v>865551</v>
       </c>
       <c r="R63" t="n">
-        <v>7447338</v>
+        <v>7447126</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6907,12 +6911,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -6923,32 +6927,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126891915</v>
+        <v>126887985</v>
       </c>
       <c r="B64" t="n">
-        <v>80146</v>
+        <v>98443</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6958,13 +6962,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>865551</v>
+        <v>865583</v>
       </c>
       <c r="R64" t="n">
-        <v>7447126</v>
+        <v>7447137</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7008,26 +7012,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126888002</v>
+        <v>126893312</v>
       </c>
       <c r="B65" t="n">
-        <v>78681</v>
+        <v>77992</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7035,21 +7035,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>353</v>
+        <v>6487</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7059,13 +7059,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>865512</v>
+        <v>865598</v>
       </c>
       <c r="R65" t="n">
-        <v>7447340</v>
+        <v>7447181</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7109,44 +7109,48 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr"/>
+          <t>Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126891925</v>
+        <v>126892998</v>
       </c>
       <c r="B66" t="n">
-        <v>98442</v>
+        <v>80145</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7156,10 +7160,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>865527</v>
+        <v>865477</v>
       </c>
       <c r="R66" t="n">
-        <v>7447333</v>
+        <v>7447327</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7206,12 +7210,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7222,32 +7226,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126893010</v>
+        <v>126891925</v>
       </c>
       <c r="B67" t="n">
-        <v>80989</v>
+        <v>98443</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1049</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7257,10 +7261,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>865490</v>
+        <v>865527</v>
       </c>
       <c r="R67" t="n">
-        <v>7447332</v>
+        <v>7447333</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7307,12 +7311,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7326,7 +7330,7 @@
         <v>126893000</v>
       </c>
       <c r="B68" t="n">
-        <v>92808</v>
+        <v>92809</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7424,10 +7428,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126893312</v>
+        <v>126888002</v>
       </c>
       <c r="B69" t="n">
-        <v>77992</v>
+        <v>78681</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7435,21 +7439,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6487</v>
+        <v>353</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7459,13 +7463,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>865598</v>
+        <v>865512</v>
       </c>
       <c r="R69" t="n">
-        <v>7447181</v>
+        <v>7447340</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7509,48 +7513,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126892998</v>
+        <v>126893010</v>
       </c>
       <c r="B70" t="n">
-        <v>80145</v>
+        <v>80989</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6461</v>
+        <v>1049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7560,10 +7560,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>865477</v>
+        <v>865490</v>
       </c>
       <c r="R70" t="n">
-        <v>7447327</v>
+        <v>7447332</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7748,32 +7748,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126892187</v>
+        <v>126891911</v>
       </c>
       <c r="B72" t="n">
-        <v>91486</v>
+        <v>91291</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1503</v>
+        <v>5447</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7783,10 +7783,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>865509</v>
+        <v>865557</v>
       </c>
       <c r="R72" t="n">
-        <v>7447371</v>
+        <v>7447153</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7833,12 +7833,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -7849,32 +7849,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126893012</v>
+        <v>126893282</v>
       </c>
       <c r="B73" t="n">
-        <v>91486</v>
+        <v>79014</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7884,10 +7884,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>865559</v>
+        <v>865611</v>
       </c>
       <c r="R73" t="n">
-        <v>7447299</v>
+        <v>7446989</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7934,12 +7934,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -7950,32 +7950,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126891911</v>
+        <v>126891926</v>
       </c>
       <c r="B74" t="n">
-        <v>91290</v>
+        <v>98443</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7985,10 +7985,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>865557</v>
+        <v>865541</v>
       </c>
       <c r="R74" t="n">
-        <v>7447153</v>
+        <v>7447113</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8051,32 +8051,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126893282</v>
+        <v>126893012</v>
       </c>
       <c r="B75" t="n">
-        <v>79014</v>
+        <v>91487</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8086,10 +8086,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>865611</v>
+        <v>865559</v>
       </c>
       <c r="R75" t="n">
-        <v>7446989</v>
+        <v>7447299</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8136,12 +8136,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8152,10 +8152,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126891926</v>
+        <v>126892187</v>
       </c>
       <c r="B76" t="n">
-        <v>98442</v>
+        <v>91487</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8163,21 +8163,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>1503</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8187,10 +8187,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>865541</v>
+        <v>865509</v>
       </c>
       <c r="R76" t="n">
-        <v>7447113</v>
+        <v>7447371</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8237,12 +8237,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8253,10 +8253,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126888001</v>
+        <v>126893270</v>
       </c>
       <c r="B77" t="n">
-        <v>78681</v>
+        <v>92809</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8264,21 +8264,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8288,13 +8288,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>865527</v>
+        <v>865491</v>
       </c>
       <c r="R77" t="n">
-        <v>7447205</v>
+        <v>7447267</v>
       </c>
       <c r="S77" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8338,22 +8338,26 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr"/>
+          <t>Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126893270</v>
+        <v>126891929</v>
       </c>
       <c r="B78" t="n">
-        <v>92808</v>
+        <v>79014</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8361,21 +8365,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8385,10 +8389,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>865491</v>
+        <v>865535</v>
       </c>
       <c r="R78" t="n">
-        <v>7447267</v>
+        <v>7447142</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8435,12 +8439,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8451,10 +8455,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126891929</v>
+        <v>126888001</v>
       </c>
       <c r="B79" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8462,21 +8466,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8486,13 +8490,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>865535</v>
+        <v>865527</v>
       </c>
       <c r="R79" t="n">
-        <v>7447142</v>
+        <v>7447205</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8536,19 +8540,15 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
-        </is>
-      </c>
-      <c r="AY79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8767,7 +8767,7 @@
         <v>126887974</v>
       </c>
       <c r="B82" t="n">
-        <v>97326</v>
+        <v>97327</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8861,32 +8861,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126888457</v>
+        <v>126893003</v>
       </c>
       <c r="B83" t="n">
-        <v>91486</v>
+        <v>80153</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1503</v>
+        <v>6464</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8896,10 +8896,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>865528</v>
+        <v>865532</v>
       </c>
       <c r="R83" t="n">
-        <v>7447201</v>
+        <v>7447307</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8946,12 +8946,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -8962,32 +8962,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126892185</v>
+        <v>126892271</v>
       </c>
       <c r="B84" t="n">
-        <v>91486</v>
+        <v>80152</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1503</v>
+        <v>6463</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8997,10 +8997,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>865490</v>
+        <v>865610</v>
       </c>
       <c r="R84" t="n">
-        <v>7447287</v>
+        <v>7447145</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9047,12 +9047,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9063,10 +9063,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126892175</v>
+        <v>126888454</v>
       </c>
       <c r="B85" t="n">
-        <v>92808</v>
+        <v>57817</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9074,34 +9074,42 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2079</v>
+        <v>103021</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>865509</v>
+        <v>865481</v>
       </c>
       <c r="R85" t="n">
-        <v>7447217</v>
+        <v>7447376</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9148,12 +9156,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -9164,10 +9172,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126887978</v>
+        <v>126892175</v>
       </c>
       <c r="B86" t="n">
-        <v>92808</v>
+        <v>92809</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9199,13 +9207,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>865521</v>
+        <v>865509</v>
       </c>
       <c r="R86" t="n">
-        <v>7447240</v>
+        <v>7447217</v>
       </c>
       <c r="S86" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9249,22 +9257,26 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY86" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126893277</v>
+        <v>126887978</v>
       </c>
       <c r="B87" t="n">
-        <v>80989</v>
+        <v>92809</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9272,21 +9284,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1049</v>
+        <v>2079</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9296,13 +9308,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>865647</v>
+        <v>865521</v>
       </c>
       <c r="R87" t="n">
-        <v>7447060</v>
+        <v>7447240</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9346,26 +9358,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
-        </is>
-      </c>
-      <c r="AY87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
         <v>126892192</v>
       </c>
       <c r="B88" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9463,32 +9471,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126893003</v>
+        <v>126893277</v>
       </c>
       <c r="B89" t="n">
-        <v>80153</v>
+        <v>80989</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6464</v>
+        <v>1049</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9498,10 +9506,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>865532</v>
+        <v>865647</v>
       </c>
       <c r="R89" t="n">
-        <v>7447307</v>
+        <v>7447060</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9548,12 +9556,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -9564,32 +9572,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126892271</v>
+        <v>126892185</v>
       </c>
       <c r="B90" t="n">
-        <v>80152</v>
+        <v>91487</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6463</v>
+        <v>1503</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9599,10 +9607,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>865610</v>
+        <v>865490</v>
       </c>
       <c r="R90" t="n">
-        <v>7447145</v>
+        <v>7447287</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9649,12 +9657,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -9665,53 +9673,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126888454</v>
+        <v>126888457</v>
       </c>
       <c r="B91" t="n">
-        <v>57817</v>
+        <v>91487</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>103021</v>
+        <v>1503</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>865481</v>
+        <v>865528</v>
       </c>
       <c r="R91" t="n">
-        <v>7447376</v>
+        <v>7447201</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9777,7 +9777,7 @@
         <v>126893278</v>
       </c>
       <c r="B92" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
         <v>126892181</v>
       </c>
       <c r="B93" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9976,32 +9976,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126893281</v>
+        <v>126887968</v>
       </c>
       <c r="B94" t="n">
-        <v>91486</v>
+        <v>57817</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1503</v>
+        <v>103021</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10011,13 +10011,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>865513</v>
+        <v>865523</v>
       </c>
       <c r="R94" t="n">
-        <v>7447339</v>
+        <v>7447217</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10061,26 +10061,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
-        </is>
-      </c>
-      <c r="AY94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
         <v>126892178</v>
       </c>
       <c r="B95" t="n">
-        <v>92808</v>
+        <v>92809</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10181,7 +10177,7 @@
         <v>126893025</v>
       </c>
       <c r="B96" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10279,32 +10275,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126887968</v>
+        <v>126892981</v>
       </c>
       <c r="B97" t="n">
-        <v>57817</v>
+        <v>91291</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10314,13 +10310,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>865523</v>
+        <v>865553</v>
       </c>
       <c r="R97" t="n">
-        <v>7447217</v>
+        <v>7447278</v>
       </c>
       <c r="S97" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10364,22 +10360,26 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY97" t="inlineStr"/>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126888000</v>
+        <v>126892267</v>
       </c>
       <c r="B98" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10387,21 +10387,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10411,13 +10411,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>865597</v>
+        <v>865516</v>
       </c>
       <c r="R98" t="n">
-        <v>7447186</v>
+        <v>7447351</v>
       </c>
       <c r="S98" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10461,22 +10461,26 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY98" t="inlineStr"/>
+          <t>Svea Nikula</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126893023</v>
+        <v>126893281</v>
       </c>
       <c r="B99" t="n">
-        <v>91726</v>
+        <v>91487</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10484,21 +10488,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>715</v>
+        <v>1503</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Finporing</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Gloeoporus pannocinctus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Romell) J.Erikss.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10508,10 +10512,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>865473</v>
+        <v>865513</v>
       </c>
       <c r="R99" t="n">
-        <v>7447321</v>
+        <v>7447339</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10558,12 +10562,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -10574,32 +10578,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126892981</v>
+        <v>126893023</v>
       </c>
       <c r="B100" t="n">
-        <v>91290</v>
+        <v>91727</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5447</v>
+        <v>715</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Finporing</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Gloeoporus pannocinctus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) J.Erikss.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10609,10 +10613,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>865553</v>
+        <v>865473</v>
       </c>
       <c r="R100" t="n">
-        <v>7447278</v>
+        <v>7447321</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10675,10 +10679,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126892267</v>
+        <v>126888000</v>
       </c>
       <c r="B101" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10686,21 +10690,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10710,13 +10714,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>865516</v>
+        <v>865597</v>
       </c>
       <c r="R101" t="n">
-        <v>7447351</v>
+        <v>7447186</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10760,26 +10764,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
-        </is>
-      </c>
-      <c r="AY101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
         <v>126887997</v>
       </c>
       <c r="B102" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10873,32 +10873,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126892186</v>
+        <v>126893033</v>
       </c>
       <c r="B103" t="n">
-        <v>91486</v>
+        <v>78420</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1503</v>
+        <v>6437</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10908,10 +10908,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>865491</v>
+        <v>865500</v>
       </c>
       <c r="R103" t="n">
-        <v>7447290</v>
+        <v>7447283</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10958,12 +10958,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -10974,32 +10974,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126893033</v>
+        <v>126891923</v>
       </c>
       <c r="B104" t="n">
-        <v>78420</v>
+        <v>80021</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6437</v>
+        <v>6456</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11009,10 +11009,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>865500</v>
+        <v>865536</v>
       </c>
       <c r="R104" t="n">
-        <v>7447283</v>
+        <v>7447112</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11059,12 +11059,12 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -11075,32 +11075,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126891923</v>
+        <v>126892186</v>
       </c>
       <c r="B105" t="n">
-        <v>80021</v>
+        <v>91487</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6456</v>
+        <v>1503</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11110,10 +11110,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>865536</v>
+        <v>865491</v>
       </c>
       <c r="R105" t="n">
-        <v>7447112</v>
+        <v>7447290</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11160,12 +11160,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
@@ -11179,7 +11179,7 @@
         <v>126887980</v>
       </c>
       <c r="B106" t="n">
-        <v>92808</v>
+        <v>92809</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11377,7 +11377,7 @@
         <v>126893310</v>
       </c>
       <c r="B108" t="n">
-        <v>91586</v>
+        <v>91587</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11475,10 +11475,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126892263</v>
+        <v>126887990</v>
       </c>
       <c r="B109" t="n">
-        <v>56840</v>
+        <v>79014</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11486,45 +11486,37 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>865544</v>
+        <v>865447</v>
       </c>
       <c r="R109" t="n">
-        <v>7447281</v>
+        <v>7447371</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -11568,73 +11560,57 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
-        </is>
-      </c>
-      <c r="AY109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126892018</v>
+        <v>126892191</v>
       </c>
       <c r="B110" t="n">
-        <v>57817</v>
+        <v>91587</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>103021</v>
+        <v>65</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr"/>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>865561</v>
+        <v>865540</v>
       </c>
       <c r="R110" t="n">
-        <v>7447155</v>
+        <v>7447366</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11681,12 +11657,12 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
@@ -11697,10 +11673,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126892191</v>
+        <v>126887987</v>
       </c>
       <c r="B111" t="n">
-        <v>91586</v>
+        <v>91487</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11708,21 +11684,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>65</v>
+        <v>1503</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11732,13 +11708,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>865540</v>
+        <v>865510</v>
       </c>
       <c r="R111" t="n">
-        <v>7447366</v>
+        <v>7447247</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -11782,19 +11758,15 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11899,10 +11871,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126887977</v>
+        <v>126892263</v>
       </c>
       <c r="B113" t="n">
-        <v>92808</v>
+        <v>56840</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11910,37 +11882,45 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>2079</v>
+        <v>102612</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>865643</v>
+        <v>865544</v>
       </c>
       <c r="R113" t="n">
-        <v>7447067</v>
+        <v>7447281</v>
       </c>
       <c r="S113" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -11984,44 +11964,48 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY113" t="inlineStr"/>
+          <t>Svea Nikula</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126887987</v>
+        <v>126887965</v>
       </c>
       <c r="B114" t="n">
-        <v>91486</v>
+        <v>57479</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1503</v>
+        <v>102976</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12031,10 +12015,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>865510</v>
+        <v>865583</v>
       </c>
       <c r="R114" t="n">
-        <v>7447247</v>
+        <v>7447214</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -12093,32 +12077,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126887990</v>
+        <v>126887975</v>
       </c>
       <c r="B115" t="n">
-        <v>79014</v>
+        <v>97327</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12128,10 +12112,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>865447</v>
+        <v>865479</v>
       </c>
       <c r="R115" t="n">
-        <v>7447371</v>
+        <v>7447358</v>
       </c>
       <c r="S115" t="n">
         <v>25</v>
@@ -12190,32 +12174,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126887965</v>
+        <v>126887976</v>
       </c>
       <c r="B116" t="n">
-        <v>57479</v>
+        <v>97327</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>102976</v>
+        <v>221941</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12225,10 +12209,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>865583</v>
+        <v>865452</v>
       </c>
       <c r="R116" t="n">
-        <v>7447214</v>
+        <v>7447334</v>
       </c>
       <c r="S116" t="n">
         <v>25</v>
@@ -12287,10 +12271,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126891928</v>
+        <v>126892024</v>
       </c>
       <c r="B117" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12322,10 +12306,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>865549</v>
+        <v>865546</v>
       </c>
       <c r="R117" t="n">
-        <v>7447136</v>
+        <v>7447138</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12372,12 +12356,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
@@ -12388,32 +12372,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126887975</v>
+        <v>126887977</v>
       </c>
       <c r="B118" t="n">
-        <v>97326</v>
+        <v>92809</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>221941</v>
+        <v>2079</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12423,10 +12407,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>865479</v>
+        <v>865643</v>
       </c>
       <c r="R118" t="n">
-        <v>7447358</v>
+        <v>7447067</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -12485,48 +12469,60 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126887976</v>
+        <v>126892018</v>
       </c>
       <c r="B119" t="n">
-        <v>97326</v>
+        <v>57817</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>221941</v>
+        <v>103021</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>865452</v>
+        <v>865561</v>
       </c>
       <c r="R119" t="n">
-        <v>7447334</v>
+        <v>7447155</v>
       </c>
       <c r="S119" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -12570,22 +12566,26 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY119" t="inlineStr"/>
+          <t>Julia Frejd</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126892024</v>
+        <v>126891928</v>
       </c>
       <c r="B120" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12617,10 +12617,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>865546</v>
+        <v>865549</v>
       </c>
       <c r="R120" t="n">
-        <v>7447138</v>
+        <v>7447136</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12667,12 +12667,12 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
@@ -12683,10 +12683,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126893262</v>
+        <v>126887981</v>
       </c>
       <c r="B121" t="n">
-        <v>91290</v>
+        <v>80153</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12694,21 +12694,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5447</v>
+        <v>6464</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12718,13 +12718,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>865522</v>
+        <v>865448</v>
       </c>
       <c r="R121" t="n">
-        <v>7447308</v>
+        <v>7447345</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -12768,48 +12768,44 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
-        </is>
-      </c>
-      <c r="AY121" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126893260</v>
+        <v>126892170</v>
       </c>
       <c r="B122" t="n">
-        <v>91247</v>
+        <v>57479</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>3242</v>
+        <v>102976</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12819,10 +12815,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>865498</v>
+        <v>865489</v>
       </c>
       <c r="R122" t="n">
-        <v>7447359</v>
+        <v>7447377</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12857,6 +12853,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Förbiflygande</t>
+        </is>
+      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
@@ -12869,12 +12870,12 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
@@ -12986,32 +12987,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126887981</v>
+        <v>126893260</v>
       </c>
       <c r="B124" t="n">
-        <v>80153</v>
+        <v>91248</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6464</v>
+        <v>3242</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13021,13 +13022,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>865448</v>
+        <v>865498</v>
       </c>
       <c r="R124" t="n">
-        <v>7447345</v>
+        <v>7447359</v>
       </c>
       <c r="S124" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13071,44 +13072,48 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY124" t="inlineStr"/>
+          <t>Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126893308</v>
+        <v>126893267</v>
       </c>
       <c r="B125" t="n">
-        <v>91586</v>
+        <v>92809</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>65</v>
+        <v>2079</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13118,10 +13123,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>865659</v>
+        <v>865648</v>
       </c>
       <c r="R125" t="n">
-        <v>7447048</v>
+        <v>7447056</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13184,32 +13189,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126893267</v>
+        <v>126893262</v>
       </c>
       <c r="B126" t="n">
-        <v>92808</v>
+        <v>91291</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>2079</v>
+        <v>5447</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13219,10 +13224,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>865648</v>
+        <v>865522</v>
       </c>
       <c r="R126" t="n">
-        <v>7447056</v>
+        <v>7447308</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13285,32 +13290,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126892170</v>
+        <v>126893308</v>
       </c>
       <c r="B127" t="n">
-        <v>57479</v>
+        <v>91587</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>102976</v>
+        <v>65</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13320,10 +13325,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>865489</v>
+        <v>865659</v>
       </c>
       <c r="R127" t="n">
-        <v>7447377</v>
+        <v>7447048</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13358,11 +13363,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>Förbiflygande</t>
-        </is>
-      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
@@ -13375,12 +13375,12 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
@@ -13391,10 +13391,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126893292</v>
+        <v>126893269</v>
       </c>
       <c r="B128" t="n">
-        <v>79014</v>
+        <v>92809</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13402,21 +13402,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13426,10 +13426,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>865501</v>
+        <v>865647</v>
       </c>
       <c r="R128" t="n">
-        <v>7447191</v>
+        <v>7447057</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13492,32 +13492,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126893313</v>
+        <v>126893274</v>
       </c>
       <c r="B129" t="n">
-        <v>78420</v>
+        <v>80153</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6437</v>
+        <v>6464</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13527,10 +13527,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>865598</v>
+        <v>865476</v>
       </c>
       <c r="R129" t="n">
-        <v>7447181</v>
+        <v>7447236</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13593,32 +13593,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126887988</v>
+        <v>126893292</v>
       </c>
       <c r="B130" t="n">
-        <v>91486</v>
+        <v>79014</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13628,13 +13628,13 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>865515</v>
+        <v>865501</v>
       </c>
       <c r="R130" t="n">
-        <v>7447377</v>
+        <v>7447191</v>
       </c>
       <c r="S130" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -13678,44 +13678,48 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY130" t="inlineStr"/>
+          <t>Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126893269</v>
+        <v>126887970</v>
       </c>
       <c r="B131" t="n">
-        <v>92808</v>
+        <v>80146</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>2079</v>
+        <v>6462</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13725,13 +13729,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>865647</v>
+        <v>865529</v>
       </c>
       <c r="R131" t="n">
-        <v>7447057</v>
+        <v>7447327</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -13775,48 +13779,44 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
-        </is>
-      </c>
-      <c r="AY131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126887970</v>
+        <v>126893313</v>
       </c>
       <c r="B132" t="n">
-        <v>80146</v>
+        <v>78420</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6462</v>
+        <v>6437</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13826,13 +13826,13 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>865529</v>
+        <v>865598</v>
       </c>
       <c r="R132" t="n">
-        <v>7447327</v>
+        <v>7447181</v>
       </c>
       <c r="S132" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -13876,44 +13876,48 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY132" t="inlineStr"/>
+          <t>Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126893274</v>
+        <v>126887988</v>
       </c>
       <c r="B133" t="n">
-        <v>80153</v>
+        <v>91487</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6464</v>
+        <v>1503</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13923,13 +13927,13 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>865476</v>
+        <v>865515</v>
       </c>
       <c r="R133" t="n">
-        <v>7447236</v>
+        <v>7447377</v>
       </c>
       <c r="S133" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -13973,48 +13977,44 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
-        </is>
-      </c>
-      <c r="AY133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126892189</v>
+        <v>126892256</v>
       </c>
       <c r="B134" t="n">
-        <v>79014</v>
+        <v>91291</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14024,10 +14024,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>865551</v>
+        <v>865491</v>
       </c>
       <c r="R134" t="n">
-        <v>7447310</v>
+        <v>7447326</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14074,12 +14074,12 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
@@ -14093,7 +14093,7 @@
         <v>126892176</v>
       </c>
       <c r="B135" t="n">
-        <v>92808</v>
+        <v>92809</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14191,32 +14191,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126892256</v>
+        <v>126892189</v>
       </c>
       <c r="B136" t="n">
-        <v>91290</v>
+        <v>79014</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14226,10 +14226,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>865491</v>
+        <v>865551</v>
       </c>
       <c r="R136" t="n">
-        <v>7447326</v>
+        <v>7447310</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14276,12 +14276,12 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
@@ -14695,7 +14695,7 @@
         <v>126888456</v>
       </c>
       <c r="B141" t="n">
-        <v>92808</v>
+        <v>92809</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14793,32 +14793,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126887971</v>
+        <v>126892253</v>
       </c>
       <c r="B142" t="n">
-        <v>80146</v>
+        <v>91248</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6462</v>
+        <v>3242</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14828,13 +14828,13 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>865452</v>
+        <v>865491</v>
       </c>
       <c r="R142" t="n">
-        <v>7447318</v>
+        <v>7447326</v>
       </c>
       <c r="S142" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -14878,19 +14878,23 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY142" t="inlineStr"/>
+          <t>Svea Nikula</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126891917</v>
+        <v>126887971</v>
       </c>
       <c r="B143" t="n">
         <v>80146</v>
@@ -14925,13 +14929,13 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>865561</v>
+        <v>865452</v>
       </c>
       <c r="R143" t="n">
-        <v>7447152</v>
+        <v>7447318</v>
       </c>
       <c r="S143" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -14975,48 +14979,44 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
-        </is>
-      </c>
-      <c r="AY143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>126892253</v>
+        <v>126892991</v>
       </c>
       <c r="B144" t="n">
-        <v>91247</v>
+        <v>80146</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>3242</v>
+        <v>6462</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15026,10 +15026,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>865491</v>
+        <v>865531</v>
       </c>
       <c r="R144" t="n">
-        <v>7447326</v>
+        <v>7447308</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15076,12 +15076,12 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
@@ -15092,7 +15092,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126892991</v>
+        <v>126891917</v>
       </c>
       <c r="B145" t="n">
         <v>80146</v>
@@ -15127,10 +15127,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>865531</v>
+        <v>865561</v>
       </c>
       <c r="R145" t="n">
-        <v>7447308</v>
+        <v>7447152</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15177,12 +15177,12 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
@@ -15395,32 +15395,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126892983</v>
+        <v>126893264</v>
       </c>
       <c r="B148" t="n">
-        <v>79632</v>
+        <v>57479</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6453</v>
+        <v>102976</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15430,10 +15430,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>865546</v>
+        <v>865598</v>
       </c>
       <c r="R148" t="n">
-        <v>7447275</v>
+        <v>7447180</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15480,12 +15480,12 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
@@ -15496,32 +15496,32 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126893264</v>
+        <v>126892983</v>
       </c>
       <c r="B149" t="n">
-        <v>57479</v>
+        <v>79632</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>102976</v>
+        <v>6453</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15531,10 +15531,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>865598</v>
+        <v>865546</v>
       </c>
       <c r="R149" t="n">
-        <v>7447180</v>
+        <v>7447275</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15581,12 +15581,12 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
@@ -15600,7 +15600,7 @@
         <v>126892980</v>
       </c>
       <c r="B150" t="n">
-        <v>91290</v>
+        <v>91291</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15701,7 +15701,7 @@
         <v>126893259</v>
       </c>
       <c r="B151" t="n">
-        <v>91247</v>
+        <v>91248</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15903,7 +15903,7 @@
         <v>126892023</v>
       </c>
       <c r="B153" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16014,10 +16014,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>126893011</v>
+        <v>126892974</v>
       </c>
       <c r="B154" t="n">
-        <v>80989</v>
+        <v>91248</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16025,21 +16025,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1049</v>
+        <v>3242</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16049,10 +16049,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>865498</v>
+        <v>865494</v>
       </c>
       <c r="R154" t="n">
-        <v>7447379</v>
+        <v>7447322</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16115,32 +16115,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126887979</v>
+        <v>126892255</v>
       </c>
       <c r="B155" t="n">
-        <v>92808</v>
+        <v>91291</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>2079</v>
+        <v>5447</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16150,13 +16150,13 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>865510</v>
+        <v>865462</v>
       </c>
       <c r="R155" t="n">
-        <v>7447251</v>
+        <v>7447413</v>
       </c>
       <c r="S155" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -16200,44 +16200,48 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY155" t="inlineStr"/>
+          <t>Svea Nikula</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>126892255</v>
+        <v>126887979</v>
       </c>
       <c r="B156" t="n">
-        <v>91290</v>
+        <v>92809</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>5447</v>
+        <v>2079</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16247,13 +16251,13 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>865462</v>
+        <v>865510</v>
       </c>
       <c r="R156" t="n">
-        <v>7447413</v>
+        <v>7447251</v>
       </c>
       <c r="S156" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -16297,26 +16301,22 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
-        </is>
-      </c>
-      <c r="AY156" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126892974</v>
+        <v>126892272</v>
       </c>
       <c r="B157" t="n">
-        <v>91247</v>
+        <v>77992</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16324,21 +16324,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>3242</v>
+        <v>6487</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16348,10 +16348,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>865494</v>
+        <v>865528</v>
       </c>
       <c r="R157" t="n">
-        <v>7447322</v>
+        <v>7447192</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16398,12 +16398,12 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
@@ -16414,10 +16414,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>126892272</v>
+        <v>126893011</v>
       </c>
       <c r="B158" t="n">
-        <v>77992</v>
+        <v>80989</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16425,21 +16425,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6487</v>
+        <v>1049</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16449,10 +16449,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>865528</v>
+        <v>865498</v>
       </c>
       <c r="R158" t="n">
-        <v>7447192</v>
+        <v>7447379</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16499,12 +16499,12 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
@@ -16515,10 +16515,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>126891924</v>
+        <v>126893291</v>
       </c>
       <c r="B159" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16526,37 +16526,34 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
-      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>865562</v>
+        <v>865507</v>
       </c>
       <c r="R159" t="n">
-        <v>7447150</v>
+        <v>7447151</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16597,19 +16594,18 @@
       <c r="AE159" t="b">
         <v>0</v>
       </c>
-      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
@@ -16620,32 +16616,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>126893291</v>
+        <v>126888458</v>
       </c>
       <c r="B160" t="n">
-        <v>79014</v>
+        <v>91487</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16655,10 +16651,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>865507</v>
+        <v>865502</v>
       </c>
       <c r="R160" t="n">
-        <v>7447151</v>
+        <v>7447310</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16705,12 +16701,12 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
@@ -16721,10 +16717,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>126887961</v>
+        <v>126893272</v>
       </c>
       <c r="B161" t="n">
-        <v>79632</v>
+        <v>92809</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16732,21 +16728,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16756,13 +16752,13 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>865602</v>
+        <v>865520</v>
       </c>
       <c r="R161" t="n">
-        <v>7447176</v>
+        <v>7447337</v>
       </c>
       <c r="S161" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -16806,22 +16802,26 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY161" t="inlineStr"/>
+          <t>Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>126893265</v>
+        <v>126892016</v>
       </c>
       <c r="B162" t="n">
-        <v>80146</v>
+        <v>91291</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16829,21 +16829,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16853,10 +16853,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>865530</v>
+        <v>865558</v>
       </c>
       <c r="R162" t="n">
-        <v>7447304</v>
+        <v>7447154</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16903,12 +16903,12 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
@@ -16919,45 +16919,48 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>126891919</v>
+        <v>126891924</v>
       </c>
       <c r="B163" t="n">
-        <v>80146</v>
+        <v>78772</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>865447</v>
+        <v>865562</v>
       </c>
       <c r="R163" t="n">
-        <v>7447440</v>
+        <v>7447150</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -16998,6 +17001,7 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
+      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
@@ -17020,32 +17024,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>126893272</v>
+        <v>126893265</v>
       </c>
       <c r="B164" t="n">
-        <v>92808</v>
+        <v>80146</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>2079</v>
+        <v>6462</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17055,10 +17059,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>865520</v>
+        <v>865530</v>
       </c>
       <c r="R164" t="n">
-        <v>7447337</v>
+        <v>7447304</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17121,32 +17125,32 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>126888458</v>
+        <v>126887961</v>
       </c>
       <c r="B165" t="n">
-        <v>91486</v>
+        <v>79632</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17156,13 +17160,13 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>865502</v>
+        <v>865602</v>
       </c>
       <c r="R165" t="n">
-        <v>7447310</v>
+        <v>7447176</v>
       </c>
       <c r="S165" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -17206,26 +17210,22 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
-        </is>
-      </c>
-      <c r="AY165" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>126892016</v>
+        <v>126891919</v>
       </c>
       <c r="B166" t="n">
-        <v>91290</v>
+        <v>80146</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17233,21 +17233,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17257,10 +17257,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>865558</v>
+        <v>865447</v>
       </c>
       <c r="R166" t="n">
-        <v>7447154</v>
+        <v>7447440</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17307,12 +17307,12 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
@@ -17323,10 +17323,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>126893031</v>
+        <v>126893284</v>
       </c>
       <c r="B167" t="n">
-        <v>77992</v>
+        <v>79014</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17334,21 +17334,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17358,10 +17358,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>865490</v>
+        <v>865543</v>
       </c>
       <c r="R167" t="n">
-        <v>7447338</v>
+        <v>7447053</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17408,12 +17408,12 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
@@ -17424,32 +17424,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>126892988</v>
+        <v>126893031</v>
       </c>
       <c r="B168" t="n">
-        <v>57479</v>
+        <v>77992</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>102976</v>
+        <v>6487</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17459,10 +17459,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>865530</v>
+        <v>865490</v>
       </c>
       <c r="R168" t="n">
-        <v>7447298</v>
+        <v>7447338</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17528,7 +17528,7 @@
         <v>126893021</v>
       </c>
       <c r="B169" t="n">
-        <v>91586</v>
+        <v>91587</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17629,7 +17629,7 @@
         <v>126893309</v>
       </c>
       <c r="B170" t="n">
-        <v>91586</v>
+        <v>91587</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17727,32 +17727,32 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>126893284</v>
+        <v>126892988</v>
       </c>
       <c r="B171" t="n">
-        <v>79014</v>
+        <v>57479</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>102976</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -17762,10 +17762,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>865543</v>
+        <v>865530</v>
       </c>
       <c r="R171" t="n">
-        <v>7447053</v>
+        <v>7447298</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17812,12 +17812,12 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
@@ -17828,32 +17828,32 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>126892188</v>
+        <v>126892986</v>
       </c>
       <c r="B172" t="n">
-        <v>91486</v>
+        <v>79603</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>1503</v>
+        <v>229821</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -17863,10 +17863,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>865520</v>
+        <v>865489</v>
       </c>
       <c r="R172" t="n">
-        <v>7447364</v>
+        <v>7447329</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -17913,12 +17913,12 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
@@ -17929,10 +17929,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>126893263</v>
+        <v>126892174</v>
       </c>
       <c r="B173" t="n">
-        <v>91325</v>
+        <v>92809</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17940,21 +17940,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1202</v>
+        <v>2079</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -17964,10 +17964,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>865485</v>
+        <v>865517</v>
       </c>
       <c r="R173" t="n">
-        <v>7447224</v>
+        <v>7447401</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18014,12 +18014,12 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
@@ -18030,32 +18030,32 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>126887986</v>
+        <v>126892997</v>
       </c>
       <c r="B174" t="n">
-        <v>91486</v>
+        <v>79038</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>1503</v>
+        <v>6434</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18065,13 +18065,13 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>865539</v>
+        <v>865545</v>
       </c>
       <c r="R174" t="n">
-        <v>7447206</v>
+        <v>7447323</v>
       </c>
       <c r="S174" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -18115,22 +18115,26 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY174" t="inlineStr"/>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>126892174</v>
+        <v>126893314</v>
       </c>
       <c r="B175" t="n">
-        <v>92808</v>
+        <v>78420</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18138,21 +18142,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>2079</v>
+        <v>6437</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18162,10 +18166,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>865517</v>
+        <v>865647</v>
       </c>
       <c r="R175" t="n">
-        <v>7447401</v>
+        <v>7447060</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18212,12 +18216,12 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
@@ -18228,10 +18232,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>126892986</v>
+        <v>126891913</v>
       </c>
       <c r="B176" t="n">
-        <v>79603</v>
+        <v>79632</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18239,21 +18243,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18263,10 +18267,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>865489</v>
+        <v>865557</v>
       </c>
       <c r="R176" t="n">
-        <v>7447329</v>
+        <v>7447153</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18313,12 +18317,12 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr">
@@ -18329,32 +18333,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>126892997</v>
+        <v>126893294</v>
       </c>
       <c r="B177" t="n">
-        <v>79038</v>
+        <v>79014</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18364,10 +18368,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>865545</v>
+        <v>865457</v>
       </c>
       <c r="R177" t="n">
-        <v>7447323</v>
+        <v>7447523</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18414,12 +18418,12 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
@@ -18430,32 +18434,32 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>126893294</v>
+        <v>126892188</v>
       </c>
       <c r="B178" t="n">
-        <v>79014</v>
+        <v>91487</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18465,10 +18469,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>865457</v>
+        <v>865520</v>
       </c>
       <c r="R178" t="n">
-        <v>7447523</v>
+        <v>7447364</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18515,12 +18519,12 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr">
@@ -18531,32 +18535,32 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>126893314</v>
+        <v>126887986</v>
       </c>
       <c r="B179" t="n">
-        <v>78420</v>
+        <v>91487</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6437</v>
+        <v>1503</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -18566,13 +18570,13 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>865647</v>
+        <v>865539</v>
       </c>
       <c r="R179" t="n">
-        <v>7447060</v>
+        <v>7447206</v>
       </c>
       <c r="S179" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -18616,26 +18620,22 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
-        </is>
-      </c>
-      <c r="AY179" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>126891913</v>
+        <v>126893263</v>
       </c>
       <c r="B180" t="n">
-        <v>79632</v>
+        <v>91326</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18643,21 +18643,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -18667,10 +18667,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>865557</v>
+        <v>865485</v>
       </c>
       <c r="R180" t="n">
-        <v>7447153</v>
+        <v>7447224</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18717,12 +18717,12 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">

--- a/artfynd/A 52625-2022 artfynd.xlsx
+++ b/artfynd/A 52625-2022 artfynd.xlsx
@@ -1584,48 +1584,59 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126887991</v>
+        <v>126892270</v>
       </c>
       <c r="B11" t="n">
-        <v>79014</v>
+        <v>91900</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>865422</v>
+        <v>865437</v>
       </c>
       <c r="R11" t="n">
-        <v>7447458</v>
+        <v>7447594</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1663,25 +1674,30 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Svea Nikula, Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126887992</v>
+        <v>126887991</v>
       </c>
       <c r="B12" t="n">
         <v>79014</v>
@@ -1716,10 +1732,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>865406</v>
+        <v>865422</v>
       </c>
       <c r="R12" t="n">
-        <v>7447461</v>
+        <v>7447458</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1778,32 +1794,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126892999</v>
+        <v>126887992</v>
       </c>
       <c r="B13" t="n">
-        <v>80145</v>
+        <v>79014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1813,13 +1829,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>865426</v>
+        <v>865406</v>
       </c>
       <c r="R13" t="n">
-        <v>7447493</v>
+        <v>7447461</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1863,26 +1879,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126892173</v>
+        <v>126892999</v>
       </c>
       <c r="B14" t="n">
-        <v>80146</v>
+        <v>80145</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1890,21 +1902,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1914,10 +1926,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>865379</v>
+        <v>865426</v>
       </c>
       <c r="R14" t="n">
-        <v>7447558</v>
+        <v>7447493</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1964,12 +1976,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -1980,56 +1992,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126892270</v>
+        <v>126892173</v>
       </c>
       <c r="B15" t="n">
-        <v>91900</v>
+        <v>80146</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>760</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>865437</v>
+        <v>865379</v>
       </c>
       <c r="R15" t="n">
-        <v>7447594</v>
+        <v>7447558</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2070,19 +2071,18 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Svea Nikula, Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -3605,32 +3605,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126892021</v>
+        <v>126893299</v>
       </c>
       <c r="B31" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3640,10 +3640,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>865441</v>
+        <v>865406</v>
       </c>
       <c r="R31" t="n">
-        <v>7447441</v>
+        <v>7447648</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3690,12 +3690,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -3706,32 +3706,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126893299</v>
+        <v>126892021</v>
       </c>
       <c r="B32" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3741,10 +3741,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>865406</v>
+        <v>865441</v>
       </c>
       <c r="R32" t="n">
-        <v>7447648</v>
+        <v>7447441</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3791,12 +3791,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
@@ -5213,27 +5213,27 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126893028</v>
+        <v>126887994</v>
       </c>
       <c r="B47" t="n">
-        <v>80152</v>
+        <v>79014</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5248,13 +5248,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>865390</v>
+        <v>865368</v>
       </c>
       <c r="R47" t="n">
-        <v>7447609</v>
+        <v>7447606</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5298,26 +5298,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126892020</v>
+        <v>126893028</v>
       </c>
       <c r="B48" t="n">
-        <v>80146</v>
+        <v>80152</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5325,21 +5321,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5349,10 +5345,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>865440</v>
+        <v>865390</v>
       </c>
       <c r="R48" t="n">
-        <v>7447393</v>
+        <v>7447609</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5399,12 +5395,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5415,32 +5411,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126887994</v>
+        <v>126892020</v>
       </c>
       <c r="B49" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5450,13 +5446,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>865368</v>
+        <v>865440</v>
       </c>
       <c r="R49" t="n">
-        <v>7447606</v>
+        <v>7447393</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5500,15 +5496,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr"/>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -7748,32 +7748,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126891911</v>
+        <v>126893012</v>
       </c>
       <c r="B72" t="n">
-        <v>91291</v>
+        <v>91487</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5447</v>
+        <v>1503</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7783,10 +7783,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>865557</v>
+        <v>865559</v>
       </c>
       <c r="R72" t="n">
-        <v>7447153</v>
+        <v>7447299</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7833,12 +7833,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -7849,32 +7849,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126893282</v>
+        <v>126892187</v>
       </c>
       <c r="B73" t="n">
-        <v>79014</v>
+        <v>91487</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7884,10 +7884,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>865611</v>
+        <v>865509</v>
       </c>
       <c r="R73" t="n">
-        <v>7446989</v>
+        <v>7447371</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7934,12 +7934,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -7950,32 +7950,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126891926</v>
+        <v>126891911</v>
       </c>
       <c r="B74" t="n">
-        <v>98443</v>
+        <v>91291</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7985,10 +7985,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>865541</v>
+        <v>865557</v>
       </c>
       <c r="R74" t="n">
-        <v>7447113</v>
+        <v>7447153</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8051,32 +8051,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126893012</v>
+        <v>126893282</v>
       </c>
       <c r="B75" t="n">
-        <v>91487</v>
+        <v>79014</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8086,10 +8086,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>865559</v>
+        <v>865611</v>
       </c>
       <c r="R75" t="n">
-        <v>7447299</v>
+        <v>7446989</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8136,12 +8136,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8152,10 +8152,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126892187</v>
+        <v>126891926</v>
       </c>
       <c r="B76" t="n">
-        <v>91487</v>
+        <v>98443</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8163,21 +8163,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1503</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8187,10 +8187,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>865509</v>
+        <v>865541</v>
       </c>
       <c r="R76" t="n">
-        <v>7447371</v>
+        <v>7447113</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8237,12 +8237,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8354,32 +8354,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126891929</v>
+        <v>126887974</v>
       </c>
       <c r="B78" t="n">
-        <v>79014</v>
+        <v>97327</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8389,13 +8389,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>865535</v>
+        <v>865641</v>
       </c>
       <c r="R78" t="n">
-        <v>7447142</v>
+        <v>7447070</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8439,26 +8439,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126888001</v>
+        <v>126891929</v>
       </c>
       <c r="B79" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8466,21 +8462,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8490,13 +8486,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>865527</v>
+        <v>865535</v>
       </c>
       <c r="R79" t="n">
-        <v>7447205</v>
+        <v>7447142</v>
       </c>
       <c r="S79" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8540,22 +8536,26 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY79" t="inlineStr"/>
+          <t>Amanda Rudelius</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126891930</v>
+        <v>126891914</v>
       </c>
       <c r="B80" t="n">
-        <v>8436</v>
+        <v>80146</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8563,43 +8563,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106554</v>
+        <v>6462</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>865561</v>
+        <v>865539</v>
       </c>
       <c r="R80" t="n">
-        <v>7447167</v>
+        <v>7447115</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8640,7 +8631,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8663,32 +8653,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126891914</v>
+        <v>126888001</v>
       </c>
       <c r="B81" t="n">
-        <v>80146</v>
+        <v>78681</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6462</v>
+        <v>353</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8698,13 +8688,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>865539</v>
+        <v>865527</v>
       </c>
       <c r="R81" t="n">
-        <v>7447115</v>
+        <v>7447205</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8748,26 +8738,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
-        </is>
-      </c>
-      <c r="AY81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126887974</v>
+        <v>126891930</v>
       </c>
       <c r="B82" t="n">
-        <v>97327</v>
+        <v>8436</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8775,37 +8761,46 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221941</v>
+        <v>106554</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>865641</v>
+        <v>865561</v>
       </c>
       <c r="R82" t="n">
-        <v>7447070</v>
+        <v>7447167</v>
       </c>
       <c r="S82" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8843,21 +8838,26 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr"/>
+          <t>Amanda Rudelius</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8962,32 +8962,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126892271</v>
+        <v>126892175</v>
       </c>
       <c r="B84" t="n">
-        <v>80152</v>
+        <v>92809</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6463</v>
+        <v>2079</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8997,10 +8997,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>865610</v>
+        <v>865509</v>
       </c>
       <c r="R84" t="n">
-        <v>7447145</v>
+        <v>7447217</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9047,12 +9047,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9063,10 +9063,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126888454</v>
+        <v>126887978</v>
       </c>
       <c r="B85" t="n">
-        <v>57817</v>
+        <v>92809</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9074,45 +9074,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>103021</v>
+        <v>2079</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>865481</v>
+        <v>865521</v>
       </c>
       <c r="R85" t="n">
-        <v>7447376</v>
+        <v>7447240</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9156,48 +9148,44 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
-        </is>
-      </c>
-      <c r="AY85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126892175</v>
+        <v>126892192</v>
       </c>
       <c r="B86" t="n">
-        <v>92809</v>
+        <v>92616</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9207,10 +9195,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>865509</v>
+        <v>865502</v>
       </c>
       <c r="R86" t="n">
-        <v>7447217</v>
+        <v>7447389</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9273,32 +9261,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126887978</v>
+        <v>126892271</v>
       </c>
       <c r="B87" t="n">
-        <v>92809</v>
+        <v>80152</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2079</v>
+        <v>6463</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9308,13 +9296,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>865521</v>
+        <v>865610</v>
       </c>
       <c r="R87" t="n">
-        <v>7447240</v>
+        <v>7447145</v>
       </c>
       <c r="S87" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9358,44 +9346,48 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY87" t="inlineStr"/>
+          <t>Svea Nikula</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126892192</v>
+        <v>126893277</v>
       </c>
       <c r="B88" t="n">
-        <v>92616</v>
+        <v>80989</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9405,10 +9397,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>865502</v>
+        <v>865647</v>
       </c>
       <c r="R88" t="n">
-        <v>7447389</v>
+        <v>7447060</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9455,12 +9447,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -9471,32 +9463,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126893277</v>
+        <v>126892185</v>
       </c>
       <c r="B89" t="n">
-        <v>80989</v>
+        <v>91487</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1049</v>
+        <v>1503</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9506,10 +9498,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>865647</v>
+        <v>865490</v>
       </c>
       <c r="R89" t="n">
-        <v>7447060</v>
+        <v>7447287</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9556,12 +9548,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -9572,7 +9564,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126892185</v>
+        <v>126888457</v>
       </c>
       <c r="B90" t="n">
         <v>91487</v>
@@ -9607,10 +9599,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>865490</v>
+        <v>865528</v>
       </c>
       <c r="R90" t="n">
-        <v>7447287</v>
+        <v>7447201</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9657,12 +9649,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -9673,45 +9665,53 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126888457</v>
+        <v>126888454</v>
       </c>
       <c r="B91" t="n">
-        <v>91487</v>
+        <v>57817</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1503</v>
+        <v>103021</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>865528</v>
+        <v>865481</v>
       </c>
       <c r="R91" t="n">
-        <v>7447201</v>
+        <v>7447376</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9976,10 +9976,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126887968</v>
+        <v>126892178</v>
       </c>
       <c r="B94" t="n">
-        <v>57817</v>
+        <v>92809</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9987,21 +9987,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103021</v>
+        <v>2079</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10011,13 +10011,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>865523</v>
+        <v>865509</v>
       </c>
       <c r="R94" t="n">
-        <v>7447217</v>
+        <v>7447375</v>
       </c>
       <c r="S94" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10061,44 +10061,48 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY94" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126892178</v>
+        <v>126893025</v>
       </c>
       <c r="B95" t="n">
-        <v>92809</v>
+        <v>92616</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10108,10 +10112,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>865509</v>
+        <v>865518</v>
       </c>
       <c r="R95" t="n">
-        <v>7447375</v>
+        <v>7447235</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10158,12 +10162,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -10174,10 +10178,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126893025</v>
+        <v>126892981</v>
       </c>
       <c r="B96" t="n">
-        <v>92616</v>
+        <v>91291</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10185,21 +10189,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10209,10 +10213,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>865518</v>
+        <v>865553</v>
       </c>
       <c r="R96" t="n">
-        <v>7447235</v>
+        <v>7447278</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10275,32 +10279,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126892981</v>
+        <v>126892267</v>
       </c>
       <c r="B97" t="n">
-        <v>91291</v>
+        <v>79014</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10310,10 +10314,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>865553</v>
+        <v>865516</v>
       </c>
       <c r="R97" t="n">
-        <v>7447278</v>
+        <v>7447351</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10360,12 +10364,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -10376,32 +10380,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126892267</v>
+        <v>126893281</v>
       </c>
       <c r="B98" t="n">
-        <v>79014</v>
+        <v>91487</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10411,10 +10415,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>865516</v>
+        <v>865513</v>
       </c>
       <c r="R98" t="n">
-        <v>7447351</v>
+        <v>7447339</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10461,12 +10465,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10477,10 +10481,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126893281</v>
+        <v>126893023</v>
       </c>
       <c r="B99" t="n">
-        <v>91487</v>
+        <v>91727</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10488,21 +10492,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1503</v>
+        <v>715</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Finporing</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Gloeoporus pannocinctus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Romell) J.Erikss.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10512,10 +10516,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>865513</v>
+        <v>865473</v>
       </c>
       <c r="R99" t="n">
-        <v>7447339</v>
+        <v>7447321</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10562,12 +10566,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -10578,32 +10582,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126893023</v>
+        <v>126888000</v>
       </c>
       <c r="B100" t="n">
-        <v>91727</v>
+        <v>78681</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>715</v>
+        <v>353</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Finporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Gloeoporus pannocinctus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Romell) J.Erikss.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10613,13 +10617,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>865473</v>
+        <v>865597</v>
       </c>
       <c r="R100" t="n">
-        <v>7447321</v>
+        <v>7447186</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10663,26 +10667,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
-        </is>
-      </c>
-      <c r="AY100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126888000</v>
+        <v>126887968</v>
       </c>
       <c r="B101" t="n">
-        <v>78681</v>
+        <v>57817</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10690,21 +10690,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10714,10 +10714,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>865597</v>
+        <v>865523</v>
       </c>
       <c r="R101" t="n">
-        <v>7447186</v>
+        <v>7447217</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -11475,32 +11475,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126887990</v>
+        <v>126887975</v>
       </c>
       <c r="B109" t="n">
-        <v>79014</v>
+        <v>97327</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11510,10 +11510,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>865447</v>
+        <v>865479</v>
       </c>
       <c r="R109" t="n">
-        <v>7447371</v>
+        <v>7447358</v>
       </c>
       <c r="S109" t="n">
         <v>25</v>
@@ -11572,32 +11572,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126892191</v>
+        <v>126887976</v>
       </c>
       <c r="B110" t="n">
-        <v>91587</v>
+        <v>97327</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>65</v>
+        <v>221941</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11607,13 +11607,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>865540</v>
+        <v>865452</v>
       </c>
       <c r="R110" t="n">
-        <v>7447366</v>
+        <v>7447334</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -11657,48 +11657,44 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126887987</v>
+        <v>126887977</v>
       </c>
       <c r="B111" t="n">
-        <v>91487</v>
+        <v>92809</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1503</v>
+        <v>2079</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11708,10 +11704,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>865510</v>
+        <v>865643</v>
       </c>
       <c r="R111" t="n">
-        <v>7447247</v>
+        <v>7447067</v>
       </c>
       <c r="S111" t="n">
         <v>25</v>
@@ -11770,10 +11766,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126893009</v>
+        <v>126887990</v>
       </c>
       <c r="B112" t="n">
-        <v>80989</v>
+        <v>79014</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11781,21 +11777,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11805,13 +11801,13 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>865553</v>
+        <v>865447</v>
       </c>
       <c r="R112" t="n">
-        <v>7447326</v>
+        <v>7447371</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -11855,69 +11851,57 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
-        </is>
-      </c>
-      <c r="AY112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126892263</v>
+        <v>126892191</v>
       </c>
       <c r="B113" t="n">
-        <v>56840</v>
+        <v>91587</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>102612</v>
+        <v>65</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>865544</v>
+        <v>865540</v>
       </c>
       <c r="R113" t="n">
-        <v>7447281</v>
+        <v>7447366</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11964,12 +11948,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -11980,32 +11964,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126887965</v>
+        <v>126887987</v>
       </c>
       <c r="B114" t="n">
-        <v>57479</v>
+        <v>91487</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>102976</v>
+        <v>1503</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12015,10 +11999,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>865583</v>
+        <v>865510</v>
       </c>
       <c r="R114" t="n">
-        <v>7447214</v>
+        <v>7447247</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -12077,32 +12061,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126887975</v>
+        <v>126893009</v>
       </c>
       <c r="B115" t="n">
-        <v>97327</v>
+        <v>80989</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>221941</v>
+        <v>1049</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12112,13 +12096,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>865479</v>
+        <v>865553</v>
       </c>
       <c r="R115" t="n">
-        <v>7447358</v>
+        <v>7447326</v>
       </c>
       <c r="S115" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12162,60 +12146,72 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY115" t="inlineStr"/>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126887976</v>
+        <v>126892263</v>
       </c>
       <c r="B116" t="n">
-        <v>97327</v>
+        <v>56840</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>221941</v>
+        <v>102612</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>865452</v>
+        <v>865544</v>
       </c>
       <c r="R116" t="n">
-        <v>7447334</v>
+        <v>7447281</v>
       </c>
       <c r="S116" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12259,44 +12255,48 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY116" t="inlineStr"/>
+          <t>Svea Nikula</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126892024</v>
+        <v>126887965</v>
       </c>
       <c r="B117" t="n">
-        <v>98443</v>
+        <v>57479</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220787</v>
+        <v>102976</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12306,13 +12306,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>865546</v>
+        <v>865583</v>
       </c>
       <c r="R117" t="n">
-        <v>7447138</v>
+        <v>7447214</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12356,26 +12356,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126887977</v>
+        <v>126892018</v>
       </c>
       <c r="B118" t="n">
-        <v>92809</v>
+        <v>57817</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12383,37 +12379,49 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>2079</v>
+        <v>103021</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>865643</v>
+        <v>865561</v>
       </c>
       <c r="R118" t="n">
-        <v>7447067</v>
+        <v>7447155</v>
       </c>
       <c r="S118" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -12457,69 +12465,61 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY118" t="inlineStr"/>
+          <t>Julia Frejd</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126892018</v>
+        <v>126891928</v>
       </c>
       <c r="B119" t="n">
-        <v>57817</v>
+        <v>98443</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>865561</v>
+        <v>865549</v>
       </c>
       <c r="R119" t="n">
-        <v>7447155</v>
+        <v>7447136</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12566,12 +12566,12 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
@@ -12582,7 +12582,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126891928</v>
+        <v>126892024</v>
       </c>
       <c r="B120" t="n">
         <v>98443</v>
@@ -12617,10 +12617,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>865549</v>
+        <v>865546</v>
       </c>
       <c r="R120" t="n">
-        <v>7447136</v>
+        <v>7447138</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12667,12 +12667,12 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
@@ -12683,32 +12683,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126887981</v>
+        <v>126893030</v>
       </c>
       <c r="B121" t="n">
-        <v>80153</v>
+        <v>77992</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6464</v>
+        <v>6487</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12718,13 +12718,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>865448</v>
+        <v>865545</v>
       </c>
       <c r="R121" t="n">
-        <v>7447345</v>
+        <v>7447323</v>
       </c>
       <c r="S121" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -12768,44 +12768,48 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY121" t="inlineStr"/>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126892170</v>
+        <v>126893260</v>
       </c>
       <c r="B122" t="n">
-        <v>57479</v>
+        <v>91248</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>102976</v>
+        <v>3242</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12815,10 +12819,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>865489</v>
+        <v>865498</v>
       </c>
       <c r="R122" t="n">
-        <v>7447377</v>
+        <v>7447359</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12853,11 +12857,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Förbiflygande</t>
-        </is>
-      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
@@ -12870,12 +12869,12 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
@@ -12886,10 +12885,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126893030</v>
+        <v>126893267</v>
       </c>
       <c r="B123" t="n">
-        <v>77992</v>
+        <v>92809</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12897,21 +12896,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6487</v>
+        <v>2079</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12921,10 +12920,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>865545</v>
+        <v>865648</v>
       </c>
       <c r="R123" t="n">
-        <v>7447323</v>
+        <v>7447056</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12971,12 +12970,12 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
@@ -12987,32 +12986,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126893260</v>
+        <v>126893262</v>
       </c>
       <c r="B124" t="n">
-        <v>91248</v>
+        <v>91291</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>3242</v>
+        <v>5447</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13022,10 +13021,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>865498</v>
+        <v>865522</v>
       </c>
       <c r="R124" t="n">
-        <v>7447359</v>
+        <v>7447308</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13088,32 +13087,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126893267</v>
+        <v>126893308</v>
       </c>
       <c r="B125" t="n">
-        <v>92809</v>
+        <v>91587</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>2079</v>
+        <v>65</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13123,10 +13122,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>865648</v>
+        <v>865659</v>
       </c>
       <c r="R125" t="n">
-        <v>7447056</v>
+        <v>7447048</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13189,10 +13188,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126893262</v>
+        <v>126887981</v>
       </c>
       <c r="B126" t="n">
-        <v>91291</v>
+        <v>80153</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13200,21 +13199,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>5447</v>
+        <v>6464</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13224,13 +13223,13 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>865522</v>
+        <v>865448</v>
       </c>
       <c r="R126" t="n">
-        <v>7447308</v>
+        <v>7447345</v>
       </c>
       <c r="S126" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13274,48 +13273,44 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
-        </is>
-      </c>
-      <c r="AY126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126893308</v>
+        <v>126892170</v>
       </c>
       <c r="B127" t="n">
-        <v>91587</v>
+        <v>57479</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>65</v>
+        <v>102976</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13325,10 +13320,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>865659</v>
+        <v>865489</v>
       </c>
       <c r="R127" t="n">
-        <v>7447048</v>
+        <v>7447377</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13363,6 +13358,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Förbiflygande</t>
+        </is>
+      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
@@ -13375,12 +13375,12 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
@@ -13989,32 +13989,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126892256</v>
+        <v>126892189</v>
       </c>
       <c r="B134" t="n">
-        <v>91291</v>
+        <v>79014</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14024,10 +14024,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>865491</v>
+        <v>865551</v>
       </c>
       <c r="R134" t="n">
-        <v>7447326</v>
+        <v>7447310</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14074,12 +14074,12 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
@@ -14090,10 +14090,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126892176</v>
+        <v>126893290</v>
       </c>
       <c r="B135" t="n">
-        <v>92809</v>
+        <v>79014</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14101,21 +14101,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14125,10 +14125,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>865490</v>
+        <v>865505</v>
       </c>
       <c r="R135" t="n">
-        <v>7447287</v>
+        <v>7447150</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14175,12 +14175,12 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
@@ -14191,32 +14191,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126892189</v>
+        <v>126892256</v>
       </c>
       <c r="B136" t="n">
-        <v>79014</v>
+        <v>91291</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14226,10 +14226,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>865551</v>
+        <v>865491</v>
       </c>
       <c r="R136" t="n">
-        <v>7447310</v>
+        <v>7447326</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14276,12 +14276,12 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
@@ -14292,10 +14292,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126893290</v>
+        <v>126892176</v>
       </c>
       <c r="B137" t="n">
-        <v>79014</v>
+        <v>92809</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14303,21 +14303,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14327,10 +14327,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>865505</v>
+        <v>865490</v>
       </c>
       <c r="R137" t="n">
-        <v>7447150</v>
+        <v>7447287</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14377,12 +14377,12 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
@@ -16014,10 +16014,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>126892974</v>
+        <v>126893011</v>
       </c>
       <c r="B154" t="n">
-        <v>91248</v>
+        <v>80989</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16025,21 +16025,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>3242</v>
+        <v>1049</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16049,10 +16049,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>865494</v>
+        <v>865498</v>
       </c>
       <c r="R154" t="n">
-        <v>7447322</v>
+        <v>7447379</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16115,32 +16115,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126892255</v>
+        <v>126892272</v>
       </c>
       <c r="B155" t="n">
-        <v>91291</v>
+        <v>77992</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>5447</v>
+        <v>6487</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16150,10 +16150,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>865462</v>
+        <v>865528</v>
       </c>
       <c r="R155" t="n">
-        <v>7447413</v>
+        <v>7447192</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16216,10 +16216,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>126887979</v>
+        <v>126892974</v>
       </c>
       <c r="B156" t="n">
-        <v>92809</v>
+        <v>91248</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16227,21 +16227,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>2079</v>
+        <v>3242</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16251,13 +16251,13 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>865510</v>
+        <v>865494</v>
       </c>
       <c r="R156" t="n">
-        <v>7447251</v>
+        <v>7447322</v>
       </c>
       <c r="S156" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -16301,44 +16301,48 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY156" t="inlineStr"/>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126892272</v>
+        <v>126892255</v>
       </c>
       <c r="B157" t="n">
-        <v>77992</v>
+        <v>91291</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6487</v>
+        <v>5447</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16348,10 +16352,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>865528</v>
+        <v>865462</v>
       </c>
       <c r="R157" t="n">
-        <v>7447192</v>
+        <v>7447413</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16414,10 +16418,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>126893011</v>
+        <v>126887979</v>
       </c>
       <c r="B158" t="n">
-        <v>80989</v>
+        <v>92809</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16425,21 +16429,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>1049</v>
+        <v>2079</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16449,13 +16453,13 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>865498</v>
+        <v>865510</v>
       </c>
       <c r="R158" t="n">
-        <v>7447379</v>
+        <v>7447251</v>
       </c>
       <c r="S158" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -16499,19 +16503,15 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
-        </is>
-      </c>
-      <c r="AY158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -17323,10 +17323,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>126893284</v>
+        <v>126893031</v>
       </c>
       <c r="B167" t="n">
-        <v>79014</v>
+        <v>77992</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17334,21 +17334,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17358,10 +17358,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>865543</v>
+        <v>865490</v>
       </c>
       <c r="R167" t="n">
-        <v>7447053</v>
+        <v>7447338</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17408,12 +17408,12 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
@@ -17424,10 +17424,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>126893031</v>
+        <v>126893284</v>
       </c>
       <c r="B168" t="n">
-        <v>77992</v>
+        <v>79014</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17435,21 +17435,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17459,10 +17459,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>865490</v>
+        <v>865543</v>
       </c>
       <c r="R168" t="n">
-        <v>7447338</v>
+        <v>7447053</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17509,12 +17509,12 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
@@ -17828,32 +17828,32 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>126892986</v>
+        <v>126892997</v>
       </c>
       <c r="B172" t="n">
-        <v>79603</v>
+        <v>79038</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>229821</v>
+        <v>6434</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -17863,10 +17863,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>865489</v>
+        <v>865545</v>
       </c>
       <c r="R172" t="n">
-        <v>7447329</v>
+        <v>7447323</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -17929,10 +17929,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>126892174</v>
+        <v>126893314</v>
       </c>
       <c r="B173" t="n">
-        <v>92809</v>
+        <v>78420</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17940,21 +17940,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>2079</v>
+        <v>6437</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -17964,10 +17964,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>865517</v>
+        <v>865647</v>
       </c>
       <c r="R173" t="n">
-        <v>7447401</v>
+        <v>7447060</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18014,12 +18014,12 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
@@ -18030,32 +18030,32 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>126892997</v>
+        <v>126891913</v>
       </c>
       <c r="B174" t="n">
-        <v>79038</v>
+        <v>79632</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18065,10 +18065,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>865545</v>
+        <v>865557</v>
       </c>
       <c r="R174" t="n">
-        <v>7447323</v>
+        <v>7447153</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18115,12 +18115,12 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr">
@@ -18131,10 +18131,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>126893314</v>
+        <v>126892986</v>
       </c>
       <c r="B175" t="n">
-        <v>78420</v>
+        <v>79603</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18142,21 +18142,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18166,10 +18166,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>865647</v>
+        <v>865489</v>
       </c>
       <c r="R175" t="n">
-        <v>7447060</v>
+        <v>7447329</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18216,12 +18216,12 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
@@ -18232,10 +18232,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>126891913</v>
+        <v>126892174</v>
       </c>
       <c r="B176" t="n">
-        <v>79632</v>
+        <v>92809</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18243,21 +18243,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18267,10 +18267,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>865557</v>
+        <v>865517</v>
       </c>
       <c r="R176" t="n">
-        <v>7447153</v>
+        <v>7447401</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18317,12 +18317,12 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr">

--- a/artfynd/A 52625-2022 artfynd.xlsx
+++ b/artfynd/A 52625-2022 artfynd.xlsx
@@ -1180,32 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126893275</v>
+        <v>126893295</v>
       </c>
       <c r="B7" t="n">
-        <v>80153</v>
+        <v>79014</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>865427</v>
+        <v>865429</v>
       </c>
       <c r="R7" t="n">
-        <v>7447587</v>
+        <v>7447550</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,32 +1281,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126892019</v>
+        <v>126893300</v>
       </c>
       <c r="B8" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>865429</v>
+        <v>865378</v>
       </c>
       <c r="R8" t="n">
-        <v>7447523</v>
+        <v>7447665</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1366,12 +1366,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1382,32 +1382,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126893295</v>
+        <v>126893275</v>
       </c>
       <c r="B9" t="n">
-        <v>79014</v>
+        <v>80153</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>865429</v>
+        <v>865427</v>
       </c>
       <c r="R9" t="n">
-        <v>7447550</v>
+        <v>7447587</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1483,32 +1483,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126893300</v>
+        <v>126892019</v>
       </c>
       <c r="B10" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>865378</v>
+        <v>865429</v>
       </c>
       <c r="R10" t="n">
-        <v>7447665</v>
+        <v>7447523</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1568,12 +1568,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -2296,7 +2296,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126893301</v>
+        <v>126893017</v>
       </c>
       <c r="B18" t="n">
         <v>79014</v>
@@ -2331,10 +2331,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>865382</v>
+        <v>865409</v>
       </c>
       <c r="R18" t="n">
-        <v>7447699</v>
+        <v>7447573</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2381,12 +2381,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2397,7 +2397,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126893017</v>
+        <v>126893301</v>
       </c>
       <c r="B19" t="n">
         <v>79014</v>
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>865409</v>
+        <v>865382</v>
       </c>
       <c r="R19" t="n">
-        <v>7447573</v>
+        <v>7447699</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2482,12 +2482,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -3807,32 +3807,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126887969</v>
+        <v>126892259</v>
       </c>
       <c r="B33" t="n">
-        <v>57817</v>
+        <v>98464</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>865406</v>
+        <v>865411</v>
       </c>
       <c r="R33" t="n">
-        <v>7447461</v>
+        <v>7447533</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3892,44 +3892,48 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
+          <t>Svea Nikula</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126892262</v>
+        <v>126887969</v>
       </c>
       <c r="B34" t="n">
-        <v>80153</v>
+        <v>57817</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3939,13 +3943,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>865404</v>
+        <v>865406</v>
       </c>
       <c r="R34" t="n">
-        <v>7447633</v>
+        <v>7447461</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3989,48 +3993,44 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126893306</v>
+        <v>126892262</v>
       </c>
       <c r="B35" t="n">
-        <v>82855</v>
+        <v>80153</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4040,10 +4040,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>865378</v>
+        <v>865404</v>
       </c>
       <c r="R35" t="n">
-        <v>7447665</v>
+        <v>7447633</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4090,12 +4090,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4106,32 +4106,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126892259</v>
+        <v>126893306</v>
       </c>
       <c r="B36" t="n">
-        <v>98464</v>
+        <v>82855</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221952</v>
+        <v>1312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4141,10 +4141,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>865411</v>
+        <v>865378</v>
       </c>
       <c r="R36" t="n">
-        <v>7447533</v>
+        <v>7447665</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4191,12 +4191,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4506,32 +4506,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126892989</v>
+        <v>126893266</v>
       </c>
       <c r="B40" t="n">
-        <v>57817</v>
+        <v>80146</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4541,10 +4541,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>865425</v>
+        <v>865423</v>
       </c>
       <c r="R40" t="n">
-        <v>7447474</v>
+        <v>7447628</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4591,12 +4591,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4607,32 +4607,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126893266</v>
+        <v>126892989</v>
       </c>
       <c r="B41" t="n">
-        <v>80146</v>
+        <v>57817</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4642,10 +4642,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>865423</v>
+        <v>865425</v>
       </c>
       <c r="R41" t="n">
-        <v>7447628</v>
+        <v>7447474</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4692,12 +4692,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4708,32 +4708,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126893022</v>
+        <v>126893297</v>
       </c>
       <c r="B42" t="n">
-        <v>98360</v>
+        <v>79014</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4743,10 +4743,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>865404</v>
+        <v>865416</v>
       </c>
       <c r="R42" t="n">
-        <v>7447471</v>
+        <v>7447594</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4793,12 +4793,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -4809,32 +4809,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126893297</v>
+        <v>126893022</v>
       </c>
       <c r="B43" t="n">
-        <v>79014</v>
+        <v>98360</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4844,10 +4844,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>865416</v>
+        <v>865404</v>
       </c>
       <c r="R43" t="n">
-        <v>7447594</v>
+        <v>7447471</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4894,12 +4894,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -4910,32 +4910,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126893273</v>
+        <v>126892268</v>
       </c>
       <c r="B44" t="n">
-        <v>80153</v>
+        <v>79014</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4945,10 +4945,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>865406</v>
+        <v>865411</v>
       </c>
       <c r="R44" t="n">
-        <v>7447648</v>
+        <v>7447532</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4995,12 +4995,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5011,32 +5011,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126892268</v>
+        <v>126893273</v>
       </c>
       <c r="B45" t="n">
-        <v>79014</v>
+        <v>80153</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5046,10 +5046,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>865411</v>
+        <v>865406</v>
       </c>
       <c r="R45" t="n">
-        <v>7447532</v>
+        <v>7447648</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5096,12 +5096,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5213,27 +5213,27 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126887994</v>
+        <v>126893028</v>
       </c>
       <c r="B47" t="n">
-        <v>79014</v>
+        <v>80152</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5248,13 +5248,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>865368</v>
+        <v>865390</v>
       </c>
       <c r="R47" t="n">
-        <v>7447606</v>
+        <v>7447609</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5298,22 +5298,26 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126893028</v>
+        <v>126892020</v>
       </c>
       <c r="B48" t="n">
-        <v>80152</v>
+        <v>80146</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5321,21 +5325,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5345,10 +5349,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>865390</v>
+        <v>865440</v>
       </c>
       <c r="R48" t="n">
-        <v>7447609</v>
+        <v>7447393</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5395,12 +5399,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5411,32 +5415,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126892020</v>
+        <v>126887994</v>
       </c>
       <c r="B49" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5446,13 +5450,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>865440</v>
+        <v>865368</v>
       </c>
       <c r="R49" t="n">
-        <v>7447393</v>
+        <v>7447606</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5496,48 +5500,44 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126887983</v>
+        <v>126892254</v>
       </c>
       <c r="B50" t="n">
-        <v>80153</v>
+        <v>75138</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5547,13 +5547,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>865378</v>
+        <v>865423</v>
       </c>
       <c r="R50" t="n">
-        <v>7447577</v>
+        <v>7447468</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5597,44 +5597,48 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr"/>
+          <t>Svea Nikula</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126892254</v>
+        <v>126887983</v>
       </c>
       <c r="B51" t="n">
-        <v>75138</v>
+        <v>80153</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6440</v>
+        <v>6464</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5644,13 +5648,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>865423</v>
+        <v>865378</v>
       </c>
       <c r="R51" t="n">
-        <v>7447468</v>
+        <v>7447577</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5694,19 +5698,15 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5816,10 +5816,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126892026</v>
+        <v>126892985</v>
       </c>
       <c r="B53" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5827,21 +5827,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5851,10 +5851,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>865538</v>
+        <v>865491</v>
       </c>
       <c r="R53" t="n">
-        <v>7447072</v>
+        <v>7447332</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5901,12 +5901,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -5917,10 +5917,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126892029</v>
+        <v>126892273</v>
       </c>
       <c r="B54" t="n">
-        <v>79014</v>
+        <v>78420</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5928,21 +5928,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5952,10 +5952,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>865448</v>
+        <v>865528</v>
       </c>
       <c r="R54" t="n">
-        <v>7447418</v>
+        <v>7447193</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6002,12 +6002,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6018,32 +6018,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126892273</v>
+        <v>126891916</v>
       </c>
       <c r="B55" t="n">
-        <v>78420</v>
+        <v>80146</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6437</v>
+        <v>6462</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6053,10 +6053,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>865528</v>
+        <v>865546</v>
       </c>
       <c r="R55" t="n">
-        <v>7447193</v>
+        <v>7447133</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6103,12 +6103,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6119,10 +6119,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126892985</v>
+        <v>126893008</v>
       </c>
       <c r="B56" t="n">
-        <v>79632</v>
+        <v>80989</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6130,21 +6130,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>865491</v>
+        <v>865545</v>
       </c>
       <c r="R56" t="n">
-        <v>7447332</v>
+        <v>7447322</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6220,32 +6220,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126891916</v>
+        <v>126893280</v>
       </c>
       <c r="B57" t="n">
-        <v>80146</v>
+        <v>91487</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6462</v>
+        <v>1503</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6255,10 +6255,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>865546</v>
+        <v>865490</v>
       </c>
       <c r="R57" t="n">
-        <v>7447133</v>
+        <v>7447213</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6305,12 +6305,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6321,32 +6321,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126893280</v>
+        <v>126892026</v>
       </c>
       <c r="B58" t="n">
-        <v>91487</v>
+        <v>79014</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6356,10 +6356,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>865490</v>
+        <v>865538</v>
       </c>
       <c r="R58" t="n">
-        <v>7447213</v>
+        <v>7447072</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6406,12 +6406,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6422,10 +6422,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126893008</v>
+        <v>126892029</v>
       </c>
       <c r="B59" t="n">
-        <v>80989</v>
+        <v>79014</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6433,21 +6433,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6457,10 +6457,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>865545</v>
+        <v>865448</v>
       </c>
       <c r="R59" t="n">
-        <v>7447322</v>
+        <v>7447418</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6507,12 +6507,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6624,32 +6624,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126892177</v>
+        <v>126892982</v>
       </c>
       <c r="B61" t="n">
-        <v>92809</v>
+        <v>91291</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2079</v>
+        <v>5447</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6659,10 +6659,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>865522</v>
+        <v>865526</v>
       </c>
       <c r="R61" t="n">
-        <v>7447338</v>
+        <v>7447273</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6709,12 +6709,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6725,10 +6725,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126892982</v>
+        <v>126891915</v>
       </c>
       <c r="B62" t="n">
-        <v>91291</v>
+        <v>80146</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6736,21 +6736,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6760,10 +6760,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>865526</v>
+        <v>865551</v>
       </c>
       <c r="R62" t="n">
-        <v>7447273</v>
+        <v>7447126</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6810,12 +6810,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -6826,32 +6826,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126891915</v>
+        <v>126892177</v>
       </c>
       <c r="B63" t="n">
-        <v>80146</v>
+        <v>92809</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6462</v>
+        <v>2079</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6861,10 +6861,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>865551</v>
+        <v>865522</v>
       </c>
       <c r="R63" t="n">
-        <v>7447126</v>
+        <v>7447338</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6911,12 +6911,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7024,10 +7024,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126893312</v>
+        <v>126893010</v>
       </c>
       <c r="B65" t="n">
-        <v>77992</v>
+        <v>80989</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7035,21 +7035,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6487</v>
+        <v>1049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7059,10 +7059,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>865598</v>
+        <v>865490</v>
       </c>
       <c r="R65" t="n">
-        <v>7447181</v>
+        <v>7447332</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7109,12 +7109,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7125,32 +7125,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126892998</v>
+        <v>126888002</v>
       </c>
       <c r="B66" t="n">
-        <v>80145</v>
+        <v>78681</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6461</v>
+        <v>353</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7160,13 +7160,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>865477</v>
+        <v>865512</v>
       </c>
       <c r="R66" t="n">
-        <v>7447327</v>
+        <v>7447340</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7210,48 +7210,44 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126891925</v>
+        <v>126893000</v>
       </c>
       <c r="B67" t="n">
-        <v>98443</v>
+        <v>92809</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>2079</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7261,10 +7257,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>865527</v>
+        <v>865559</v>
       </c>
       <c r="R67" t="n">
-        <v>7447333</v>
+        <v>7447299</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7311,12 +7307,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7327,10 +7323,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126893000</v>
+        <v>126893312</v>
       </c>
       <c r="B68" t="n">
-        <v>92809</v>
+        <v>77992</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7338,21 +7334,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2079</v>
+        <v>6487</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7362,10 +7358,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>865559</v>
+        <v>865598</v>
       </c>
       <c r="R68" t="n">
-        <v>7447299</v>
+        <v>7447181</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7412,12 +7408,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7428,32 +7424,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126888002</v>
+        <v>126892998</v>
       </c>
       <c r="B69" t="n">
-        <v>78681</v>
+        <v>80145</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>353</v>
+        <v>6461</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7463,13 +7459,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>865512</v>
+        <v>865477</v>
       </c>
       <c r="R69" t="n">
-        <v>7447340</v>
+        <v>7447327</v>
       </c>
       <c r="S69" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7513,44 +7509,48 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr"/>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126893010</v>
+        <v>126891925</v>
       </c>
       <c r="B70" t="n">
-        <v>80989</v>
+        <v>98443</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1049</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7560,10 +7560,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>865490</v>
+        <v>865527</v>
       </c>
       <c r="R70" t="n">
-        <v>7447332</v>
+        <v>7447333</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7610,12 +7610,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7748,7 +7748,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126893012</v>
+        <v>126892187</v>
       </c>
       <c r="B72" t="n">
         <v>91487</v>
@@ -7783,10 +7783,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>865559</v>
+        <v>865509</v>
       </c>
       <c r="R72" t="n">
-        <v>7447299</v>
+        <v>7447371</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7833,12 +7833,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -7849,7 +7849,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126892187</v>
+        <v>126893012</v>
       </c>
       <c r="B73" t="n">
         <v>91487</v>
@@ -7884,10 +7884,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>865509</v>
+        <v>865559</v>
       </c>
       <c r="R73" t="n">
-        <v>7447371</v>
+        <v>7447299</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7934,12 +7934,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -7950,32 +7950,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126891911</v>
+        <v>126893282</v>
       </c>
       <c r="B74" t="n">
-        <v>91291</v>
+        <v>79014</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7985,10 +7985,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>865557</v>
+        <v>865611</v>
       </c>
       <c r="R74" t="n">
-        <v>7447153</v>
+        <v>7446989</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8035,12 +8035,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8051,32 +8051,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126893282</v>
+        <v>126891911</v>
       </c>
       <c r="B75" t="n">
-        <v>79014</v>
+        <v>91291</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8086,10 +8086,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>865611</v>
+        <v>865557</v>
       </c>
       <c r="R75" t="n">
-        <v>7446989</v>
+        <v>7447153</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8136,12 +8136,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8253,10 +8253,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126893270</v>
+        <v>126888001</v>
       </c>
       <c r="B77" t="n">
-        <v>92809</v>
+        <v>78681</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8264,21 +8264,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8288,13 +8288,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>865491</v>
+        <v>865527</v>
       </c>
       <c r="R77" t="n">
-        <v>7447267</v>
+        <v>7447205</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8338,48 +8338,44 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126887974</v>
+        <v>126891929</v>
       </c>
       <c r="B78" t="n">
-        <v>97327</v>
+        <v>79014</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8389,13 +8385,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>865641</v>
+        <v>865535</v>
       </c>
       <c r="R78" t="n">
-        <v>7447070</v>
+        <v>7447142</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8439,22 +8435,26 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr"/>
+          <t>Amanda Rudelius</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126891929</v>
+        <v>126893270</v>
       </c>
       <c r="B79" t="n">
-        <v>79014</v>
+        <v>92809</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8462,21 +8462,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8486,10 +8486,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>865535</v>
+        <v>865491</v>
       </c>
       <c r="R79" t="n">
-        <v>7447142</v>
+        <v>7447267</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8536,12 +8536,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8653,48 +8653,57 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126888001</v>
+        <v>126891930</v>
       </c>
       <c r="B81" t="n">
-        <v>78681</v>
+        <v>8436</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>353</v>
+        <v>106554</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>865527</v>
+        <v>865561</v>
       </c>
       <c r="R81" t="n">
-        <v>7447205</v>
+        <v>7447167</v>
       </c>
       <c r="S81" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8732,28 +8741,33 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY81" t="inlineStr"/>
+          <t>Amanda Rudelius</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126891930</v>
+        <v>126887974</v>
       </c>
       <c r="B82" t="n">
-        <v>8436</v>
+        <v>97327</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8761,46 +8775,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106554</v>
+        <v>221941</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>865561</v>
+        <v>865641</v>
       </c>
       <c r="R82" t="n">
-        <v>7447167</v>
+        <v>7447070</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8838,55 +8843,50 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126893003</v>
+        <v>126892175</v>
       </c>
       <c r="B83" t="n">
-        <v>80153</v>
+        <v>92809</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6464</v>
+        <v>2079</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8896,10 +8896,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>865532</v>
+        <v>865509</v>
       </c>
       <c r="R83" t="n">
-        <v>7447307</v>
+        <v>7447217</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8946,12 +8946,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -8962,7 +8962,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126892175</v>
+        <v>126887978</v>
       </c>
       <c r="B84" t="n">
         <v>92809</v>
@@ -8997,13 +8997,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>865509</v>
+        <v>865521</v>
       </c>
       <c r="R84" t="n">
-        <v>7447217</v>
+        <v>7447240</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9047,48 +9047,44 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126887978</v>
+        <v>126888457</v>
       </c>
       <c r="B85" t="n">
-        <v>92809</v>
+        <v>91487</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2079</v>
+        <v>1503</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9098,13 +9094,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>865521</v>
+        <v>865528</v>
       </c>
       <c r="R85" t="n">
-        <v>7447240</v>
+        <v>7447201</v>
       </c>
       <c r="S85" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9148,44 +9144,48 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY85" t="inlineStr"/>
+          <t>Alva Dahlqvist Cederstrand</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126892192</v>
+        <v>126892185</v>
       </c>
       <c r="B86" t="n">
-        <v>92616</v>
+        <v>91487</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9195,10 +9195,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>865502</v>
+        <v>865490</v>
       </c>
       <c r="R86" t="n">
-        <v>7447389</v>
+        <v>7447287</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9261,10 +9261,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126892271</v>
+        <v>126892192</v>
       </c>
       <c r="B87" t="n">
-        <v>80152</v>
+        <v>92616</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9272,21 +9272,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6463</v>
+        <v>4364</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9296,10 +9296,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>865610</v>
+        <v>865502</v>
       </c>
       <c r="R87" t="n">
-        <v>7447145</v>
+        <v>7447389</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9346,12 +9346,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -9362,32 +9362,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126893277</v>
+        <v>126893003</v>
       </c>
       <c r="B88" t="n">
-        <v>80989</v>
+        <v>80153</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1049</v>
+        <v>6464</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9397,10 +9397,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>865647</v>
+        <v>865532</v>
       </c>
       <c r="R88" t="n">
-        <v>7447060</v>
+        <v>7447307</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9447,12 +9447,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -9463,32 +9463,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126892185</v>
+        <v>126892271</v>
       </c>
       <c r="B89" t="n">
-        <v>91487</v>
+        <v>80152</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1503</v>
+        <v>6463</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9498,10 +9498,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>865490</v>
+        <v>865610</v>
       </c>
       <c r="R89" t="n">
-        <v>7447287</v>
+        <v>7447145</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9548,12 +9548,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -9564,32 +9564,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126888457</v>
+        <v>126893277</v>
       </c>
       <c r="B90" t="n">
-        <v>91487</v>
+        <v>80989</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1503</v>
+        <v>1049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9599,10 +9599,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>865528</v>
+        <v>865647</v>
       </c>
       <c r="R90" t="n">
-        <v>7447201</v>
+        <v>7447060</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9649,12 +9649,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -9976,32 +9976,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126892178</v>
+        <v>126893025</v>
       </c>
       <c r="B94" t="n">
-        <v>92809</v>
+        <v>92616</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10011,10 +10011,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>865509</v>
+        <v>865518</v>
       </c>
       <c r="R94" t="n">
-        <v>7447375</v>
+        <v>7447235</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10061,12 +10061,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -10077,10 +10077,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126893025</v>
+        <v>126892981</v>
       </c>
       <c r="B95" t="n">
-        <v>92616</v>
+        <v>91291</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10088,21 +10088,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10112,10 +10112,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>865518</v>
+        <v>865553</v>
       </c>
       <c r="R95" t="n">
-        <v>7447235</v>
+        <v>7447278</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10178,32 +10178,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126892981</v>
+        <v>126892267</v>
       </c>
       <c r="B96" t="n">
-        <v>91291</v>
+        <v>79014</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10213,10 +10213,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>865553</v>
+        <v>865516</v>
       </c>
       <c r="R96" t="n">
-        <v>7447278</v>
+        <v>7447351</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10263,12 +10263,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10279,10 +10279,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126892267</v>
+        <v>126887968</v>
       </c>
       <c r="B97" t="n">
-        <v>79014</v>
+        <v>57817</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10290,21 +10290,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10314,13 +10314,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>865516</v>
+        <v>865523</v>
       </c>
       <c r="R97" t="n">
-        <v>7447351</v>
+        <v>7447217</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10364,26 +10364,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
-        </is>
-      </c>
-      <c r="AY97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126893281</v>
+        <v>126893023</v>
       </c>
       <c r="B98" t="n">
-        <v>91487</v>
+        <v>91727</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10391,21 +10387,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1503</v>
+        <v>715</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Finporing</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Gloeoporus pannocinctus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Romell) J.Erikss.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10415,10 +10411,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>865513</v>
+        <v>865473</v>
       </c>
       <c r="R98" t="n">
-        <v>7447339</v>
+        <v>7447321</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10465,12 +10461,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10481,32 +10477,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126893023</v>
+        <v>126888000</v>
       </c>
       <c r="B99" t="n">
-        <v>91727</v>
+        <v>78681</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>715</v>
+        <v>353</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Finporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Gloeoporus pannocinctus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Romell) J.Erikss.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10516,13 +10512,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>865473</v>
+        <v>865597</v>
       </c>
       <c r="R99" t="n">
-        <v>7447321</v>
+        <v>7447186</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10566,26 +10562,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
-        </is>
-      </c>
-      <c r="AY99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126888000</v>
+        <v>126892178</v>
       </c>
       <c r="B100" t="n">
-        <v>78681</v>
+        <v>92809</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10593,21 +10585,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10617,13 +10609,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>865597</v>
+        <v>865509</v>
       </c>
       <c r="R100" t="n">
-        <v>7447186</v>
+        <v>7447375</v>
       </c>
       <c r="S100" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10667,44 +10659,48 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY100" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126887968</v>
+        <v>126893281</v>
       </c>
       <c r="B101" t="n">
-        <v>57817</v>
+        <v>91487</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>103021</v>
+        <v>1503</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10714,13 +10710,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>865523</v>
+        <v>865513</v>
       </c>
       <c r="R101" t="n">
-        <v>7447217</v>
+        <v>7447339</v>
       </c>
       <c r="S101" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10764,15 +10760,19 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY101" t="inlineStr"/>
+          <t>Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10873,32 +10873,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126893033</v>
+        <v>126892186</v>
       </c>
       <c r="B103" t="n">
-        <v>78420</v>
+        <v>91487</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6437</v>
+        <v>1503</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10908,10 +10908,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>865500</v>
+        <v>865491</v>
       </c>
       <c r="R103" t="n">
-        <v>7447283</v>
+        <v>7447290</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10958,12 +10958,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -11075,32 +11075,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126892186</v>
+        <v>126893033</v>
       </c>
       <c r="B105" t="n">
-        <v>91487</v>
+        <v>78420</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1503</v>
+        <v>6437</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11110,10 +11110,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>865491</v>
+        <v>865500</v>
       </c>
       <c r="R105" t="n">
-        <v>7447290</v>
+        <v>7447283</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11160,12 +11160,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
@@ -11475,32 +11475,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126887975</v>
+        <v>126892191</v>
       </c>
       <c r="B109" t="n">
-        <v>97327</v>
+        <v>91587</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>221941</v>
+        <v>65</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11510,13 +11510,13 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>865479</v>
+        <v>865540</v>
       </c>
       <c r="R109" t="n">
-        <v>7447358</v>
+        <v>7447366</v>
       </c>
       <c r="S109" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -11560,44 +11560,48 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY109" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126887976</v>
+        <v>126893009</v>
       </c>
       <c r="B110" t="n">
-        <v>97327</v>
+        <v>80989</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>221941</v>
+        <v>1049</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11607,13 +11611,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>865452</v>
+        <v>865553</v>
       </c>
       <c r="R110" t="n">
-        <v>7447334</v>
+        <v>7447326</v>
       </c>
       <c r="S110" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -11657,22 +11661,26 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY110" t="inlineStr"/>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126887977</v>
+        <v>126887990</v>
       </c>
       <c r="B111" t="n">
-        <v>92809</v>
+        <v>79014</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11680,21 +11688,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11704,10 +11712,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>865643</v>
+        <v>865447</v>
       </c>
       <c r="R111" t="n">
-        <v>7447067</v>
+        <v>7447371</v>
       </c>
       <c r="S111" t="n">
         <v>25</v>
@@ -11766,32 +11774,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126887990</v>
+        <v>126887975</v>
       </c>
       <c r="B112" t="n">
-        <v>79014</v>
+        <v>97327</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11801,10 +11809,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>865447</v>
+        <v>865479</v>
       </c>
       <c r="R112" t="n">
-        <v>7447371</v>
+        <v>7447358</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -11863,32 +11871,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126892191</v>
+        <v>126887976</v>
       </c>
       <c r="B113" t="n">
-        <v>91587</v>
+        <v>97327</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>65</v>
+        <v>221941</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11898,13 +11906,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>865540</v>
+        <v>865452</v>
       </c>
       <c r="R113" t="n">
-        <v>7447366</v>
+        <v>7447334</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -11948,48 +11956,44 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126887987</v>
+        <v>126887977</v>
       </c>
       <c r="B114" t="n">
-        <v>91487</v>
+        <v>92809</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1503</v>
+        <v>2079</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11999,10 +12003,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>865510</v>
+        <v>865643</v>
       </c>
       <c r="R114" t="n">
-        <v>7447247</v>
+        <v>7447067</v>
       </c>
       <c r="S114" t="n">
         <v>25</v>
@@ -12061,32 +12065,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126893009</v>
+        <v>126887987</v>
       </c>
       <c r="B115" t="n">
-        <v>80989</v>
+        <v>91487</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1049</v>
+        <v>1503</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12096,13 +12100,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>865553</v>
+        <v>865510</v>
       </c>
       <c r="R115" t="n">
-        <v>7447326</v>
+        <v>7447247</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12146,19 +12150,15 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
-        </is>
-      </c>
-      <c r="AY115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12683,10 +12683,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126893030</v>
+        <v>126893267</v>
       </c>
       <c r="B121" t="n">
-        <v>77992</v>
+        <v>92809</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12694,21 +12694,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6487</v>
+        <v>2079</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12718,10 +12718,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>865545</v>
+        <v>865648</v>
       </c>
       <c r="R121" t="n">
-        <v>7447323</v>
+        <v>7447056</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12768,12 +12768,12 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
@@ -12885,32 +12885,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126893267</v>
+        <v>126893308</v>
       </c>
       <c r="B123" t="n">
-        <v>92809</v>
+        <v>91587</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>2079</v>
+        <v>65</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12920,10 +12920,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>865648</v>
+        <v>865659</v>
       </c>
       <c r="R123" t="n">
-        <v>7447056</v>
+        <v>7447048</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13087,32 +13087,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126893308</v>
+        <v>126893030</v>
       </c>
       <c r="B125" t="n">
-        <v>91587</v>
+        <v>77992</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>65</v>
+        <v>6487</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13122,10 +13122,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>865659</v>
+        <v>865545</v>
       </c>
       <c r="R125" t="n">
-        <v>7447048</v>
+        <v>7447323</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13172,12 +13172,12 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
@@ -13391,32 +13391,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126893269</v>
+        <v>126887988</v>
       </c>
       <c r="B128" t="n">
-        <v>92809</v>
+        <v>91487</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>2079</v>
+        <v>1503</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13426,13 +13426,13 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>865647</v>
+        <v>865515</v>
       </c>
       <c r="R128" t="n">
-        <v>7447057</v>
+        <v>7447377</v>
       </c>
       <c r="S128" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13476,26 +13476,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
-        </is>
-      </c>
-      <c r="AY128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126893274</v>
+        <v>126887970</v>
       </c>
       <c r="B129" t="n">
-        <v>80153</v>
+        <v>80146</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13503,21 +13499,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13527,13 +13523,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>865476</v>
+        <v>865529</v>
       </c>
       <c r="R129" t="n">
-        <v>7447236</v>
+        <v>7447327</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -13577,48 +13573,44 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
-        </is>
-      </c>
-      <c r="AY129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126893292</v>
+        <v>126893274</v>
       </c>
       <c r="B130" t="n">
-        <v>79014</v>
+        <v>80153</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13628,10 +13620,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>865501</v>
+        <v>865476</v>
       </c>
       <c r="R130" t="n">
-        <v>7447191</v>
+        <v>7447236</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13694,32 +13686,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126887970</v>
+        <v>126893269</v>
       </c>
       <c r="B131" t="n">
-        <v>80146</v>
+        <v>92809</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6462</v>
+        <v>2079</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13729,13 +13721,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>865529</v>
+        <v>865647</v>
       </c>
       <c r="R131" t="n">
-        <v>7447327</v>
+        <v>7447057</v>
       </c>
       <c r="S131" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -13779,22 +13771,26 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY131" t="inlineStr"/>
+          <t>Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126893313</v>
+        <v>126893292</v>
       </c>
       <c r="B132" t="n">
-        <v>78420</v>
+        <v>79014</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13802,21 +13798,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13826,10 +13822,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>865598</v>
+        <v>865501</v>
       </c>
       <c r="R132" t="n">
-        <v>7447181</v>
+        <v>7447191</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13892,32 +13888,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126887988</v>
+        <v>126893313</v>
       </c>
       <c r="B133" t="n">
-        <v>91487</v>
+        <v>78420</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1503</v>
+        <v>6437</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13927,13 +13923,13 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>865515</v>
+        <v>865598</v>
       </c>
       <c r="R133" t="n">
-        <v>7447377</v>
+        <v>7447181</v>
       </c>
       <c r="S133" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -13977,15 +13973,19 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY133" t="inlineStr"/>
+          <t>Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14090,32 +14090,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126893290</v>
+        <v>126892256</v>
       </c>
       <c r="B135" t="n">
-        <v>79014</v>
+        <v>91291</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14125,10 +14125,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>865505</v>
+        <v>865491</v>
       </c>
       <c r="R135" t="n">
-        <v>7447150</v>
+        <v>7447326</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14175,12 +14175,12 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
@@ -14191,32 +14191,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126892256</v>
+        <v>126893290</v>
       </c>
       <c r="B136" t="n">
-        <v>91291</v>
+        <v>79014</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14226,10 +14226,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>865491</v>
+        <v>865505</v>
       </c>
       <c r="R136" t="n">
-        <v>7447326</v>
+        <v>7447150</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14276,12 +14276,12 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
@@ -14292,10 +14292,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126892176</v>
+        <v>126893034</v>
       </c>
       <c r="B137" t="n">
-        <v>92809</v>
+        <v>78420</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14303,21 +14303,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>2079</v>
+        <v>6437</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14327,10 +14327,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>865490</v>
+        <v>865544</v>
       </c>
       <c r="R137" t="n">
-        <v>7447287</v>
+        <v>7447321</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14377,12 +14377,12 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
@@ -14393,10 +14393,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126893034</v>
+        <v>126892176</v>
       </c>
       <c r="B138" t="n">
-        <v>78420</v>
+        <v>92809</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14404,21 +14404,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6437</v>
+        <v>2079</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14428,10 +14428,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>865544</v>
+        <v>865490</v>
       </c>
       <c r="R138" t="n">
-        <v>7447321</v>
+        <v>7447287</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14478,12 +14478,12 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
@@ -14692,10 +14692,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126888456</v>
+        <v>126892253</v>
       </c>
       <c r="B141" t="n">
-        <v>92809</v>
+        <v>91248</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14703,21 +14703,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2079</v>
+        <v>3242</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14727,10 +14727,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>865506</v>
+        <v>865491</v>
       </c>
       <c r="R141" t="n">
-        <v>7447238</v>
+        <v>7447326</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14777,12 +14777,12 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
@@ -14793,10 +14793,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126892253</v>
+        <v>126888456</v>
       </c>
       <c r="B142" t="n">
-        <v>91248</v>
+        <v>92809</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14804,21 +14804,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>3242</v>
+        <v>2079</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14828,10 +14828,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>865491</v>
+        <v>865506</v>
       </c>
       <c r="R142" t="n">
-        <v>7447326</v>
+        <v>7447238</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14878,12 +14878,12 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
@@ -15193,7 +15193,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126892266</v>
+        <v>126888459</v>
       </c>
       <c r="B146" t="n">
         <v>79014</v>
@@ -15228,10 +15228,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>865495</v>
+        <v>865501</v>
       </c>
       <c r="R146" t="n">
-        <v>7447285</v>
+        <v>7447386</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15278,12 +15278,12 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
@@ -15294,7 +15294,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>126888459</v>
+        <v>126892266</v>
       </c>
       <c r="B147" t="n">
         <v>79014</v>
@@ -15329,10 +15329,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>865501</v>
+        <v>865495</v>
       </c>
       <c r="R147" t="n">
-        <v>7447386</v>
+        <v>7447285</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15379,12 +15379,12 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
@@ -15597,32 +15597,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126892980</v>
+        <v>126893259</v>
       </c>
       <c r="B150" t="n">
-        <v>91291</v>
+        <v>91248</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>5447</v>
+        <v>3242</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15632,10 +15632,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>865554</v>
+        <v>865646</v>
       </c>
       <c r="R150" t="n">
-        <v>7447301</v>
+        <v>7447063</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15682,12 +15682,12 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
@@ -15698,32 +15698,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126893259</v>
+        <v>126892980</v>
       </c>
       <c r="B151" t="n">
-        <v>91248</v>
+        <v>91291</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>3242</v>
+        <v>5447</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15733,10 +15733,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>865646</v>
+        <v>865554</v>
       </c>
       <c r="R151" t="n">
-        <v>7447063</v>
+        <v>7447301</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15783,12 +15783,12 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
@@ -16115,10 +16115,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126892272</v>
+        <v>126887979</v>
       </c>
       <c r="B155" t="n">
-        <v>77992</v>
+        <v>92809</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16126,21 +16126,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6487</v>
+        <v>2079</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16150,13 +16150,13 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>865528</v>
+        <v>865510</v>
       </c>
       <c r="R155" t="n">
-        <v>7447192</v>
+        <v>7447251</v>
       </c>
       <c r="S155" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -16200,19 +16200,15 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
-        </is>
-      </c>
-      <c r="AY155" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16418,10 +16414,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>126887979</v>
+        <v>126892272</v>
       </c>
       <c r="B158" t="n">
-        <v>92809</v>
+        <v>77992</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16429,21 +16425,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>2079</v>
+        <v>6487</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16453,13 +16449,13 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>865510</v>
+        <v>865528</v>
       </c>
       <c r="R158" t="n">
-        <v>7447251</v>
+        <v>7447192</v>
       </c>
       <c r="S158" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -16503,22 +16499,26 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY158" t="inlineStr"/>
+          <t>Svea Nikula</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>126893291</v>
+        <v>126893272</v>
       </c>
       <c r="B159" t="n">
-        <v>79014</v>
+        <v>92809</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16526,21 +16526,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16550,10 +16550,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>865507</v>
+        <v>865520</v>
       </c>
       <c r="R159" t="n">
-        <v>7447151</v>
+        <v>7447337</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16717,10 +16717,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>126893272</v>
+        <v>126893291</v>
       </c>
       <c r="B161" t="n">
-        <v>92809</v>
+        <v>79014</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16728,21 +16728,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16752,10 +16752,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>865520</v>
+        <v>865507</v>
       </c>
       <c r="R161" t="n">
-        <v>7447337</v>
+        <v>7447151</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17024,32 +17024,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>126893265</v>
+        <v>126887961</v>
       </c>
       <c r="B164" t="n">
-        <v>80146</v>
+        <v>79632</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17059,13 +17059,13 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>865530</v>
+        <v>865602</v>
       </c>
       <c r="R164" t="n">
-        <v>7447304</v>
+        <v>7447176</v>
       </c>
       <c r="S164" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -17109,48 +17109,44 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
-        </is>
-      </c>
-      <c r="AY164" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>126887961</v>
+        <v>126893265</v>
       </c>
       <c r="B165" t="n">
-        <v>79632</v>
+        <v>80146</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6453</v>
+        <v>6462</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17160,13 +17156,13 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>865602</v>
+        <v>865530</v>
       </c>
       <c r="R165" t="n">
-        <v>7447176</v>
+        <v>7447304</v>
       </c>
       <c r="S165" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -17210,15 +17206,19 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY165" t="inlineStr"/>
+          <t>Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -17323,32 +17323,32 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>126893031</v>
+        <v>126893021</v>
       </c>
       <c r="B167" t="n">
-        <v>77992</v>
+        <v>91587</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6487</v>
+        <v>65</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17358,10 +17358,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>865490</v>
+        <v>865547</v>
       </c>
       <c r="R167" t="n">
-        <v>7447338</v>
+        <v>7447316</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17424,32 +17424,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>126893284</v>
+        <v>126893309</v>
       </c>
       <c r="B168" t="n">
-        <v>79014</v>
+        <v>91587</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17459,7 +17459,7 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>865543</v>
+        <v>865661</v>
       </c>
       <c r="R168" t="n">
         <v>7447053</v>
@@ -17525,32 +17525,32 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>126893021</v>
+        <v>126893031</v>
       </c>
       <c r="B169" t="n">
-        <v>91587</v>
+        <v>77992</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>65</v>
+        <v>6487</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17560,10 +17560,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>865547</v>
+        <v>865490</v>
       </c>
       <c r="R169" t="n">
-        <v>7447316</v>
+        <v>7447338</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17626,32 +17626,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>126893309</v>
+        <v>126892988</v>
       </c>
       <c r="B170" t="n">
-        <v>91587</v>
+        <v>57479</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>65</v>
+        <v>102976</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17661,10 +17661,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>865661</v>
+        <v>865530</v>
       </c>
       <c r="R170" t="n">
-        <v>7447053</v>
+        <v>7447298</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17711,12 +17711,12 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr">
@@ -17727,32 +17727,32 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>126892988</v>
+        <v>126893284</v>
       </c>
       <c r="B171" t="n">
-        <v>57479</v>
+        <v>79014</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>102976</v>
+        <v>6425</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -17762,10 +17762,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>865530</v>
+        <v>865543</v>
       </c>
       <c r="R171" t="n">
-        <v>7447298</v>
+        <v>7447053</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17812,12 +17812,12 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
@@ -17828,32 +17828,32 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>126892997</v>
+        <v>126893263</v>
       </c>
       <c r="B172" t="n">
-        <v>79038</v>
+        <v>91326</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6434</v>
+        <v>1202</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -17863,10 +17863,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>865545</v>
+        <v>865485</v>
       </c>
       <c r="R172" t="n">
-        <v>7447323</v>
+        <v>7447224</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -17913,12 +17913,12 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
@@ -17929,10 +17929,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>126893314</v>
+        <v>126892174</v>
       </c>
       <c r="B173" t="n">
-        <v>78420</v>
+        <v>92809</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17940,21 +17940,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6437</v>
+        <v>2079</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -17964,10 +17964,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>865647</v>
+        <v>865517</v>
       </c>
       <c r="R173" t="n">
-        <v>7447060</v>
+        <v>7447401</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18014,12 +18014,12 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
@@ -18030,32 +18030,32 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>126891913</v>
+        <v>126892188</v>
       </c>
       <c r="B174" t="n">
-        <v>79632</v>
+        <v>91487</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18065,10 +18065,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>865557</v>
+        <v>865520</v>
       </c>
       <c r="R174" t="n">
-        <v>7447153</v>
+        <v>7447364</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18115,12 +18115,12 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr">
@@ -18131,32 +18131,32 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>126892986</v>
+        <v>126887986</v>
       </c>
       <c r="B175" t="n">
-        <v>79603</v>
+        <v>91487</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>229821</v>
+        <v>1503</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18166,13 +18166,13 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>865489</v>
+        <v>865539</v>
       </c>
       <c r="R175" t="n">
-        <v>7447329</v>
+        <v>7447206</v>
       </c>
       <c r="S175" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -18216,26 +18216,22 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
-        </is>
-      </c>
-      <c r="AY175" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>126892174</v>
+        <v>126893294</v>
       </c>
       <c r="B176" t="n">
-        <v>92809</v>
+        <v>79014</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18243,21 +18239,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18267,10 +18263,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>865517</v>
+        <v>865457</v>
       </c>
       <c r="R176" t="n">
-        <v>7447401</v>
+        <v>7447523</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18317,12 +18313,12 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr">
@@ -18333,10 +18329,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>126893294</v>
+        <v>126891913</v>
       </c>
       <c r="B177" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18344,21 +18340,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18368,10 +18364,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>865457</v>
+        <v>865557</v>
       </c>
       <c r="R177" t="n">
-        <v>7447523</v>
+        <v>7447153</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18418,12 +18414,12 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
@@ -18434,32 +18430,32 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>126892188</v>
+        <v>126892997</v>
       </c>
       <c r="B178" t="n">
-        <v>91487</v>
+        <v>79038</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>1503</v>
+        <v>6434</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18469,10 +18465,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>865520</v>
+        <v>865545</v>
       </c>
       <c r="R178" t="n">
-        <v>7447364</v>
+        <v>7447323</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18519,12 +18515,12 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr">
@@ -18535,32 +18531,32 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>126887986</v>
+        <v>126893314</v>
       </c>
       <c r="B179" t="n">
-        <v>91487</v>
+        <v>78420</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>1503</v>
+        <v>6437</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -18570,13 +18566,13 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>865539</v>
+        <v>865647</v>
       </c>
       <c r="R179" t="n">
-        <v>7447206</v>
+        <v>7447060</v>
       </c>
       <c r="S179" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -18620,22 +18616,26 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY179" t="inlineStr"/>
+          <t>Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>126893263</v>
+        <v>126892986</v>
       </c>
       <c r="B180" t="n">
-        <v>91326</v>
+        <v>79603</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18643,21 +18643,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -18667,10 +18667,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>865485</v>
+        <v>865489</v>
       </c>
       <c r="R180" t="n">
-        <v>7447224</v>
+        <v>7447329</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18717,12 +18717,12 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">

--- a/artfynd/A 52625-2022 artfynd.xlsx
+++ b/artfynd/A 52625-2022 artfynd.xlsx
@@ -877,32 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126892265</v>
+        <v>126893005</v>
       </c>
       <c r="B4" t="n">
-        <v>91344</v>
+        <v>80153</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>865431</v>
+        <v>865370</v>
       </c>
       <c r="R4" t="n">
-        <v>7447451</v>
+        <v>7447622</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,12 +962,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126893005</v>
+        <v>126891922</v>
       </c>
       <c r="B5" t="n">
-        <v>80153</v>
+        <v>80146</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>865370</v>
+        <v>865415</v>
       </c>
       <c r="R5" t="n">
-        <v>7447622</v>
+        <v>7447651</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,12 +1063,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1079,32 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126891922</v>
+        <v>126892265</v>
       </c>
       <c r="B6" t="n">
-        <v>80146</v>
+        <v>91344</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>865415</v>
+        <v>865431</v>
       </c>
       <c r="R6" t="n">
-        <v>7447651</v>
+        <v>7447451</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,12 +1164,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1180,32 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126893295</v>
+        <v>126893275</v>
       </c>
       <c r="B7" t="n">
-        <v>79014</v>
+        <v>80153</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>865429</v>
+        <v>865427</v>
       </c>
       <c r="R7" t="n">
-        <v>7447550</v>
+        <v>7447587</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,32 +1281,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126893300</v>
+        <v>126892019</v>
       </c>
       <c r="B8" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>865378</v>
+        <v>865429</v>
       </c>
       <c r="R8" t="n">
-        <v>7447665</v>
+        <v>7447523</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1366,12 +1366,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1382,32 +1382,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126893275</v>
+        <v>126893295</v>
       </c>
       <c r="B9" t="n">
-        <v>80153</v>
+        <v>79014</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>865427</v>
+        <v>865429</v>
       </c>
       <c r="R9" t="n">
-        <v>7447587</v>
+        <v>7447550</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1483,32 +1483,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126892019</v>
+        <v>126893300</v>
       </c>
       <c r="B10" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>865429</v>
+        <v>865378</v>
       </c>
       <c r="R10" t="n">
-        <v>7447523</v>
+        <v>7447665</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1568,12 +1568,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1584,59 +1584,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126892270</v>
+        <v>126887991</v>
       </c>
       <c r="B11" t="n">
-        <v>91900</v>
+        <v>79014</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>865437</v>
+        <v>865422</v>
       </c>
       <c r="R11" t="n">
-        <v>7447594</v>
+        <v>7447458</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1674,30 +1663,25 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Svea Nikula, Jonas Göransson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126887991</v>
+        <v>126887992</v>
       </c>
       <c r="B12" t="n">
         <v>79014</v>
@@ -1732,10 +1716,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>865422</v>
+        <v>865406</v>
       </c>
       <c r="R12" t="n">
-        <v>7447458</v>
+        <v>7447461</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1794,32 +1778,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126887992</v>
+        <v>126892999</v>
       </c>
       <c r="B13" t="n">
-        <v>79014</v>
+        <v>80145</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1829,13 +1813,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>865406</v>
+        <v>865426</v>
       </c>
       <c r="R13" t="n">
-        <v>7447461</v>
+        <v>7447493</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1879,22 +1863,26 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126892999</v>
+        <v>126892173</v>
       </c>
       <c r="B14" t="n">
-        <v>80145</v>
+        <v>80146</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1902,21 +1890,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1926,10 +1914,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>865426</v>
+        <v>865379</v>
       </c>
       <c r="R14" t="n">
-        <v>7447493</v>
+        <v>7447558</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1976,12 +1964,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -1992,45 +1980,56 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126892173</v>
+        <v>126892270</v>
       </c>
       <c r="B15" t="n">
-        <v>80146</v>
+        <v>91900</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>760</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>865379</v>
+        <v>865437</v>
       </c>
       <c r="R15" t="n">
-        <v>7447558</v>
+        <v>7447594</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2071,18 +2070,19 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Svea Nikula, Jonas Göransson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2296,7 +2296,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126893017</v>
+        <v>126893301</v>
       </c>
       <c r="B18" t="n">
         <v>79014</v>
@@ -2331,10 +2331,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>865409</v>
+        <v>865382</v>
       </c>
       <c r="R18" t="n">
-        <v>7447573</v>
+        <v>7447699</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2381,12 +2381,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2397,7 +2397,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126893301</v>
+        <v>126893017</v>
       </c>
       <c r="B19" t="n">
         <v>79014</v>
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>865382</v>
+        <v>865409</v>
       </c>
       <c r="R19" t="n">
-        <v>7447699</v>
+        <v>7447573</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2482,12 +2482,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -3807,32 +3807,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126892259</v>
+        <v>126893306</v>
       </c>
       <c r="B33" t="n">
-        <v>98464</v>
+        <v>82855</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221952</v>
+        <v>1312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3842,10 +3842,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>865411</v>
+        <v>865378</v>
       </c>
       <c r="R33" t="n">
-        <v>7447533</v>
+        <v>7447665</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3892,12 +3892,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -3908,32 +3908,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126887969</v>
+        <v>126892262</v>
       </c>
       <c r="B34" t="n">
-        <v>57817</v>
+        <v>80153</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3943,13 +3943,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>865406</v>
+        <v>865404</v>
       </c>
       <c r="R34" t="n">
-        <v>7447461</v>
+        <v>7447633</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3993,44 +3993,48 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
+          <t>Svea Nikula</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126892262</v>
+        <v>126887969</v>
       </c>
       <c r="B35" t="n">
-        <v>80153</v>
+        <v>57817</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4040,13 +4044,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>865404</v>
+        <v>865406</v>
       </c>
       <c r="R35" t="n">
-        <v>7447633</v>
+        <v>7447461</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4090,48 +4094,44 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126893306</v>
+        <v>126892259</v>
       </c>
       <c r="B36" t="n">
-        <v>82855</v>
+        <v>98464</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>221952</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4141,10 +4141,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>865378</v>
+        <v>865411</v>
       </c>
       <c r="R36" t="n">
-        <v>7447665</v>
+        <v>7447533</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4191,12 +4191,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4308,10 +4308,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126887993</v>
+        <v>126892978</v>
       </c>
       <c r="B38" t="n">
-        <v>79014</v>
+        <v>75138</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4319,21 +4319,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4343,13 +4343,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>865389</v>
+        <v>865423</v>
       </c>
       <c r="R38" t="n">
-        <v>7447521</v>
+        <v>7447442</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4393,22 +4393,26 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126892978</v>
+        <v>126887993</v>
       </c>
       <c r="B39" t="n">
-        <v>75138</v>
+        <v>79014</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4416,21 +4420,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4440,13 +4444,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>865423</v>
+        <v>865389</v>
       </c>
       <c r="R39" t="n">
-        <v>7447442</v>
+        <v>7447521</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4490,19 +4494,15 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5816,10 +5816,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126892985</v>
+        <v>126893008</v>
       </c>
       <c r="B53" t="n">
-        <v>79632</v>
+        <v>80989</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5827,21 +5827,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5851,10 +5851,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>865491</v>
+        <v>865545</v>
       </c>
       <c r="R53" t="n">
-        <v>7447332</v>
+        <v>7447322</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5917,10 +5917,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126892273</v>
+        <v>126892026</v>
       </c>
       <c r="B54" t="n">
-        <v>78420</v>
+        <v>79014</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5928,21 +5928,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5952,10 +5952,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>865528</v>
+        <v>865538</v>
       </c>
       <c r="R54" t="n">
-        <v>7447193</v>
+        <v>7447072</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6002,12 +6002,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6018,32 +6018,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126891916</v>
+        <v>126892029</v>
       </c>
       <c r="B55" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6053,10 +6053,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>865546</v>
+        <v>865448</v>
       </c>
       <c r="R55" t="n">
-        <v>7447133</v>
+        <v>7447418</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6103,12 +6103,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6119,10 +6119,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126893008</v>
+        <v>126892985</v>
       </c>
       <c r="B56" t="n">
-        <v>80989</v>
+        <v>79632</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6130,21 +6130,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>865545</v>
+        <v>865491</v>
       </c>
       <c r="R56" t="n">
-        <v>7447322</v>
+        <v>7447332</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6321,10 +6321,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126892026</v>
+        <v>126892273</v>
       </c>
       <c r="B58" t="n">
-        <v>79014</v>
+        <v>78420</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6332,21 +6332,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6356,10 +6356,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>865538</v>
+        <v>865528</v>
       </c>
       <c r="R58" t="n">
-        <v>7447072</v>
+        <v>7447193</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6406,12 +6406,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6422,32 +6422,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126892029</v>
+        <v>126891916</v>
       </c>
       <c r="B59" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6457,10 +6457,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>865448</v>
+        <v>865546</v>
       </c>
       <c r="R59" t="n">
-        <v>7447418</v>
+        <v>7447133</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6507,12 +6507,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6624,32 +6624,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126892982</v>
+        <v>126892177</v>
       </c>
       <c r="B61" t="n">
-        <v>91291</v>
+        <v>92809</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5447</v>
+        <v>2079</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6659,10 +6659,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>865526</v>
+        <v>865522</v>
       </c>
       <c r="R61" t="n">
-        <v>7447273</v>
+        <v>7447338</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6709,12 +6709,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6725,10 +6725,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126891915</v>
+        <v>126892982</v>
       </c>
       <c r="B62" t="n">
-        <v>80146</v>
+        <v>91291</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6736,21 +6736,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6760,10 +6760,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>865551</v>
+        <v>865526</v>
       </c>
       <c r="R62" t="n">
-        <v>7447126</v>
+        <v>7447273</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6810,12 +6810,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -6826,32 +6826,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126892177</v>
+        <v>126891915</v>
       </c>
       <c r="B63" t="n">
-        <v>92809</v>
+        <v>80146</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2079</v>
+        <v>6462</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6861,10 +6861,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>865522</v>
+        <v>865551</v>
       </c>
       <c r="R63" t="n">
-        <v>7447338</v>
+        <v>7447126</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6911,12 +6911,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7525,45 +7525,61 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126891925</v>
+        <v>126892183</v>
       </c>
       <c r="B70" t="n">
-        <v>98443</v>
+        <v>56840</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>pulli</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>pulli/nyligen flygga ungar</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>865527</v>
+        <v>865484</v>
       </c>
       <c r="R70" t="n">
-        <v>7447333</v>
+        <v>7447494</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7598,6 +7614,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Stötte up 5st kycklingar, höll till under en och samma fallen gran</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -7610,12 +7631,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7626,61 +7647,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126892183</v>
+        <v>126891925</v>
       </c>
       <c r="B71" t="n">
-        <v>56840</v>
+        <v>98443</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>pulli</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>pulli/nyligen flygga ungar</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>865484</v>
+        <v>865527</v>
       </c>
       <c r="R71" t="n">
-        <v>7447494</v>
+        <v>7447333</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7715,11 +7720,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Stötte up 5st kycklingar, höll till under en och samma fallen gran</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -7732,12 +7732,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -7748,32 +7748,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126892187</v>
+        <v>126893282</v>
       </c>
       <c r="B72" t="n">
-        <v>91487</v>
+        <v>79014</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7783,10 +7783,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>865509</v>
+        <v>865611</v>
       </c>
       <c r="R72" t="n">
-        <v>7447371</v>
+        <v>7446989</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7833,12 +7833,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -7849,7 +7849,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126893012</v>
+        <v>126892187</v>
       </c>
       <c r="B73" t="n">
         <v>91487</v>
@@ -7884,10 +7884,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>865559</v>
+        <v>865509</v>
       </c>
       <c r="R73" t="n">
-        <v>7447299</v>
+        <v>7447371</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7934,12 +7934,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -7950,32 +7950,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126893282</v>
+        <v>126893012</v>
       </c>
       <c r="B74" t="n">
-        <v>79014</v>
+        <v>91487</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7985,10 +7985,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>865611</v>
+        <v>865559</v>
       </c>
       <c r="R74" t="n">
-        <v>7446989</v>
+        <v>7447299</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8035,12 +8035,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -9564,10 +9564,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126893277</v>
+        <v>126888454</v>
       </c>
       <c r="B90" t="n">
-        <v>80989</v>
+        <v>57817</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9575,34 +9575,42 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1049</v>
+        <v>103021</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>865647</v>
+        <v>865481</v>
       </c>
       <c r="R90" t="n">
-        <v>7447060</v>
+        <v>7447376</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9649,12 +9657,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -9665,53 +9673,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126888454</v>
+        <v>126893278</v>
       </c>
       <c r="B91" t="n">
-        <v>57817</v>
+        <v>98443</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>865481</v>
+        <v>865551</v>
       </c>
       <c r="R91" t="n">
-        <v>7447376</v>
+        <v>7447276</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9758,12 +9758,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -9774,7 +9774,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126893278</v>
+        <v>126892181</v>
       </c>
       <c r="B92" t="n">
         <v>98443</v>
@@ -9809,10 +9809,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>865551</v>
+        <v>865459</v>
       </c>
       <c r="R92" t="n">
-        <v>7447276</v>
+        <v>7447305</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9859,12 +9859,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -9875,32 +9875,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126892181</v>
+        <v>126893277</v>
       </c>
       <c r="B93" t="n">
-        <v>98443</v>
+        <v>80989</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>1049</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9910,10 +9910,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>865459</v>
+        <v>865647</v>
       </c>
       <c r="R93" t="n">
-        <v>7447305</v>
+        <v>7447060</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9960,12 +9960,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -9976,32 +9976,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126893025</v>
+        <v>126888000</v>
       </c>
       <c r="B94" t="n">
-        <v>92616</v>
+        <v>78681</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10011,13 +10011,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>865518</v>
+        <v>865597</v>
       </c>
       <c r="R94" t="n">
-        <v>7447235</v>
+        <v>7447186</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10061,48 +10061,44 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
-        </is>
-      </c>
-      <c r="AY94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126892981</v>
+        <v>126887968</v>
       </c>
       <c r="B95" t="n">
-        <v>91291</v>
+        <v>57817</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10112,13 +10108,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>865553</v>
+        <v>865523</v>
       </c>
       <c r="R95" t="n">
-        <v>7447278</v>
+        <v>7447217</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10162,48 +10158,44 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
-        </is>
-      </c>
-      <c r="AY95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126892267</v>
+        <v>126887997</v>
       </c>
       <c r="B96" t="n">
-        <v>79014</v>
+        <v>98360</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10213,13 +10205,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>865516</v>
+        <v>865448</v>
       </c>
       <c r="R96" t="n">
-        <v>7447351</v>
+        <v>7447350</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10263,48 +10255,44 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
-        </is>
-      </c>
-      <c r="AY96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126887968</v>
+        <v>126893023</v>
       </c>
       <c r="B97" t="n">
-        <v>57817</v>
+        <v>91727</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>103021</v>
+        <v>715</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Finporing</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Gloeoporus pannocinctus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Romell) J.Erikss.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10314,13 +10302,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>865523</v>
+        <v>865473</v>
       </c>
       <c r="R97" t="n">
-        <v>7447217</v>
+        <v>7447321</v>
       </c>
       <c r="S97" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10364,44 +10352,48 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY97" t="inlineStr"/>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126893023</v>
+        <v>126892178</v>
       </c>
       <c r="B98" t="n">
-        <v>91727</v>
+        <v>92809</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>715</v>
+        <v>2079</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Finporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Gloeoporus pannocinctus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Romell) J.Erikss.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10411,10 +10403,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>865473</v>
+        <v>865509</v>
       </c>
       <c r="R98" t="n">
-        <v>7447321</v>
+        <v>7447375</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10461,12 +10453,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10477,32 +10469,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126888000</v>
+        <v>126893281</v>
       </c>
       <c r="B99" t="n">
-        <v>78681</v>
+        <v>91487</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10512,13 +10504,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>865597</v>
+        <v>865513</v>
       </c>
       <c r="R99" t="n">
-        <v>7447186</v>
+        <v>7447339</v>
       </c>
       <c r="S99" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10562,44 +10554,48 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY99" t="inlineStr"/>
+          <t>Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126892178</v>
+        <v>126893025</v>
       </c>
       <c r="B100" t="n">
-        <v>92809</v>
+        <v>92616</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10609,10 +10605,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>865509</v>
+        <v>865518</v>
       </c>
       <c r="R100" t="n">
-        <v>7447375</v>
+        <v>7447235</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10659,12 +10655,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -10675,32 +10671,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126893281</v>
+        <v>126892981</v>
       </c>
       <c r="B101" t="n">
-        <v>91487</v>
+        <v>91291</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1503</v>
+        <v>5447</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10710,10 +10706,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>865513</v>
+        <v>865553</v>
       </c>
       <c r="R101" t="n">
-        <v>7447339</v>
+        <v>7447278</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10760,12 +10756,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -10776,32 +10772,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126887997</v>
+        <v>126892267</v>
       </c>
       <c r="B102" t="n">
-        <v>98360</v>
+        <v>79014</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10811,13 +10807,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>865448</v>
+        <v>865516</v>
       </c>
       <c r="R102" t="n">
-        <v>7447350</v>
+        <v>7447351</v>
       </c>
       <c r="S102" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -10861,44 +10857,48 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY102" t="inlineStr"/>
+          <t>Svea Nikula</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126892186</v>
+        <v>126891923</v>
       </c>
       <c r="B103" t="n">
-        <v>91487</v>
+        <v>80021</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1503</v>
+        <v>6456</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10908,10 +10908,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>865491</v>
+        <v>865536</v>
       </c>
       <c r="R103" t="n">
-        <v>7447290</v>
+        <v>7447112</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10958,12 +10958,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -10974,32 +10974,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>126891923</v>
+        <v>126893033</v>
       </c>
       <c r="B104" t="n">
-        <v>80021</v>
+        <v>78420</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6456</v>
+        <v>6437</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11009,10 +11009,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>865536</v>
+        <v>865500</v>
       </c>
       <c r="R104" t="n">
-        <v>7447112</v>
+        <v>7447283</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11059,12 +11059,12 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -11075,32 +11075,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126893033</v>
+        <v>126892186</v>
       </c>
       <c r="B105" t="n">
-        <v>78420</v>
+        <v>91487</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6437</v>
+        <v>1503</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11110,10 +11110,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>865500</v>
+        <v>865491</v>
       </c>
       <c r="R105" t="n">
-        <v>7447283</v>
+        <v>7447290</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11160,12 +11160,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
@@ -11176,32 +11176,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126887980</v>
+        <v>126893310</v>
       </c>
       <c r="B106" t="n">
-        <v>92809</v>
+        <v>91587</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>2079</v>
+        <v>65</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11211,13 +11211,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>865511</v>
+        <v>865653</v>
       </c>
       <c r="R106" t="n">
-        <v>7447249</v>
+        <v>7447052</v>
       </c>
       <c r="S106" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11261,22 +11261,26 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY106" t="inlineStr"/>
+          <t>Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126892028</v>
+        <v>126887980</v>
       </c>
       <c r="B107" t="n">
-        <v>79014</v>
+        <v>92809</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11284,21 +11288,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11308,13 +11312,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>865533</v>
+        <v>865511</v>
       </c>
       <c r="R107" t="n">
-        <v>7447130</v>
+        <v>7447249</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11358,48 +11362,44 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126893310</v>
+        <v>126892028</v>
       </c>
       <c r="B108" t="n">
-        <v>91587</v>
+        <v>79014</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11409,10 +11409,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>865653</v>
+        <v>865533</v>
       </c>
       <c r="R108" t="n">
-        <v>7447052</v>
+        <v>7447130</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11459,12 +11459,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
@@ -12683,10 +12683,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126893267</v>
+        <v>126893260</v>
       </c>
       <c r="B121" t="n">
-        <v>92809</v>
+        <v>91248</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12694,21 +12694,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>2079</v>
+        <v>3242</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12718,10 +12718,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>865648</v>
+        <v>865498</v>
       </c>
       <c r="R121" t="n">
-        <v>7447056</v>
+        <v>7447359</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12784,32 +12784,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126893260</v>
+        <v>126893262</v>
       </c>
       <c r="B122" t="n">
-        <v>91248</v>
+        <v>91291</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>3242</v>
+        <v>5447</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12819,10 +12819,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>865498</v>
+        <v>865522</v>
       </c>
       <c r="R122" t="n">
-        <v>7447359</v>
+        <v>7447308</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12885,32 +12885,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126893308</v>
+        <v>126893030</v>
       </c>
       <c r="B123" t="n">
-        <v>91587</v>
+        <v>77992</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>65</v>
+        <v>6487</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12920,10 +12920,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>865659</v>
+        <v>865545</v>
       </c>
       <c r="R123" t="n">
-        <v>7447048</v>
+        <v>7447323</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12970,12 +12970,12 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
@@ -12986,10 +12986,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126893262</v>
+        <v>126887981</v>
       </c>
       <c r="B124" t="n">
-        <v>91291</v>
+        <v>80153</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12997,21 +12997,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5447</v>
+        <v>6464</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13021,13 +13021,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>865522</v>
+        <v>865448</v>
       </c>
       <c r="R124" t="n">
-        <v>7447308</v>
+        <v>7447345</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13071,48 +13071,44 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
-        </is>
-      </c>
-      <c r="AY124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126893030</v>
+        <v>126893308</v>
       </c>
       <c r="B125" t="n">
-        <v>77992</v>
+        <v>91587</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6487</v>
+        <v>65</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13122,10 +13118,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>865545</v>
+        <v>865659</v>
       </c>
       <c r="R125" t="n">
-        <v>7447323</v>
+        <v>7447048</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13172,12 +13168,12 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
@@ -13188,32 +13184,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126887981</v>
+        <v>126893267</v>
       </c>
       <c r="B126" t="n">
-        <v>80153</v>
+        <v>92809</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6464</v>
+        <v>2079</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13223,13 +13219,13 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>865448</v>
+        <v>865648</v>
       </c>
       <c r="R126" t="n">
-        <v>7447345</v>
+        <v>7447056</v>
       </c>
       <c r="S126" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13273,15 +13269,19 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY126" t="inlineStr"/>
+          <t>Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13391,32 +13391,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126887988</v>
+        <v>126893269</v>
       </c>
       <c r="B128" t="n">
-        <v>91487</v>
+        <v>92809</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1503</v>
+        <v>2079</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13426,13 +13426,13 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>865515</v>
+        <v>865647</v>
       </c>
       <c r="R128" t="n">
-        <v>7447377</v>
+        <v>7447057</v>
       </c>
       <c r="S128" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13476,44 +13476,48 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY128" t="inlineStr"/>
+          <t>Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126887970</v>
+        <v>126893292</v>
       </c>
       <c r="B129" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13523,13 +13527,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>865529</v>
+        <v>865501</v>
       </c>
       <c r="R129" t="n">
-        <v>7447327</v>
+        <v>7447191</v>
       </c>
       <c r="S129" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -13573,44 +13577,48 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY129" t="inlineStr"/>
+          <t>Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126893274</v>
+        <v>126893313</v>
       </c>
       <c r="B130" t="n">
-        <v>80153</v>
+        <v>78420</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6464</v>
+        <v>6437</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13620,10 +13628,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>865476</v>
+        <v>865598</v>
       </c>
       <c r="R130" t="n">
-        <v>7447236</v>
+        <v>7447181</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13686,32 +13694,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126893269</v>
+        <v>126887970</v>
       </c>
       <c r="B131" t="n">
-        <v>92809</v>
+        <v>80146</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>2079</v>
+        <v>6462</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13721,13 +13729,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>865647</v>
+        <v>865529</v>
       </c>
       <c r="R131" t="n">
-        <v>7447057</v>
+        <v>7447327</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -13771,48 +13779,44 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
-        </is>
-      </c>
-      <c r="AY131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126893292</v>
+        <v>126893274</v>
       </c>
       <c r="B132" t="n">
-        <v>79014</v>
+        <v>80153</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13822,10 +13826,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>865501</v>
+        <v>865476</v>
       </c>
       <c r="R132" t="n">
-        <v>7447191</v>
+        <v>7447236</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13888,32 +13892,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126893313</v>
+        <v>126887988</v>
       </c>
       <c r="B133" t="n">
-        <v>78420</v>
+        <v>91487</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6437</v>
+        <v>1503</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13923,13 +13927,13 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>865598</v>
+        <v>865515</v>
       </c>
       <c r="R133" t="n">
-        <v>7447181</v>
+        <v>7447377</v>
       </c>
       <c r="S133" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -13973,26 +13977,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
-        </is>
-      </c>
-      <c r="AY133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126892189</v>
+        <v>126892176</v>
       </c>
       <c r="B134" t="n">
-        <v>79014</v>
+        <v>92809</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14000,21 +14000,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14024,10 +14024,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>865551</v>
+        <v>865490</v>
       </c>
       <c r="R134" t="n">
-        <v>7447310</v>
+        <v>7447287</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14090,32 +14090,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126892256</v>
+        <v>126892189</v>
       </c>
       <c r="B135" t="n">
-        <v>91291</v>
+        <v>79014</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14125,10 +14125,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>865491</v>
+        <v>865551</v>
       </c>
       <c r="R135" t="n">
-        <v>7447326</v>
+        <v>7447310</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14175,12 +14175,12 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
@@ -14191,32 +14191,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126893290</v>
+        <v>126892256</v>
       </c>
       <c r="B136" t="n">
-        <v>79014</v>
+        <v>91291</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14226,10 +14226,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>865505</v>
+        <v>865491</v>
       </c>
       <c r="R136" t="n">
-        <v>7447150</v>
+        <v>7447326</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14276,12 +14276,12 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
@@ -14292,10 +14292,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126893034</v>
+        <v>126893290</v>
       </c>
       <c r="B137" t="n">
-        <v>78420</v>
+        <v>79014</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14303,21 +14303,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14327,10 +14327,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>865544</v>
+        <v>865505</v>
       </c>
       <c r="R137" t="n">
-        <v>7447321</v>
+        <v>7447150</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14377,12 +14377,12 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
@@ -14393,10 +14393,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126892176</v>
+        <v>126892984</v>
       </c>
       <c r="B138" t="n">
-        <v>92809</v>
+        <v>79632</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14404,21 +14404,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14428,10 +14428,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>865490</v>
+        <v>865523</v>
       </c>
       <c r="R138" t="n">
-        <v>7447287</v>
+        <v>7447267</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14478,12 +14478,12 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
@@ -14494,7 +14494,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126892984</v>
+        <v>126887962</v>
       </c>
       <c r="B139" t="n">
         <v>79632</v>
@@ -14529,13 +14529,13 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>865523</v>
+        <v>865519</v>
       </c>
       <c r="R139" t="n">
-        <v>7447267</v>
+        <v>7447214</v>
       </c>
       <c r="S139" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -14579,26 +14579,22 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
-        </is>
-      </c>
-      <c r="AY139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126887962</v>
+        <v>126893034</v>
       </c>
       <c r="B140" t="n">
-        <v>79632</v>
+        <v>78420</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14606,21 +14602,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14630,13 +14626,13 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>865519</v>
+        <v>865544</v>
       </c>
       <c r="R140" t="n">
-        <v>7447214</v>
+        <v>7447321</v>
       </c>
       <c r="S140" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -14680,22 +14676,26 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY140" t="inlineStr"/>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126892253</v>
+        <v>126888456</v>
       </c>
       <c r="B141" t="n">
-        <v>91248</v>
+        <v>92809</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14703,21 +14703,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>3242</v>
+        <v>2079</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14727,10 +14727,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>865491</v>
+        <v>865506</v>
       </c>
       <c r="R141" t="n">
-        <v>7447326</v>
+        <v>7447238</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14777,12 +14777,12 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
@@ -14793,32 +14793,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126888456</v>
+        <v>126887971</v>
       </c>
       <c r="B142" t="n">
-        <v>92809</v>
+        <v>80146</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>2079</v>
+        <v>6462</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14828,13 +14828,13 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>865506</v>
+        <v>865452</v>
       </c>
       <c r="R142" t="n">
-        <v>7447238</v>
+        <v>7447318</v>
       </c>
       <c r="S142" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -14878,23 +14878,19 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
-        </is>
-      </c>
-      <c r="AY142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126887971</v>
+        <v>126892991</v>
       </c>
       <c r="B143" t="n">
         <v>80146</v>
@@ -14929,13 +14925,13 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>865452</v>
+        <v>865531</v>
       </c>
       <c r="R143" t="n">
-        <v>7447318</v>
+        <v>7447308</v>
       </c>
       <c r="S143" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -14979,19 +14975,23 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY143" t="inlineStr"/>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>126892991</v>
+        <v>126891917</v>
       </c>
       <c r="B144" t="n">
         <v>80146</v>
@@ -15026,10 +15026,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>865531</v>
+        <v>865561</v>
       </c>
       <c r="R144" t="n">
-        <v>7447308</v>
+        <v>7447152</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15076,12 +15076,12 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
@@ -15092,32 +15092,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126891917</v>
+        <v>126892253</v>
       </c>
       <c r="B145" t="n">
-        <v>80146</v>
+        <v>91248</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6462</v>
+        <v>3242</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15127,10 +15127,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>865561</v>
+        <v>865491</v>
       </c>
       <c r="R145" t="n">
-        <v>7447152</v>
+        <v>7447326</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15177,12 +15177,12 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">

--- a/artfynd/A 52625-2022 artfynd.xlsx
+++ b/artfynd/A 52625-2022 artfynd.xlsx
@@ -877,32 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126893005</v>
+        <v>126892265</v>
       </c>
       <c r="B4" t="n">
-        <v>80153</v>
+        <v>91344</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>865370</v>
+        <v>865431</v>
       </c>
       <c r="R4" t="n">
-        <v>7447622</v>
+        <v>7447451</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,12 +962,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126891922</v>
+        <v>126893005</v>
       </c>
       <c r="B5" t="n">
-        <v>80146</v>
+        <v>80153</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>865415</v>
+        <v>865370</v>
       </c>
       <c r="R5" t="n">
-        <v>7447651</v>
+        <v>7447622</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,12 +1063,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1079,32 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126892265</v>
+        <v>126891922</v>
       </c>
       <c r="B6" t="n">
-        <v>91344</v>
+        <v>80146</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>865431</v>
+        <v>865415</v>
       </c>
       <c r="R6" t="n">
-        <v>7447451</v>
+        <v>7447651</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,12 +1164,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1584,48 +1584,59 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126887991</v>
+        <v>126892270</v>
       </c>
       <c r="B11" t="n">
-        <v>79014</v>
+        <v>91900</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>865422</v>
+        <v>865437</v>
       </c>
       <c r="R11" t="n">
-        <v>7447458</v>
+        <v>7447594</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1663,25 +1674,30 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Svea Nikula, Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126887992</v>
+        <v>126887991</v>
       </c>
       <c r="B12" t="n">
         <v>79014</v>
@@ -1716,10 +1732,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>865406</v>
+        <v>865422</v>
       </c>
       <c r="R12" t="n">
-        <v>7447461</v>
+        <v>7447458</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1778,32 +1794,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126892999</v>
+        <v>126887992</v>
       </c>
       <c r="B13" t="n">
-        <v>80145</v>
+        <v>79014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1813,13 +1829,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>865426</v>
+        <v>865406</v>
       </c>
       <c r="R13" t="n">
-        <v>7447493</v>
+        <v>7447461</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1863,26 +1879,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126892173</v>
+        <v>126892999</v>
       </c>
       <c r="B14" t="n">
-        <v>80146</v>
+        <v>80145</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1890,21 +1902,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1914,10 +1926,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>865379</v>
+        <v>865426</v>
       </c>
       <c r="R14" t="n">
-        <v>7447558</v>
+        <v>7447493</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1964,12 +1976,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -1980,56 +1992,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126892270</v>
+        <v>126892173</v>
       </c>
       <c r="B15" t="n">
-        <v>91900</v>
+        <v>80146</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>760</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>865437</v>
+        <v>865379</v>
       </c>
       <c r="R15" t="n">
-        <v>7447594</v>
+        <v>7447558</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2070,19 +2071,18 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Svea Nikula, Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2093,32 +2093,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126893016</v>
+        <v>126892264</v>
       </c>
       <c r="B16" t="n">
-        <v>79014</v>
+        <v>58516</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>208249</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>865412</v>
+        <v>865410</v>
       </c>
       <c r="R16" t="n">
-        <v>7447514</v>
+        <v>7447525</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2172,18 +2172,19 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2194,32 +2195,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126892264</v>
+        <v>126893016</v>
       </c>
       <c r="B17" t="n">
-        <v>58516</v>
+        <v>79014</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>208249</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2229,10 +2230,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>865410</v>
+        <v>865412</v>
       </c>
       <c r="R17" t="n">
-        <v>7447525</v>
+        <v>7447514</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2273,19 +2274,18 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2296,7 +2296,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126893301</v>
+        <v>126893017</v>
       </c>
       <c r="B18" t="n">
         <v>79014</v>
@@ -2331,10 +2331,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>865382</v>
+        <v>865409</v>
       </c>
       <c r="R18" t="n">
-        <v>7447699</v>
+        <v>7447573</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2381,12 +2381,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2397,7 +2397,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126893017</v>
+        <v>126893301</v>
       </c>
       <c r="B19" t="n">
         <v>79014</v>
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>865409</v>
+        <v>865382</v>
       </c>
       <c r="R19" t="n">
-        <v>7447573</v>
+        <v>7447699</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2482,12 +2482,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -4308,10 +4308,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126892978</v>
+        <v>126887993</v>
       </c>
       <c r="B38" t="n">
-        <v>75138</v>
+        <v>79014</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4319,21 +4319,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4343,13 +4343,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>865423</v>
+        <v>865389</v>
       </c>
       <c r="R38" t="n">
-        <v>7447442</v>
+        <v>7447521</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4393,26 +4393,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126887993</v>
+        <v>126892978</v>
       </c>
       <c r="B39" t="n">
-        <v>79014</v>
+        <v>75138</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4420,21 +4416,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4444,13 +4440,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>865389</v>
+        <v>865423</v>
       </c>
       <c r="R39" t="n">
-        <v>7447521</v>
+        <v>7447442</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4494,15 +4490,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5213,27 +5213,27 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126893028</v>
+        <v>126887994</v>
       </c>
       <c r="B47" t="n">
-        <v>80152</v>
+        <v>79014</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5248,13 +5248,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>865390</v>
+        <v>865368</v>
       </c>
       <c r="R47" t="n">
-        <v>7447609</v>
+        <v>7447606</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5298,26 +5298,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126892020</v>
+        <v>126893028</v>
       </c>
       <c r="B48" t="n">
-        <v>80146</v>
+        <v>80152</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5325,21 +5321,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5349,10 +5345,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>865440</v>
+        <v>865390</v>
       </c>
       <c r="R48" t="n">
-        <v>7447393</v>
+        <v>7447609</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5399,12 +5395,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5415,32 +5411,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126887994</v>
+        <v>126892020</v>
       </c>
       <c r="B49" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5450,13 +5446,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>865368</v>
+        <v>865440</v>
       </c>
       <c r="R49" t="n">
-        <v>7447606</v>
+        <v>7447393</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5500,15 +5496,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr"/>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5816,10 +5816,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126893008</v>
+        <v>126892985</v>
       </c>
       <c r="B53" t="n">
-        <v>80989</v>
+        <v>79632</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5827,21 +5827,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1049</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5851,10 +5851,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>865545</v>
+        <v>865491</v>
       </c>
       <c r="R53" t="n">
-        <v>7447322</v>
+        <v>7447332</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5917,10 +5917,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126892026</v>
+        <v>126892273</v>
       </c>
       <c r="B54" t="n">
-        <v>79014</v>
+        <v>78420</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5928,21 +5928,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5952,10 +5952,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>865538</v>
+        <v>865528</v>
       </c>
       <c r="R54" t="n">
-        <v>7447072</v>
+        <v>7447193</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6002,12 +6002,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6018,32 +6018,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126892029</v>
+        <v>126891916</v>
       </c>
       <c r="B55" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6053,10 +6053,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>865448</v>
+        <v>865546</v>
       </c>
       <c r="R55" t="n">
-        <v>7447418</v>
+        <v>7447133</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6103,12 +6103,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6119,10 +6119,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126892985</v>
+        <v>126893008</v>
       </c>
       <c r="B56" t="n">
-        <v>79632</v>
+        <v>80989</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6130,21 +6130,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>1049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>865491</v>
+        <v>865545</v>
       </c>
       <c r="R56" t="n">
-        <v>7447332</v>
+        <v>7447322</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6321,10 +6321,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126892273</v>
+        <v>126892026</v>
       </c>
       <c r="B58" t="n">
-        <v>78420</v>
+        <v>79014</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6332,21 +6332,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6356,10 +6356,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>865528</v>
+        <v>865538</v>
       </c>
       <c r="R58" t="n">
-        <v>7447193</v>
+        <v>7447072</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6406,12 +6406,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6422,32 +6422,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126891916</v>
+        <v>126892029</v>
       </c>
       <c r="B59" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6457,10 +6457,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>865546</v>
+        <v>865448</v>
       </c>
       <c r="R59" t="n">
-        <v>7447133</v>
+        <v>7447418</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6507,12 +6507,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6624,32 +6624,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126892177</v>
+        <v>126892982</v>
       </c>
       <c r="B61" t="n">
-        <v>92809</v>
+        <v>91291</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2079</v>
+        <v>5447</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6659,10 +6659,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>865522</v>
+        <v>865526</v>
       </c>
       <c r="R61" t="n">
-        <v>7447338</v>
+        <v>7447273</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6709,12 +6709,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6725,10 +6725,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126892982</v>
+        <v>126891915</v>
       </c>
       <c r="B62" t="n">
-        <v>91291</v>
+        <v>80146</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6736,21 +6736,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6760,10 +6760,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>865526</v>
+        <v>865551</v>
       </c>
       <c r="R62" t="n">
-        <v>7447273</v>
+        <v>7447126</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6810,12 +6810,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -6826,32 +6826,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126891915</v>
+        <v>126892177</v>
       </c>
       <c r="B63" t="n">
-        <v>80146</v>
+        <v>92809</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6462</v>
+        <v>2079</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6861,10 +6861,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>865551</v>
+        <v>865522</v>
       </c>
       <c r="R63" t="n">
-        <v>7447126</v>
+        <v>7447338</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6911,12 +6911,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7748,32 +7748,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126893282</v>
+        <v>126892187</v>
       </c>
       <c r="B72" t="n">
-        <v>79014</v>
+        <v>91487</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7783,10 +7783,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>865611</v>
+        <v>865509</v>
       </c>
       <c r="R72" t="n">
-        <v>7446989</v>
+        <v>7447371</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7833,12 +7833,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -7849,7 +7849,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126892187</v>
+        <v>126893012</v>
       </c>
       <c r="B73" t="n">
         <v>91487</v>
@@ -7884,10 +7884,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>865509</v>
+        <v>865559</v>
       </c>
       <c r="R73" t="n">
-        <v>7447371</v>
+        <v>7447299</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7934,12 +7934,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -7950,32 +7950,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126893012</v>
+        <v>126893282</v>
       </c>
       <c r="B74" t="n">
-        <v>91487</v>
+        <v>79014</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7985,10 +7985,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>865559</v>
+        <v>865611</v>
       </c>
       <c r="R74" t="n">
-        <v>7447299</v>
+        <v>7446989</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8035,12 +8035,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8253,48 +8253,57 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126888001</v>
+        <v>126891930</v>
       </c>
       <c r="B77" t="n">
-        <v>78681</v>
+        <v>8436</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>353</v>
+        <v>106554</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>865527</v>
+        <v>865561</v>
       </c>
       <c r="R77" t="n">
-        <v>7447205</v>
+        <v>7447167</v>
       </c>
       <c r="S77" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8332,50 +8341,55 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr"/>
+          <t>Amanda Rudelius</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126891929</v>
+        <v>126887974</v>
       </c>
       <c r="B78" t="n">
-        <v>79014</v>
+        <v>97327</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8385,13 +8399,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>865535</v>
+        <v>865641</v>
       </c>
       <c r="R78" t="n">
-        <v>7447142</v>
+        <v>7447070</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8435,26 +8449,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126893270</v>
+        <v>126888001</v>
       </c>
       <c r="B79" t="n">
-        <v>92809</v>
+        <v>78681</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8462,21 +8472,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8486,13 +8496,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>865491</v>
+        <v>865527</v>
       </c>
       <c r="R79" t="n">
-        <v>7447267</v>
+        <v>7447205</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8536,48 +8546,44 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
-        </is>
-      </c>
-      <c r="AY79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126891914</v>
+        <v>126891929</v>
       </c>
       <c r="B80" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8587,10 +8593,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>865539</v>
+        <v>865535</v>
       </c>
       <c r="R80" t="n">
-        <v>7447115</v>
+        <v>7447142</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8653,54 +8659,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126891930</v>
+        <v>126893270</v>
       </c>
       <c r="B81" t="n">
-        <v>8436</v>
+        <v>92809</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>106554</v>
+        <v>2079</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>865561</v>
+        <v>865491</v>
       </c>
       <c r="R81" t="n">
-        <v>7447167</v>
+        <v>7447267</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8741,19 +8738,18 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -8764,10 +8760,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126887974</v>
+        <v>126891914</v>
       </c>
       <c r="B82" t="n">
-        <v>97327</v>
+        <v>80146</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8775,21 +8771,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221941</v>
+        <v>6462</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8799,13 +8795,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>865641</v>
+        <v>865539</v>
       </c>
       <c r="R82" t="n">
-        <v>7447070</v>
+        <v>7447115</v>
       </c>
       <c r="S82" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8849,15 +8845,19 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr"/>
+          <t>Amanda Rudelius</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9564,10 +9564,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126888454</v>
+        <v>126893277</v>
       </c>
       <c r="B90" t="n">
-        <v>57817</v>
+        <v>80989</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9575,42 +9575,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>103021</v>
+        <v>1049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>865481</v>
+        <v>865647</v>
       </c>
       <c r="R90" t="n">
-        <v>7447376</v>
+        <v>7447060</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9657,12 +9649,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -9673,45 +9665,53 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126893278</v>
+        <v>126888454</v>
       </c>
       <c r="B91" t="n">
-        <v>98443</v>
+        <v>57817</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>865551</v>
+        <v>865481</v>
       </c>
       <c r="R91" t="n">
-        <v>7447276</v>
+        <v>7447376</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9758,12 +9758,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -9774,7 +9774,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126892181</v>
+        <v>126893278</v>
       </c>
       <c r="B92" t="n">
         <v>98443</v>
@@ -9809,10 +9809,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>865459</v>
+        <v>865551</v>
       </c>
       <c r="R92" t="n">
-        <v>7447305</v>
+        <v>7447276</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9859,12 +9859,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -9875,32 +9875,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126893277</v>
+        <v>126892181</v>
       </c>
       <c r="B93" t="n">
-        <v>80989</v>
+        <v>98443</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1049</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9910,10 +9910,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>865647</v>
+        <v>865459</v>
       </c>
       <c r="R93" t="n">
-        <v>7447060</v>
+        <v>7447305</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9960,12 +9960,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -9976,32 +9976,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126888000</v>
+        <v>126893025</v>
       </c>
       <c r="B94" t="n">
-        <v>78681</v>
+        <v>92616</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10011,13 +10011,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>865597</v>
+        <v>865518</v>
       </c>
       <c r="R94" t="n">
-        <v>7447186</v>
+        <v>7447235</v>
       </c>
       <c r="S94" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10061,44 +10061,48 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY94" t="inlineStr"/>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126887968</v>
+        <v>126892981</v>
       </c>
       <c r="B95" t="n">
-        <v>57817</v>
+        <v>91291</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10108,13 +10112,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>865523</v>
+        <v>865553</v>
       </c>
       <c r="R95" t="n">
-        <v>7447217</v>
+        <v>7447278</v>
       </c>
       <c r="S95" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10158,44 +10162,48 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY95" t="inlineStr"/>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126887997</v>
+        <v>126892267</v>
       </c>
       <c r="B96" t="n">
-        <v>98360</v>
+        <v>79014</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10205,13 +10213,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>865448</v>
+        <v>865516</v>
       </c>
       <c r="R96" t="n">
-        <v>7447350</v>
+        <v>7447351</v>
       </c>
       <c r="S96" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10255,44 +10263,48 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY96" t="inlineStr"/>
+          <t>Svea Nikula</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126893023</v>
+        <v>126887968</v>
       </c>
       <c r="B97" t="n">
-        <v>91727</v>
+        <v>57817</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>715</v>
+        <v>103021</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Finporing</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Gloeoporus pannocinctus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Romell) J.Erikss.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10302,13 +10314,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>865473</v>
+        <v>865523</v>
       </c>
       <c r="R97" t="n">
-        <v>7447321</v>
+        <v>7447217</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10352,48 +10364,44 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
-        </is>
-      </c>
-      <c r="AY97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126892178</v>
+        <v>126893023</v>
       </c>
       <c r="B98" t="n">
-        <v>92809</v>
+        <v>91727</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2079</v>
+        <v>715</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Finporing</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Gloeoporus pannocinctus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell) J.Erikss.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10403,10 +10411,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>865509</v>
+        <v>865473</v>
       </c>
       <c r="R98" t="n">
-        <v>7447375</v>
+        <v>7447321</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10453,12 +10461,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -10469,32 +10477,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126893281</v>
+        <v>126888000</v>
       </c>
       <c r="B99" t="n">
-        <v>91487</v>
+        <v>78681</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10504,13 +10512,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>865513</v>
+        <v>865597</v>
       </c>
       <c r="R99" t="n">
-        <v>7447339</v>
+        <v>7447186</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10554,48 +10562,44 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
-        </is>
-      </c>
-      <c r="AY99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126893025</v>
+        <v>126892178</v>
       </c>
       <c r="B100" t="n">
-        <v>92616</v>
+        <v>92809</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10605,10 +10609,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>865518</v>
+        <v>865509</v>
       </c>
       <c r="R100" t="n">
-        <v>7447235</v>
+        <v>7447375</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10655,12 +10659,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -10671,32 +10675,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126892981</v>
+        <v>126893281</v>
       </c>
       <c r="B101" t="n">
-        <v>91291</v>
+        <v>91487</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5447</v>
+        <v>1503</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10706,10 +10710,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>865553</v>
+        <v>865513</v>
       </c>
       <c r="R101" t="n">
-        <v>7447278</v>
+        <v>7447339</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10756,12 +10760,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -10772,32 +10776,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126892267</v>
+        <v>126887997</v>
       </c>
       <c r="B102" t="n">
-        <v>79014</v>
+        <v>98360</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10807,13 +10811,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>865516</v>
+        <v>865448</v>
       </c>
       <c r="R102" t="n">
-        <v>7447351</v>
+        <v>7447350</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -10857,19 +10861,15 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
-        </is>
-      </c>
-      <c r="AY102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11176,32 +11176,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126893310</v>
+        <v>126887980</v>
       </c>
       <c r="B106" t="n">
-        <v>91587</v>
+        <v>92809</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>65</v>
+        <v>2079</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11211,13 +11211,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>865653</v>
+        <v>865511</v>
       </c>
       <c r="R106" t="n">
-        <v>7447052</v>
+        <v>7447249</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11261,26 +11261,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
-        </is>
-      </c>
-      <c r="AY106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126887980</v>
+        <v>126892028</v>
       </c>
       <c r="B107" t="n">
-        <v>92809</v>
+        <v>79014</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11288,21 +11284,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11312,13 +11308,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>865511</v>
+        <v>865533</v>
       </c>
       <c r="R107" t="n">
-        <v>7447249</v>
+        <v>7447130</v>
       </c>
       <c r="S107" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11362,44 +11358,48 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY107" t="inlineStr"/>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126892028</v>
+        <v>126893310</v>
       </c>
       <c r="B108" t="n">
-        <v>79014</v>
+        <v>91587</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11409,10 +11409,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>865533</v>
+        <v>865653</v>
       </c>
       <c r="R108" t="n">
-        <v>7447130</v>
+        <v>7447052</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11459,12 +11459,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
@@ -11475,32 +11475,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126892191</v>
+        <v>126893009</v>
       </c>
       <c r="B109" t="n">
-        <v>91587</v>
+        <v>80989</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>65</v>
+        <v>1049</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11510,10 +11510,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>865540</v>
+        <v>865553</v>
       </c>
       <c r="R109" t="n">
-        <v>7447366</v>
+        <v>7447326</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11560,12 +11560,12 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
@@ -11576,10 +11576,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126893009</v>
+        <v>126887977</v>
       </c>
       <c r="B110" t="n">
-        <v>80989</v>
+        <v>92809</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11587,21 +11587,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1049</v>
+        <v>2079</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11611,13 +11611,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>865553</v>
+        <v>865643</v>
       </c>
       <c r="R110" t="n">
-        <v>7447326</v>
+        <v>7447067</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -11661,48 +11661,44 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
-        </is>
-      </c>
-      <c r="AY110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126887990</v>
+        <v>126887987</v>
       </c>
       <c r="B111" t="n">
-        <v>79014</v>
+        <v>91487</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11712,10 +11708,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>865447</v>
+        <v>865510</v>
       </c>
       <c r="R111" t="n">
-        <v>7447371</v>
+        <v>7447247</v>
       </c>
       <c r="S111" t="n">
         <v>25</v>
@@ -11774,32 +11770,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126887975</v>
+        <v>126887990</v>
       </c>
       <c r="B112" t="n">
-        <v>97327</v>
+        <v>79014</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11809,10 +11805,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>865479</v>
+        <v>865447</v>
       </c>
       <c r="R112" t="n">
-        <v>7447358</v>
+        <v>7447371</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -11871,32 +11867,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126887976</v>
+        <v>126887965</v>
       </c>
       <c r="B113" t="n">
-        <v>97327</v>
+        <v>57479</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>221941</v>
+        <v>102976</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11906,10 +11902,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>865452</v>
+        <v>865583</v>
       </c>
       <c r="R113" t="n">
-        <v>7447334</v>
+        <v>7447214</v>
       </c>
       <c r="S113" t="n">
         <v>25</v>
@@ -11968,10 +11964,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126887977</v>
+        <v>126892018</v>
       </c>
       <c r="B114" t="n">
-        <v>92809</v>
+        <v>57817</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11979,37 +11975,49 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2079</v>
+        <v>103021</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>865643</v>
+        <v>865561</v>
       </c>
       <c r="R114" t="n">
-        <v>7447067</v>
+        <v>7447155</v>
       </c>
       <c r="S114" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12053,60 +12061,72 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY114" t="inlineStr"/>
+          <t>Julia Frejd</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126887987</v>
+        <v>126892263</v>
       </c>
       <c r="B115" t="n">
-        <v>91487</v>
+        <v>56840</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1503</v>
+        <v>102612</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>865510</v>
+        <v>865544</v>
       </c>
       <c r="R115" t="n">
-        <v>7447247</v>
+        <v>7447281</v>
       </c>
       <c r="S115" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12150,65 +12170,61 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY115" t="inlineStr"/>
+          <t>Svea Nikula</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126892263</v>
+        <v>126891928</v>
       </c>
       <c r="B116" t="n">
-        <v>56840</v>
+        <v>98443</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>865544</v>
+        <v>865549</v>
       </c>
       <c r="R116" t="n">
-        <v>7447281</v>
+        <v>7447136</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12255,12 +12271,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
@@ -12271,32 +12287,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126887965</v>
+        <v>126892024</v>
       </c>
       <c r="B117" t="n">
-        <v>57479</v>
+        <v>98443</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>102976</v>
+        <v>220787</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12306,13 +12322,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>865583</v>
+        <v>865546</v>
       </c>
       <c r="R117" t="n">
-        <v>7447214</v>
+        <v>7447138</v>
       </c>
       <c r="S117" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12356,72 +12372,64 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY117" t="inlineStr"/>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126892018</v>
+        <v>126887975</v>
       </c>
       <c r="B118" t="n">
-        <v>57817</v>
+        <v>97327</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>103021</v>
+        <v>221941</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>865561</v>
+        <v>865479</v>
       </c>
       <c r="R118" t="n">
-        <v>7447155</v>
+        <v>7447358</v>
       </c>
       <c r="S118" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -12465,48 +12473,44 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
-        </is>
-      </c>
-      <c r="AY118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126891928</v>
+        <v>126887976</v>
       </c>
       <c r="B119" t="n">
-        <v>98443</v>
+        <v>97327</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12516,13 +12520,13 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>865549</v>
+        <v>865452</v>
       </c>
       <c r="R119" t="n">
-        <v>7447136</v>
+        <v>7447334</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -12566,26 +12570,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
-        </is>
-      </c>
-      <c r="AY119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126892024</v>
+        <v>126892191</v>
       </c>
       <c r="B120" t="n">
-        <v>98443</v>
+        <v>91587</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12593,21 +12593,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>220787</v>
+        <v>65</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12617,10 +12617,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>865546</v>
+        <v>865540</v>
       </c>
       <c r="R120" t="n">
-        <v>7447138</v>
+        <v>7447366</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12667,12 +12667,12 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
@@ -12683,10 +12683,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126893260</v>
+        <v>126893267</v>
       </c>
       <c r="B121" t="n">
-        <v>91248</v>
+        <v>92809</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12694,21 +12694,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>3242</v>
+        <v>2079</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12718,10 +12718,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>865498</v>
+        <v>865648</v>
       </c>
       <c r="R121" t="n">
-        <v>7447359</v>
+        <v>7447056</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12784,32 +12784,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126893262</v>
+        <v>126893260</v>
       </c>
       <c r="B122" t="n">
-        <v>91291</v>
+        <v>91248</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>5447</v>
+        <v>3242</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12819,10 +12819,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>865522</v>
+        <v>865498</v>
       </c>
       <c r="R122" t="n">
-        <v>7447308</v>
+        <v>7447359</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12885,32 +12885,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126893030</v>
+        <v>126893308</v>
       </c>
       <c r="B123" t="n">
-        <v>77992</v>
+        <v>91587</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6487</v>
+        <v>65</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12920,10 +12920,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>865545</v>
+        <v>865659</v>
       </c>
       <c r="R123" t="n">
-        <v>7447323</v>
+        <v>7447048</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12970,12 +12970,12 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
@@ -12986,10 +12986,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126887981</v>
+        <v>126893262</v>
       </c>
       <c r="B124" t="n">
-        <v>80153</v>
+        <v>91291</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12997,21 +12997,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6464</v>
+        <v>5447</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13021,13 +13021,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>865448</v>
+        <v>865522</v>
       </c>
       <c r="R124" t="n">
-        <v>7447345</v>
+        <v>7447308</v>
       </c>
       <c r="S124" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13071,44 +13071,48 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY124" t="inlineStr"/>
+          <t>Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126893308</v>
+        <v>126893030</v>
       </c>
       <c r="B125" t="n">
-        <v>91587</v>
+        <v>77992</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>65</v>
+        <v>6487</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13118,10 +13122,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>865659</v>
+        <v>865545</v>
       </c>
       <c r="R125" t="n">
-        <v>7447048</v>
+        <v>7447323</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13168,12 +13172,12 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
@@ -13184,32 +13188,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126893267</v>
+        <v>126887981</v>
       </c>
       <c r="B126" t="n">
-        <v>92809</v>
+        <v>80153</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>2079</v>
+        <v>6464</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13219,13 +13223,13 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>865648</v>
+        <v>865448</v>
       </c>
       <c r="R126" t="n">
-        <v>7447056</v>
+        <v>7447345</v>
       </c>
       <c r="S126" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13269,19 +13273,15 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
-        </is>
-      </c>
-      <c r="AY126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14393,10 +14393,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126892984</v>
+        <v>126893034</v>
       </c>
       <c r="B138" t="n">
-        <v>79632</v>
+        <v>78420</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14404,21 +14404,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14428,10 +14428,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>865523</v>
+        <v>865544</v>
       </c>
       <c r="R138" t="n">
-        <v>7447267</v>
+        <v>7447321</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14494,7 +14494,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126887962</v>
+        <v>126892984</v>
       </c>
       <c r="B139" t="n">
         <v>79632</v>
@@ -14529,13 +14529,13 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>865519</v>
+        <v>865523</v>
       </c>
       <c r="R139" t="n">
-        <v>7447214</v>
+        <v>7447267</v>
       </c>
       <c r="S139" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -14579,22 +14579,26 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY139" t="inlineStr"/>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126893034</v>
+        <v>126887962</v>
       </c>
       <c r="B140" t="n">
-        <v>78420</v>
+        <v>79632</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14602,21 +14606,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14626,13 +14630,13 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>865544</v>
+        <v>865519</v>
       </c>
       <c r="R140" t="n">
-        <v>7447321</v>
+        <v>7447214</v>
       </c>
       <c r="S140" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -14676,26 +14680,22 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
-        </is>
-      </c>
-      <c r="AY140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126888456</v>
+        <v>126892253</v>
       </c>
       <c r="B141" t="n">
-        <v>92809</v>
+        <v>91248</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14703,21 +14703,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2079</v>
+        <v>3242</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14727,10 +14727,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>865506</v>
+        <v>865491</v>
       </c>
       <c r="R141" t="n">
-        <v>7447238</v>
+        <v>7447326</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14777,12 +14777,12 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
@@ -14793,32 +14793,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126887971</v>
+        <v>126888456</v>
       </c>
       <c r="B142" t="n">
-        <v>80146</v>
+        <v>92809</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6462</v>
+        <v>2079</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14828,13 +14828,13 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>865452</v>
+        <v>865506</v>
       </c>
       <c r="R142" t="n">
-        <v>7447318</v>
+        <v>7447238</v>
       </c>
       <c r="S142" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -14878,19 +14878,23 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY142" t="inlineStr"/>
+          <t>Alva Dahlqvist Cederstrand</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126892991</v>
+        <v>126887971</v>
       </c>
       <c r="B143" t="n">
         <v>80146</v>
@@ -14925,13 +14929,13 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>865531</v>
+        <v>865452</v>
       </c>
       <c r="R143" t="n">
-        <v>7447308</v>
+        <v>7447318</v>
       </c>
       <c r="S143" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -14975,23 +14979,19 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
-        </is>
-      </c>
-      <c r="AY143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>126891917</v>
+        <v>126892991</v>
       </c>
       <c r="B144" t="n">
         <v>80146</v>
@@ -15026,10 +15026,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>865561</v>
+        <v>865531</v>
       </c>
       <c r="R144" t="n">
-        <v>7447152</v>
+        <v>7447308</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15076,12 +15076,12 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
@@ -15092,32 +15092,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126892253</v>
+        <v>126891917</v>
       </c>
       <c r="B145" t="n">
-        <v>91248</v>
+        <v>80146</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>3242</v>
+        <v>6462</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15127,10 +15127,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>865491</v>
+        <v>865561</v>
       </c>
       <c r="R145" t="n">
-        <v>7447326</v>
+        <v>7447152</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15177,12 +15177,12 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
@@ -16115,32 +16115,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126887979</v>
+        <v>126892255</v>
       </c>
       <c r="B155" t="n">
-        <v>92809</v>
+        <v>91291</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>2079</v>
+        <v>5447</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16150,13 +16150,13 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>865510</v>
+        <v>865462</v>
       </c>
       <c r="R155" t="n">
-        <v>7447251</v>
+        <v>7447413</v>
       </c>
       <c r="S155" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -16200,22 +16200,26 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY155" t="inlineStr"/>
+          <t>Svea Nikula</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>126892974</v>
+        <v>126892272</v>
       </c>
       <c r="B156" t="n">
-        <v>91248</v>
+        <v>77992</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16223,21 +16227,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>3242</v>
+        <v>6487</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16247,10 +16251,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>865494</v>
+        <v>865528</v>
       </c>
       <c r="R156" t="n">
-        <v>7447322</v>
+        <v>7447192</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16297,12 +16301,12 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
@@ -16313,32 +16317,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126892255</v>
+        <v>126887979</v>
       </c>
       <c r="B157" t="n">
-        <v>91291</v>
+        <v>92809</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>5447</v>
+        <v>2079</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16348,13 +16352,13 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>865462</v>
+        <v>865510</v>
       </c>
       <c r="R157" t="n">
-        <v>7447413</v>
+        <v>7447251</v>
       </c>
       <c r="S157" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -16398,26 +16402,22 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
-        </is>
-      </c>
-      <c r="AY157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>126892272</v>
+        <v>126892974</v>
       </c>
       <c r="B158" t="n">
-        <v>77992</v>
+        <v>91248</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16425,21 +16425,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6487</v>
+        <v>3242</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16449,10 +16449,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>865528</v>
+        <v>865494</v>
       </c>
       <c r="R158" t="n">
-        <v>7447192</v>
+        <v>7447322</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16499,12 +16499,12 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
@@ -16515,32 +16515,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>126893272</v>
+        <v>126888458</v>
       </c>
       <c r="B159" t="n">
-        <v>92809</v>
+        <v>91487</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>2079</v>
+        <v>1503</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16550,10 +16550,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>865520</v>
+        <v>865502</v>
       </c>
       <c r="R159" t="n">
-        <v>7447337</v>
+        <v>7447310</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16600,12 +16600,12 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
@@ -16616,32 +16616,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>126888458</v>
+        <v>126893291</v>
       </c>
       <c r="B160" t="n">
-        <v>91487</v>
+        <v>79014</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16651,10 +16651,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>865502</v>
+        <v>865507</v>
       </c>
       <c r="R160" t="n">
-        <v>7447310</v>
+        <v>7447151</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16701,12 +16701,12 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
@@ -16717,32 +16717,32 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>126893291</v>
+        <v>126892016</v>
       </c>
       <c r="B161" t="n">
-        <v>79014</v>
+        <v>91291</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16752,10 +16752,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>865507</v>
+        <v>865558</v>
       </c>
       <c r="R161" t="n">
-        <v>7447151</v>
+        <v>7447154</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16802,12 +16802,12 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
@@ -16818,45 +16818,48 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>126892016</v>
+        <v>126891924</v>
       </c>
       <c r="B162" t="n">
-        <v>91291</v>
+        <v>78772</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>865558</v>
+        <v>865562</v>
       </c>
       <c r="R162" t="n">
-        <v>7447154</v>
+        <v>7447150</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16897,18 +16900,19 @@
       <c r="AE162" t="b">
         <v>0</v>
       </c>
+      <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="b">
         <v>0</v>
       </c>
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
@@ -16919,10 +16923,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>126891924</v>
+        <v>126887961</v>
       </c>
       <c r="B163" t="n">
-        <v>78772</v>
+        <v>79632</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16930,40 +16934,37 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
-      <c r="K163" t="inlineStr"/>
-      <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>865562</v>
+        <v>865602</v>
       </c>
       <c r="R163" t="n">
-        <v>7447150</v>
+        <v>7447176</v>
       </c>
       <c r="S163" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -17001,33 +17002,28 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
-      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
-        </is>
-      </c>
-      <c r="AY163" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>126887961</v>
+        <v>126893272</v>
       </c>
       <c r="B164" t="n">
-        <v>79632</v>
+        <v>92809</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17035,21 +17031,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17059,13 +17055,13 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>865602</v>
+        <v>865520</v>
       </c>
       <c r="R164" t="n">
-        <v>7447176</v>
+        <v>7447337</v>
       </c>
       <c r="S164" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -17109,15 +17105,19 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY164" t="inlineStr"/>
+          <t>Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -17323,32 +17323,32 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>126893021</v>
+        <v>126892988</v>
       </c>
       <c r="B167" t="n">
-        <v>91587</v>
+        <v>57479</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>65</v>
+        <v>102976</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17358,10 +17358,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>865547</v>
+        <v>865530</v>
       </c>
       <c r="R167" t="n">
-        <v>7447316</v>
+        <v>7447298</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17424,7 +17424,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>126893309</v>
+        <v>126893021</v>
       </c>
       <c r="B168" t="n">
         <v>91587</v>
@@ -17459,10 +17459,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>865661</v>
+        <v>865547</v>
       </c>
       <c r="R168" t="n">
-        <v>7447053</v>
+        <v>7447316</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17509,12 +17509,12 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
@@ -17525,32 +17525,32 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>126893031</v>
+        <v>126893309</v>
       </c>
       <c r="B169" t="n">
-        <v>77992</v>
+        <v>91587</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6487</v>
+        <v>65</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17560,10 +17560,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>865490</v>
+        <v>865661</v>
       </c>
       <c r="R169" t="n">
-        <v>7447338</v>
+        <v>7447053</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17610,12 +17610,12 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
@@ -17626,32 +17626,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>126892988</v>
+        <v>126893284</v>
       </c>
       <c r="B170" t="n">
-        <v>57479</v>
+        <v>79014</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>102976</v>
+        <v>6425</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17661,10 +17661,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>865530</v>
+        <v>865543</v>
       </c>
       <c r="R170" t="n">
-        <v>7447298</v>
+        <v>7447053</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17711,12 +17711,12 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr">
@@ -17727,10 +17727,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>126893284</v>
+        <v>126893031</v>
       </c>
       <c r="B171" t="n">
-        <v>79014</v>
+        <v>77992</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17738,21 +17738,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -17762,10 +17762,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>865543</v>
+        <v>865490</v>
       </c>
       <c r="R171" t="n">
-        <v>7447053</v>
+        <v>7447338</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17812,12 +17812,12 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
@@ -18228,10 +18228,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>126893294</v>
+        <v>126891913</v>
       </c>
       <c r="B176" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18239,21 +18239,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18263,10 +18263,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>865457</v>
+        <v>865557</v>
       </c>
       <c r="R176" t="n">
-        <v>7447523</v>
+        <v>7447153</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18313,12 +18313,12 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr">
@@ -18329,10 +18329,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>126891913</v>
+        <v>126892986</v>
       </c>
       <c r="B177" t="n">
-        <v>79632</v>
+        <v>79603</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18340,21 +18340,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18364,10 +18364,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>865557</v>
+        <v>865489</v>
       </c>
       <c r="R177" t="n">
-        <v>7447153</v>
+        <v>7447329</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18414,12 +18414,12 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
@@ -18430,32 +18430,32 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>126892997</v>
+        <v>126893294</v>
       </c>
       <c r="B178" t="n">
-        <v>79038</v>
+        <v>79014</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18465,10 +18465,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>865545</v>
+        <v>865457</v>
       </c>
       <c r="R178" t="n">
-        <v>7447323</v>
+        <v>7447523</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18515,12 +18515,12 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr">
@@ -18531,32 +18531,32 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>126893314</v>
+        <v>126892997</v>
       </c>
       <c r="B179" t="n">
-        <v>78420</v>
+        <v>79038</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6437</v>
+        <v>6434</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -18566,10 +18566,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>865647</v>
+        <v>865545</v>
       </c>
       <c r="R179" t="n">
-        <v>7447060</v>
+        <v>7447323</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18616,12 +18616,12 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
@@ -18632,10 +18632,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>126892986</v>
+        <v>126893314</v>
       </c>
       <c r="B180" t="n">
-        <v>79603</v>
+        <v>78420</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18643,21 +18643,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -18667,10 +18667,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>865489</v>
+        <v>865647</v>
       </c>
       <c r="R180" t="n">
-        <v>7447329</v>
+        <v>7447060</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18717,12 +18717,12 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">

--- a/artfynd/A 52625-2022 artfynd.xlsx
+++ b/artfynd/A 52625-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126891921</v>
       </c>
       <c r="B2" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126891918</v>
       </c>
       <c r="B3" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>126892265</v>
       </c>
       <c r="B4" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126893005</v>
+        <v>126891922</v>
       </c>
       <c r="B5" t="n">
-        <v>80153</v>
+        <v>80150</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>865370</v>
+        <v>865415</v>
       </c>
       <c r="R5" t="n">
-        <v>7447622</v>
+        <v>7447651</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,12 +1063,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126891922</v>
+        <v>126893005</v>
       </c>
       <c r="B6" t="n">
-        <v>80146</v>
+        <v>80157</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>865415</v>
+        <v>865370</v>
       </c>
       <c r="R6" t="n">
-        <v>7447651</v>
+        <v>7447622</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,12 +1164,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1180,32 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126893275</v>
+        <v>126893295</v>
       </c>
       <c r="B7" t="n">
-        <v>80153</v>
+        <v>79018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>865427</v>
+        <v>865429</v>
       </c>
       <c r="R7" t="n">
-        <v>7447587</v>
+        <v>7447550</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,32 +1281,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126892019</v>
+        <v>126893300</v>
       </c>
       <c r="B8" t="n">
-        <v>80146</v>
+        <v>79018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>865429</v>
+        <v>865378</v>
       </c>
       <c r="R8" t="n">
-        <v>7447523</v>
+        <v>7447665</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1366,12 +1366,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1382,32 +1382,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126893295</v>
+        <v>126892019</v>
       </c>
       <c r="B9" t="n">
-        <v>79014</v>
+        <v>80150</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1420,7 +1420,7 @@
         <v>865429</v>
       </c>
       <c r="R9" t="n">
-        <v>7447550</v>
+        <v>7447523</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1467,12 +1467,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1483,32 +1483,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126893300</v>
+        <v>126893275</v>
       </c>
       <c r="B10" t="n">
-        <v>79014</v>
+        <v>80157</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>865378</v>
+        <v>865427</v>
       </c>
       <c r="R10" t="n">
-        <v>7447665</v>
+        <v>7447587</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1587,7 +1587,7 @@
         <v>126892270</v>
       </c>
       <c r="B11" t="n">
-        <v>91900</v>
+        <v>91904</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1697,32 +1697,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126887991</v>
+        <v>126892999</v>
       </c>
       <c r="B12" t="n">
-        <v>79014</v>
+        <v>80149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1732,13 +1732,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>865422</v>
+        <v>865426</v>
       </c>
       <c r="R12" t="n">
-        <v>7447458</v>
+        <v>7447493</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1782,44 +1782,48 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126887992</v>
+        <v>126892173</v>
       </c>
       <c r="B13" t="n">
-        <v>79014</v>
+        <v>80150</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1829,13 +1833,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>865406</v>
+        <v>865379</v>
       </c>
       <c r="R13" t="n">
-        <v>7447461</v>
+        <v>7447558</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1879,44 +1883,48 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126892999</v>
+        <v>126887991</v>
       </c>
       <c r="B14" t="n">
-        <v>80145</v>
+        <v>79018</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1926,13 +1934,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>865426</v>
+        <v>865422</v>
       </c>
       <c r="R14" t="n">
-        <v>7447493</v>
+        <v>7447458</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1976,48 +1984,44 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126892173</v>
+        <v>126887992</v>
       </c>
       <c r="B15" t="n">
-        <v>80146</v>
+        <v>79018</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2027,13 +2031,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>865379</v>
+        <v>865406</v>
       </c>
       <c r="R15" t="n">
-        <v>7447558</v>
+        <v>7447461</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2077,26 +2081,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>126892264</v>
       </c>
       <c r="B16" t="n">
-        <v>58516</v>
+        <v>58520</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>126893016</v>
       </c>
       <c r="B17" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2296,10 +2296,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126893017</v>
+        <v>126893301</v>
       </c>
       <c r="B18" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2331,10 +2331,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>865409</v>
+        <v>865382</v>
       </c>
       <c r="R18" t="n">
-        <v>7447573</v>
+        <v>7447699</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2381,12 +2381,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2397,10 +2397,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126893301</v>
+        <v>126893017</v>
       </c>
       <c r="B19" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>865382</v>
+        <v>865409</v>
       </c>
       <c r="R19" t="n">
-        <v>7447699</v>
+        <v>7447573</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2482,12 +2482,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2501,7 +2501,7 @@
         <v>126893004</v>
       </c>
       <c r="B20" t="n">
-        <v>80153</v>
+        <v>80157</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2599,32 +2599,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126893293</v>
+        <v>126891920</v>
       </c>
       <c r="B21" t="n">
-        <v>79014</v>
+        <v>80150</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2634,10 +2634,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>865430</v>
+        <v>865438</v>
       </c>
       <c r="R21" t="n">
-        <v>7447483</v>
+        <v>7447459</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2684,12 +2684,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2700,10 +2700,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126891920</v>
+        <v>126892172</v>
       </c>
       <c r="B22" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2735,10 +2735,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>865438</v>
+        <v>865436</v>
       </c>
       <c r="R22" t="n">
-        <v>7447459</v>
+        <v>7447532</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2785,12 +2785,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2801,10 +2801,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126892172</v>
+        <v>126893276</v>
       </c>
       <c r="B23" t="n">
-        <v>80146</v>
+        <v>80157</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2812,21 +2812,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2836,10 +2836,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>865436</v>
+        <v>865406</v>
       </c>
       <c r="R23" t="n">
-        <v>7447532</v>
+        <v>7447661</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2886,12 +2886,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2902,32 +2902,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126893276</v>
+        <v>126893293</v>
       </c>
       <c r="B24" t="n">
-        <v>80153</v>
+        <v>79018</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2937,10 +2937,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>865406</v>
+        <v>865430</v>
       </c>
       <c r="R24" t="n">
-        <v>7447661</v>
+        <v>7447483</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3003,32 +3003,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126888460</v>
+        <v>126892261</v>
       </c>
       <c r="B25" t="n">
-        <v>79014</v>
+        <v>80157</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>865380</v>
+        <v>865434</v>
       </c>
       <c r="R25" t="n">
-        <v>7447610</v>
+        <v>7447569</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3088,12 +3088,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3104,10 +3104,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126892261</v>
+        <v>126887982</v>
       </c>
       <c r="B26" t="n">
-        <v>80153</v>
+        <v>80157</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3142,10 +3142,10 @@
         <v>865434</v>
       </c>
       <c r="R26" t="n">
-        <v>7447569</v>
+        <v>7447388</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3189,48 +3189,44 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126887982</v>
+        <v>126888460</v>
       </c>
       <c r="B27" t="n">
-        <v>80153</v>
+        <v>79018</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3240,13 +3236,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>865434</v>
+        <v>865380</v>
       </c>
       <c r="R27" t="n">
-        <v>7447388</v>
+        <v>7447610</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3290,44 +3286,48 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Alva Dahlqvist Cederstrand</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126892179</v>
+        <v>126893015</v>
       </c>
       <c r="B28" t="n">
-        <v>80153</v>
+        <v>79018</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>865377</v>
+        <v>865423</v>
       </c>
       <c r="R28" t="n">
-        <v>7447525</v>
+        <v>7447442</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3387,12 +3387,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3403,32 +3403,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126892030</v>
+        <v>126892179</v>
       </c>
       <c r="B29" t="n">
-        <v>79014</v>
+        <v>80157</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3438,10 +3438,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>865389</v>
+        <v>865377</v>
       </c>
       <c r="R29" t="n">
-        <v>7447613</v>
+        <v>7447525</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3488,12 +3488,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3504,10 +3504,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126893015</v>
+        <v>126892030</v>
       </c>
       <c r="B30" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3539,10 +3539,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>865423</v>
+        <v>865389</v>
       </c>
       <c r="R30" t="n">
-        <v>7447442</v>
+        <v>7447613</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3589,12 +3589,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3608,7 +3608,7 @@
         <v>126893299</v>
       </c>
       <c r="B31" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         <v>126892021</v>
       </c>
       <c r="B32" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3807,32 +3807,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126893306</v>
+        <v>126892262</v>
       </c>
       <c r="B33" t="n">
-        <v>82855</v>
+        <v>80157</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3842,10 +3842,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>865378</v>
+        <v>865404</v>
       </c>
       <c r="R33" t="n">
-        <v>7447665</v>
+        <v>7447633</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3892,12 +3892,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -3908,32 +3908,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126892262</v>
+        <v>126887969</v>
       </c>
       <c r="B34" t="n">
-        <v>80153</v>
+        <v>57821</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3943,13 +3943,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>865404</v>
+        <v>865406</v>
       </c>
       <c r="R34" t="n">
-        <v>7447633</v>
+        <v>7447461</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3993,26 +3993,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126887969</v>
+        <v>126893306</v>
       </c>
       <c r="B35" t="n">
-        <v>57817</v>
+        <v>82859</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4020,21 +4016,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4044,13 +4040,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>865406</v>
+        <v>865378</v>
       </c>
       <c r="R35" t="n">
-        <v>7447461</v>
+        <v>7447665</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4094,22 +4090,26 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
+          <t>Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
         <v>126892259</v>
       </c>
       <c r="B36" t="n">
-        <v>98464</v>
+        <v>98468</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4210,7 +4210,7 @@
         <v>126893298</v>
       </c>
       <c r="B37" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         <v>126887993</v>
       </c>
       <c r="B38" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         <v>126892978</v>
       </c>
       <c r="B39" t="n">
-        <v>75138</v>
+        <v>75142</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         <v>126893266</v>
       </c>
       <c r="B40" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>126892989</v>
       </c>
       <c r="B41" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>126893297</v>
       </c>
       <c r="B42" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>126893022</v>
       </c>
       <c r="B43" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4910,32 +4910,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126892268</v>
+        <v>126893273</v>
       </c>
       <c r="B44" t="n">
-        <v>79014</v>
+        <v>80157</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4945,10 +4945,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>865411</v>
+        <v>865406</v>
       </c>
       <c r="R44" t="n">
-        <v>7447532</v>
+        <v>7447648</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4995,12 +4995,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -5011,10 +5011,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126893273</v>
+        <v>126892258</v>
       </c>
       <c r="B45" t="n">
-        <v>80153</v>
+        <v>80150</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5022,21 +5022,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5046,10 +5046,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>865406</v>
+        <v>865430</v>
       </c>
       <c r="R45" t="n">
-        <v>7447648</v>
+        <v>7447566</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5096,12 +5096,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5112,32 +5112,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126892258</v>
+        <v>126892268</v>
       </c>
       <c r="B46" t="n">
-        <v>80146</v>
+        <v>79018</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5147,10 +5147,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>865430</v>
+        <v>865411</v>
       </c>
       <c r="R46" t="n">
-        <v>7447566</v>
+        <v>7447532</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5216,7 +5216,7 @@
         <v>126887994</v>
       </c>
       <c r="B47" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5310,10 +5310,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126893028</v>
+        <v>126892020</v>
       </c>
       <c r="B48" t="n">
-        <v>80152</v>
+        <v>80150</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5321,21 +5321,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5345,10 +5345,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>865390</v>
+        <v>865440</v>
       </c>
       <c r="R48" t="n">
-        <v>7447609</v>
+        <v>7447393</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5395,12 +5395,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5411,10 +5411,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126892020</v>
+        <v>126893028</v>
       </c>
       <c r="B49" t="n">
-        <v>80146</v>
+        <v>80156</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5422,21 +5422,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5446,10 +5446,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>865440</v>
+        <v>865390</v>
       </c>
       <c r="R49" t="n">
-        <v>7447393</v>
+        <v>7447609</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5496,12 +5496,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5515,7 +5515,7 @@
         <v>126892254</v>
       </c>
       <c r="B50" t="n">
-        <v>75138</v>
+        <v>75142</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>126887983</v>
       </c>
       <c r="B51" t="n">
-        <v>80153</v>
+        <v>80157</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>126765146</v>
       </c>
       <c r="B52" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5816,10 +5816,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126892985</v>
+        <v>126892026</v>
       </c>
       <c r="B53" t="n">
-        <v>79632</v>
+        <v>79018</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5827,21 +5827,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5851,10 +5851,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>865491</v>
+        <v>865538</v>
       </c>
       <c r="R53" t="n">
-        <v>7447332</v>
+        <v>7447072</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5901,12 +5901,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -5917,10 +5917,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126892273</v>
+        <v>126892029</v>
       </c>
       <c r="B54" t="n">
-        <v>78420</v>
+        <v>79018</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5928,21 +5928,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5952,10 +5952,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>865528</v>
+        <v>865448</v>
       </c>
       <c r="R54" t="n">
-        <v>7447193</v>
+        <v>7447418</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6002,12 +6002,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6018,32 +6018,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126891916</v>
+        <v>126892273</v>
       </c>
       <c r="B55" t="n">
-        <v>80146</v>
+        <v>78424</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6462</v>
+        <v>6437</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6053,10 +6053,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>865546</v>
+        <v>865528</v>
       </c>
       <c r="R55" t="n">
-        <v>7447133</v>
+        <v>7447193</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6103,12 +6103,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6119,32 +6119,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126893008</v>
+        <v>126891927</v>
       </c>
       <c r="B56" t="n">
-        <v>80989</v>
+        <v>98447</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1049</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>865545</v>
+        <v>865543</v>
       </c>
       <c r="R56" t="n">
-        <v>7447322</v>
+        <v>7447122</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6204,12 +6204,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6223,7 +6223,7 @@
         <v>126893280</v>
       </c>
       <c r="B57" t="n">
-        <v>91487</v>
+        <v>91491</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6321,10 +6321,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126892026</v>
+        <v>126893008</v>
       </c>
       <c r="B58" t="n">
-        <v>79014</v>
+        <v>80993</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6332,21 +6332,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6356,10 +6356,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>865538</v>
+        <v>865545</v>
       </c>
       <c r="R58" t="n">
-        <v>7447072</v>
+        <v>7447322</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6406,12 +6406,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6422,10 +6422,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126892029</v>
+        <v>126892985</v>
       </c>
       <c r="B59" t="n">
-        <v>79014</v>
+        <v>79636</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6433,21 +6433,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6457,10 +6457,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>865448</v>
+        <v>865491</v>
       </c>
       <c r="R59" t="n">
-        <v>7447418</v>
+        <v>7447332</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6507,12 +6507,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6523,32 +6523,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126891927</v>
+        <v>126891916</v>
       </c>
       <c r="B60" t="n">
-        <v>98443</v>
+        <v>80150</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6558,10 +6558,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>865543</v>
+        <v>865546</v>
       </c>
       <c r="R60" t="n">
-        <v>7447122</v>
+        <v>7447133</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6624,32 +6624,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126892982</v>
+        <v>126892177</v>
       </c>
       <c r="B61" t="n">
-        <v>91291</v>
+        <v>92813</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5447</v>
+        <v>2079</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6659,10 +6659,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>865526</v>
+        <v>865522</v>
       </c>
       <c r="R61" t="n">
-        <v>7447273</v>
+        <v>7447338</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6709,12 +6709,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6725,10 +6725,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126891915</v>
+        <v>126892982</v>
       </c>
       <c r="B62" t="n">
-        <v>80146</v>
+        <v>91295</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6736,21 +6736,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6760,10 +6760,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>865551</v>
+        <v>865526</v>
       </c>
       <c r="R62" t="n">
-        <v>7447126</v>
+        <v>7447273</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6810,12 +6810,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -6826,32 +6826,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126892177</v>
+        <v>126891915</v>
       </c>
       <c r="B63" t="n">
-        <v>92809</v>
+        <v>80150</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2079</v>
+        <v>6462</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6861,10 +6861,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>865522</v>
+        <v>865551</v>
       </c>
       <c r="R63" t="n">
-        <v>7447338</v>
+        <v>7447126</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6911,12 +6911,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -6930,7 +6930,7 @@
         <v>126887985</v>
       </c>
       <c r="B64" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7024,10 +7024,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126893010</v>
+        <v>126893000</v>
       </c>
       <c r="B65" t="n">
-        <v>80989</v>
+        <v>92813</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7035,21 +7035,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1049</v>
+        <v>2079</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7059,10 +7059,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>865490</v>
+        <v>865559</v>
       </c>
       <c r="R65" t="n">
-        <v>7447332</v>
+        <v>7447299</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7125,32 +7125,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126888002</v>
+        <v>126892998</v>
       </c>
       <c r="B66" t="n">
-        <v>78681</v>
+        <v>80149</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>353</v>
+        <v>6461</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7160,13 +7160,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>865512</v>
+        <v>865477</v>
       </c>
       <c r="R66" t="n">
-        <v>7447340</v>
+        <v>7447327</v>
       </c>
       <c r="S66" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7210,22 +7210,26 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr"/>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126893000</v>
+        <v>126893312</v>
       </c>
       <c r="B67" t="n">
-        <v>92809</v>
+        <v>77996</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7233,21 +7237,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2079</v>
+        <v>6487</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7257,10 +7261,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>865559</v>
+        <v>865598</v>
       </c>
       <c r="R67" t="n">
-        <v>7447299</v>
+        <v>7447181</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7307,12 +7311,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7323,10 +7327,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126893312</v>
+        <v>126892183</v>
       </c>
       <c r="B68" t="n">
-        <v>77992</v>
+        <v>56844</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7334,34 +7338,50 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6487</v>
+        <v>102612</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>pulli</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>pulli/nyligen flygga ungar</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>865598</v>
+        <v>865484</v>
       </c>
       <c r="R68" t="n">
-        <v>7447181</v>
+        <v>7447494</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7396,6 +7416,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Stötte up 5st kycklingar, höll till under en och samma fallen gran</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -7408,12 +7433,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7424,32 +7449,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126892998</v>
+        <v>126888002</v>
       </c>
       <c r="B69" t="n">
-        <v>80145</v>
+        <v>78685</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6461</v>
+        <v>353</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7459,13 +7484,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>865477</v>
+        <v>865512</v>
       </c>
       <c r="R69" t="n">
-        <v>7447327</v>
+        <v>7447340</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7509,26 +7534,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126892183</v>
+        <v>126893010</v>
       </c>
       <c r="B70" t="n">
-        <v>56840</v>
+        <v>80993</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7536,50 +7557,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>102612</v>
+        <v>1049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>pulli</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>pulli/nyligen flygga ungar</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>865484</v>
+        <v>865490</v>
       </c>
       <c r="R70" t="n">
-        <v>7447494</v>
+        <v>7447332</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7614,11 +7619,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Stötte up 5st kycklingar, höll till under en och samma fallen gran</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -7631,12 +7631,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7650,7 +7650,7 @@
         <v>126891925</v>
       </c>
       <c r="B71" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7748,10 +7748,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126892187</v>
+        <v>126891926</v>
       </c>
       <c r="B72" t="n">
-        <v>91487</v>
+        <v>98447</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7759,21 +7759,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1503</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7783,10 +7783,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>865509</v>
+        <v>865541</v>
       </c>
       <c r="R72" t="n">
-        <v>7447371</v>
+        <v>7447113</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7833,12 +7833,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -7849,10 +7849,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126893012</v>
+        <v>126892187</v>
       </c>
       <c r="B73" t="n">
-        <v>91487</v>
+        <v>91491</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7884,10 +7884,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>865559</v>
+        <v>865509</v>
       </c>
       <c r="R73" t="n">
-        <v>7447299</v>
+        <v>7447371</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7934,12 +7934,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -7950,32 +7950,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126893282</v>
+        <v>126893012</v>
       </c>
       <c r="B74" t="n">
-        <v>79014</v>
+        <v>91491</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7985,10 +7985,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>865611</v>
+        <v>865559</v>
       </c>
       <c r="R74" t="n">
-        <v>7446989</v>
+        <v>7447299</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8035,12 +8035,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8054,7 +8054,7 @@
         <v>126891911</v>
       </c>
       <c r="B75" t="n">
-        <v>91291</v>
+        <v>91295</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8152,32 +8152,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126891926</v>
+        <v>126893282</v>
       </c>
       <c r="B76" t="n">
-        <v>98443</v>
+        <v>79018</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8187,10 +8187,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>865541</v>
+        <v>865611</v>
       </c>
       <c r="R76" t="n">
-        <v>7447113</v>
+        <v>7446989</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8237,12 +8237,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8256,7 +8256,7 @@
         <v>126891930</v>
       </c>
       <c r="B77" t="n">
-        <v>8436</v>
+        <v>8439</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         <v>126887974</v>
       </c>
       <c r="B78" t="n">
-        <v>97327</v>
+        <v>97331</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         <v>126888001</v>
       </c>
       <c r="B79" t="n">
-        <v>78681</v>
+        <v>78685</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8558,32 +8558,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126891929</v>
+        <v>126891914</v>
       </c>
       <c r="B80" t="n">
-        <v>79014</v>
+        <v>80150</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8593,10 +8593,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>865535</v>
+        <v>865539</v>
       </c>
       <c r="R80" t="n">
-        <v>7447142</v>
+        <v>7447115</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8659,10 +8659,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126893270</v>
+        <v>126891929</v>
       </c>
       <c r="B81" t="n">
-        <v>92809</v>
+        <v>79018</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8670,21 +8670,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8694,10 +8694,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>865491</v>
+        <v>865535</v>
       </c>
       <c r="R81" t="n">
-        <v>7447267</v>
+        <v>7447142</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8744,12 +8744,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -8760,32 +8760,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126891914</v>
+        <v>126893270</v>
       </c>
       <c r="B82" t="n">
-        <v>80146</v>
+        <v>92813</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6462</v>
+        <v>2079</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8795,10 +8795,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>865539</v>
+        <v>865491</v>
       </c>
       <c r="R82" t="n">
-        <v>7447115</v>
+        <v>7447267</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8845,12 +8845,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -8861,32 +8861,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126892175</v>
+        <v>126888457</v>
       </c>
       <c r="B83" t="n">
-        <v>92809</v>
+        <v>91491</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2079</v>
+        <v>1503</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8896,10 +8896,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>865509</v>
+        <v>865528</v>
       </c>
       <c r="R83" t="n">
-        <v>7447217</v>
+        <v>7447201</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8946,12 +8946,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -8962,32 +8962,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126887978</v>
+        <v>126892185</v>
       </c>
       <c r="B84" t="n">
-        <v>92809</v>
+        <v>91491</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2079</v>
+        <v>1503</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8997,13 +8997,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>865521</v>
+        <v>865490</v>
       </c>
       <c r="R84" t="n">
-        <v>7447240</v>
+        <v>7447287</v>
       </c>
       <c r="S84" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9047,44 +9047,48 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY84" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126888457</v>
+        <v>126892175</v>
       </c>
       <c r="B85" t="n">
-        <v>91487</v>
+        <v>92813</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1503</v>
+        <v>2079</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9094,10 +9098,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>865528</v>
+        <v>865509</v>
       </c>
       <c r="R85" t="n">
-        <v>7447201</v>
+        <v>7447217</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9144,12 +9148,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -9160,32 +9164,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126892185</v>
+        <v>126887978</v>
       </c>
       <c r="B86" t="n">
-        <v>91487</v>
+        <v>92813</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1503</v>
+        <v>2079</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9195,13 +9199,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>865490</v>
+        <v>865521</v>
       </c>
       <c r="R86" t="n">
-        <v>7447287</v>
+        <v>7447240</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9245,26 +9249,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
         <v>126892192</v>
       </c>
       <c r="B87" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9362,10 +9362,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126893003</v>
+        <v>126892271</v>
       </c>
       <c r="B88" t="n">
-        <v>80153</v>
+        <v>80156</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9373,21 +9373,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9397,10 +9397,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>865532</v>
+        <v>865610</v>
       </c>
       <c r="R88" t="n">
-        <v>7447307</v>
+        <v>7447145</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9447,12 +9447,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -9463,32 +9463,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126892271</v>
+        <v>126893278</v>
       </c>
       <c r="B89" t="n">
-        <v>80152</v>
+        <v>98447</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9498,10 +9498,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>865610</v>
+        <v>865551</v>
       </c>
       <c r="R89" t="n">
-        <v>7447145</v>
+        <v>7447276</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9548,12 +9548,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -9564,32 +9564,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126893277</v>
+        <v>126892181</v>
       </c>
       <c r="B90" t="n">
-        <v>80989</v>
+        <v>98447</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1049</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9599,10 +9599,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>865647</v>
+        <v>865459</v>
       </c>
       <c r="R90" t="n">
-        <v>7447060</v>
+        <v>7447305</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9649,12 +9649,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -9668,7 +9668,7 @@
         <v>126888454</v>
       </c>
       <c r="B91" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9774,32 +9774,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126893278</v>
+        <v>126893277</v>
       </c>
       <c r="B92" t="n">
-        <v>98443</v>
+        <v>80993</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>1049</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9809,10 +9809,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>865551</v>
+        <v>865647</v>
       </c>
       <c r="R92" t="n">
-        <v>7447276</v>
+        <v>7447060</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9875,32 +9875,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126892181</v>
+        <v>126893003</v>
       </c>
       <c r="B93" t="n">
-        <v>98443</v>
+        <v>80157</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9910,10 +9910,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>865459</v>
+        <v>865532</v>
       </c>
       <c r="R93" t="n">
-        <v>7447305</v>
+        <v>7447307</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9960,12 +9960,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -9976,32 +9976,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126893025</v>
+        <v>126888000</v>
       </c>
       <c r="B94" t="n">
-        <v>92616</v>
+        <v>78685</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10011,13 +10011,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>865518</v>
+        <v>865597</v>
       </c>
       <c r="R94" t="n">
-        <v>7447235</v>
+        <v>7447186</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10061,48 +10061,44 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
-        </is>
-      </c>
-      <c r="AY94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126892981</v>
+        <v>126887968</v>
       </c>
       <c r="B95" t="n">
-        <v>91291</v>
+        <v>57821</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10112,13 +10108,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>865553</v>
+        <v>865523</v>
       </c>
       <c r="R95" t="n">
-        <v>7447278</v>
+        <v>7447217</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10162,48 +10158,44 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
-        </is>
-      </c>
-      <c r="AY95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126892267</v>
+        <v>126893023</v>
       </c>
       <c r="B96" t="n">
-        <v>79014</v>
+        <v>91731</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>715</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Finporing</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Gloeoporus pannocinctus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) J.Erikss.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10213,10 +10205,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>865516</v>
+        <v>865473</v>
       </c>
       <c r="R96" t="n">
-        <v>7447351</v>
+        <v>7447321</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10263,12 +10255,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10279,32 +10271,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126887968</v>
+        <v>126893281</v>
       </c>
       <c r="B97" t="n">
-        <v>57817</v>
+        <v>91491</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>103021</v>
+        <v>1503</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10314,13 +10306,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>865523</v>
+        <v>865513</v>
       </c>
       <c r="R97" t="n">
-        <v>7447217</v>
+        <v>7447339</v>
       </c>
       <c r="S97" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10364,44 +10356,48 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY97" t="inlineStr"/>
+          <t>Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126893023</v>
+        <v>126893025</v>
       </c>
       <c r="B98" t="n">
-        <v>91727</v>
+        <v>92620</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>715</v>
+        <v>4364</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Finporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Gloeoporus pannocinctus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Romell) J.Erikss.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10411,10 +10407,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>865473</v>
+        <v>865518</v>
       </c>
       <c r="R98" t="n">
-        <v>7447321</v>
+        <v>7447235</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10477,32 +10473,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126888000</v>
+        <v>126892981</v>
       </c>
       <c r="B99" t="n">
-        <v>78681</v>
+        <v>91295</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10512,13 +10508,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>865597</v>
+        <v>865553</v>
       </c>
       <c r="R99" t="n">
-        <v>7447186</v>
+        <v>7447278</v>
       </c>
       <c r="S99" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -10562,22 +10558,26 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY99" t="inlineStr"/>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
         <v>126892178</v>
       </c>
       <c r="B100" t="n">
-        <v>92809</v>
+        <v>92813</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10675,32 +10675,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126893281</v>
+        <v>126892267</v>
       </c>
       <c r="B101" t="n">
-        <v>91487</v>
+        <v>79018</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10710,10 +10710,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>865513</v>
+        <v>865516</v>
       </c>
       <c r="R101" t="n">
-        <v>7447339</v>
+        <v>7447351</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10760,12 +10760,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -10779,7 +10779,7 @@
         <v>126887997</v>
       </c>
       <c r="B102" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10873,32 +10873,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126891923</v>
+        <v>126892186</v>
       </c>
       <c r="B103" t="n">
-        <v>80021</v>
+        <v>91491</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6456</v>
+        <v>1503</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10908,10 +10908,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>865536</v>
+        <v>865491</v>
       </c>
       <c r="R103" t="n">
-        <v>7447112</v>
+        <v>7447290</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10958,12 +10958,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -10977,7 +10977,7 @@
         <v>126893033</v>
       </c>
       <c r="B104" t="n">
-        <v>78420</v>
+        <v>78424</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11075,32 +11075,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126892186</v>
+        <v>126891923</v>
       </c>
       <c r="B105" t="n">
-        <v>91487</v>
+        <v>80025</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1503</v>
+        <v>6456</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11110,10 +11110,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>865491</v>
+        <v>865536</v>
       </c>
       <c r="R105" t="n">
-        <v>7447290</v>
+        <v>7447112</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11160,12 +11160,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
@@ -11176,32 +11176,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126887980</v>
+        <v>126893310</v>
       </c>
       <c r="B106" t="n">
-        <v>92809</v>
+        <v>91591</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>2079</v>
+        <v>65</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11211,13 +11211,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>865511</v>
+        <v>865653</v>
       </c>
       <c r="R106" t="n">
-        <v>7447249</v>
+        <v>7447052</v>
       </c>
       <c r="S106" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11261,22 +11261,26 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY106" t="inlineStr"/>
+          <t>Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126892028</v>
+        <v>126887980</v>
       </c>
       <c r="B107" t="n">
-        <v>79014</v>
+        <v>92813</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11284,21 +11288,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11308,13 +11312,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>865533</v>
+        <v>865511</v>
       </c>
       <c r="R107" t="n">
-        <v>7447130</v>
+        <v>7447249</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11358,48 +11362,44 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126893310</v>
+        <v>126892028</v>
       </c>
       <c r="B108" t="n">
-        <v>91587</v>
+        <v>79018</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11409,10 +11409,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>865653</v>
+        <v>865533</v>
       </c>
       <c r="R108" t="n">
-        <v>7447052</v>
+        <v>7447130</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11459,12 +11459,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
@@ -11475,32 +11475,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126893009</v>
+        <v>126891928</v>
       </c>
       <c r="B109" t="n">
-        <v>80989</v>
+        <v>98447</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1049</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11510,10 +11510,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>865553</v>
+        <v>865549</v>
       </c>
       <c r="R109" t="n">
-        <v>7447326</v>
+        <v>7447136</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11560,12 +11560,12 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
@@ -11576,32 +11576,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126887977</v>
+        <v>126892024</v>
       </c>
       <c r="B110" t="n">
-        <v>92809</v>
+        <v>98447</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>2079</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11611,13 +11611,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>865643</v>
+        <v>865546</v>
       </c>
       <c r="R110" t="n">
-        <v>7447067</v>
+        <v>7447138</v>
       </c>
       <c r="S110" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -11661,44 +11661,48 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY110" t="inlineStr"/>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126887987</v>
+        <v>126887975</v>
       </c>
       <c r="B111" t="n">
-        <v>91487</v>
+        <v>97331</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1503</v>
+        <v>221941</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11708,10 +11712,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>865510</v>
+        <v>865479</v>
       </c>
       <c r="R111" t="n">
-        <v>7447247</v>
+        <v>7447358</v>
       </c>
       <c r="S111" t="n">
         <v>25</v>
@@ -11770,32 +11774,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126887990</v>
+        <v>126887976</v>
       </c>
       <c r="B112" t="n">
-        <v>79014</v>
+        <v>97331</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11805,10 +11809,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>865447</v>
+        <v>865452</v>
       </c>
       <c r="R112" t="n">
-        <v>7447371</v>
+        <v>7447334</v>
       </c>
       <c r="S112" t="n">
         <v>25</v>
@@ -11870,7 +11874,7 @@
         <v>126887965</v>
       </c>
       <c r="B113" t="n">
-        <v>57479</v>
+        <v>57483</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11967,7 +11971,7 @@
         <v>126892018</v>
       </c>
       <c r="B114" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12080,7 +12084,7 @@
         <v>126892263</v>
       </c>
       <c r="B115" t="n">
-        <v>56840</v>
+        <v>56844</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12186,10 +12190,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126891928</v>
+        <v>126892191</v>
       </c>
       <c r="B116" t="n">
-        <v>98443</v>
+        <v>91591</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12197,21 +12201,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220787</v>
+        <v>65</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12221,10 +12225,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>865549</v>
+        <v>865540</v>
       </c>
       <c r="R116" t="n">
-        <v>7447136</v>
+        <v>7447366</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12271,12 +12275,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
@@ -12287,32 +12291,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126892024</v>
+        <v>126893009</v>
       </c>
       <c r="B117" t="n">
-        <v>98443</v>
+        <v>80993</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220787</v>
+        <v>1049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12322,10 +12326,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>865546</v>
+        <v>865553</v>
       </c>
       <c r="R117" t="n">
-        <v>7447138</v>
+        <v>7447326</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12372,12 +12376,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
@@ -12388,32 +12392,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126887975</v>
+        <v>126887987</v>
       </c>
       <c r="B118" t="n">
-        <v>97327</v>
+        <v>91491</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>221941</v>
+        <v>1503</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12423,10 +12427,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>865479</v>
+        <v>865510</v>
       </c>
       <c r="R118" t="n">
-        <v>7447358</v>
+        <v>7447247</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -12485,32 +12489,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126887976</v>
+        <v>126887977</v>
       </c>
       <c r="B119" t="n">
-        <v>97327</v>
+        <v>92813</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>221941</v>
+        <v>2079</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12520,10 +12524,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>865452</v>
+        <v>865643</v>
       </c>
       <c r="R119" t="n">
-        <v>7447334</v>
+        <v>7447067</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -12582,32 +12586,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126892191</v>
+        <v>126887990</v>
       </c>
       <c r="B120" t="n">
-        <v>91587</v>
+        <v>79018</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12617,13 +12621,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>865540</v>
+        <v>865447</v>
       </c>
       <c r="R120" t="n">
-        <v>7447366</v>
+        <v>7447371</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -12667,48 +12671,44 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY120" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126893267</v>
+        <v>126892170</v>
       </c>
       <c r="B121" t="n">
-        <v>92809</v>
+        <v>57483</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>2079</v>
+        <v>102976</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12718,10 +12718,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>865648</v>
+        <v>865489</v>
       </c>
       <c r="R121" t="n">
-        <v>7447056</v>
+        <v>7447377</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12756,6 +12756,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Förbiflygande</t>
+        </is>
+      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
@@ -12768,12 +12773,12 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
@@ -12784,32 +12789,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126893260</v>
+        <v>126893308</v>
       </c>
       <c r="B122" t="n">
-        <v>91248</v>
+        <v>91591</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>3242</v>
+        <v>65</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12819,10 +12824,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>865498</v>
+        <v>865659</v>
       </c>
       <c r="R122" t="n">
-        <v>7447359</v>
+        <v>7447048</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12885,32 +12890,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126893308</v>
+        <v>126893262</v>
       </c>
       <c r="B123" t="n">
-        <v>91587</v>
+        <v>91295</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>65</v>
+        <v>5447</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12920,10 +12925,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>865659</v>
+        <v>865522</v>
       </c>
       <c r="R123" t="n">
-        <v>7447048</v>
+        <v>7447308</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12986,32 +12991,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126893262</v>
+        <v>126893260</v>
       </c>
       <c r="B124" t="n">
-        <v>91291</v>
+        <v>91252</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5447</v>
+        <v>3242</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13021,10 +13026,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>865522</v>
+        <v>865498</v>
       </c>
       <c r="R124" t="n">
-        <v>7447308</v>
+        <v>7447359</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13087,10 +13092,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126893030</v>
+        <v>126893267</v>
       </c>
       <c r="B125" t="n">
-        <v>77992</v>
+        <v>92813</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13098,21 +13103,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6487</v>
+        <v>2079</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13122,10 +13127,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>865545</v>
+        <v>865648</v>
       </c>
       <c r="R125" t="n">
-        <v>7447323</v>
+        <v>7447056</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13172,12 +13177,12 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
@@ -13188,32 +13193,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126887981</v>
+        <v>126893030</v>
       </c>
       <c r="B126" t="n">
-        <v>80153</v>
+        <v>77996</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6464</v>
+        <v>6487</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13223,13 +13228,13 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>865448</v>
+        <v>865545</v>
       </c>
       <c r="R126" t="n">
-        <v>7447345</v>
+        <v>7447323</v>
       </c>
       <c r="S126" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13273,44 +13278,48 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY126" t="inlineStr"/>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126892170</v>
+        <v>126887981</v>
       </c>
       <c r="B127" t="n">
-        <v>57479</v>
+        <v>80157</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>102976</v>
+        <v>6464</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13320,13 +13329,13 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>865489</v>
+        <v>865448</v>
       </c>
       <c r="R127" t="n">
-        <v>7447377</v>
+        <v>7447345</v>
       </c>
       <c r="S127" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -13356,11 +13365,6 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>Förbiflygande</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13375,48 +13379,44 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126893269</v>
+        <v>126893274</v>
       </c>
       <c r="B128" t="n">
-        <v>92809</v>
+        <v>80157</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>2079</v>
+        <v>6464</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13426,10 +13426,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>865647</v>
+        <v>865476</v>
       </c>
       <c r="R128" t="n">
-        <v>7447057</v>
+        <v>7447236</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13492,32 +13492,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126893292</v>
+        <v>126887988</v>
       </c>
       <c r="B129" t="n">
-        <v>79014</v>
+        <v>91491</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13527,13 +13527,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>865501</v>
+        <v>865515</v>
       </c>
       <c r="R129" t="n">
-        <v>7447191</v>
+        <v>7447377</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -13577,26 +13577,22 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
-        </is>
-      </c>
-      <c r="AY129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126893313</v>
+        <v>126893292</v>
       </c>
       <c r="B130" t="n">
-        <v>78420</v>
+        <v>79018</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13604,21 +13600,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13628,10 +13624,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>865598</v>
+        <v>865501</v>
       </c>
       <c r="R130" t="n">
-        <v>7447181</v>
+        <v>7447191</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13694,32 +13690,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126887970</v>
+        <v>126893313</v>
       </c>
       <c r="B131" t="n">
-        <v>80146</v>
+        <v>78424</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6462</v>
+        <v>6437</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13729,13 +13725,13 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>865529</v>
+        <v>865598</v>
       </c>
       <c r="R131" t="n">
-        <v>7447327</v>
+        <v>7447181</v>
       </c>
       <c r="S131" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -13779,44 +13775,48 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY131" t="inlineStr"/>
+          <t>Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126893274</v>
+        <v>126893269</v>
       </c>
       <c r="B132" t="n">
-        <v>80153</v>
+        <v>92813</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6464</v>
+        <v>2079</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13826,10 +13826,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>865476</v>
+        <v>865647</v>
       </c>
       <c r="R132" t="n">
-        <v>7447236</v>
+        <v>7447057</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13892,32 +13892,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126887988</v>
+        <v>126887970</v>
       </c>
       <c r="B133" t="n">
-        <v>91487</v>
+        <v>80150</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1503</v>
+        <v>6462</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13927,10 +13927,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>865515</v>
+        <v>865529</v>
       </c>
       <c r="R133" t="n">
-        <v>7447377</v>
+        <v>7447327</v>
       </c>
       <c r="S133" t="n">
         <v>25</v>
@@ -13989,32 +13989,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126892176</v>
+        <v>126892256</v>
       </c>
       <c r="B134" t="n">
-        <v>92809</v>
+        <v>91295</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>2079</v>
+        <v>5447</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14024,10 +14024,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>865490</v>
+        <v>865491</v>
       </c>
       <c r="R134" t="n">
-        <v>7447287</v>
+        <v>7447326</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14074,12 +14074,12 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
@@ -14090,10 +14090,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126892189</v>
+        <v>126892176</v>
       </c>
       <c r="B135" t="n">
-        <v>79014</v>
+        <v>92813</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14101,21 +14101,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14125,10 +14125,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>865551</v>
+        <v>865490</v>
       </c>
       <c r="R135" t="n">
-        <v>7447310</v>
+        <v>7447287</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14191,32 +14191,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126892256</v>
+        <v>126892189</v>
       </c>
       <c r="B136" t="n">
-        <v>91291</v>
+        <v>79018</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14226,10 +14226,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>865491</v>
+        <v>865551</v>
       </c>
       <c r="R136" t="n">
-        <v>7447326</v>
+        <v>7447310</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14276,12 +14276,12 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
@@ -14295,7 +14295,7 @@
         <v>126893290</v>
       </c>
       <c r="B137" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14393,10 +14393,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126893034</v>
+        <v>126887962</v>
       </c>
       <c r="B138" t="n">
-        <v>78420</v>
+        <v>79636</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14404,21 +14404,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14428,13 +14428,13 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>865544</v>
+        <v>865519</v>
       </c>
       <c r="R138" t="n">
-        <v>7447321</v>
+        <v>7447214</v>
       </c>
       <c r="S138" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -14478,26 +14478,22 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
-        </is>
-      </c>
-      <c r="AY138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126892984</v>
+        <v>126893034</v>
       </c>
       <c r="B139" t="n">
-        <v>79632</v>
+        <v>78424</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14505,21 +14501,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14529,10 +14525,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>865523</v>
+        <v>865544</v>
       </c>
       <c r="R139" t="n">
-        <v>7447267</v>
+        <v>7447321</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14595,10 +14591,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126887962</v>
+        <v>126892984</v>
       </c>
       <c r="B140" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14630,13 +14626,13 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>865519</v>
+        <v>865523</v>
       </c>
       <c r="R140" t="n">
-        <v>7447214</v>
+        <v>7447267</v>
       </c>
       <c r="S140" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -14680,22 +14676,26 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY140" t="inlineStr"/>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126892253</v>
+        <v>126888456</v>
       </c>
       <c r="B141" t="n">
-        <v>91248</v>
+        <v>92813</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14703,21 +14703,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>3242</v>
+        <v>2079</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14727,10 +14727,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>865491</v>
+        <v>865506</v>
       </c>
       <c r="R141" t="n">
-        <v>7447326</v>
+        <v>7447238</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14777,12 +14777,12 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
@@ -14793,10 +14793,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126888456</v>
+        <v>126892253</v>
       </c>
       <c r="B142" t="n">
-        <v>92809</v>
+        <v>91252</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14804,21 +14804,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>2079</v>
+        <v>3242</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14828,10 +14828,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>865506</v>
+        <v>865491</v>
       </c>
       <c r="R142" t="n">
-        <v>7447238</v>
+        <v>7447326</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14878,12 +14878,12 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
@@ -14897,7 +14897,7 @@
         <v>126887971</v>
       </c>
       <c r="B143" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14994,7 +14994,7 @@
         <v>126892991</v>
       </c>
       <c r="B144" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15095,7 +15095,7 @@
         <v>126891917</v>
       </c>
       <c r="B145" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>126888459</v>
       </c>
       <c r="B146" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15294,10 +15294,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>126892266</v>
+        <v>126892983</v>
       </c>
       <c r="B147" t="n">
-        <v>79014</v>
+        <v>79636</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15305,21 +15305,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15329,10 +15329,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>865495</v>
+        <v>865546</v>
       </c>
       <c r="R147" t="n">
-        <v>7447285</v>
+        <v>7447275</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15379,12 +15379,12 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
@@ -15398,7 +15398,7 @@
         <v>126893264</v>
       </c>
       <c r="B148" t="n">
-        <v>57479</v>
+        <v>57483</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15496,10 +15496,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126892983</v>
+        <v>126892266</v>
       </c>
       <c r="B149" t="n">
-        <v>79632</v>
+        <v>79018</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15507,21 +15507,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15531,10 +15531,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>865546</v>
+        <v>865495</v>
       </c>
       <c r="R149" t="n">
-        <v>7447275</v>
+        <v>7447285</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15581,12 +15581,12 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
@@ -15597,32 +15597,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126893259</v>
+        <v>126892980</v>
       </c>
       <c r="B150" t="n">
-        <v>91248</v>
+        <v>91295</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>3242</v>
+        <v>5447</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15632,10 +15632,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>865646</v>
+        <v>865554</v>
       </c>
       <c r="R150" t="n">
-        <v>7447063</v>
+        <v>7447301</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15682,12 +15682,12 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
@@ -15698,32 +15698,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126892980</v>
+        <v>126893259</v>
       </c>
       <c r="B151" t="n">
-        <v>91291</v>
+        <v>91252</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>5447</v>
+        <v>3242</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15733,10 +15733,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>865554</v>
+        <v>865646</v>
       </c>
       <c r="R151" t="n">
-        <v>7447301</v>
+        <v>7447063</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15783,12 +15783,12 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
@@ -15802,7 +15802,7 @@
         <v>126891909</v>
       </c>
       <c r="B152" t="n">
-        <v>75138</v>
+        <v>75142</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15903,7 +15903,7 @@
         <v>126892023</v>
       </c>
       <c r="B153" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16014,32 +16014,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>126893011</v>
+        <v>126892255</v>
       </c>
       <c r="B154" t="n">
-        <v>80989</v>
+        <v>91295</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1049</v>
+        <v>5447</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16049,10 +16049,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>865498</v>
+        <v>865462</v>
       </c>
       <c r="R154" t="n">
-        <v>7447379</v>
+        <v>7447413</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16099,12 +16099,12 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
@@ -16115,32 +16115,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126892255</v>
+        <v>126892974</v>
       </c>
       <c r="B155" t="n">
-        <v>91291</v>
+        <v>91252</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>5447</v>
+        <v>3242</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16150,10 +16150,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>865462</v>
+        <v>865494</v>
       </c>
       <c r="R155" t="n">
-        <v>7447413</v>
+        <v>7447322</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16200,12 +16200,12 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
@@ -16216,10 +16216,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>126892272</v>
+        <v>126887979</v>
       </c>
       <c r="B156" t="n">
-        <v>77992</v>
+        <v>92813</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16227,21 +16227,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6487</v>
+        <v>2079</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16251,13 +16251,13 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>865528</v>
+        <v>865510</v>
       </c>
       <c r="R156" t="n">
-        <v>7447192</v>
+        <v>7447251</v>
       </c>
       <c r="S156" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -16301,26 +16301,22 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
-        </is>
-      </c>
-      <c r="AY156" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126887979</v>
+        <v>126892272</v>
       </c>
       <c r="B157" t="n">
-        <v>92809</v>
+        <v>77996</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16328,21 +16324,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>2079</v>
+        <v>6487</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16352,13 +16348,13 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>865510</v>
+        <v>865528</v>
       </c>
       <c r="R157" t="n">
-        <v>7447251</v>
+        <v>7447192</v>
       </c>
       <c r="S157" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -16402,22 +16398,26 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY157" t="inlineStr"/>
+          <t>Svea Nikula</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>126892974</v>
+        <v>126893011</v>
       </c>
       <c r="B158" t="n">
-        <v>91248</v>
+        <v>80993</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16425,21 +16425,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>3242</v>
+        <v>1049</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16449,10 +16449,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>865494</v>
+        <v>865498</v>
       </c>
       <c r="R158" t="n">
-        <v>7447322</v>
+        <v>7447379</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16518,7 +16518,7 @@
         <v>126888458</v>
       </c>
       <c r="B159" t="n">
-        <v>91487</v>
+        <v>91491</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16616,32 +16616,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>126893291</v>
+        <v>126892016</v>
       </c>
       <c r="B160" t="n">
-        <v>79014</v>
+        <v>91295</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16651,10 +16651,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>865507</v>
+        <v>865558</v>
       </c>
       <c r="R160" t="n">
-        <v>7447151</v>
+        <v>7447154</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16701,12 +16701,12 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
@@ -16717,32 +16717,32 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>126892016</v>
+        <v>126893272</v>
       </c>
       <c r="B161" t="n">
-        <v>91291</v>
+        <v>92813</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>5447</v>
+        <v>2079</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16752,10 +16752,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>865558</v>
+        <v>865520</v>
       </c>
       <c r="R161" t="n">
-        <v>7447154</v>
+        <v>7447337</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16802,12 +16802,12 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
@@ -16818,48 +16818,45 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>126891924</v>
+        <v>126893265</v>
       </c>
       <c r="B162" t="n">
-        <v>78772</v>
+        <v>80150</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
-      <c r="J162" t="inlineStr"/>
-      <c r="K162" t="inlineStr"/>
-      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>865562</v>
+        <v>865530</v>
       </c>
       <c r="R162" t="n">
-        <v>7447150</v>
+        <v>7447304</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16900,19 +16897,18 @@
       <c r="AE162" t="b">
         <v>0</v>
       </c>
-      <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="b">
         <v>0</v>
       </c>
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
@@ -16926,7 +16922,7 @@
         <v>126887961</v>
       </c>
       <c r="B163" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17020,32 +17016,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>126893272</v>
+        <v>126891919</v>
       </c>
       <c r="B164" t="n">
-        <v>92809</v>
+        <v>80150</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>2079</v>
+        <v>6462</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17055,10 +17051,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>865520</v>
+        <v>865447</v>
       </c>
       <c r="R164" t="n">
-        <v>7447337</v>
+        <v>7447440</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17105,12 +17101,12 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
@@ -17121,45 +17117,48 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>126893265</v>
+        <v>126891924</v>
       </c>
       <c r="B165" t="n">
-        <v>80146</v>
+        <v>78776</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>865530</v>
+        <v>865562</v>
       </c>
       <c r="R165" t="n">
-        <v>7447304</v>
+        <v>7447150</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17200,18 +17199,19 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
+      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
@@ -17222,32 +17222,32 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>126891919</v>
+        <v>126893291</v>
       </c>
       <c r="B166" t="n">
-        <v>80146</v>
+        <v>79018</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17257,10 +17257,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>865447</v>
+        <v>865507</v>
       </c>
       <c r="R166" t="n">
-        <v>7447440</v>
+        <v>7447151</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17307,12 +17307,12 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
@@ -17326,7 +17326,7 @@
         <v>126892988</v>
       </c>
       <c r="B167" t="n">
-        <v>57479</v>
+        <v>57483</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -17427,7 +17427,7 @@
         <v>126893021</v>
       </c>
       <c r="B168" t="n">
-        <v>91587</v>
+        <v>91591</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17528,7 +17528,7 @@
         <v>126893309</v>
       </c>
       <c r="B169" t="n">
-        <v>91587</v>
+        <v>91591</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17629,7 +17629,7 @@
         <v>126893284</v>
       </c>
       <c r="B170" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17730,7 +17730,7 @@
         <v>126893031</v>
       </c>
       <c r="B171" t="n">
-        <v>77992</v>
+        <v>77996</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17828,32 +17828,32 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>126893263</v>
+        <v>126892188</v>
       </c>
       <c r="B172" t="n">
-        <v>91326</v>
+        <v>91491</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>1202</v>
+        <v>1503</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -17863,10 +17863,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>865485</v>
+        <v>865520</v>
       </c>
       <c r="R172" t="n">
-        <v>7447224</v>
+        <v>7447364</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -17913,12 +17913,12 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
@@ -17929,10 +17929,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>126892174</v>
+        <v>126893263</v>
       </c>
       <c r="B173" t="n">
-        <v>92809</v>
+        <v>91330</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17940,21 +17940,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>2079</v>
+        <v>1202</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -17964,10 +17964,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>865517</v>
+        <v>865485</v>
       </c>
       <c r="R173" t="n">
-        <v>7447401</v>
+        <v>7447224</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18014,12 +18014,12 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
@@ -18030,10 +18030,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>126892188</v>
+        <v>126887986</v>
       </c>
       <c r="B174" t="n">
-        <v>91487</v>
+        <v>91491</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18065,13 +18065,13 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>865520</v>
+        <v>865539</v>
       </c>
       <c r="R174" t="n">
-        <v>7447364</v>
+        <v>7447206</v>
       </c>
       <c r="S174" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -18115,48 +18115,44 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY174" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>126887986</v>
+        <v>126892174</v>
       </c>
       <c r="B175" t="n">
-        <v>91487</v>
+        <v>92813</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>1503</v>
+        <v>2079</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18166,13 +18162,13 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>865539</v>
+        <v>865517</v>
       </c>
       <c r="R175" t="n">
-        <v>7447206</v>
+        <v>7447401</v>
       </c>
       <c r="S175" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -18216,22 +18212,26 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY175" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
         <v>126891913</v>
       </c>
       <c r="B176" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18329,32 +18329,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>126892986</v>
+        <v>126892997</v>
       </c>
       <c r="B177" t="n">
-        <v>79603</v>
+        <v>79042</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>229821</v>
+        <v>6434</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18364,10 +18364,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>865489</v>
+        <v>865545</v>
       </c>
       <c r="R177" t="n">
-        <v>7447329</v>
+        <v>7447323</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18433,7 +18433,7 @@
         <v>126893294</v>
       </c>
       <c r="B178" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18531,32 +18531,32 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>126892997</v>
+        <v>126893314</v>
       </c>
       <c r="B179" t="n">
-        <v>79038</v>
+        <v>78424</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6434</v>
+        <v>6437</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -18566,10 +18566,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>865545</v>
+        <v>865647</v>
       </c>
       <c r="R179" t="n">
-        <v>7447323</v>
+        <v>7447060</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18616,12 +18616,12 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
@@ -18632,10 +18632,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>126893314</v>
+        <v>126892986</v>
       </c>
       <c r="B180" t="n">
-        <v>78420</v>
+        <v>79607</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18643,21 +18643,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -18667,10 +18667,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>865647</v>
+        <v>865489</v>
       </c>
       <c r="R180" t="n">
-        <v>7447060</v>
+        <v>7447329</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18717,12 +18717,12 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">

--- a/artfynd/A 52625-2022 artfynd.xlsx
+++ b/artfynd/A 52625-2022 artfynd.xlsx
@@ -978,10 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126891922</v>
+        <v>126893005</v>
       </c>
       <c r="B5" t="n">
-        <v>80150</v>
+        <v>80157</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -989,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>865415</v>
+        <v>865370</v>
       </c>
       <c r="R5" t="n">
-        <v>7447651</v>
+        <v>7447622</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,12 +1063,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126893005</v>
+        <v>126891922</v>
       </c>
       <c r="B6" t="n">
-        <v>80157</v>
+        <v>80150</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>865370</v>
+        <v>865415</v>
       </c>
       <c r="R6" t="n">
-        <v>7447622</v>
+        <v>7447651</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,12 +1164,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1180,32 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126893295</v>
+        <v>126893275</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>80157</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>865429</v>
+        <v>865427</v>
       </c>
       <c r="R7" t="n">
-        <v>7447550</v>
+        <v>7447587</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,32 +1281,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126893300</v>
+        <v>126892019</v>
       </c>
       <c r="B8" t="n">
-        <v>79018</v>
+        <v>80150</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>865378</v>
+        <v>865429</v>
       </c>
       <c r="R8" t="n">
-        <v>7447665</v>
+        <v>7447523</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1366,12 +1366,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1382,32 +1382,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126892019</v>
+        <v>126893300</v>
       </c>
       <c r="B9" t="n">
-        <v>80150</v>
+        <v>79018</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>865429</v>
+        <v>865378</v>
       </c>
       <c r="R9" t="n">
-        <v>7447523</v>
+        <v>7447665</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1467,12 +1467,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1483,32 +1483,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126893275</v>
+        <v>126893295</v>
       </c>
       <c r="B10" t="n">
-        <v>80157</v>
+        <v>79018</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>865427</v>
+        <v>865429</v>
       </c>
       <c r="R10" t="n">
-        <v>7447587</v>
+        <v>7447550</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1584,59 +1584,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126892270</v>
+        <v>126887991</v>
       </c>
       <c r="B11" t="n">
-        <v>91904</v>
+        <v>79018</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>865437</v>
+        <v>865422</v>
       </c>
       <c r="R11" t="n">
-        <v>7447594</v>
+        <v>7447458</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1674,55 +1663,50 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Svea Nikula, Jonas Göransson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126892999</v>
+        <v>126887992</v>
       </c>
       <c r="B12" t="n">
-        <v>80149</v>
+        <v>79018</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1732,13 +1716,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>865426</v>
+        <v>865406</v>
       </c>
       <c r="R12" t="n">
-        <v>7447493</v>
+        <v>7447461</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1782,61 +1766,68 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126892173</v>
+        <v>126892270</v>
       </c>
       <c r="B13" t="n">
-        <v>80150</v>
+        <v>91904</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>760</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>865379</v>
+        <v>865437</v>
       </c>
       <c r="R13" t="n">
-        <v>7447558</v>
+        <v>7447594</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1877,18 +1868,19 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Svea Nikula, Jonas Göransson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1899,32 +1891,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126887991</v>
+        <v>126892999</v>
       </c>
       <c r="B14" t="n">
-        <v>79018</v>
+        <v>80149</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1934,13 +1926,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>865422</v>
+        <v>865426</v>
       </c>
       <c r="R14" t="n">
-        <v>7447458</v>
+        <v>7447493</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1984,44 +1976,48 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126887992</v>
+        <v>126892173</v>
       </c>
       <c r="B15" t="n">
-        <v>79018</v>
+        <v>80150</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2031,13 +2027,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>865406</v>
+        <v>865379</v>
       </c>
       <c r="R15" t="n">
-        <v>7447461</v>
+        <v>7447558</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2081,44 +2077,48 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126892264</v>
+        <v>126893016</v>
       </c>
       <c r="B16" t="n">
-        <v>58520</v>
+        <v>79018</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>208249</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>865410</v>
+        <v>865412</v>
       </c>
       <c r="R16" t="n">
-        <v>7447525</v>
+        <v>7447514</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2172,19 +2172,18 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
@@ -2195,32 +2194,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126893016</v>
+        <v>126892264</v>
       </c>
       <c r="B17" t="n">
-        <v>79018</v>
+        <v>58520</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>208249</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2230,10 +2229,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>865412</v>
+        <v>865410</v>
       </c>
       <c r="R17" t="n">
-        <v>7447514</v>
+        <v>7447525</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2274,18 +2273,19 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2599,32 +2599,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126891920</v>
+        <v>126893293</v>
       </c>
       <c r="B21" t="n">
-        <v>80150</v>
+        <v>79018</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2634,10 +2634,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>865438</v>
+        <v>865430</v>
       </c>
       <c r="R21" t="n">
-        <v>7447459</v>
+        <v>7447483</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2684,12 +2684,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2700,7 +2700,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126892172</v>
+        <v>126891920</v>
       </c>
       <c r="B22" t="n">
         <v>80150</v>
@@ -2735,10 +2735,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>865436</v>
+        <v>865438</v>
       </c>
       <c r="R22" t="n">
-        <v>7447532</v>
+        <v>7447459</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2785,12 +2785,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2801,10 +2801,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126893276</v>
+        <v>126892172</v>
       </c>
       <c r="B23" t="n">
-        <v>80157</v>
+        <v>80150</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2812,21 +2812,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2836,10 +2836,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>865406</v>
+        <v>865436</v>
       </c>
       <c r="R23" t="n">
-        <v>7447661</v>
+        <v>7447532</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2886,12 +2886,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2902,32 +2902,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126893293</v>
+        <v>126893276</v>
       </c>
       <c r="B24" t="n">
-        <v>79018</v>
+        <v>80157</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2937,10 +2937,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>865430</v>
+        <v>865406</v>
       </c>
       <c r="R24" t="n">
-        <v>7447483</v>
+        <v>7447661</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3003,7 +3003,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126892261</v>
+        <v>126887982</v>
       </c>
       <c r="B25" t="n">
         <v>80157</v>
@@ -3041,10 +3041,10 @@
         <v>865434</v>
       </c>
       <c r="R25" t="n">
-        <v>7447569</v>
+        <v>7447388</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3088,23 +3088,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126887982</v>
+        <v>126892261</v>
       </c>
       <c r="B26" t="n">
         <v>80157</v>
@@ -3142,10 +3138,10 @@
         <v>865434</v>
       </c>
       <c r="R26" t="n">
-        <v>7447388</v>
+        <v>7447569</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3189,15 +3185,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
+          <t>Svea Nikula</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3302,32 +3302,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126893015</v>
+        <v>126892179</v>
       </c>
       <c r="B28" t="n">
-        <v>79018</v>
+        <v>80157</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3337,10 +3337,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>865423</v>
+        <v>865377</v>
       </c>
       <c r="R28" t="n">
-        <v>7447442</v>
+        <v>7447525</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3387,12 +3387,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3403,32 +3403,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126892179</v>
+        <v>126892030</v>
       </c>
       <c r="B29" t="n">
-        <v>80157</v>
+        <v>79018</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3438,10 +3438,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>865377</v>
+        <v>865389</v>
       </c>
       <c r="R29" t="n">
-        <v>7447525</v>
+        <v>7447613</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3488,12 +3488,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3504,7 +3504,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126892030</v>
+        <v>126893015</v>
       </c>
       <c r="B30" t="n">
         <v>79018</v>
@@ -3539,10 +3539,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>865389</v>
+        <v>865423</v>
       </c>
       <c r="R30" t="n">
-        <v>7447613</v>
+        <v>7447442</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3589,12 +3589,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -3807,32 +3807,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126892262</v>
+        <v>126893306</v>
       </c>
       <c r="B33" t="n">
-        <v>80157</v>
+        <v>82859</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3842,10 +3842,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>865404</v>
+        <v>865378</v>
       </c>
       <c r="R33" t="n">
-        <v>7447633</v>
+        <v>7447665</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3892,12 +3892,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -3908,32 +3908,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126887969</v>
+        <v>126892262</v>
       </c>
       <c r="B34" t="n">
-        <v>57821</v>
+        <v>80157</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3943,13 +3943,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>865406</v>
+        <v>865404</v>
       </c>
       <c r="R34" t="n">
-        <v>7447461</v>
+        <v>7447633</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3993,22 +3993,26 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
+          <t>Svea Nikula</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126893306</v>
+        <v>126887969</v>
       </c>
       <c r="B35" t="n">
-        <v>82859</v>
+        <v>57821</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4016,21 +4020,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4040,13 +4044,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>865378</v>
+        <v>865406</v>
       </c>
       <c r="R35" t="n">
-        <v>7447665</v>
+        <v>7447461</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4090,19 +4094,15 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4308,10 +4308,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126887993</v>
+        <v>126892978</v>
       </c>
       <c r="B38" t="n">
-        <v>79018</v>
+        <v>75142</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4319,21 +4319,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4343,13 +4343,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>865389</v>
+        <v>865423</v>
       </c>
       <c r="R38" t="n">
-        <v>7447521</v>
+        <v>7447442</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4393,22 +4393,26 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126892978</v>
+        <v>126887993</v>
       </c>
       <c r="B39" t="n">
-        <v>75142</v>
+        <v>79018</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4416,21 +4420,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4440,13 +4444,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>865423</v>
+        <v>865389</v>
       </c>
       <c r="R39" t="n">
-        <v>7447442</v>
+        <v>7447521</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4490,19 +4494,15 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5213,27 +5213,27 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126887994</v>
+        <v>126893028</v>
       </c>
       <c r="B47" t="n">
-        <v>79018</v>
+        <v>80156</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5248,13 +5248,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>865368</v>
+        <v>865390</v>
       </c>
       <c r="R47" t="n">
-        <v>7447606</v>
+        <v>7447609</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5298,15 +5298,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5411,27 +5415,27 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126893028</v>
+        <v>126887994</v>
       </c>
       <c r="B49" t="n">
-        <v>80156</v>
+        <v>79018</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5446,13 +5450,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>865390</v>
+        <v>865368</v>
       </c>
       <c r="R49" t="n">
-        <v>7447609</v>
+        <v>7447606</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5496,48 +5500,44 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126892254</v>
+        <v>126887983</v>
       </c>
       <c r="B50" t="n">
-        <v>75142</v>
+        <v>80157</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6440</v>
+        <v>6464</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5547,13 +5547,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>865423</v>
+        <v>865378</v>
       </c>
       <c r="R50" t="n">
-        <v>7447468</v>
+        <v>7447577</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5597,48 +5597,44 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126887983</v>
+        <v>126892254</v>
       </c>
       <c r="B51" t="n">
-        <v>80157</v>
+        <v>75142</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6464</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5648,13 +5644,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>865378</v>
+        <v>865423</v>
       </c>
       <c r="R51" t="n">
-        <v>7447577</v>
+        <v>7447468</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5698,15 +5694,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
+          <t>Svea Nikula</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5816,10 +5816,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126892026</v>
+        <v>126893008</v>
       </c>
       <c r="B53" t="n">
-        <v>79018</v>
+        <v>80993</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5827,21 +5827,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5851,10 +5851,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>865538</v>
+        <v>865545</v>
       </c>
       <c r="R53" t="n">
-        <v>7447072</v>
+        <v>7447322</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5901,12 +5901,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
@@ -5917,32 +5917,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126892029</v>
+        <v>126893280</v>
       </c>
       <c r="B54" t="n">
-        <v>79018</v>
+        <v>91491</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5952,10 +5952,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>865448</v>
+        <v>865490</v>
       </c>
       <c r="R54" t="n">
-        <v>7447418</v>
+        <v>7447213</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6002,12 +6002,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6018,10 +6018,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126892273</v>
+        <v>126892026</v>
       </c>
       <c r="B55" t="n">
-        <v>78424</v>
+        <v>79018</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6029,21 +6029,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6053,10 +6053,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>865528</v>
+        <v>865538</v>
       </c>
       <c r="R55" t="n">
-        <v>7447193</v>
+        <v>7447072</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6103,12 +6103,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6119,32 +6119,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126891927</v>
+        <v>126892029</v>
       </c>
       <c r="B56" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>865543</v>
+        <v>865448</v>
       </c>
       <c r="R56" t="n">
-        <v>7447122</v>
+        <v>7447418</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6204,12 +6204,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6220,32 +6220,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126893280</v>
+        <v>126892985</v>
       </c>
       <c r="B57" t="n">
-        <v>91491</v>
+        <v>79636</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6255,10 +6255,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>865490</v>
+        <v>865491</v>
       </c>
       <c r="R57" t="n">
-        <v>7447213</v>
+        <v>7447332</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6305,12 +6305,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6321,10 +6321,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126893008</v>
+        <v>126892273</v>
       </c>
       <c r="B58" t="n">
-        <v>80993</v>
+        <v>78424</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6332,21 +6332,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1049</v>
+        <v>6437</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6356,10 +6356,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>865545</v>
+        <v>865528</v>
       </c>
       <c r="R58" t="n">
-        <v>7447322</v>
+        <v>7447193</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6406,12 +6406,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
@@ -6422,32 +6422,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126892985</v>
+        <v>126891916</v>
       </c>
       <c r="B59" t="n">
-        <v>79636</v>
+        <v>80150</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6462</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6457,10 +6457,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>865491</v>
+        <v>865546</v>
       </c>
       <c r="R59" t="n">
-        <v>7447332</v>
+        <v>7447133</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6507,12 +6507,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6523,32 +6523,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126891916</v>
+        <v>126891927</v>
       </c>
       <c r="B60" t="n">
-        <v>80150</v>
+        <v>98447</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6558,10 +6558,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>865546</v>
+        <v>865543</v>
       </c>
       <c r="R60" t="n">
-        <v>7447133</v>
+        <v>7447122</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6725,10 +6725,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126892982</v>
+        <v>126891915</v>
       </c>
       <c r="B62" t="n">
-        <v>91295</v>
+        <v>80150</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6736,21 +6736,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6760,10 +6760,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>865526</v>
+        <v>865551</v>
       </c>
       <c r="R62" t="n">
-        <v>7447273</v>
+        <v>7447126</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6810,12 +6810,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -6826,10 +6826,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126891915</v>
+        <v>126892982</v>
       </c>
       <c r="B63" t="n">
-        <v>80150</v>
+        <v>91295</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6837,21 +6837,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6861,10 +6861,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>865551</v>
+        <v>865526</v>
       </c>
       <c r="R63" t="n">
-        <v>7447126</v>
+        <v>7447273</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6911,12 +6911,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
@@ -7024,10 +7024,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126893000</v>
+        <v>126893010</v>
       </c>
       <c r="B65" t="n">
-        <v>92813</v>
+        <v>80993</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7035,21 +7035,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2079</v>
+        <v>1049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7059,10 +7059,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>865559</v>
+        <v>865490</v>
       </c>
       <c r="R65" t="n">
-        <v>7447299</v>
+        <v>7447332</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7125,32 +7125,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126892998</v>
+        <v>126888002</v>
       </c>
       <c r="B66" t="n">
-        <v>80149</v>
+        <v>78685</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6461</v>
+        <v>353</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7160,13 +7160,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>865477</v>
+        <v>865512</v>
       </c>
       <c r="R66" t="n">
-        <v>7447327</v>
+        <v>7447340</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7210,19 +7210,15 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7327,61 +7323,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126892183</v>
+        <v>126892998</v>
       </c>
       <c r="B68" t="n">
-        <v>56844</v>
+        <v>80149</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>102612</v>
+        <v>6461</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>pulli</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>pulli/nyligen flygga ungar</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>865484</v>
+        <v>865477</v>
       </c>
       <c r="R68" t="n">
-        <v>7447494</v>
+        <v>7447327</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7416,11 +7396,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Stötte up 5st kycklingar, höll till under en och samma fallen gran</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -7433,12 +7408,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7449,32 +7424,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126888002</v>
+        <v>126891925</v>
       </c>
       <c r="B69" t="n">
-        <v>78685</v>
+        <v>98447</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7484,13 +7459,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>865512</v>
+        <v>865527</v>
       </c>
       <c r="R69" t="n">
-        <v>7447340</v>
+        <v>7447333</v>
       </c>
       <c r="S69" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7534,22 +7509,26 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr"/>
+          <t>Amanda Rudelius</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126893010</v>
+        <v>126893000</v>
       </c>
       <c r="B70" t="n">
-        <v>80993</v>
+        <v>92813</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7557,21 +7536,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1049</v>
+        <v>2079</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7581,10 +7560,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>865490</v>
+        <v>865559</v>
       </c>
       <c r="R70" t="n">
-        <v>7447332</v>
+        <v>7447299</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7647,45 +7626,61 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126891925</v>
+        <v>126892183</v>
       </c>
       <c r="B71" t="n">
-        <v>98447</v>
+        <v>56844</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>pulli</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>pulli/nyligen flygga ungar</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>865527</v>
+        <v>865484</v>
       </c>
       <c r="R71" t="n">
-        <v>7447333</v>
+        <v>7447494</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7720,6 +7715,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Stötte up 5st kycklingar, höll till under en och samma fallen gran</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -7732,12 +7732,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -7748,32 +7748,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126891926</v>
+        <v>126893282</v>
       </c>
       <c r="B72" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7783,10 +7783,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>865541</v>
+        <v>865611</v>
       </c>
       <c r="R72" t="n">
-        <v>7447113</v>
+        <v>7446989</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7833,12 +7833,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -7849,10 +7849,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126892187</v>
+        <v>126891926</v>
       </c>
       <c r="B73" t="n">
-        <v>91491</v>
+        <v>98447</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7860,21 +7860,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1503</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7884,10 +7884,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>865509</v>
+        <v>865541</v>
       </c>
       <c r="R73" t="n">
-        <v>7447371</v>
+        <v>7447113</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7934,12 +7934,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -7950,7 +7950,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126893012</v>
+        <v>126892187</v>
       </c>
       <c r="B74" t="n">
         <v>91491</v>
@@ -7985,10 +7985,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>865559</v>
+        <v>865509</v>
       </c>
       <c r="R74" t="n">
-        <v>7447299</v>
+        <v>7447371</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8035,12 +8035,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8051,32 +8051,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126891911</v>
+        <v>126893012</v>
       </c>
       <c r="B75" t="n">
-        <v>91295</v>
+        <v>91491</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5447</v>
+        <v>1503</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8086,10 +8086,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>865557</v>
+        <v>865559</v>
       </c>
       <c r="R75" t="n">
-        <v>7447153</v>
+        <v>7447299</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8136,12 +8136,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8152,32 +8152,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126893282</v>
+        <v>126891911</v>
       </c>
       <c r="B76" t="n">
-        <v>79018</v>
+        <v>91295</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8187,10 +8187,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>865611</v>
+        <v>865557</v>
       </c>
       <c r="R76" t="n">
-        <v>7446989</v>
+        <v>7447153</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8237,12 +8237,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8253,54 +8253,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126891930</v>
+        <v>126891929</v>
       </c>
       <c r="B77" t="n">
-        <v>8439</v>
+        <v>79018</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106554</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>865561</v>
+        <v>865535</v>
       </c>
       <c r="R77" t="n">
-        <v>7447167</v>
+        <v>7447142</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8341,7 +8332,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8364,10 +8354,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126887974</v>
+        <v>126891930</v>
       </c>
       <c r="B78" t="n">
-        <v>97331</v>
+        <v>8439</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8375,37 +8365,46 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221941</v>
+        <v>106554</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>865641</v>
+        <v>865561</v>
       </c>
       <c r="R78" t="n">
-        <v>7447070</v>
+        <v>7447167</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8443,21 +8442,26 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr"/>
+          <t>Amanda Rudelius</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8558,32 +8562,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126891914</v>
+        <v>126893270</v>
       </c>
       <c r="B80" t="n">
-        <v>80150</v>
+        <v>92813</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6462</v>
+        <v>2079</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8593,10 +8597,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>865539</v>
+        <v>865491</v>
       </c>
       <c r="R80" t="n">
-        <v>7447115</v>
+        <v>7447267</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8643,12 +8647,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -8659,32 +8663,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126891929</v>
+        <v>126891914</v>
       </c>
       <c r="B81" t="n">
-        <v>79018</v>
+        <v>80150</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8694,10 +8698,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>865535</v>
+        <v>865539</v>
       </c>
       <c r="R81" t="n">
-        <v>7447142</v>
+        <v>7447115</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8760,32 +8764,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126893270</v>
+        <v>126887974</v>
       </c>
       <c r="B82" t="n">
-        <v>92813</v>
+        <v>97331</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2079</v>
+        <v>221941</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8795,13 +8799,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>865491</v>
+        <v>865641</v>
       </c>
       <c r="R82" t="n">
-        <v>7447267</v>
+        <v>7447070</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8845,19 +8849,15 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9362,10 +9362,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126892271</v>
+        <v>126893003</v>
       </c>
       <c r="B88" t="n">
-        <v>80156</v>
+        <v>80157</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9373,21 +9373,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9397,10 +9397,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>865610</v>
+        <v>865532</v>
       </c>
       <c r="R88" t="n">
-        <v>7447145</v>
+        <v>7447307</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9447,12 +9447,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
@@ -9463,32 +9463,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126893278</v>
+        <v>126892271</v>
       </c>
       <c r="B89" t="n">
-        <v>98447</v>
+        <v>80156</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9498,10 +9498,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>865551</v>
+        <v>865610</v>
       </c>
       <c r="R89" t="n">
-        <v>7447276</v>
+        <v>7447145</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9548,12 +9548,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -9564,7 +9564,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126892181</v>
+        <v>126893278</v>
       </c>
       <c r="B90" t="n">
         <v>98447</v>
@@ -9599,10 +9599,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>865459</v>
+        <v>865551</v>
       </c>
       <c r="R90" t="n">
-        <v>7447305</v>
+        <v>7447276</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9649,12 +9649,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -9665,53 +9665,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126888454</v>
+        <v>126892181</v>
       </c>
       <c r="B91" t="n">
-        <v>57821</v>
+        <v>98447</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>865481</v>
+        <v>865459</v>
       </c>
       <c r="R91" t="n">
-        <v>7447376</v>
+        <v>7447305</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9758,12 +9750,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -9875,45 +9867,53 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126893003</v>
+        <v>126888454</v>
       </c>
       <c r="B93" t="n">
-        <v>80157</v>
+        <v>57821</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>865532</v>
+        <v>865481</v>
       </c>
       <c r="R93" t="n">
-        <v>7447307</v>
+        <v>7447376</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9960,12 +9960,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -9976,32 +9976,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126888000</v>
+        <v>126893025</v>
       </c>
       <c r="B94" t="n">
-        <v>78685</v>
+        <v>92620</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10011,13 +10011,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>865597</v>
+        <v>865518</v>
       </c>
       <c r="R94" t="n">
-        <v>7447186</v>
+        <v>7447235</v>
       </c>
       <c r="S94" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10061,44 +10061,48 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY94" t="inlineStr"/>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126887968</v>
+        <v>126892981</v>
       </c>
       <c r="B95" t="n">
-        <v>57821</v>
+        <v>91295</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10108,13 +10112,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>865523</v>
+        <v>865553</v>
       </c>
       <c r="R95" t="n">
-        <v>7447217</v>
+        <v>7447278</v>
       </c>
       <c r="S95" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10158,44 +10162,48 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY95" t="inlineStr"/>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126893023</v>
+        <v>126892267</v>
       </c>
       <c r="B96" t="n">
-        <v>91731</v>
+        <v>79018</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>715</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Finporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Gloeoporus pannocinctus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Romell) J.Erikss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10205,10 +10213,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>865473</v>
+        <v>865516</v>
       </c>
       <c r="R96" t="n">
-        <v>7447321</v>
+        <v>7447351</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10255,12 +10263,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10271,32 +10279,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126893281</v>
+        <v>126888000</v>
       </c>
       <c r="B97" t="n">
-        <v>91491</v>
+        <v>78685</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10306,13 +10314,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>865513</v>
+        <v>865597</v>
       </c>
       <c r="R97" t="n">
-        <v>7447339</v>
+        <v>7447186</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10356,48 +10364,44 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
-        </is>
-      </c>
-      <c r="AY97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126893025</v>
+        <v>126893023</v>
       </c>
       <c r="B98" t="n">
-        <v>92620</v>
+        <v>91731</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4364</v>
+        <v>715</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Finporing</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Gloeoporus pannocinctus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) J.Erikss.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10407,10 +10411,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>865518</v>
+        <v>865473</v>
       </c>
       <c r="R98" t="n">
-        <v>7447235</v>
+        <v>7447321</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10473,32 +10477,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126892981</v>
+        <v>126893281</v>
       </c>
       <c r="B99" t="n">
-        <v>91295</v>
+        <v>91491</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5447</v>
+        <v>1503</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10508,10 +10512,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>865553</v>
+        <v>865513</v>
       </c>
       <c r="R99" t="n">
-        <v>7447278</v>
+        <v>7447339</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10558,12 +10562,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -10675,10 +10679,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126892267</v>
+        <v>126887968</v>
       </c>
       <c r="B101" t="n">
-        <v>79018</v>
+        <v>57821</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10686,21 +10690,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10710,13 +10714,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>865516</v>
+        <v>865523</v>
       </c>
       <c r="R101" t="n">
-        <v>7447351</v>
+        <v>7447217</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10760,19 +10764,15 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
-        </is>
-      </c>
-      <c r="AY101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10873,32 +10873,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126892186</v>
+        <v>126891923</v>
       </c>
       <c r="B103" t="n">
-        <v>91491</v>
+        <v>80025</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1503</v>
+        <v>6456</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10908,10 +10908,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>865491</v>
+        <v>865536</v>
       </c>
       <c r="R103" t="n">
-        <v>7447290</v>
+        <v>7447112</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10958,12 +10958,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -11075,32 +11075,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126891923</v>
+        <v>126892186</v>
       </c>
       <c r="B105" t="n">
-        <v>80025</v>
+        <v>91491</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6456</v>
+        <v>1503</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11110,10 +11110,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>865536</v>
+        <v>865491</v>
       </c>
       <c r="R105" t="n">
-        <v>7447112</v>
+        <v>7447290</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11160,12 +11160,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
@@ -11475,10 +11475,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126891928</v>
+        <v>126892191</v>
       </c>
       <c r="B109" t="n">
-        <v>98447</v>
+        <v>91591</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11486,21 +11486,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>65</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11510,10 +11510,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>865549</v>
+        <v>865540</v>
       </c>
       <c r="R109" t="n">
-        <v>7447136</v>
+        <v>7447366</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11560,12 +11560,12 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
@@ -11576,32 +11576,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126892024</v>
+        <v>126893009</v>
       </c>
       <c r="B110" t="n">
-        <v>98447</v>
+        <v>80993</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>1049</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11611,10 +11611,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>865546</v>
+        <v>865553</v>
       </c>
       <c r="R110" t="n">
-        <v>7447138</v>
+        <v>7447326</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11661,12 +11661,12 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
@@ -11677,32 +11677,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>126887975</v>
+        <v>126887990</v>
       </c>
       <c r="B111" t="n">
-        <v>97331</v>
+        <v>79018</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11712,10 +11712,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>865479</v>
+        <v>865447</v>
       </c>
       <c r="R111" t="n">
-        <v>7447358</v>
+        <v>7447371</v>
       </c>
       <c r="S111" t="n">
         <v>25</v>
@@ -11774,48 +11774,56 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126887976</v>
+        <v>126892263</v>
       </c>
       <c r="B112" t="n">
-        <v>97331</v>
+        <v>56844</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>221941</v>
+        <v>102612</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>865452</v>
+        <v>865544</v>
       </c>
       <c r="R112" t="n">
-        <v>7447334</v>
+        <v>7447281</v>
       </c>
       <c r="S112" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -11859,44 +11867,48 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY112" t="inlineStr"/>
+          <t>Svea Nikula</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126887965</v>
+        <v>126891928</v>
       </c>
       <c r="B113" t="n">
-        <v>57483</v>
+        <v>98447</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>102976</v>
+        <v>220787</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11906,13 +11918,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>865583</v>
+        <v>865549</v>
       </c>
       <c r="R113" t="n">
-        <v>7447214</v>
+        <v>7447136</v>
       </c>
       <c r="S113" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -11956,69 +11968,61 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY113" t="inlineStr"/>
+          <t>Amanda Rudelius</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126892018</v>
+        <v>126892024</v>
       </c>
       <c r="B114" t="n">
-        <v>57821</v>
+        <v>98447</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>865561</v>
+        <v>865546</v>
       </c>
       <c r="R114" t="n">
-        <v>7447155</v>
+        <v>7447138</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12070,7 +12074,7 @@
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
@@ -12081,56 +12085,48 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126892263</v>
+        <v>126887975</v>
       </c>
       <c r="B115" t="n">
-        <v>56844</v>
+        <v>97331</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>102612</v>
+        <v>221941</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>865544</v>
+        <v>865479</v>
       </c>
       <c r="R115" t="n">
-        <v>7447281</v>
+        <v>7447358</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12174,48 +12170,44 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
-        </is>
-      </c>
-      <c r="AY115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126892191</v>
+        <v>126887976</v>
       </c>
       <c r="B116" t="n">
-        <v>91591</v>
+        <v>97331</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>65</v>
+        <v>221941</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12225,13 +12217,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>865540</v>
+        <v>865452</v>
       </c>
       <c r="R116" t="n">
-        <v>7447366</v>
+        <v>7447334</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12275,26 +12267,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126893009</v>
+        <v>126887977</v>
       </c>
       <c r="B117" t="n">
-        <v>80993</v>
+        <v>92813</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12302,21 +12290,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1049</v>
+        <v>2079</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12326,13 +12314,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>865553</v>
+        <v>865643</v>
       </c>
       <c r="R117" t="n">
-        <v>7447326</v>
+        <v>7447067</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12376,19 +12364,15 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
-        </is>
-      </c>
-      <c r="AY117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12489,32 +12473,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126887977</v>
+        <v>126887965</v>
       </c>
       <c r="B119" t="n">
-        <v>92813</v>
+        <v>57483</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>2079</v>
+        <v>102976</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12524,10 +12508,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>865643</v>
+        <v>865583</v>
       </c>
       <c r="R119" t="n">
-        <v>7447067</v>
+        <v>7447214</v>
       </c>
       <c r="S119" t="n">
         <v>25</v>
@@ -12586,10 +12570,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>126887990</v>
+        <v>126892018</v>
       </c>
       <c r="B120" t="n">
-        <v>79018</v>
+        <v>57821</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12597,37 +12581,49 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>865447</v>
+        <v>865561</v>
       </c>
       <c r="R120" t="n">
-        <v>7447371</v>
+        <v>7447155</v>
       </c>
       <c r="S120" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -12671,44 +12667,48 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY120" t="inlineStr"/>
+          <t>Julia Frejd</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>126892170</v>
+        <v>126893308</v>
       </c>
       <c r="B121" t="n">
-        <v>57483</v>
+        <v>91591</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>102976</v>
+        <v>65</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12718,10 +12718,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>865489</v>
+        <v>865659</v>
       </c>
       <c r="R121" t="n">
-        <v>7447377</v>
+        <v>7447048</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12756,11 +12756,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Förbiflygande</t>
-        </is>
-      </c>
       <c r="AD121" t="b">
         <v>0</v>
       </c>
@@ -12773,12 +12768,12 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
@@ -12789,32 +12784,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126893308</v>
+        <v>126893267</v>
       </c>
       <c r="B122" t="n">
-        <v>91591</v>
+        <v>92813</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>65</v>
+        <v>2079</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12824,10 +12819,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>865659</v>
+        <v>865648</v>
       </c>
       <c r="R122" t="n">
-        <v>7447048</v>
+        <v>7447056</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12890,32 +12885,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126893262</v>
+        <v>126893030</v>
       </c>
       <c r="B123" t="n">
-        <v>91295</v>
+        <v>77996</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5447</v>
+        <v>6487</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12925,10 +12920,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>865522</v>
+        <v>865545</v>
       </c>
       <c r="R123" t="n">
-        <v>7447308</v>
+        <v>7447323</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12975,12 +12970,12 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
@@ -12991,32 +12986,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126893260</v>
+        <v>126887981</v>
       </c>
       <c r="B124" t="n">
-        <v>91252</v>
+        <v>80157</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>3242</v>
+        <v>6464</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13026,13 +13021,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>865498</v>
+        <v>865448</v>
       </c>
       <c r="R124" t="n">
-        <v>7447359</v>
+        <v>7447345</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13076,26 +13071,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
-        </is>
-      </c>
-      <c r="AY124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126893267</v>
+        <v>126893260</v>
       </c>
       <c r="B125" t="n">
-        <v>92813</v>
+        <v>91252</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13103,21 +13094,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>2079</v>
+        <v>3242</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13127,10 +13118,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>865648</v>
+        <v>865498</v>
       </c>
       <c r="R125" t="n">
-        <v>7447056</v>
+        <v>7447359</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13193,32 +13184,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126893030</v>
+        <v>126893262</v>
       </c>
       <c r="B126" t="n">
-        <v>77996</v>
+        <v>91295</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6487</v>
+        <v>5447</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13228,10 +13219,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>865545</v>
+        <v>865522</v>
       </c>
       <c r="R126" t="n">
-        <v>7447323</v>
+        <v>7447308</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13278,12 +13269,12 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
@@ -13294,32 +13285,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126887981</v>
+        <v>126892170</v>
       </c>
       <c r="B127" t="n">
-        <v>80157</v>
+        <v>57483</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6464</v>
+        <v>102976</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13329,13 +13320,13 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>865448</v>
+        <v>865489</v>
       </c>
       <c r="R127" t="n">
-        <v>7447345</v>
+        <v>7447377</v>
       </c>
       <c r="S127" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -13365,6 +13356,11 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Förbiflygande</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13379,44 +13375,48 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY127" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>126893274</v>
+        <v>126887988</v>
       </c>
       <c r="B128" t="n">
-        <v>80157</v>
+        <v>91491</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6464</v>
+        <v>1503</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13426,13 +13426,13 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>865476</v>
+        <v>865515</v>
       </c>
       <c r="R128" t="n">
-        <v>7447236</v>
+        <v>7447377</v>
       </c>
       <c r="S128" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13476,48 +13476,44 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
-        </is>
-      </c>
-      <c r="AY128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126887988</v>
+        <v>126893269</v>
       </c>
       <c r="B129" t="n">
-        <v>91491</v>
+        <v>92813</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1503</v>
+        <v>2079</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13527,13 +13523,13 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>865515</v>
+        <v>865647</v>
       </c>
       <c r="R129" t="n">
-        <v>7447377</v>
+        <v>7447057</v>
       </c>
       <c r="S129" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -13577,44 +13573,48 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY129" t="inlineStr"/>
+          <t>Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126893292</v>
+        <v>126887970</v>
       </c>
       <c r="B130" t="n">
-        <v>79018</v>
+        <v>80150</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13624,13 +13624,13 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>865501</v>
+        <v>865529</v>
       </c>
       <c r="R130" t="n">
-        <v>7447191</v>
+        <v>7447327</v>
       </c>
       <c r="S130" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -13674,48 +13674,44 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
-        </is>
-      </c>
-      <c r="AY130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126893313</v>
+        <v>126893274</v>
       </c>
       <c r="B131" t="n">
-        <v>78424</v>
+        <v>80157</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6437</v>
+        <v>6464</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13725,10 +13721,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>865598</v>
+        <v>865476</v>
       </c>
       <c r="R131" t="n">
-        <v>7447181</v>
+        <v>7447236</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13791,10 +13787,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126893269</v>
+        <v>126893292</v>
       </c>
       <c r="B132" t="n">
-        <v>92813</v>
+        <v>79018</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13802,21 +13798,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13826,10 +13822,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>865647</v>
+        <v>865501</v>
       </c>
       <c r="R132" t="n">
-        <v>7447057</v>
+        <v>7447191</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13892,32 +13888,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126887970</v>
+        <v>126893313</v>
       </c>
       <c r="B133" t="n">
-        <v>80150</v>
+        <v>78424</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6462</v>
+        <v>6437</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -13927,13 +13923,13 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>865529</v>
+        <v>865598</v>
       </c>
       <c r="R133" t="n">
-        <v>7447327</v>
+        <v>7447181</v>
       </c>
       <c r="S133" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -13977,44 +13973,48 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY133" t="inlineStr"/>
+          <t>Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126892256</v>
+        <v>126887962</v>
       </c>
       <c r="B134" t="n">
-        <v>91295</v>
+        <v>79636</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14024,13 +14024,13 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>865491</v>
+        <v>865519</v>
       </c>
       <c r="R134" t="n">
-        <v>7447326</v>
+        <v>7447214</v>
       </c>
       <c r="S134" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14074,26 +14074,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
-        </is>
-      </c>
-      <c r="AY134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126892176</v>
+        <v>126893290</v>
       </c>
       <c r="B135" t="n">
-        <v>92813</v>
+        <v>79018</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14101,21 +14097,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14125,10 +14121,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>865490</v>
+        <v>865505</v>
       </c>
       <c r="R135" t="n">
-        <v>7447287</v>
+        <v>7447150</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14175,12 +14171,12 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
@@ -14191,10 +14187,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126892189</v>
+        <v>126892176</v>
       </c>
       <c r="B136" t="n">
-        <v>79018</v>
+        <v>92813</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14202,21 +14198,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14226,10 +14222,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>865551</v>
+        <v>865490</v>
       </c>
       <c r="R136" t="n">
-        <v>7447310</v>
+        <v>7447287</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14292,32 +14288,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126893290</v>
+        <v>126892256</v>
       </c>
       <c r="B137" t="n">
-        <v>79018</v>
+        <v>91295</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14327,10 +14323,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>865505</v>
+        <v>865491</v>
       </c>
       <c r="R137" t="n">
-        <v>7447150</v>
+        <v>7447326</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14377,12 +14373,12 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
@@ -14393,7 +14389,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126887962</v>
+        <v>126892984</v>
       </c>
       <c r="B138" t="n">
         <v>79636</v>
@@ -14428,13 +14424,13 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>865519</v>
+        <v>865523</v>
       </c>
       <c r="R138" t="n">
-        <v>7447214</v>
+        <v>7447267</v>
       </c>
       <c r="S138" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -14478,22 +14474,26 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY138" t="inlineStr"/>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126893034</v>
+        <v>126892189</v>
       </c>
       <c r="B139" t="n">
-        <v>78424</v>
+        <v>79018</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14501,21 +14501,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14525,10 +14525,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>865544</v>
+        <v>865551</v>
       </c>
       <c r="R139" t="n">
-        <v>7447321</v>
+        <v>7447310</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14575,12 +14575,12 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
@@ -14591,10 +14591,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126892984</v>
+        <v>126893034</v>
       </c>
       <c r="B140" t="n">
-        <v>79636</v>
+        <v>78424</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14602,21 +14602,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14626,10 +14626,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>865523</v>
+        <v>865544</v>
       </c>
       <c r="R140" t="n">
-        <v>7447267</v>
+        <v>7447321</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15193,10 +15193,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126888459</v>
+        <v>126892983</v>
       </c>
       <c r="B146" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15204,21 +15204,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15228,10 +15228,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>865501</v>
+        <v>865546</v>
       </c>
       <c r="R146" t="n">
-        <v>7447386</v>
+        <v>7447275</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15278,12 +15278,12 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
@@ -15294,10 +15294,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>126892983</v>
+        <v>126892266</v>
       </c>
       <c r="B147" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15305,21 +15305,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15329,10 +15329,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>865546</v>
+        <v>865495</v>
       </c>
       <c r="R147" t="n">
-        <v>7447275</v>
+        <v>7447285</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15379,12 +15379,12 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
@@ -15395,32 +15395,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126893264</v>
+        <v>126888459</v>
       </c>
       <c r="B148" t="n">
-        <v>57483</v>
+        <v>79018</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>102976</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15430,10 +15430,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>865598</v>
+        <v>865501</v>
       </c>
       <c r="R148" t="n">
-        <v>7447180</v>
+        <v>7447386</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15480,12 +15480,12 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
@@ -15496,32 +15496,32 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126892266</v>
+        <v>126893264</v>
       </c>
       <c r="B149" t="n">
-        <v>79018</v>
+        <v>57483</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>102976</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15531,10 +15531,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>865495</v>
+        <v>865598</v>
       </c>
       <c r="R149" t="n">
-        <v>7447285</v>
+        <v>7447180</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15581,12 +15581,12 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
@@ -15597,32 +15597,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126892980</v>
+        <v>126891909</v>
       </c>
       <c r="B150" t="n">
-        <v>91295</v>
+        <v>75142</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15632,10 +15632,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>865554</v>
+        <v>865542</v>
       </c>
       <c r="R150" t="n">
-        <v>7447301</v>
+        <v>7447122</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15682,12 +15682,12 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
@@ -15698,45 +15698,57 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126893259</v>
+        <v>126892023</v>
       </c>
       <c r="B151" t="n">
-        <v>91252</v>
+        <v>98447</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>3242</v>
+        <v>220787</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>865646</v>
+        <v>865539</v>
       </c>
       <c r="R151" t="n">
-        <v>7447063</v>
+        <v>7447133</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15777,18 +15789,19 @@
       <c r="AE151" t="b">
         <v>0</v>
       </c>
+      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
@@ -15799,32 +15812,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>126891909</v>
+        <v>126892980</v>
       </c>
       <c r="B152" t="n">
-        <v>75142</v>
+        <v>91295</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15834,10 +15847,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>865542</v>
+        <v>865554</v>
       </c>
       <c r="R152" t="n">
-        <v>7447122</v>
+        <v>7447301</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15884,12 +15897,12 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
@@ -15900,57 +15913,45 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>126892023</v>
+        <v>126893259</v>
       </c>
       <c r="B153" t="n">
-        <v>98447</v>
+        <v>91252</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>220787</v>
+        <v>3242</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K153" t="inlineStr"/>
-      <c r="L153" t="inlineStr"/>
-      <c r="N153" t="inlineStr"/>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>865539</v>
+        <v>865646</v>
       </c>
       <c r="R153" t="n">
-        <v>7447133</v>
+        <v>7447063</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -15991,19 +15992,18 @@
       <c r="AE153" t="b">
         <v>0</v>
       </c>
-      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
       </c>
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
@@ -16014,32 +16014,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>126892255</v>
+        <v>126893011</v>
       </c>
       <c r="B154" t="n">
-        <v>91295</v>
+        <v>80993</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>5447</v>
+        <v>1049</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16049,10 +16049,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>865462</v>
+        <v>865498</v>
       </c>
       <c r="R154" t="n">
-        <v>7447413</v>
+        <v>7447379</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16099,12 +16099,12 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
@@ -16115,10 +16115,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126892974</v>
+        <v>126887979</v>
       </c>
       <c r="B155" t="n">
-        <v>91252</v>
+        <v>92813</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16126,21 +16126,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>3242</v>
+        <v>2079</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16150,13 +16150,13 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>865494</v>
+        <v>865510</v>
       </c>
       <c r="R155" t="n">
-        <v>7447322</v>
+        <v>7447251</v>
       </c>
       <c r="S155" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -16200,26 +16200,22 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
-        </is>
-      </c>
-      <c r="AY155" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>126887979</v>
+        <v>126892974</v>
       </c>
       <c r="B156" t="n">
-        <v>92813</v>
+        <v>91252</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16227,21 +16223,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>2079</v>
+        <v>3242</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16251,13 +16247,13 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>865510</v>
+        <v>865494</v>
       </c>
       <c r="R156" t="n">
-        <v>7447251</v>
+        <v>7447322</v>
       </c>
       <c r="S156" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -16301,44 +16297,48 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY156" t="inlineStr"/>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126892272</v>
+        <v>126892255</v>
       </c>
       <c r="B157" t="n">
-        <v>77996</v>
+        <v>91295</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6487</v>
+        <v>5447</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16348,10 +16348,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>865528</v>
+        <v>865462</v>
       </c>
       <c r="R157" t="n">
-        <v>7447192</v>
+        <v>7447413</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16414,10 +16414,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>126893011</v>
+        <v>126892272</v>
       </c>
       <c r="B158" t="n">
-        <v>80993</v>
+        <v>77996</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16425,21 +16425,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>1049</v>
+        <v>6487</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16449,10 +16449,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>865498</v>
+        <v>865528</v>
       </c>
       <c r="R158" t="n">
-        <v>7447379</v>
+        <v>7447192</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16499,12 +16499,12 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
@@ -16515,32 +16515,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>126888458</v>
+        <v>126893291</v>
       </c>
       <c r="B159" t="n">
-        <v>91491</v>
+        <v>79018</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16550,10 +16550,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>865502</v>
+        <v>865507</v>
       </c>
       <c r="R159" t="n">
-        <v>7447310</v>
+        <v>7447151</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16600,12 +16600,12 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
@@ -16616,32 +16616,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>126892016</v>
+        <v>126893272</v>
       </c>
       <c r="B160" t="n">
-        <v>91295</v>
+        <v>92813</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>5447</v>
+        <v>2079</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16651,10 +16651,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>865558</v>
+        <v>865520</v>
       </c>
       <c r="R160" t="n">
-        <v>7447154</v>
+        <v>7447337</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16701,12 +16701,12 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
@@ -16717,32 +16717,32 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>126893272</v>
+        <v>126888458</v>
       </c>
       <c r="B161" t="n">
-        <v>92813</v>
+        <v>91491</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>2079</v>
+        <v>1503</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16752,10 +16752,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>865520</v>
+        <v>865502</v>
       </c>
       <c r="R161" t="n">
-        <v>7447337</v>
+        <v>7447310</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16802,12 +16802,12 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
@@ -17117,48 +17117,45 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>126891924</v>
+        <v>126892016</v>
       </c>
       <c r="B165" t="n">
-        <v>78776</v>
+        <v>91295</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>865562</v>
+        <v>865558</v>
       </c>
       <c r="R165" t="n">
-        <v>7447150</v>
+        <v>7447154</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17199,19 +17196,18 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
-      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
@@ -17222,10 +17218,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>126893291</v>
+        <v>126891924</v>
       </c>
       <c r="B166" t="n">
-        <v>79018</v>
+        <v>78776</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17233,34 +17229,37 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
+      <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>865507</v>
+        <v>865562</v>
       </c>
       <c r="R166" t="n">
-        <v>7447151</v>
+        <v>7447150</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17301,18 +17300,19 @@
       <c r="AE166" t="b">
         <v>0</v>
       </c>
+      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
       </c>
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
@@ -17323,32 +17323,32 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>126892988</v>
+        <v>126893021</v>
       </c>
       <c r="B167" t="n">
-        <v>57483</v>
+        <v>91591</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>102976</v>
+        <v>65</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17358,10 +17358,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>865530</v>
+        <v>865547</v>
       </c>
       <c r="R167" t="n">
-        <v>7447298</v>
+        <v>7447316</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17424,7 +17424,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>126893021</v>
+        <v>126893309</v>
       </c>
       <c r="B168" t="n">
         <v>91591</v>
@@ -17459,10 +17459,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>865547</v>
+        <v>865661</v>
       </c>
       <c r="R168" t="n">
-        <v>7447316</v>
+        <v>7447053</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17509,12 +17509,12 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
@@ -17525,32 +17525,32 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>126893309</v>
+        <v>126893284</v>
       </c>
       <c r="B169" t="n">
-        <v>91591</v>
+        <v>79018</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17560,7 +17560,7 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>865661</v>
+        <v>865543</v>
       </c>
       <c r="R169" t="n">
         <v>7447053</v>
@@ -17626,10 +17626,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>126893284</v>
+        <v>126893031</v>
       </c>
       <c r="B170" t="n">
-        <v>79018</v>
+        <v>77996</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17637,21 +17637,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17661,10 +17661,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>865543</v>
+        <v>865490</v>
       </c>
       <c r="R170" t="n">
-        <v>7447053</v>
+        <v>7447338</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17711,12 +17711,12 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr">
@@ -17727,32 +17727,32 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>126893031</v>
+        <v>126892988</v>
       </c>
       <c r="B171" t="n">
-        <v>77996</v>
+        <v>57483</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6487</v>
+        <v>102976</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -17762,10 +17762,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>865490</v>
+        <v>865530</v>
       </c>
       <c r="R171" t="n">
-        <v>7447338</v>
+        <v>7447298</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17929,32 +17929,32 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>126893263</v>
+        <v>126887986</v>
       </c>
       <c r="B173" t="n">
-        <v>91330</v>
+        <v>91491</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1202</v>
+        <v>1503</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -17964,13 +17964,13 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>865485</v>
+        <v>865539</v>
       </c>
       <c r="R173" t="n">
-        <v>7447224</v>
+        <v>7447206</v>
       </c>
       <c r="S173" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -18014,48 +18014,44 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
-        </is>
-      </c>
-      <c r="AY173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>126887986</v>
+        <v>126892174</v>
       </c>
       <c r="B174" t="n">
-        <v>91491</v>
+        <v>92813</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>1503</v>
+        <v>2079</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18065,13 +18061,13 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>865539</v>
+        <v>865517</v>
       </c>
       <c r="R174" t="n">
-        <v>7447206</v>
+        <v>7447401</v>
       </c>
       <c r="S174" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -18115,44 +18111,48 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY174" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>126892174</v>
+        <v>126892997</v>
       </c>
       <c r="B175" t="n">
-        <v>92813</v>
+        <v>79042</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>2079</v>
+        <v>6434</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18162,10 +18162,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>865517</v>
+        <v>865545</v>
       </c>
       <c r="R175" t="n">
-        <v>7447401</v>
+        <v>7447323</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18212,12 +18212,12 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
@@ -18228,10 +18228,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>126891913</v>
+        <v>126893314</v>
       </c>
       <c r="B176" t="n">
-        <v>79636</v>
+        <v>78424</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -18239,21 +18239,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18263,10 +18263,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>865557</v>
+        <v>865647</v>
       </c>
       <c r="R176" t="n">
-        <v>7447153</v>
+        <v>7447060</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18313,12 +18313,12 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr">
@@ -18329,32 +18329,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>126892997</v>
+        <v>126891913</v>
       </c>
       <c r="B177" t="n">
-        <v>79042</v>
+        <v>79636</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18364,10 +18364,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>865545</v>
+        <v>865557</v>
       </c>
       <c r="R177" t="n">
-        <v>7447323</v>
+        <v>7447153</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18414,12 +18414,12 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
@@ -18430,10 +18430,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>126893294</v>
+        <v>126893263</v>
       </c>
       <c r="B178" t="n">
-        <v>79018</v>
+        <v>91330</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18441,21 +18441,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18465,10 +18465,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>865457</v>
+        <v>865485</v>
       </c>
       <c r="R178" t="n">
-        <v>7447523</v>
+        <v>7447224</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18531,10 +18531,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>126893314</v>
+        <v>126893294</v>
       </c>
       <c r="B179" t="n">
-        <v>78424</v>
+        <v>79018</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -18542,21 +18542,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -18566,10 +18566,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>865647</v>
+        <v>865457</v>
       </c>
       <c r="R179" t="n">
-        <v>7447060</v>
+        <v>7447523</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>

--- a/artfynd/A 52625-2022 artfynd.xlsx
+++ b/artfynd/A 52625-2022 artfynd.xlsx
@@ -1180,32 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126893275</v>
+        <v>126893295</v>
       </c>
       <c r="B7" t="n">
-        <v>80157</v>
+        <v>79018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>865427</v>
+        <v>865429</v>
       </c>
       <c r="R7" t="n">
-        <v>7447587</v>
+        <v>7447550</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,10 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126892019</v>
+        <v>126893275</v>
       </c>
       <c r="B8" t="n">
-        <v>80150</v>
+        <v>80157</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1292,21 +1292,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>865429</v>
+        <v>865427</v>
       </c>
       <c r="R8" t="n">
-        <v>7447523</v>
+        <v>7447587</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1366,12 +1366,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1382,32 +1382,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126893300</v>
+        <v>126892019</v>
       </c>
       <c r="B9" t="n">
-        <v>79018</v>
+        <v>80150</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>865378</v>
+        <v>865429</v>
       </c>
       <c r="R9" t="n">
-        <v>7447665</v>
+        <v>7447523</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1467,12 +1467,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1483,7 +1483,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126893295</v>
+        <v>126893300</v>
       </c>
       <c r="B10" t="n">
         <v>79018</v>
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>865429</v>
+        <v>865378</v>
       </c>
       <c r="R10" t="n">
-        <v>7447550</v>
+        <v>7447665</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1584,32 +1584,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126887991</v>
+        <v>126892999</v>
       </c>
       <c r="B11" t="n">
-        <v>79018</v>
+        <v>80149</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1619,13 +1619,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>865422</v>
+        <v>865426</v>
       </c>
       <c r="R11" t="n">
-        <v>7447458</v>
+        <v>7447493</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1669,60 +1669,75 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126887992</v>
+        <v>126892270</v>
       </c>
       <c r="B12" t="n">
-        <v>79018</v>
+        <v>91904</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>865406</v>
+        <v>865437</v>
       </c>
       <c r="R12" t="n">
-        <v>7447461</v>
+        <v>7447594</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1760,77 +1775,71 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Svea Nikula, Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126892270</v>
+        <v>126887991</v>
       </c>
       <c r="B13" t="n">
-        <v>91904</v>
+        <v>79018</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>865437</v>
+        <v>865422</v>
       </c>
       <c r="R13" t="n">
-        <v>7447594</v>
+        <v>7447458</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1868,33 +1877,28 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Svea Nikula, Jonas Göransson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126892999</v>
+        <v>126892173</v>
       </c>
       <c r="B14" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1902,21 +1906,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1926,10 +1930,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>865426</v>
+        <v>865379</v>
       </c>
       <c r="R14" t="n">
-        <v>7447493</v>
+        <v>7447558</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1976,12 +1980,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -1992,32 +1996,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126892173</v>
+        <v>126887992</v>
       </c>
       <c r="B15" t="n">
-        <v>80150</v>
+        <v>79018</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2027,13 +2031,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>865379</v>
+        <v>865406</v>
       </c>
       <c r="R15" t="n">
-        <v>7447558</v>
+        <v>7447461</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2077,19 +2081,15 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -5917,32 +5917,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126893280</v>
+        <v>126892985</v>
       </c>
       <c r="B54" t="n">
-        <v>91491</v>
+        <v>79636</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5952,10 +5952,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>865490</v>
+        <v>865491</v>
       </c>
       <c r="R54" t="n">
-        <v>7447213</v>
+        <v>7447332</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6002,12 +6002,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -6018,32 +6018,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126892026</v>
+        <v>126891916</v>
       </c>
       <c r="B55" t="n">
-        <v>79018</v>
+        <v>80150</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6053,10 +6053,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>865538</v>
+        <v>865546</v>
       </c>
       <c r="R55" t="n">
-        <v>7447072</v>
+        <v>7447133</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6103,12 +6103,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6119,32 +6119,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126892029</v>
+        <v>126891927</v>
       </c>
       <c r="B56" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6154,10 +6154,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>865448</v>
+        <v>865543</v>
       </c>
       <c r="R56" t="n">
-        <v>7447418</v>
+        <v>7447122</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6204,12 +6204,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6220,32 +6220,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126892985</v>
+        <v>126893280</v>
       </c>
       <c r="B57" t="n">
-        <v>79636</v>
+        <v>91491</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6255,10 +6255,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>865491</v>
+        <v>865490</v>
       </c>
       <c r="R57" t="n">
-        <v>7447332</v>
+        <v>7447213</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6305,12 +6305,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6422,32 +6422,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126891916</v>
+        <v>126892026</v>
       </c>
       <c r="B59" t="n">
-        <v>80150</v>
+        <v>79018</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6457,10 +6457,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>865546</v>
+        <v>865538</v>
       </c>
       <c r="R59" t="n">
-        <v>7447133</v>
+        <v>7447072</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6507,12 +6507,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6523,32 +6523,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126891927</v>
+        <v>126892029</v>
       </c>
       <c r="B60" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6558,10 +6558,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>865543</v>
+        <v>865448</v>
       </c>
       <c r="R60" t="n">
-        <v>7447122</v>
+        <v>7447418</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6608,12 +6608,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Anton Lundberg, Alva Dahlqvist Cederstrand, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
@@ -7222,10 +7222,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126893312</v>
+        <v>126893000</v>
       </c>
       <c r="B67" t="n">
-        <v>77996</v>
+        <v>92813</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7233,21 +7233,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6487</v>
+        <v>2079</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7257,10 +7257,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>865598</v>
+        <v>865559</v>
       </c>
       <c r="R67" t="n">
-        <v>7447181</v>
+        <v>7447299</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7307,12 +7307,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7323,32 +7323,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126892998</v>
+        <v>126893312</v>
       </c>
       <c r="B68" t="n">
-        <v>80149</v>
+        <v>77996</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6461</v>
+        <v>6487</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7358,10 +7358,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>865477</v>
+        <v>865598</v>
       </c>
       <c r="R68" t="n">
-        <v>7447327</v>
+        <v>7447181</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7408,12 +7408,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7424,32 +7424,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126891925</v>
+        <v>126892998</v>
       </c>
       <c r="B69" t="n">
-        <v>98447</v>
+        <v>80149</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7459,10 +7459,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>865527</v>
+        <v>865477</v>
       </c>
       <c r="R69" t="n">
-        <v>7447333</v>
+        <v>7447327</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7509,12 +7509,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -7525,10 +7525,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126893000</v>
+        <v>126892183</v>
       </c>
       <c r="B70" t="n">
-        <v>92813</v>
+        <v>56844</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7536,34 +7536,50 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2079</v>
+        <v>102612</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>pulli</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>pulli/nyligen flygga ungar</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>865559</v>
+        <v>865484</v>
       </c>
       <c r="R70" t="n">
-        <v>7447299</v>
+        <v>7447494</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7598,6 +7614,11 @@
           <t>2025-07-24</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Stötte up 5st kycklingar, höll till under en och samma fallen gran</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -7610,12 +7631,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7626,61 +7647,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126892183</v>
+        <v>126891925</v>
       </c>
       <c r="B71" t="n">
-        <v>56844</v>
+        <v>98447</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>pulli</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>pulli/nyligen flygga ungar</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>865484</v>
+        <v>865527</v>
       </c>
       <c r="R71" t="n">
-        <v>7447494</v>
+        <v>7447333</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7715,11 +7720,6 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Stötte up 5st kycklingar, höll till under en och samma fallen gran</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -7732,12 +7732,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -7748,32 +7748,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126893282</v>
+        <v>126891911</v>
       </c>
       <c r="B72" t="n">
-        <v>79018</v>
+        <v>91295</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7783,10 +7783,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>865611</v>
+        <v>865557</v>
       </c>
       <c r="R72" t="n">
-        <v>7446989</v>
+        <v>7447153</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7833,12 +7833,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -7849,10 +7849,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126891926</v>
+        <v>126892187</v>
       </c>
       <c r="B73" t="n">
-        <v>98447</v>
+        <v>91491</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7860,21 +7860,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>1503</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7884,10 +7884,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>865541</v>
+        <v>865509</v>
       </c>
       <c r="R73" t="n">
-        <v>7447113</v>
+        <v>7447371</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7934,12 +7934,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -7950,7 +7950,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126892187</v>
+        <v>126893012</v>
       </c>
       <c r="B74" t="n">
         <v>91491</v>
@@ -7985,10 +7985,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>865509</v>
+        <v>865559</v>
       </c>
       <c r="R74" t="n">
-        <v>7447371</v>
+        <v>7447299</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8035,12 +8035,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8051,32 +8051,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126893012</v>
+        <v>126893282</v>
       </c>
       <c r="B75" t="n">
-        <v>91491</v>
+        <v>79018</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8086,10 +8086,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>865559</v>
+        <v>865611</v>
       </c>
       <c r="R75" t="n">
-        <v>7447299</v>
+        <v>7446989</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8136,12 +8136,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8152,32 +8152,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126891911</v>
+        <v>126891926</v>
       </c>
       <c r="B76" t="n">
-        <v>91295</v>
+        <v>98447</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8187,10 +8187,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>865557</v>
+        <v>865541</v>
       </c>
       <c r="R76" t="n">
-        <v>7447153</v>
+        <v>7447113</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9976,32 +9976,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126893025</v>
+        <v>126888000</v>
       </c>
       <c r="B94" t="n">
-        <v>92620</v>
+        <v>78685</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10011,13 +10011,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>865518</v>
+        <v>865597</v>
       </c>
       <c r="R94" t="n">
-        <v>7447235</v>
+        <v>7447186</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10061,48 +10061,44 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
-        </is>
-      </c>
-      <c r="AY94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126892981</v>
+        <v>126893023</v>
       </c>
       <c r="B95" t="n">
-        <v>91295</v>
+        <v>91731</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5447</v>
+        <v>715</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Finporing</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Gloeoporus pannocinctus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) J.Erikss.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10112,10 +10108,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>865553</v>
+        <v>865473</v>
       </c>
       <c r="R95" t="n">
-        <v>7447278</v>
+        <v>7447321</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10178,32 +10174,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126892267</v>
+        <v>126893281</v>
       </c>
       <c r="B96" t="n">
-        <v>79018</v>
+        <v>91491</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10213,10 +10209,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>865516</v>
+        <v>865513</v>
       </c>
       <c r="R96" t="n">
-        <v>7447351</v>
+        <v>7447339</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10263,12 +10259,12 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -10279,10 +10275,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126888000</v>
+        <v>126892178</v>
       </c>
       <c r="B97" t="n">
-        <v>78685</v>
+        <v>92813</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10290,21 +10286,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10314,13 +10310,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>865597</v>
+        <v>865509</v>
       </c>
       <c r="R97" t="n">
-        <v>7447186</v>
+        <v>7447375</v>
       </c>
       <c r="S97" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10364,44 +10360,48 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY97" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126893023</v>
+        <v>126893025</v>
       </c>
       <c r="B98" t="n">
-        <v>91731</v>
+        <v>92620</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>715</v>
+        <v>4364</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Finporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Gloeoporus pannocinctus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Romell) J.Erikss.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10411,10 +10411,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>865473</v>
+        <v>865518</v>
       </c>
       <c r="R98" t="n">
-        <v>7447321</v>
+        <v>7447235</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10477,32 +10477,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>126893281</v>
+        <v>126892981</v>
       </c>
       <c r="B99" t="n">
-        <v>91491</v>
+        <v>91295</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1503</v>
+        <v>5447</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10512,10 +10512,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>865513</v>
+        <v>865553</v>
       </c>
       <c r="R99" t="n">
-        <v>7447339</v>
+        <v>7447278</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10562,12 +10562,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -10578,10 +10578,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126892178</v>
+        <v>126892267</v>
       </c>
       <c r="B100" t="n">
-        <v>92813</v>
+        <v>79018</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10589,21 +10589,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10613,10 +10613,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>865509</v>
+        <v>865516</v>
       </c>
       <c r="R100" t="n">
-        <v>7447375</v>
+        <v>7447351</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10663,12 +10663,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -13989,10 +13989,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126887962</v>
+        <v>126893290</v>
       </c>
       <c r="B134" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14000,21 +14000,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14024,13 +14024,13 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>865519</v>
+        <v>865505</v>
       </c>
       <c r="R134" t="n">
-        <v>7447214</v>
+        <v>7447150</v>
       </c>
       <c r="S134" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14074,22 +14074,26 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY134" t="inlineStr"/>
+          <t>Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126893290</v>
+        <v>126892176</v>
       </c>
       <c r="B135" t="n">
-        <v>79018</v>
+        <v>92813</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14097,21 +14101,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14121,10 +14125,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>865505</v>
+        <v>865490</v>
       </c>
       <c r="R135" t="n">
-        <v>7447150</v>
+        <v>7447287</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14171,12 +14175,12 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
@@ -14187,32 +14191,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126892176</v>
+        <v>126892256</v>
       </c>
       <c r="B136" t="n">
-        <v>92813</v>
+        <v>91295</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>2079</v>
+        <v>5447</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14222,10 +14226,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>865490</v>
+        <v>865491</v>
       </c>
       <c r="R136" t="n">
-        <v>7447287</v>
+        <v>7447326</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14272,12 +14276,12 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Svea Nikula</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
@@ -14288,32 +14292,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126892256</v>
+        <v>126892984</v>
       </c>
       <c r="B137" t="n">
-        <v>91295</v>
+        <v>79636</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14323,10 +14327,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>865491</v>
+        <v>865523</v>
       </c>
       <c r="R137" t="n">
-        <v>7447326</v>
+        <v>7447267</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14373,12 +14377,12 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Svea Nikula</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
@@ -14389,10 +14393,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126892984</v>
+        <v>126892189</v>
       </c>
       <c r="B138" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14400,21 +14404,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14424,10 +14428,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>865523</v>
+        <v>865551</v>
       </c>
       <c r="R138" t="n">
-        <v>7447267</v>
+        <v>7447310</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14474,12 +14478,12 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
@@ -14490,10 +14494,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126892189</v>
+        <v>126887962</v>
       </c>
       <c r="B139" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14501,21 +14505,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14525,13 +14529,13 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>865551</v>
+        <v>865519</v>
       </c>
       <c r="R139" t="n">
-        <v>7447310</v>
+        <v>7447214</v>
       </c>
       <c r="S139" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -14575,19 +14579,15 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -16515,32 +16515,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>126893291</v>
+        <v>126892016</v>
       </c>
       <c r="B159" t="n">
-        <v>79018</v>
+        <v>91295</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16550,10 +16550,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>865507</v>
+        <v>865558</v>
       </c>
       <c r="R159" t="n">
-        <v>7447151</v>
+        <v>7447154</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16600,12 +16600,12 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
@@ -16616,10 +16616,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>126893272</v>
+        <v>126891924</v>
       </c>
       <c r="B160" t="n">
-        <v>92813</v>
+        <v>78776</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16627,34 +16627,37 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>865520</v>
+        <v>865562</v>
       </c>
       <c r="R160" t="n">
-        <v>7447337</v>
+        <v>7447150</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16695,18 +16698,19 @@
       <c r="AE160" t="b">
         <v>0</v>
       </c>
+      <c r="AF160" t="inlineStr"/>
       <c r="AG160" t="b">
         <v>0</v>
       </c>
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
@@ -16717,32 +16721,32 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>126888458</v>
+        <v>126893265</v>
       </c>
       <c r="B161" t="n">
-        <v>91491</v>
+        <v>80150</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>1503</v>
+        <v>6462</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16752,10 +16756,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>865502</v>
+        <v>865530</v>
       </c>
       <c r="R161" t="n">
-        <v>7447310</v>
+        <v>7447304</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16802,12 +16806,12 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
@@ -16818,32 +16822,32 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>126893265</v>
+        <v>126887961</v>
       </c>
       <c r="B162" t="n">
-        <v>80150</v>
+        <v>79636</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16853,13 +16857,13 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>865530</v>
+        <v>865602</v>
       </c>
       <c r="R162" t="n">
-        <v>7447304</v>
+        <v>7447176</v>
       </c>
       <c r="S162" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -16903,48 +16907,44 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
-        </is>
-      </c>
-      <c r="AY162" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>126887961</v>
+        <v>126891919</v>
       </c>
       <c r="B163" t="n">
-        <v>79636</v>
+        <v>80150</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6453</v>
+        <v>6462</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -16954,13 +16954,13 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>865602</v>
+        <v>865447</v>
       </c>
       <c r="R163" t="n">
-        <v>7447176</v>
+        <v>7447440</v>
       </c>
       <c r="S163" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -17004,44 +17004,48 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY163" t="inlineStr"/>
+          <t>Amanda Rudelius</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>126891919</v>
+        <v>126893291</v>
       </c>
       <c r="B164" t="n">
-        <v>80150</v>
+        <v>79018</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17051,10 +17055,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>865447</v>
+        <v>865507</v>
       </c>
       <c r="R164" t="n">
-        <v>7447440</v>
+        <v>7447151</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17101,12 +17105,12 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
@@ -17117,32 +17121,32 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>126892016</v>
+        <v>126893272</v>
       </c>
       <c r="B165" t="n">
-        <v>91295</v>
+        <v>92813</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>5447</v>
+        <v>2079</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17152,10 +17156,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>865558</v>
+        <v>865520</v>
       </c>
       <c r="R165" t="n">
-        <v>7447154</v>
+        <v>7447337</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17202,12 +17206,12 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
@@ -17218,48 +17222,45 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>126891924</v>
+        <v>126888458</v>
       </c>
       <c r="B166" t="n">
-        <v>78776</v>
+        <v>91491</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
-      <c r="J166" t="inlineStr"/>
-      <c r="K166" t="inlineStr"/>
-      <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
           <t>Nikinjärvi, Nb</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>865562</v>
+        <v>865502</v>
       </c>
       <c r="R166" t="n">
-        <v>7447150</v>
+        <v>7447310</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17300,19 +17301,18 @@
       <c r="AE166" t="b">
         <v>0</v>
       </c>
-      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
       </c>
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
@@ -17323,32 +17323,32 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>126893021</v>
+        <v>126892988</v>
       </c>
       <c r="B167" t="n">
-        <v>91591</v>
+        <v>57483</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>65</v>
+        <v>102976</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17358,10 +17358,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>865547</v>
+        <v>865530</v>
       </c>
       <c r="R167" t="n">
-        <v>7447316</v>
+        <v>7447298</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17424,7 +17424,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>126893309</v>
+        <v>126893021</v>
       </c>
       <c r="B168" t="n">
         <v>91591</v>
@@ -17459,10 +17459,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>865661</v>
+        <v>865547</v>
       </c>
       <c r="R168" t="n">
-        <v>7447053</v>
+        <v>7447316</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17509,12 +17509,12 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
@@ -17525,32 +17525,32 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>126893284</v>
+        <v>126893309</v>
       </c>
       <c r="B169" t="n">
-        <v>79018</v>
+        <v>91591</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17560,7 +17560,7 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>865543</v>
+        <v>865661</v>
       </c>
       <c r="R169" t="n">
         <v>7447053</v>
@@ -17626,10 +17626,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>126893031</v>
+        <v>126893284</v>
       </c>
       <c r="B170" t="n">
-        <v>77996</v>
+        <v>79018</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17637,21 +17637,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17661,10 +17661,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>865490</v>
+        <v>865543</v>
       </c>
       <c r="R170" t="n">
-        <v>7447338</v>
+        <v>7447053</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17711,12 +17711,12 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr">
@@ -17727,32 +17727,32 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>126892988</v>
+        <v>126893031</v>
       </c>
       <c r="B171" t="n">
-        <v>57483</v>
+        <v>77996</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>102976</v>
+        <v>6487</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -17762,10 +17762,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>865530</v>
+        <v>865490</v>
       </c>
       <c r="R171" t="n">
-        <v>7447298</v>
+        <v>7447338</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17828,32 +17828,32 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>126892188</v>
+        <v>126893294</v>
       </c>
       <c r="B172" t="n">
-        <v>91491</v>
+        <v>79018</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -17863,10 +17863,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>865520</v>
+        <v>865457</v>
       </c>
       <c r="R172" t="n">
-        <v>7447364</v>
+        <v>7447523</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -17913,12 +17913,12 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
@@ -17929,7 +17929,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>126887986</v>
+        <v>126892188</v>
       </c>
       <c r="B173" t="n">
         <v>91491</v>
@@ -17964,13 +17964,13 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>865539</v>
+        <v>865520</v>
       </c>
       <c r="R173" t="n">
-        <v>7447206</v>
+        <v>7447364</v>
       </c>
       <c r="S173" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -18014,44 +18014,48 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY173" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>126892174</v>
+        <v>126887986</v>
       </c>
       <c r="B174" t="n">
-        <v>92813</v>
+        <v>91491</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>2079</v>
+        <v>1503</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18061,13 +18065,13 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>865517</v>
+        <v>865539</v>
       </c>
       <c r="R174" t="n">
-        <v>7447401</v>
+        <v>7447206</v>
       </c>
       <c r="S174" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -18111,48 +18115,44 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY174" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>126892997</v>
+        <v>126892174</v>
       </c>
       <c r="B175" t="n">
-        <v>79042</v>
+        <v>92813</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6434</v>
+        <v>2079</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18162,10 +18162,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>865545</v>
+        <v>865517</v>
       </c>
       <c r="R175" t="n">
-        <v>7447323</v>
+        <v>7447401</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18212,12 +18212,12 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
@@ -18228,32 +18228,32 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>126893314</v>
+        <v>126892997</v>
       </c>
       <c r="B176" t="n">
-        <v>78424</v>
+        <v>79042</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6437</v>
+        <v>6434</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18263,10 +18263,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>865647</v>
+        <v>865545</v>
       </c>
       <c r="R176" t="n">
-        <v>7447060</v>
+        <v>7447323</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18313,12 +18313,12 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr">
@@ -18329,10 +18329,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>126891913</v>
+        <v>126893314</v>
       </c>
       <c r="B177" t="n">
-        <v>79636</v>
+        <v>78424</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18340,21 +18340,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18364,10 +18364,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>865557</v>
+        <v>865647</v>
       </c>
       <c r="R177" t="n">
-        <v>7447153</v>
+        <v>7447060</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18414,12 +18414,12 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Amanda Rudelius</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
@@ -18430,10 +18430,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>126893263</v>
+        <v>126892986</v>
       </c>
       <c r="B178" t="n">
-        <v>91330</v>
+        <v>79607</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18441,21 +18441,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18465,10 +18465,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>865485</v>
+        <v>865489</v>
       </c>
       <c r="R178" t="n">
-        <v>7447224</v>
+        <v>7447329</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18515,12 +18515,12 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr">
@@ -18531,10 +18531,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>126893294</v>
+        <v>126893263</v>
       </c>
       <c r="B179" t="n">
-        <v>79018</v>
+        <v>91330</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -18542,21 +18542,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -18566,10 +18566,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>865457</v>
+        <v>865485</v>
       </c>
       <c r="R179" t="n">
-        <v>7447523</v>
+        <v>7447224</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18632,10 +18632,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>126892986</v>
+        <v>126891913</v>
       </c>
       <c r="B180" t="n">
-        <v>79607</v>
+        <v>79636</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18643,21 +18643,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -18667,10 +18667,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>865489</v>
+        <v>865557</v>
       </c>
       <c r="R180" t="n">
-        <v>7447329</v>
+        <v>7447153</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18717,12 +18717,12 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Amanda Rudelius</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">

--- a/artfynd/A 52625-2022 artfynd.xlsx
+++ b/artfynd/A 52625-2022 artfynd.xlsx
@@ -1180,32 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126893295</v>
+        <v>126893275</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>80157</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>865429</v>
+        <v>865427</v>
       </c>
       <c r="R7" t="n">
-        <v>7447550</v>
+        <v>7447587</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,10 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126893275</v>
+        <v>126892019</v>
       </c>
       <c r="B8" t="n">
-        <v>80157</v>
+        <v>80150</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1292,21 +1292,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1316,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>865427</v>
+        <v>865429</v>
       </c>
       <c r="R8" t="n">
-        <v>7447587</v>
+        <v>7447523</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1366,12 +1366,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Julia Frejd</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1382,32 +1382,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126892019</v>
+        <v>126893300</v>
       </c>
       <c r="B9" t="n">
-        <v>80150</v>
+        <v>79018</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>865429</v>
+        <v>865378</v>
       </c>
       <c r="R9" t="n">
-        <v>7447523</v>
+        <v>7447665</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1467,12 +1467,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Julia Frejd</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Julia Frejd, Amanda Rudelius, August Oljeqvist, Jonas Göransson, Svea Nikula, Alva Dahlqvist Cederstrand, Anton Lundberg, Erland Lindblad</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1483,7 +1483,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126893300</v>
+        <v>126893295</v>
       </c>
       <c r="B10" t="n">
         <v>79018</v>
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>865378</v>
+        <v>865429</v>
       </c>
       <c r="R10" t="n">
-        <v>7447665</v>
+        <v>7447550</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -3807,10 +3807,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126893306</v>
+        <v>126887969</v>
       </c>
       <c r="B33" t="n">
-        <v>82859</v>
+        <v>57821</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3818,21 +3818,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>865378</v>
+        <v>865406</v>
       </c>
       <c r="R33" t="n">
-        <v>7447665</v>
+        <v>7447461</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3892,26 +3892,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2025 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126892262</v>
+        <v>126892259</v>
       </c>
       <c r="B34" t="n">
-        <v>80157</v>
+        <v>98468</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3919,21 +3915,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6464</v>
+        <v>221952</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       <